--- a/VerveStacks_POL_grids_kan50/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_POL_grids_kan50/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{93E1E741-85B7-4940-B79E-90D9AB9CF9F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53AD7C17-ABB9-48E6-BEA1-E1910FF86930}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="misc" sheetId="7" r:id="rId1"/>
@@ -862,18 +862,72 @@
     <t>pre</t>
   </si>
   <si>
+    <t>distr_solelc_spv_POL_013</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>NRGI</t>
+  </si>
+  <si>
+    <t>daynite</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_005</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_012</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_011</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_014</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_001</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_015</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_018</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_008</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 8</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_POL_002</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 2</t>
   </si>
   <si>
-    <t>NRGI</t>
-  </si>
-  <si>
-    <t>daynite</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_POL_019</t>
   </si>
   <si>
@@ -886,10 +940,40 @@
     <t>connecting solar to buses in cluster 9</t>
   </si>
   <si>
-    <t>distr_solelc_spv_POL_008</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 8</t>
+    <t>distr_solelc_spv_POL_004</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_003</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_007</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_016</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_006</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_010</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 10</t>
   </si>
   <si>
     <t>distr_solelc_spv_POL_017</t>
@@ -904,96 +988,39 @@
     <t>connecting solar to buses in cluster 20</t>
   </si>
   <si>
-    <t>distr_solelc_spv_POL_012</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_011</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_004</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_003</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_007</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_016</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_005</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_006</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_010</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_014</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_001</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_015</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_018</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_013</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 13</t>
-  </si>
-  <si>
     <t>comm-in</t>
   </si>
   <si>
     <t>ncap_cost~USD21_alt</t>
   </si>
   <si>
+    <t>e_Rzeszow_POL,e_Zamosc_POL,e_Pulawy_POL,e_Chelm_POL</t>
+  </si>
+  <si>
+    <t>e_Lubin_POL,e_Poznan_POL,e_Koszalin_POL,e_Bydgoszcz_POL</t>
+  </si>
+  <si>
+    <t>e_Krosno_POL,e_Mielec_POL,e_Debica_POL,e_Zamosc_POL</t>
+  </si>
+  <si>
+    <t>e_Lomza_POL,e_Elk_POL,e_Bialystok_POL,e_Grajewo_POL</t>
+  </si>
+  <si>
+    <t>e_BielskoBiala_POL,e_Katowice_POL,e_Krakow_POL,e_Tarnow_POL</t>
+  </si>
+  <si>
+    <t>e_Boleslawiec_POL,e_ZielonaGora_POL</t>
+  </si>
+  <si>
+    <t>e_Sosnowiec_POL,e_KedzierzynKozle_POL,e_Olesnica_POL,e_Gliwice_POL,e_Czestochowa_POL,e_Radomsko_POL,e_PiotrkowTrybunalsk_POL,e_Kielce_POL</t>
+  </si>
+  <si>
+    <t>e_Warsaw_POL,e_Lomza_POL</t>
+  </si>
+  <si>
+    <t>e_Bydgoszcz_POL,e_Gdansk_POL,e_Grudziadz_POL,e_Kwidzyn_POL</t>
+  </si>
+  <si>
     <t>e_Legnica_POL,e_Swidnica_POL,e_KedzierzynKozle_POL,e_Opole_POL</t>
   </si>
   <si>
@@ -1003,7 +1030,22 @@
     <t>e_Pulawy_POL,e_Bialystok_POL,e_Chelm_POL</t>
   </si>
   <si>
-    <t>e_Bydgoszcz_POL,e_Gdansk_POL,e_Grudziadz_POL,e_Kwidzyn_POL</t>
+    <t>e_GorzowWielkopolski_POL,e_Szczecin_POL,e_Police_POL</t>
+  </si>
+  <si>
+    <t>e_Lubin_POL,e_Swidnica_POL,e_Wroclaw_POL,e_Poznan_POL,e_Olesnica_POL</t>
+  </si>
+  <si>
+    <t>e_Koszalin_POL,e_Ustka_POL,e_Slupsk_POL</t>
+  </si>
+  <si>
+    <t>e_Olesnica_POL,e_Konin_POL,e_PiotrkowTrybunalsk_POL,e_Plock_POL</t>
+  </si>
+  <si>
+    <t>e_Plock_POL,e_Olsztyn_POL,e_Warsaw_POL</t>
+  </si>
+  <si>
+    <t>e_Elk_POL,e_Grajewo_POL</t>
   </si>
   <si>
     <t>e_Konin_POL,e_Bydgoszcz_POL,e_Wloclawek_POL,e_Kwidzyn_POL,e_Plock_POL</t>
@@ -1012,46 +1054,52 @@
     <t>e_OstrowiecSwietokrz_POL,e_Pulawy_POL,e_Warsaw_POL</t>
   </si>
   <si>
-    <t>e_Krosno_POL,e_Mielec_POL,e_Debica_POL,e_Zamosc_POL</t>
-  </si>
-  <si>
-    <t>e_Lomza_POL,e_Elk_POL,e_Bialystok_POL,e_Grajewo_POL</t>
-  </si>
-  <si>
-    <t>e_GorzowWielkopolski_POL,e_Szczecin_POL,e_Police_POL</t>
-  </si>
-  <si>
-    <t>e_Lubin_POL,e_Swidnica_POL,e_Wroclaw_POL,e_Poznan_POL,e_Olesnica_POL</t>
-  </si>
-  <si>
-    <t>e_Koszalin_POL,e_Ustka_POL,e_Slupsk_POL</t>
-  </si>
-  <si>
-    <t>e_Olesnica_POL,e_Konin_POL,e_PiotrkowTrybunalsk_POL,e_Plock_POL</t>
-  </si>
-  <si>
-    <t>e_Lubin_POL,e_Poznan_POL,e_Koszalin_POL,e_Bydgoszcz_POL</t>
-  </si>
-  <si>
-    <t>e_Plock_POL,e_Olsztyn_POL,e_Warsaw_POL</t>
-  </si>
-  <si>
-    <t>e_Elk_POL,e_Grajewo_POL</t>
-  </si>
-  <si>
-    <t>e_BielskoBiala_POL,e_Katowice_POL,e_Krakow_POL,e_Tarnow_POL</t>
-  </si>
-  <si>
-    <t>e_Boleslawiec_POL,e_ZielonaGora_POL</t>
-  </si>
-  <si>
-    <t>e_Sosnowiec_POL,e_KedzierzynKozle_POL,e_Olesnica_POL,e_Gliwice_POL,e_Czestochowa_POL,e_Radomsko_POL,e_PiotrkowTrybunalsk_POL,e_Kielce_POL</t>
-  </si>
-  <si>
-    <t>e_Warsaw_POL,e_Lomza_POL</t>
-  </si>
-  <si>
-    <t>e_Rzeszow_POL,e_Zamosc_POL,e_Pulawy_POL,e_Chelm_POL</t>
+    <t>distr_wonelc_won_POL_005</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_018</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_007</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_019</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_017</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_012</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_003</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_002</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 2</t>
   </si>
   <si>
     <t>distr_wonelc_won_POL_015</t>
@@ -1066,6 +1114,18 @@
     <t>connecting wind onshore to buses in cluster 16</t>
   </si>
   <si>
+    <t>distr_wonelc_won_POL_014</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_020</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 20</t>
+  </si>
+  <si>
     <t>distr_wonelc_won_POL_013</t>
   </si>
   <si>
@@ -1078,6 +1138,12 @@
     <t>connecting wind onshore to buses in cluster 8</t>
   </si>
   <si>
+    <t>distr_wonelc_won_POL_001</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 1</t>
+  </si>
+  <si>
     <t>distr_wonelc_won_POL_011</t>
   </si>
   <si>
@@ -1090,18 +1156,6 @@
     <t>connecting wind onshore to buses in cluster 10</t>
   </si>
   <si>
-    <t>distr_wonelc_won_POL_019</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_017</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 17</t>
-  </si>
-  <si>
     <t>distr_wonelc_won_POL_006</t>
   </si>
   <si>
@@ -1120,58 +1174,52 @@
     <t>connecting wind onshore to buses in cluster 4</t>
   </si>
   <si>
-    <t>distr_wonelc_won_POL_012</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_003</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_005</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_001</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_018</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_002</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_007</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_014</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_020</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 20</t>
+    <t>elc_won_POL_005</t>
+  </si>
+  <si>
+    <t>e_Lomza_POL,e_Elk_POL,e_Grajewo_POL,e_Bialystok_POL,e_Chelm_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_018</t>
+  </si>
+  <si>
+    <t>e_Boleslawiec_POL,e_Legnica_POL,e_Swidnica_POL,e_KedzierzynKozle_POL,e_Opole_POL,e_Olesnica_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_007</t>
+  </si>
+  <si>
+    <t>e_Warsaw_POL,e_Plock_POL,e_Olsztyn_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_019</t>
+  </si>
+  <si>
+    <t>e_Katowice_POL,e_Czestochowa_POL,e_Krakow_POL,e_Kielce_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_017</t>
+  </si>
+  <si>
+    <t>e_Tarnow_POL,e_Krosno_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_012</t>
+  </si>
+  <si>
+    <t>e_ZielonaGora_POL,e_GorzowWielkopolski_POL,e_Szczecin_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_003</t>
+  </si>
+  <si>
+    <t>e_Warsaw_POL,e_Lomza_POL,e_Pulawy_POL,e_Bialystok_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_002</t>
+  </si>
+  <si>
+    <t>e_Tarnow_POL,e_Kielce_POL,e_OstrowiecSwietokrz_POL,e_Mielec_POL,e_Pulawy_POL,e_Rzeszow_POL</t>
   </si>
   <si>
     <t>elc_won_POL_015</t>
@@ -1186,6 +1234,18 @@
     <t>e_Krosno_POL,e_Debica_POL</t>
   </si>
   <si>
+    <t>elc_won_POL_014</t>
+  </si>
+  <si>
+    <t>e_Lubin_POL,e_Poznan_POL,e_Bydgoszcz_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_020</t>
+  </si>
+  <si>
+    <t>e_Sosnowiec_POL,e_KedzierzynKozle_POL,e_Olesnica_POL,e_Gliwice_POL,e_Czestochowa_POL,e_Radomsko_POL</t>
+  </si>
+  <si>
     <t>elc_won_POL_013</t>
   </si>
   <si>
@@ -1198,6 +1258,12 @@
     <t>e_Olsztyn_POL,e_Elk_POL</t>
   </si>
   <si>
+    <t>elc_won_POL_001</t>
+  </si>
+  <si>
+    <t>e_PiotrkowTrybunalsk_POL,e_Kielce_POL,e_Warsaw_POL,e_OstrowiecSwietokrz_POL</t>
+  </si>
+  <si>
     <t>elc_won_POL_011</t>
   </si>
   <si>
@@ -1210,18 +1276,6 @@
     <t>e_Police_POL,e_Koszalin_POL,e_Poznan_POL,e_Ustka_POL,e_Bydgoszcz_POL,e_Slupsk_POL,e_Gdansk_POL</t>
   </si>
   <si>
-    <t>elc_won_POL_019</t>
-  </si>
-  <si>
-    <t>e_Katowice_POL,e_Czestochowa_POL,e_Krakow_POL,e_Kielce_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_017</t>
-  </si>
-  <si>
-    <t>e_Tarnow_POL,e_Krosno_POL</t>
-  </si>
-  <si>
     <t>elc_won_POL_006</t>
   </si>
   <si>
@@ -1237,58 +1291,52 @@
     <t>elc_won_POL_004</t>
   </si>
   <si>
-    <t>elc_won_POL_012</t>
-  </si>
-  <si>
-    <t>e_ZielonaGora_POL,e_GorzowWielkopolski_POL,e_Szczecin_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_003</t>
-  </si>
-  <si>
-    <t>e_Warsaw_POL,e_Lomza_POL,e_Pulawy_POL,e_Bialystok_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_005</t>
-  </si>
-  <si>
-    <t>e_Lomza_POL,e_Elk_POL,e_Grajewo_POL,e_Bialystok_POL,e_Chelm_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_001</t>
-  </si>
-  <si>
-    <t>e_PiotrkowTrybunalsk_POL,e_Kielce_POL,e_Warsaw_POL,e_OstrowiecSwietokrz_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_018</t>
-  </si>
-  <si>
-    <t>e_Boleslawiec_POL,e_Legnica_POL,e_Swidnica_POL,e_KedzierzynKozle_POL,e_Opole_POL,e_Olesnica_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_002</t>
-  </si>
-  <si>
-    <t>e_Tarnow_POL,e_Kielce_POL,e_OstrowiecSwietokrz_POL,e_Mielec_POL,e_Pulawy_POL,e_Rzeszow_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_007</t>
-  </si>
-  <si>
-    <t>e_Warsaw_POL,e_Plock_POL,e_Olsztyn_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_014</t>
-  </si>
-  <si>
-    <t>e_Lubin_POL,e_Poznan_POL,e_Bydgoszcz_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_020</t>
-  </si>
-  <si>
-    <t>e_Sosnowiec_POL,e_KedzierzynKozle_POL,e_Olesnica_POL,e_Gliwice_POL,e_Czestochowa_POL,e_Radomsko_POL</t>
+    <t>distr_wofelc_wof_POL_003</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_POL_005</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_POL_001</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_POL_010</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_POL_009</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_POL_004</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_POL_006</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_POL_002</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 2</t>
   </si>
   <si>
     <t>distr_wofelc_wof_POL_008</t>
@@ -1303,52 +1351,46 @@
     <t>connecting wind offshore to buses in cluster 7</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_POL_002</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_POL_004</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_POL_006</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_POL_003</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_POL_005</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_POL_001</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_POL_010</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_POL_009</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 9</t>
+    <t>elc_wof_POL_003</t>
+  </si>
+  <si>
+    <t>e_Gdansk_POL</t>
+  </si>
+  <si>
+    <t>elc_wof_POL_005</t>
+  </si>
+  <si>
+    <t>e_Gdynia_POL</t>
+  </si>
+  <si>
+    <t>elc_wof_POL_001</t>
+  </si>
+  <si>
+    <t>elc_wof_POL_010</t>
+  </si>
+  <si>
+    <t>e_Koszalin_POL</t>
+  </si>
+  <si>
+    <t>elc_wof_POL_009</t>
+  </si>
+  <si>
+    <t>e_Koszalin_POL,e_Ustka_POL</t>
+  </si>
+  <si>
+    <t>elc_wof_POL_004</t>
+  </si>
+  <si>
+    <t>e_Ustka_POL,e_Gdynia_POL</t>
+  </si>
+  <si>
+    <t>elc_wof_POL_006</t>
+  </si>
+  <si>
+    <t>elc_wof_POL_002</t>
+  </si>
+  <si>
+    <t>e_Gdynia_POL,e_Gdansk_POL</t>
   </si>
   <si>
     <t>elc_wof_POL_008</t>
@@ -1358,48 +1400,6 @@
   </si>
   <si>
     <t>elc_wof_POL_007</t>
-  </si>
-  <si>
-    <t>e_Koszalin_POL</t>
-  </si>
-  <si>
-    <t>elc_wof_POL_002</t>
-  </si>
-  <si>
-    <t>e_Gdynia_POL,e_Gdansk_POL</t>
-  </si>
-  <si>
-    <t>elc_wof_POL_004</t>
-  </si>
-  <si>
-    <t>e_Ustka_POL,e_Gdynia_POL</t>
-  </si>
-  <si>
-    <t>elc_wof_POL_006</t>
-  </si>
-  <si>
-    <t>e_Gdynia_POL</t>
-  </si>
-  <si>
-    <t>elc_wof_POL_003</t>
-  </si>
-  <si>
-    <t>e_Gdansk_POL</t>
-  </si>
-  <si>
-    <t>elc_wof_POL_005</t>
-  </si>
-  <si>
-    <t>elc_wof_POL_001</t>
-  </si>
-  <si>
-    <t>elc_wof_POL_010</t>
-  </si>
-  <si>
-    <t>elc_wof_POL_009</t>
-  </si>
-  <si>
-    <t>e_Koszalin_POL,e_Ustka_POL</t>
   </si>
   <si>
     <t>e_won_POL_001</t>
@@ -7135,7 +7135,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E985FAE2-AFCA-4646-9812-CF81BE075F18}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{132BC21B-A86A-4D87-B393-F73800E6ECD0}">
   <dimension ref="B9:BD30"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -7373,16 +7373,16 @@
         <v>244</v>
       </c>
       <c r="Y11" t="s">
-        <v>223</v>
+        <v>234</v>
       </c>
       <c r="Z11" t="s">
         <v>288</v>
       </c>
       <c r="AA11">
-        <v>0.99515616506526205</v>
+        <v>0.99606480786442353</v>
       </c>
       <c r="AB11">
-        <v>88.803640470195262</v>
+        <v>72.145189152235062</v>
       </c>
       <c r="AD11" t="s">
         <v>243</v>
@@ -7415,10 +7415,10 @@
         <v>349</v>
       </c>
       <c r="AO11">
-        <v>0.99641308487583879</v>
+        <v>0.9963019969989696</v>
       </c>
       <c r="AP11">
-        <v>65.760110609622657</v>
+        <v>67.796721685557472</v>
       </c>
       <c r="AR11" t="s">
         <v>243</v>
@@ -7451,10 +7451,10 @@
         <v>408</v>
       </c>
       <c r="BC11">
-        <v>0.99383352379209899</v>
+        <v>0.99564787435456037</v>
       </c>
       <c r="BD11">
-        <v>758.43022352327353</v>
+        <v>622.95871485949408</v>
       </c>
     </row>
     <row r="12" spans="2:56">
@@ -7519,16 +7519,16 @@
         <v>248</v>
       </c>
       <c r="Y12" t="s">
-        <v>240</v>
+        <v>226</v>
       </c>
       <c r="Z12" t="s">
         <v>289</v>
       </c>
       <c r="AA12">
-        <v>0.99728872234103139</v>
+        <v>0.99730738889353909</v>
       </c>
       <c r="AB12">
-        <v>49.70675708109188</v>
+        <v>49.364536951784054</v>
       </c>
       <c r="AD12" t="s">
         <v>243</v>
@@ -7561,10 +7561,10 @@
         <v>351</v>
       </c>
       <c r="AO12">
-        <v>0.99449756685866841</v>
+        <v>0.99622969699231045</v>
       </c>
       <c r="AP12">
-        <v>100.87794092441324</v>
+        <v>69.122221807641537</v>
       </c>
       <c r="AR12" t="s">
         <v>243</v>
@@ -7597,10 +7597,10 @@
         <v>410</v>
       </c>
       <c r="BC12">
-        <v>0.99603306101923861</v>
+        <v>0.99328660064428831</v>
       </c>
       <c r="BD12">
-        <v>594.19811056351818</v>
+        <v>799.26715189313825</v>
       </c>
     </row>
     <row r="13" spans="2:56">
@@ -7665,16 +7665,16 @@
         <v>250</v>
       </c>
       <c r="Y13" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="Z13" t="s">
         <v>290</v>
       </c>
       <c r="AA13">
-        <v>0.99583567586599486</v>
+        <v>0.99481478101166732</v>
       </c>
       <c r="AB13">
-        <v>76.34594245676044</v>
+        <v>95.062348119433295</v>
       </c>
       <c r="AD13" t="s">
         <v>243</v>
@@ -7707,10 +7707,10 @@
         <v>353</v>
       </c>
       <c r="AO13">
-        <v>0.99883902037019667</v>
+        <v>0.99653588726932718</v>
       </c>
       <c r="AP13">
-        <v>21.284626546395259</v>
+        <v>63.508733395668145</v>
       </c>
       <c r="AR13" t="s">
         <v>243</v>
@@ -7740,13 +7740,13 @@
         <v>411</v>
       </c>
       <c r="BB13" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="BC13">
-        <v>0.99353721168226494</v>
+        <v>0.99644441082752833</v>
       </c>
       <c r="BD13">
-        <v>780.55486105754892</v>
+        <v>563.48399154455342</v>
       </c>
     </row>
     <row r="14" spans="2:56">
@@ -7811,16 +7811,16 @@
         <v>252</v>
       </c>
       <c r="Y14" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="Z14" t="s">
         <v>291</v>
       </c>
       <c r="AA14">
-        <v>0.99693515631487983</v>
+        <v>0.99681878296180493</v>
       </c>
       <c r="AB14">
-        <v>56.188800893869058</v>
+        <v>58.322312366909152</v>
       </c>
       <c r="AD14" t="s">
         <v>243</v>
@@ -7853,10 +7853,10 @@
         <v>355</v>
       </c>
       <c r="AO14">
-        <v>0.99521984547821263</v>
+        <v>0.99872641243407079</v>
       </c>
       <c r="AP14">
-        <v>87.636166232768815</v>
+        <v>23.349105375368897</v>
       </c>
       <c r="AR14" t="s">
         <v>243</v>
@@ -7883,16 +7883,16 @@
         <v>393</v>
       </c>
       <c r="BA14" t="s">
+        <v>412</v>
+      </c>
+      <c r="BB14" t="s">
         <v>413</v>
       </c>
-      <c r="BB14" t="s">
-        <v>414</v>
-      </c>
       <c r="BC14">
-        <v>0.99255663966463281</v>
+        <v>0.99608994650263638</v>
       </c>
       <c r="BD14">
-        <v>853.77090504074806</v>
+        <v>589.950661136485</v>
       </c>
     </row>
     <row r="15" spans="2:56">
@@ -7957,16 +7957,16 @@
         <v>254</v>
       </c>
       <c r="Y15" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="Z15" t="s">
         <v>292</v>
       </c>
       <c r="AA15">
-        <v>0.99930490342600053</v>
+        <v>0.99790408176624201</v>
       </c>
       <c r="AB15">
-        <v>12.743437189989784</v>
+        <v>38.425167618896296</v>
       </c>
       <c r="AD15" t="s">
         <v>243</v>
@@ -7999,10 +7999,10 @@
         <v>357</v>
       </c>
       <c r="AO15">
-        <v>0.99802303154782224</v>
+        <v>0.99776911581804295</v>
       </c>
       <c r="AP15">
-        <v>36.244421623259619</v>
+        <v>40.899543335879912</v>
       </c>
       <c r="AR15" t="s">
         <v>243</v>
@@ -8029,16 +8029,16 @@
         <v>395</v>
       </c>
       <c r="BA15" t="s">
+        <v>414</v>
+      </c>
+      <c r="BB15" t="s">
         <v>415</v>
       </c>
-      <c r="BB15" t="s">
-        <v>416</v>
-      </c>
       <c r="BC15">
-        <v>0.99615739524125424</v>
+        <v>0.99399682431672776</v>
       </c>
       <c r="BD15">
-        <v>584.91448865302027</v>
+        <v>746.2371176843244</v>
       </c>
     </row>
     <row r="16" spans="2:56">
@@ -8103,16 +8103,16 @@
         <v>256</v>
       </c>
       <c r="Y16" t="s">
-        <v>241</v>
+        <v>222</v>
       </c>
       <c r="Z16" t="s">
         <v>293</v>
       </c>
       <c r="AA16">
-        <v>0.99881801309037566</v>
+        <v>0.99707401400885998</v>
       </c>
       <c r="AB16">
-        <v>21.669760009780138</v>
+        <v>53.643076504234422</v>
       </c>
       <c r="AD16" t="s">
         <v>243</v>
@@ -8145,10 +8145,10 @@
         <v>359</v>
       </c>
       <c r="AO16">
-        <v>0.99714358927215652</v>
+        <v>0.99749126227646956</v>
       </c>
       <c r="AP16">
-        <v>52.367530010463909</v>
+        <v>45.993524931390482</v>
       </c>
       <c r="AR16" t="s">
         <v>243</v>
@@ -8175,16 +8175,16 @@
         <v>397</v>
       </c>
       <c r="BA16" t="s">
+        <v>416</v>
+      </c>
+      <c r="BB16" t="s">
         <v>417</v>
       </c>
-      <c r="BB16" t="s">
-        <v>418</v>
-      </c>
       <c r="BC16">
-        <v>0.99564787435456037</v>
+        <v>0.99255663966463281</v>
       </c>
       <c r="BD16">
-        <v>622.95871485949408</v>
+        <v>853.77090504074806</v>
       </c>
     </row>
     <row r="17" spans="2:56">
@@ -8249,16 +8249,16 @@
         <v>258</v>
       </c>
       <c r="Y17" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="Z17" t="s">
         <v>294</v>
       </c>
       <c r="AA17">
-        <v>0.99481478101166732</v>
+        <v>0.99826037700975512</v>
       </c>
       <c r="AB17">
-        <v>95.062348119433295</v>
+        <v>31.893088154488542</v>
       </c>
       <c r="AD17" t="s">
         <v>243</v>
@@ -8291,10 +8291,10 @@
         <v>361</v>
       </c>
       <c r="AO17">
-        <v>0.99872641243407079</v>
+        <v>0.99807543246352515</v>
       </c>
       <c r="AP17">
-        <v>23.349105375368897</v>
+        <v>35.283738168705199</v>
       </c>
       <c r="AR17" t="s">
         <v>243</v>
@@ -8321,16 +8321,16 @@
         <v>399</v>
       </c>
       <c r="BA17" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="BB17" t="s">
-        <v>416</v>
+        <v>410</v>
       </c>
       <c r="BC17">
-        <v>0.99328660064428831</v>
+        <v>0.99615739524125424</v>
       </c>
       <c r="BD17">
-        <v>799.26715189313825</v>
+        <v>584.91448865302027</v>
       </c>
     </row>
     <row r="18" spans="2:56">
@@ -8395,16 +8395,16 @@
         <v>260</v>
       </c>
       <c r="Y18" t="s">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="Z18" t="s">
         <v>295</v>
       </c>
       <c r="AA18">
-        <v>0.99681878296180493</v>
+        <v>0.99922515067657613</v>
       </c>
       <c r="AB18">
-        <v>58.322312366909152</v>
+        <v>14.205570929438155</v>
       </c>
       <c r="AD18" t="s">
         <v>243</v>
@@ -8437,10 +8437,10 @@
         <v>363</v>
       </c>
       <c r="AO18">
-        <v>0.99776911581804295</v>
+        <v>0.99845791964146047</v>
       </c>
       <c r="AP18">
-        <v>40.899543335879912</v>
+        <v>28.2714732398913</v>
       </c>
       <c r="AR18" t="s">
         <v>243</v>
@@ -8467,16 +8467,16 @@
         <v>401</v>
       </c>
       <c r="BA18" t="s">
+        <v>419</v>
+      </c>
+      <c r="BB18" t="s">
         <v>420</v>
       </c>
-      <c r="BB18" t="s">
-        <v>418</v>
-      </c>
       <c r="BC18">
-        <v>0.99644441082752833</v>
+        <v>0.99353721168226494</v>
       </c>
       <c r="BD18">
-        <v>563.48399154455342</v>
+        <v>780.55486105754892</v>
       </c>
     </row>
     <row r="19" spans="2:56">
@@ -8541,16 +8541,16 @@
         <v>262</v>
       </c>
       <c r="Y19" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="Z19" t="s">
         <v>296</v>
       </c>
       <c r="AA19">
-        <v>0.99785589517057005</v>
+        <v>0.99693515631487983</v>
       </c>
       <c r="AB19">
-        <v>39.308588539549028</v>
+        <v>56.188800893869058</v>
       </c>
       <c r="AD19" t="s">
         <v>243</v>
@@ -8583,10 +8583,10 @@
         <v>365</v>
       </c>
       <c r="AO19">
-        <v>0.99827231256984739</v>
+        <v>0.99641308487583879</v>
       </c>
       <c r="AP19">
-        <v>31.674269552798414</v>
+        <v>65.760110609622657</v>
       </c>
       <c r="AR19" t="s">
         <v>243</v>
@@ -8616,13 +8616,13 @@
         <v>421</v>
       </c>
       <c r="BB19" t="s">
-        <v>410</v>
+        <v>422</v>
       </c>
       <c r="BC19">
-        <v>0.99608994650263638</v>
+        <v>0.99383352379209899</v>
       </c>
       <c r="BD19">
-        <v>589.950661136485</v>
+        <v>758.43022352327353</v>
       </c>
     </row>
     <row r="20" spans="2:56">
@@ -8687,16 +8687,16 @@
         <v>264</v>
       </c>
       <c r="Y20" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="Z20" t="s">
         <v>297</v>
       </c>
       <c r="AA20">
-        <v>0.99770934816564383</v>
+        <v>0.99515616506526205</v>
       </c>
       <c r="AB20">
-        <v>41.995283629862939</v>
+        <v>88.803640470195262</v>
       </c>
       <c r="AD20" t="s">
         <v>243</v>
@@ -8729,10 +8729,10 @@
         <v>367</v>
       </c>
       <c r="AO20">
-        <v>0.99635146162488653</v>
+        <v>0.99449756685866841</v>
       </c>
       <c r="AP20">
-        <v>66.889870210414614</v>
+        <v>100.87794092441324</v>
       </c>
       <c r="AR20" t="s">
         <v>243</v>
@@ -8759,16 +8759,16 @@
         <v>405</v>
       </c>
       <c r="BA20" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="BB20" t="s">
-        <v>423</v>
+        <v>413</v>
       </c>
       <c r="BC20">
-        <v>0.99399682431672776</v>
+        <v>0.99603306101923861</v>
       </c>
       <c r="BD20">
-        <v>746.2371176843244</v>
+        <v>594.19811056351818</v>
       </c>
     </row>
     <row r="21" spans="2:56">
@@ -8833,16 +8833,16 @@
         <v>266</v>
       </c>
       <c r="Y21" t="s">
-        <v>228</v>
+        <v>240</v>
       </c>
       <c r="Z21" t="s">
         <v>298</v>
       </c>
       <c r="AA21">
-        <v>0.9970292559096442</v>
+        <v>0.99728872234103139</v>
       </c>
       <c r="AB21">
-        <v>54.463641656523762</v>
+        <v>49.70675708109188</v>
       </c>
       <c r="AD21" t="s">
         <v>243</v>
@@ -8872,13 +8872,13 @@
         <v>368</v>
       </c>
       <c r="AN21" t="s">
-        <v>307</v>
+        <v>369</v>
       </c>
       <c r="AO21">
-        <v>0.99586212495478665</v>
+        <v>0.99730422320290779</v>
       </c>
       <c r="AP21">
-        <v>75.861042495577635</v>
+        <v>49.422574613357185</v>
       </c>
     </row>
     <row r="22" spans="2:56">
@@ -8943,16 +8943,16 @@
         <v>268</v>
       </c>
       <c r="Y22" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="Z22" t="s">
         <v>299</v>
       </c>
       <c r="AA22">
-        <v>0.9982126095160021</v>
+        <v>0.99583567586599486</v>
       </c>
       <c r="AB22">
-        <v>32.768825539961391</v>
+        <v>76.34594245676044</v>
       </c>
       <c r="AD22" t="s">
         <v>243</v>
@@ -8979,16 +8979,16 @@
         <v>330</v>
       </c>
       <c r="AM22" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AN22" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AO22">
-        <v>0.99749126227646956</v>
+        <v>0.99805709209211746</v>
       </c>
       <c r="AP22">
-        <v>45.993524931390482</v>
+        <v>35.619978311179104</v>
       </c>
     </row>
     <row r="23" spans="2:56">
@@ -9053,16 +9053,16 @@
         <v>270</v>
       </c>
       <c r="Y23" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="Z23" t="s">
         <v>300</v>
       </c>
       <c r="AA23">
-        <v>0.99730738889353909</v>
+        <v>0.99785589517057005</v>
       </c>
       <c r="AB23">
-        <v>49.364536951784054</v>
+        <v>39.308588539549028</v>
       </c>
       <c r="AD23" t="s">
         <v>243</v>
@@ -9089,16 +9089,16 @@
         <v>332</v>
       </c>
       <c r="AM23" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AN23" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AO23">
-        <v>0.99807543246352515</v>
+        <v>0.99883902037019667</v>
       </c>
       <c r="AP23">
-        <v>35.283738168705199</v>
+        <v>21.284626546395259</v>
       </c>
     </row>
     <row r="24" spans="2:56">
@@ -9163,16 +9163,16 @@
         <v>272</v>
       </c>
       <c r="Y24" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="Z24" t="s">
         <v>301</v>
       </c>
       <c r="AA24">
-        <v>0.99658775492800411</v>
+        <v>0.99770934816564383</v>
       </c>
       <c r="AB24">
-        <v>62.557826319923819</v>
+        <v>41.995283629862939</v>
       </c>
       <c r="AD24" t="s">
         <v>243</v>
@@ -9199,16 +9199,16 @@
         <v>334</v>
       </c>
       <c r="AM24" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AN24" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AO24">
-        <v>0.9963019969989696</v>
+        <v>0.99521984547821263</v>
       </c>
       <c r="AP24">
-        <v>67.796721685557472</v>
+        <v>87.636166232768815</v>
       </c>
     </row>
     <row r="25" spans="2:56">
@@ -9273,16 +9273,16 @@
         <v>274</v>
       </c>
       <c r="Y25" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="Z25" t="s">
         <v>302</v>
       </c>
       <c r="AA25">
-        <v>0.99510886326373238</v>
+        <v>0.9970292559096442</v>
       </c>
       <c r="AB25">
-        <v>89.670840164906522</v>
+        <v>54.463641656523762</v>
       </c>
       <c r="AD25" t="s">
         <v>243</v>
@@ -9309,10 +9309,10 @@
         <v>336</v>
       </c>
       <c r="AM25" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AN25" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AO25">
         <v>0.99871360797890252</v>
@@ -9383,16 +9383,16 @@
         <v>276</v>
       </c>
       <c r="Y26" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="Z26" t="s">
         <v>303</v>
       </c>
       <c r="AA26">
-        <v>0.99790408176624201</v>
+        <v>0.9982126095160021</v>
       </c>
       <c r="AB26">
-        <v>38.425167618896296</v>
+        <v>32.768825539961391</v>
       </c>
       <c r="AD26" t="s">
         <v>243</v>
@@ -9419,16 +9419,16 @@
         <v>338</v>
       </c>
       <c r="AM26" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AN26" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AO26">
-        <v>0.99622969699231045</v>
+        <v>0.99802303154782224</v>
       </c>
       <c r="AP26">
-        <v>69.122221807641537</v>
+        <v>36.244421623259619</v>
       </c>
     </row>
     <row r="27" spans="2:56">
@@ -9493,16 +9493,16 @@
         <v>278</v>
       </c>
       <c r="Y27" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="Z27" t="s">
         <v>304</v>
       </c>
       <c r="AA27">
-        <v>0.99707401400885998</v>
+        <v>0.99658775492800411</v>
       </c>
       <c r="AB27">
-        <v>53.643076504234422</v>
+        <v>62.557826319923819</v>
       </c>
       <c r="AD27" t="s">
         <v>243</v>
@@ -9529,16 +9529,16 @@
         <v>340</v>
       </c>
       <c r="AM27" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AN27" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AO27">
-        <v>0.99845791964146047</v>
+        <v>0.99714358927215652</v>
       </c>
       <c r="AP27">
-        <v>28.2714732398913</v>
+        <v>52.367530010463909</v>
       </c>
     </row>
     <row r="28" spans="2:56">
@@ -9603,16 +9603,16 @@
         <v>280</v>
       </c>
       <c r="Y28" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="Z28" t="s">
         <v>305</v>
       </c>
       <c r="AA28">
-        <v>0.99826037700975512</v>
+        <v>0.99510886326373238</v>
       </c>
       <c r="AB28">
-        <v>31.893088154488542</v>
+        <v>89.670840164906522</v>
       </c>
       <c r="AD28" t="s">
         <v>243</v>
@@ -9639,16 +9639,16 @@
         <v>342</v>
       </c>
       <c r="AM28" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AN28" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AO28">
-        <v>0.99653588726932718</v>
+        <v>0.99827231256984739</v>
       </c>
       <c r="AP28">
-        <v>63.508733395668145</v>
+        <v>31.674269552798414</v>
       </c>
     </row>
     <row r="29" spans="2:56">
@@ -9713,16 +9713,16 @@
         <v>282</v>
       </c>
       <c r="Y29" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="Z29" t="s">
         <v>306</v>
       </c>
       <c r="AA29">
-        <v>0.99922515067657613</v>
+        <v>0.99930490342600053</v>
       </c>
       <c r="AB29">
-        <v>14.205570929438155</v>
+        <v>12.743437189989784</v>
       </c>
       <c r="AD29" t="s">
         <v>243</v>
@@ -9749,16 +9749,16 @@
         <v>344</v>
       </c>
       <c r="AM29" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AN29" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AO29">
-        <v>0.99730422320290779</v>
+        <v>0.99635146162488653</v>
       </c>
       <c r="AP29">
-        <v>49.422574613357185</v>
+        <v>66.889870210414614</v>
       </c>
     </row>
     <row r="30" spans="2:56">
@@ -9823,16 +9823,16 @@
         <v>284</v>
       </c>
       <c r="Y30" t="s">
-        <v>234</v>
+        <v>241</v>
       </c>
       <c r="Z30" t="s">
         <v>307</v>
       </c>
       <c r="AA30">
-        <v>0.99606480786442353</v>
+        <v>0.99881801309037566</v>
       </c>
       <c r="AB30">
-        <v>72.145189152235062</v>
+        <v>21.669760009780138</v>
       </c>
       <c r="AD30" t="s">
         <v>243</v>
@@ -9859,16 +9859,16 @@
         <v>346</v>
       </c>
       <c r="AM30" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AN30" t="s">
-        <v>386</v>
+        <v>288</v>
       </c>
       <c r="AO30">
-        <v>0.99805709209211746</v>
+        <v>0.99586212495478665</v>
       </c>
       <c r="AP30">
-        <v>35.619978311179104</v>
+        <v>75.861042495577635</v>
       </c>
     </row>
   </sheetData>
@@ -9877,7 +9877,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE1CE3CD-AED3-4CAF-86CB-D6E7EF168105}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FECED44C-8F32-4276-ACE2-86D89654F16A}">
   <dimension ref="B9:Z30"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -9989,7 +9989,7 @@
         <v>424</v>
       </c>
       <c r="K11" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="L11">
         <v>0.30278350605008381</v>
@@ -10022,7 +10022,7 @@
         <v>464</v>
       </c>
       <c r="X11" t="s">
-        <v>420</v>
+        <v>411</v>
       </c>
       <c r="Y11">
         <v>0.83925000000000005</v>
@@ -10057,7 +10057,7 @@
         <v>426</v>
       </c>
       <c r="K12" t="s">
-        <v>379</v>
+        <v>362</v>
       </c>
       <c r="L12">
         <v>0.42035497786033621</v>
@@ -10090,7 +10090,7 @@
         <v>466</v>
       </c>
       <c r="X12" t="s">
-        <v>411</v>
+        <v>419</v>
       </c>
       <c r="Y12">
         <v>16.887</v>
@@ -10125,7 +10125,7 @@
         <v>428</v>
       </c>
       <c r="K13" t="s">
-        <v>371</v>
+        <v>360</v>
       </c>
       <c r="L13">
         <v>1.6077871713950227</v>
@@ -10158,7 +10158,7 @@
         <v>468</v>
       </c>
       <c r="X13" t="s">
-        <v>417</v>
+        <v>407</v>
       </c>
       <c r="Y13">
         <v>11.2965</v>
@@ -10193,7 +10193,7 @@
         <v>430</v>
       </c>
       <c r="K14" t="s">
-        <v>368</v>
+        <v>386</v>
       </c>
       <c r="L14">
         <v>2.531891424764753</v>
@@ -10226,7 +10226,7 @@
         <v>470</v>
       </c>
       <c r="X14" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="Y14">
         <v>6.6577500000000001</v>
@@ -10261,7 +10261,7 @@
         <v>432</v>
       </c>
       <c r="K15" t="s">
-        <v>373</v>
+        <v>348</v>
       </c>
       <c r="L15">
         <v>7.6497810049421515</v>
@@ -10294,7 +10294,7 @@
         <v>472</v>
       </c>
       <c r="X15" t="s">
-        <v>419</v>
+        <v>409</v>
       </c>
       <c r="Y15">
         <v>17.089500000000001</v>
@@ -10329,7 +10329,7 @@
         <v>434</v>
       </c>
       <c r="K16" t="s">
-        <v>364</v>
+        <v>382</v>
       </c>
       <c r="L16">
         <v>0.60733325583919984</v>
@@ -10362,7 +10362,7 @@
         <v>474</v>
       </c>
       <c r="X16" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="Y16">
         <v>8.8230000000000004</v>
@@ -10397,7 +10397,7 @@
         <v>436</v>
       </c>
       <c r="K17" t="s">
-        <v>381</v>
+        <v>352</v>
       </c>
       <c r="L17">
         <v>0.78389041837100704</v>
@@ -10430,7 +10430,7 @@
         <v>476</v>
       </c>
       <c r="X17" t="s">
-        <v>409</v>
+        <v>423</v>
       </c>
       <c r="Y17">
         <v>0.22650000000000001</v>
@@ -10465,7 +10465,7 @@
         <v>438</v>
       </c>
       <c r="K18" t="s">
-        <v>354</v>
+        <v>374</v>
       </c>
       <c r="L18">
         <v>3.0365724666245324</v>
@@ -10498,7 +10498,7 @@
         <v>478</v>
       </c>
       <c r="X18" t="s">
-        <v>407</v>
+        <v>421</v>
       </c>
       <c r="Y18">
         <v>9.5062499999999996</v>
@@ -10533,7 +10533,7 @@
         <v>440</v>
       </c>
       <c r="K19" t="s">
-        <v>366</v>
+        <v>384</v>
       </c>
       <c r="L19">
         <v>0.22970161230087291</v>
@@ -10566,7 +10566,7 @@
         <v>480</v>
       </c>
       <c r="X19" t="s">
-        <v>422</v>
+        <v>414</v>
       </c>
       <c r="Y19">
         <v>13.37175</v>
@@ -10601,7 +10601,7 @@
         <v>442</v>
       </c>
       <c r="K20" t="s">
-        <v>358</v>
+        <v>380</v>
       </c>
       <c r="L20">
         <v>0.27066515065379043</v>
@@ -10634,7 +10634,7 @@
         <v>482</v>
       </c>
       <c r="X20" t="s">
-        <v>421</v>
+        <v>412</v>
       </c>
       <c r="Y20">
         <v>3.9427500000000002</v>
@@ -10669,7 +10669,7 @@
         <v>444</v>
       </c>
       <c r="K21" t="s">
-        <v>356</v>
+        <v>378</v>
       </c>
       <c r="L21">
         <v>0.32193208719379746</v>
@@ -10704,7 +10704,7 @@
         <v>446</v>
       </c>
       <c r="K22" t="s">
-        <v>369</v>
+        <v>358</v>
       </c>
       <c r="L22">
         <v>0.6573344927201471</v>
@@ -10739,7 +10739,7 @@
         <v>448</v>
       </c>
       <c r="K23" t="s">
-        <v>352</v>
+        <v>372</v>
       </c>
       <c r="L23">
         <v>0.28992997651770519</v>
@@ -10774,7 +10774,7 @@
         <v>450</v>
       </c>
       <c r="K24" t="s">
-        <v>383</v>
+        <v>368</v>
       </c>
       <c r="L24">
         <v>0.74609319967150689</v>
@@ -10809,7 +10809,7 @@
         <v>452</v>
       </c>
       <c r="K25" t="s">
-        <v>348</v>
+        <v>364</v>
       </c>
       <c r="L25">
         <v>0.35328950844501877</v>
@@ -10844,7 +10844,7 @@
         <v>454</v>
       </c>
       <c r="K26" t="s">
-        <v>350</v>
+        <v>366</v>
       </c>
       <c r="L26">
         <v>0.7924639655878376</v>
@@ -10879,7 +10879,7 @@
         <v>456</v>
       </c>
       <c r="K27" t="s">
-        <v>362</v>
+        <v>356</v>
       </c>
       <c r="L27">
         <v>0.55411362221124194</v>
@@ -10914,7 +10914,7 @@
         <v>458</v>
       </c>
       <c r="K28" t="s">
-        <v>377</v>
+        <v>350</v>
       </c>
       <c r="L28">
         <v>1.4327274230737423</v>
@@ -10949,7 +10949,7 @@
         <v>460</v>
       </c>
       <c r="K29" t="s">
-        <v>360</v>
+        <v>354</v>
       </c>
       <c r="L29">
         <v>0.56742801517356967</v>
@@ -10984,7 +10984,7 @@
         <v>462</v>
       </c>
       <c r="K30" t="s">
-        <v>385</v>
+        <v>370</v>
       </c>
       <c r="L30">
         <v>0.35405891742987328</v>
@@ -10999,7 +10999,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F7317CC-3FBB-4554-B3E3-C7E174785982}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26280F15-5A85-4F23-B9C2-DF2F79DB26B8}">
   <dimension ref="B9:U116"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -14483,7 +14483,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D005EEBE-BF4F-459F-A903-B9D4DF775A15}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ED918156-C30A-418D-A997-C70692C605AA}">
   <dimension ref="B9:T88"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_POL_grids_kan50/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_POL_grids_kan50/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53AD7C17-ABB9-48E6-BEA1-E1910FF86930}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1E649D9-A650-4891-8316-C91CD15B4158}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -862,16 +862,64 @@
     <t>pre</t>
   </si>
   <si>
+    <t>distr_solelc_spv_POL_006</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>NRGI</t>
+  </si>
+  <si>
+    <t>daynite</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_010</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_003</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_007</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_016</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_014</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 14</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_POL_013</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 13</t>
   </si>
   <si>
-    <t>NRGI</t>
-  </si>
-  <si>
-    <t>daynite</t>
+    <t>distr_solelc_spv_POL_017</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_020</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 20</t>
   </si>
   <si>
     <t>distr_solelc_spv_POL_005</t>
@@ -892,10 +940,10 @@
     <t>connecting solar to buses in cluster 11</t>
   </si>
   <si>
-    <t>distr_solelc_spv_POL_014</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 14</t>
+    <t>distr_solelc_spv_POL_008</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 8</t>
   </si>
   <si>
     <t>distr_solelc_spv_POL_001</t>
@@ -916,12 +964,6 @@
     <t>connecting solar to buses in cluster 18</t>
   </si>
   <si>
-    <t>distr_solelc_spv_POL_008</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 8</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_POL_002</t>
   </si>
   <si>
@@ -946,57 +988,39 @@
     <t>connecting solar to buses in cluster 4</t>
   </si>
   <si>
-    <t>distr_solelc_spv_POL_003</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_007</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_016</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_006</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_010</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_017</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_020</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 20</t>
-  </si>
-  <si>
     <t>comm-in</t>
   </si>
   <si>
     <t>ncap_cost~USD21_alt</t>
   </si>
   <si>
+    <t>e_Plock_POL,e_Olsztyn_POL,e_Warsaw_POL</t>
+  </si>
+  <si>
+    <t>e_Elk_POL,e_Grajewo_POL</t>
+  </si>
+  <si>
+    <t>e_Lubin_POL,e_Swidnica_POL,e_Wroclaw_POL,e_Poznan_POL,e_Olesnica_POL</t>
+  </si>
+  <si>
+    <t>e_Koszalin_POL,e_Ustka_POL,e_Slupsk_POL</t>
+  </si>
+  <si>
+    <t>e_Olesnica_POL,e_Konin_POL,e_PiotrkowTrybunalsk_POL,e_Plock_POL</t>
+  </si>
+  <si>
+    <t>e_BielskoBiala_POL,e_Katowice_POL,e_Krakow_POL,e_Tarnow_POL</t>
+  </si>
+  <si>
     <t>e_Rzeszow_POL,e_Zamosc_POL,e_Pulawy_POL,e_Chelm_POL</t>
   </si>
   <si>
+    <t>e_Konin_POL,e_Bydgoszcz_POL,e_Wloclawek_POL,e_Kwidzyn_POL,e_Plock_POL</t>
+  </si>
+  <si>
+    <t>e_OstrowiecSwietokrz_POL,e_Pulawy_POL,e_Warsaw_POL</t>
+  </si>
+  <si>
     <t>e_Lubin_POL,e_Poznan_POL,e_Koszalin_POL,e_Bydgoszcz_POL</t>
   </si>
   <si>
@@ -1006,7 +1030,7 @@
     <t>e_Lomza_POL,e_Elk_POL,e_Bialystok_POL,e_Grajewo_POL</t>
   </si>
   <si>
-    <t>e_BielskoBiala_POL,e_Katowice_POL,e_Krakow_POL,e_Tarnow_POL</t>
+    <t>e_Bydgoszcz_POL,e_Gdansk_POL,e_Grudziadz_POL,e_Kwidzyn_POL</t>
   </si>
   <si>
     <t>e_Boleslawiec_POL,e_ZielonaGora_POL</t>
@@ -1018,9 +1042,6 @@
     <t>e_Warsaw_POL,e_Lomza_POL</t>
   </si>
   <si>
-    <t>e_Bydgoszcz_POL,e_Gdansk_POL,e_Grudziadz_POL,e_Kwidzyn_POL</t>
-  </si>
-  <si>
     <t>e_Legnica_POL,e_Swidnica_POL,e_KedzierzynKozle_POL,e_Opole_POL</t>
   </si>
   <si>
@@ -1033,25 +1054,40 @@
     <t>e_GorzowWielkopolski_POL,e_Szczecin_POL,e_Police_POL</t>
   </si>
   <si>
-    <t>e_Lubin_POL,e_Swidnica_POL,e_Wroclaw_POL,e_Poznan_POL,e_Olesnica_POL</t>
-  </si>
-  <si>
-    <t>e_Koszalin_POL,e_Ustka_POL,e_Slupsk_POL</t>
-  </si>
-  <si>
-    <t>e_Olesnica_POL,e_Konin_POL,e_PiotrkowTrybunalsk_POL,e_Plock_POL</t>
-  </si>
-  <si>
-    <t>e_Plock_POL,e_Olsztyn_POL,e_Warsaw_POL</t>
-  </si>
-  <si>
-    <t>e_Elk_POL,e_Grajewo_POL</t>
-  </si>
-  <si>
-    <t>e_Konin_POL,e_Bydgoszcz_POL,e_Wloclawek_POL,e_Kwidzyn_POL,e_Plock_POL</t>
-  </si>
-  <si>
-    <t>e_OstrowiecSwietokrz_POL,e_Pulawy_POL,e_Warsaw_POL</t>
+    <t>distr_wonelc_won_POL_019</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_017</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_012</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_003</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_015</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_016</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 16</t>
   </si>
   <si>
     <t>distr_wonelc_won_POL_005</t>
@@ -1060,40 +1096,76 @@
     <t>connecting wind onshore to buses in cluster 5</t>
   </si>
   <si>
+    <t>distr_wonelc_won_POL_007</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_001</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_013</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_008</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_011</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_010</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_006</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_009</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_004</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 4</t>
+  </si>
+  <si>
     <t>distr_wonelc_won_POL_018</t>
   </si>
   <si>
     <t>connecting wind onshore to buses in cluster 18</t>
   </si>
   <si>
-    <t>distr_wonelc_won_POL_007</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_019</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_017</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_012</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_003</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 3</t>
+    <t>distr_wonelc_won_POL_014</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_020</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 20</t>
   </si>
   <si>
     <t>distr_wonelc_won_POL_002</t>
@@ -1102,76 +1174,40 @@
     <t>connecting wind onshore to buses in cluster 2</t>
   </si>
   <si>
-    <t>distr_wonelc_won_POL_015</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_016</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_014</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_020</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_013</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_008</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_001</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_011</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_010</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_006</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_009</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_004</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 4</t>
+    <t>elc_won_POL_019</t>
+  </si>
+  <si>
+    <t>e_Katowice_POL,e_Czestochowa_POL,e_Krakow_POL,e_Kielce_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_017</t>
+  </si>
+  <si>
+    <t>e_Tarnow_POL,e_Krosno_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_012</t>
+  </si>
+  <si>
+    <t>e_ZielonaGora_POL,e_GorzowWielkopolski_POL,e_Szczecin_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_003</t>
+  </si>
+  <si>
+    <t>e_Warsaw_POL,e_Lomza_POL,e_Pulawy_POL,e_Bialystok_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_015</t>
+  </si>
+  <si>
+    <t>e_BielskoBiala_POL,e_Krakow_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_016</t>
+  </si>
+  <si>
+    <t>e_Krosno_POL,e_Debica_POL</t>
   </si>
   <si>
     <t>elc_won_POL_005</t>
@@ -1180,40 +1216,73 @@
     <t>e_Lomza_POL,e_Elk_POL,e_Grajewo_POL,e_Bialystok_POL,e_Chelm_POL</t>
   </si>
   <si>
+    <t>elc_won_POL_007</t>
+  </si>
+  <si>
+    <t>e_Warsaw_POL,e_Plock_POL,e_Olsztyn_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_001</t>
+  </si>
+  <si>
+    <t>e_PiotrkowTrybunalsk_POL,e_Kielce_POL,e_Warsaw_POL,e_OstrowiecSwietokrz_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_013</t>
+  </si>
+  <si>
+    <t>e_Lubin_POL,e_Wroclaw_POL,e_Poznan_POL,e_Olesnica_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_008</t>
+  </si>
+  <si>
+    <t>e_Olsztyn_POL,e_Elk_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_011</t>
+  </si>
+  <si>
+    <t>e_Boleslawiec_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_010</t>
+  </si>
+  <si>
+    <t>e_Police_POL,e_Koszalin_POL,e_Poznan_POL,e_Ustka_POL,e_Bydgoszcz_POL,e_Slupsk_POL,e_Gdansk_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_006</t>
+  </si>
+  <si>
+    <t>e_Olesnica_POL,e_Konin_POL,e_Bydgoszcz_POL,e_Wloclawek_POL,e_Kwidzyn_POL,e_Plock_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_009</t>
+  </si>
+  <si>
+    <t>e_Gdansk_POL,e_Grudziadz_POL,e_Kwidzyn_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_004</t>
+  </si>
+  <si>
     <t>elc_won_POL_018</t>
   </si>
   <si>
     <t>e_Boleslawiec_POL,e_Legnica_POL,e_Swidnica_POL,e_KedzierzynKozle_POL,e_Opole_POL,e_Olesnica_POL</t>
   </si>
   <si>
-    <t>elc_won_POL_007</t>
-  </si>
-  <si>
-    <t>e_Warsaw_POL,e_Plock_POL,e_Olsztyn_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_019</t>
-  </si>
-  <si>
-    <t>e_Katowice_POL,e_Czestochowa_POL,e_Krakow_POL,e_Kielce_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_017</t>
-  </si>
-  <si>
-    <t>e_Tarnow_POL,e_Krosno_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_012</t>
-  </si>
-  <si>
-    <t>e_ZielonaGora_POL,e_GorzowWielkopolski_POL,e_Szczecin_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_003</t>
-  </si>
-  <si>
-    <t>e_Warsaw_POL,e_Lomza_POL,e_Pulawy_POL,e_Bialystok_POL</t>
+    <t>elc_won_POL_014</t>
+  </si>
+  <si>
+    <t>e_Lubin_POL,e_Poznan_POL,e_Bydgoszcz_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_020</t>
+  </si>
+  <si>
+    <t>e_Sosnowiec_POL,e_KedzierzynKozle_POL,e_Olesnica_POL,e_Gliwice_POL,e_Czestochowa_POL,e_Radomsko_POL</t>
   </si>
   <si>
     <t>elc_won_POL_002</t>
@@ -1222,73 +1291,28 @@
     <t>e_Tarnow_POL,e_Kielce_POL,e_OstrowiecSwietokrz_POL,e_Mielec_POL,e_Pulawy_POL,e_Rzeszow_POL</t>
   </si>
   <si>
-    <t>elc_won_POL_015</t>
-  </si>
-  <si>
-    <t>e_BielskoBiala_POL,e_Krakow_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_016</t>
-  </si>
-  <si>
-    <t>e_Krosno_POL,e_Debica_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_014</t>
-  </si>
-  <si>
-    <t>e_Lubin_POL,e_Poznan_POL,e_Bydgoszcz_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_020</t>
-  </si>
-  <si>
-    <t>e_Sosnowiec_POL,e_KedzierzynKozle_POL,e_Olesnica_POL,e_Gliwice_POL,e_Czestochowa_POL,e_Radomsko_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_013</t>
-  </si>
-  <si>
-    <t>e_Lubin_POL,e_Wroclaw_POL,e_Poznan_POL,e_Olesnica_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_008</t>
-  </si>
-  <si>
-    <t>e_Olsztyn_POL,e_Elk_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_001</t>
-  </si>
-  <si>
-    <t>e_PiotrkowTrybunalsk_POL,e_Kielce_POL,e_Warsaw_POL,e_OstrowiecSwietokrz_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_011</t>
-  </si>
-  <si>
-    <t>e_Boleslawiec_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_010</t>
-  </si>
-  <si>
-    <t>e_Police_POL,e_Koszalin_POL,e_Poznan_POL,e_Ustka_POL,e_Bydgoszcz_POL,e_Slupsk_POL,e_Gdansk_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_006</t>
-  </si>
-  <si>
-    <t>e_Olesnica_POL,e_Konin_POL,e_Bydgoszcz_POL,e_Wloclawek_POL,e_Kwidzyn_POL,e_Plock_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_009</t>
-  </si>
-  <si>
-    <t>e_Gdansk_POL,e_Grudziadz_POL,e_Kwidzyn_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_004</t>
+    <t>distr_wofelc_wof_POL_002</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_POL_006</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_POL_005</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_POL_001</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 1</t>
   </si>
   <si>
     <t>distr_wofelc_wof_POL_003</t>
@@ -1297,16 +1321,16 @@
     <t>connecting wind offshore to buses in cluster 3</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_POL_005</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_POL_001</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 1</t>
+    <t>distr_wofelc_wof_POL_008</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_POL_007</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 7</t>
   </si>
   <si>
     <t>distr_wofelc_wof_POL_010</t>
@@ -1327,51 +1351,45 @@
     <t>connecting wind offshore to buses in cluster 4</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_POL_006</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_POL_002</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_POL_008</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_POL_007</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 7</t>
+    <t>elc_wof_POL_002</t>
+  </si>
+  <si>
+    <t>e_Gdynia_POL,e_Gdansk_POL</t>
+  </si>
+  <si>
+    <t>elc_wof_POL_006</t>
+  </si>
+  <si>
+    <t>e_Gdynia_POL</t>
+  </si>
+  <si>
+    <t>elc_wof_POL_005</t>
+  </si>
+  <si>
+    <t>elc_wof_POL_001</t>
+  </si>
+  <si>
+    <t>e_Gdansk_POL</t>
   </si>
   <si>
     <t>elc_wof_POL_003</t>
   </si>
   <si>
-    <t>e_Gdansk_POL</t>
-  </si>
-  <si>
-    <t>elc_wof_POL_005</t>
-  </si>
-  <si>
-    <t>e_Gdynia_POL</t>
-  </si>
-  <si>
-    <t>elc_wof_POL_001</t>
+    <t>elc_wof_POL_008</t>
+  </si>
+  <si>
+    <t>e_Police_POL,e_Koszalin_POL</t>
+  </si>
+  <si>
+    <t>elc_wof_POL_007</t>
+  </si>
+  <si>
+    <t>e_Koszalin_POL</t>
   </si>
   <si>
     <t>elc_wof_POL_010</t>
   </si>
   <si>
-    <t>e_Koszalin_POL</t>
-  </si>
-  <si>
     <t>elc_wof_POL_009</t>
   </si>
   <si>
@@ -1382,24 +1400,6 @@
   </si>
   <si>
     <t>e_Ustka_POL,e_Gdynia_POL</t>
-  </si>
-  <si>
-    <t>elc_wof_POL_006</t>
-  </si>
-  <si>
-    <t>elc_wof_POL_002</t>
-  </si>
-  <si>
-    <t>e_Gdynia_POL,e_Gdansk_POL</t>
-  </si>
-  <si>
-    <t>elc_wof_POL_008</t>
-  </si>
-  <si>
-    <t>e_Police_POL,e_Koszalin_POL</t>
-  </si>
-  <si>
-    <t>elc_wof_POL_007</t>
   </si>
   <si>
     <t>e_won_POL_001</t>
@@ -7135,7 +7135,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{132BC21B-A86A-4D87-B393-F73800E6ECD0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2CE08A0-6DFC-47C4-B0DC-4A99B678EFFC}">
   <dimension ref="B9:BD30"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -7373,16 +7373,16 @@
         <v>244</v>
       </c>
       <c r="Y11" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="Z11" t="s">
         <v>288</v>
       </c>
       <c r="AA11">
-        <v>0.99606480786442353</v>
+        <v>0.99658775492800411</v>
       </c>
       <c r="AB11">
-        <v>72.145189152235062</v>
+        <v>62.557826319923819</v>
       </c>
       <c r="AD11" t="s">
         <v>243</v>
@@ -7415,10 +7415,10 @@
         <v>349</v>
       </c>
       <c r="AO11">
-        <v>0.9963019969989696</v>
+        <v>0.99872641243407079</v>
       </c>
       <c r="AP11">
-        <v>67.796721685557472</v>
+        <v>23.349105375368897</v>
       </c>
       <c r="AR11" t="s">
         <v>243</v>
@@ -7451,10 +7451,10 @@
         <v>408</v>
       </c>
       <c r="BC11">
-        <v>0.99564787435456037</v>
+        <v>0.99353721168226494</v>
       </c>
       <c r="BD11">
-        <v>622.95871485949408</v>
+        <v>780.55486105754892</v>
       </c>
     </row>
     <row r="12" spans="2:56">
@@ -7519,16 +7519,16 @@
         <v>248</v>
       </c>
       <c r="Y12" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="Z12" t="s">
         <v>289</v>
       </c>
       <c r="AA12">
-        <v>0.99730738889353909</v>
+        <v>0.99510886326373238</v>
       </c>
       <c r="AB12">
-        <v>49.364536951784054</v>
+        <v>89.670840164906522</v>
       </c>
       <c r="AD12" t="s">
         <v>243</v>
@@ -7561,10 +7561,10 @@
         <v>351</v>
       </c>
       <c r="AO12">
-        <v>0.99622969699231045</v>
+        <v>0.99776911581804295</v>
       </c>
       <c r="AP12">
-        <v>69.122221807641537</v>
+        <v>40.899543335879912</v>
       </c>
       <c r="AR12" t="s">
         <v>243</v>
@@ -7597,10 +7597,10 @@
         <v>410</v>
       </c>
       <c r="BC12">
-        <v>0.99328660064428831</v>
+        <v>0.99615739524125424</v>
       </c>
       <c r="BD12">
-        <v>799.26715189313825</v>
+        <v>584.91448865302027</v>
       </c>
     </row>
     <row r="13" spans="2:56">
@@ -7665,16 +7665,16 @@
         <v>250</v>
       </c>
       <c r="Y13" t="s">
-        <v>233</v>
+        <v>224</v>
       </c>
       <c r="Z13" t="s">
         <v>290</v>
       </c>
       <c r="AA13">
-        <v>0.99481478101166732</v>
+        <v>0.99770934816564383</v>
       </c>
       <c r="AB13">
-        <v>95.062348119433295</v>
+        <v>41.995283629862939</v>
       </c>
       <c r="AD13" t="s">
         <v>243</v>
@@ -7707,10 +7707,10 @@
         <v>353</v>
       </c>
       <c r="AO13">
-        <v>0.99653588726932718</v>
+        <v>0.99749126227646956</v>
       </c>
       <c r="AP13">
-        <v>63.508733395668145</v>
+        <v>45.993524931390482</v>
       </c>
       <c r="AR13" t="s">
         <v>243</v>
@@ -7740,13 +7740,13 @@
         <v>411</v>
       </c>
       <c r="BB13" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="BC13">
-        <v>0.99644441082752833</v>
+        <v>0.99328660064428831</v>
       </c>
       <c r="BD13">
-        <v>563.48399154455342</v>
+        <v>799.26715189313825</v>
       </c>
     </row>
     <row r="14" spans="2:56">
@@ -7811,16 +7811,16 @@
         <v>252</v>
       </c>
       <c r="Y14" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="Z14" t="s">
         <v>291</v>
       </c>
       <c r="AA14">
-        <v>0.99681878296180493</v>
+        <v>0.9970292559096442</v>
       </c>
       <c r="AB14">
-        <v>58.322312366909152</v>
+        <v>54.463641656523762</v>
       </c>
       <c r="AD14" t="s">
         <v>243</v>
@@ -7853,10 +7853,10 @@
         <v>355</v>
       </c>
       <c r="AO14">
-        <v>0.99872641243407079</v>
+        <v>0.99807543246352515</v>
       </c>
       <c r="AP14">
-        <v>23.349105375368897</v>
+        <v>35.283738168705199</v>
       </c>
       <c r="AR14" t="s">
         <v>243</v>
@@ -7889,10 +7889,10 @@
         <v>413</v>
       </c>
       <c r="BC14">
-        <v>0.99608994650263638</v>
+        <v>0.99644441082752833</v>
       </c>
       <c r="BD14">
-        <v>589.950661136485</v>
+        <v>563.48399154455342</v>
       </c>
     </row>
     <row r="15" spans="2:56">
@@ -7957,16 +7957,16 @@
         <v>254</v>
       </c>
       <c r="Y15" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="Z15" t="s">
         <v>292</v>
       </c>
       <c r="AA15">
-        <v>0.99790408176624201</v>
+        <v>0.9982126095160021</v>
       </c>
       <c r="AB15">
-        <v>38.425167618896296</v>
+        <v>32.768825539961391</v>
       </c>
       <c r="AD15" t="s">
         <v>243</v>
@@ -7999,10 +7999,10 @@
         <v>357</v>
       </c>
       <c r="AO15">
-        <v>0.99776911581804295</v>
+        <v>0.99641308487583879</v>
       </c>
       <c r="AP15">
-        <v>40.899543335879912</v>
+        <v>65.760110609622657</v>
       </c>
       <c r="AR15" t="s">
         <v>243</v>
@@ -8032,13 +8032,13 @@
         <v>414</v>
       </c>
       <c r="BB15" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="BC15">
-        <v>0.99399682431672776</v>
+        <v>0.99564787435456037</v>
       </c>
       <c r="BD15">
-        <v>746.2371176843244</v>
+        <v>622.95871485949408</v>
       </c>
     </row>
     <row r="16" spans="2:56">
@@ -8103,16 +8103,16 @@
         <v>256</v>
       </c>
       <c r="Y16" t="s">
-        <v>222</v>
+        <v>235</v>
       </c>
       <c r="Z16" t="s">
         <v>293</v>
       </c>
       <c r="AA16">
-        <v>0.99707401400885998</v>
+        <v>0.99790408176624201</v>
       </c>
       <c r="AB16">
-        <v>53.643076504234422</v>
+        <v>38.425167618896296</v>
       </c>
       <c r="AD16" t="s">
         <v>243</v>
@@ -8145,10 +8145,10 @@
         <v>359</v>
       </c>
       <c r="AO16">
-        <v>0.99749126227646956</v>
+        <v>0.99449756685866841</v>
       </c>
       <c r="AP16">
-        <v>45.993524931390482</v>
+        <v>100.87794092441324</v>
       </c>
       <c r="AR16" t="s">
         <v>243</v>
@@ -8175,16 +8175,16 @@
         <v>397</v>
       </c>
       <c r="BA16" t="s">
+        <v>415</v>
+      </c>
+      <c r="BB16" t="s">
         <v>416</v>
       </c>
-      <c r="BB16" t="s">
-        <v>417</v>
-      </c>
       <c r="BC16">
-        <v>0.99255663966463281</v>
+        <v>0.99383352379209899</v>
       </c>
       <c r="BD16">
-        <v>853.77090504074806</v>
+        <v>758.43022352327353</v>
       </c>
     </row>
     <row r="17" spans="2:56">
@@ -8249,16 +8249,16 @@
         <v>258</v>
       </c>
       <c r="Y17" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="Z17" t="s">
         <v>294</v>
       </c>
       <c r="AA17">
-        <v>0.99826037700975512</v>
+        <v>0.99606480786442353</v>
       </c>
       <c r="AB17">
-        <v>31.893088154488542</v>
+        <v>72.145189152235062</v>
       </c>
       <c r="AD17" t="s">
         <v>243</v>
@@ -8291,10 +8291,10 @@
         <v>361</v>
       </c>
       <c r="AO17">
-        <v>0.99807543246352515</v>
+        <v>0.9963019969989696</v>
       </c>
       <c r="AP17">
-        <v>35.283738168705199</v>
+        <v>67.796721685557472</v>
       </c>
       <c r="AR17" t="s">
         <v>243</v>
@@ -8321,16 +8321,16 @@
         <v>399</v>
       </c>
       <c r="BA17" t="s">
+        <v>417</v>
+      </c>
+      <c r="BB17" t="s">
         <v>418</v>
       </c>
-      <c r="BB17" t="s">
-        <v>410</v>
-      </c>
       <c r="BC17">
-        <v>0.99615739524125424</v>
+        <v>0.99603306101923861</v>
       </c>
       <c r="BD17">
-        <v>584.91448865302027</v>
+        <v>594.19811056351818</v>
       </c>
     </row>
     <row r="18" spans="2:56">
@@ -8395,16 +8395,16 @@
         <v>260</v>
       </c>
       <c r="Y18" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="Z18" t="s">
         <v>295</v>
       </c>
       <c r="AA18">
-        <v>0.99922515067657613</v>
+        <v>0.99930490342600053</v>
       </c>
       <c r="AB18">
-        <v>14.205570929438155</v>
+        <v>12.743437189989784</v>
       </c>
       <c r="AD18" t="s">
         <v>243</v>
@@ -8437,10 +8437,10 @@
         <v>363</v>
       </c>
       <c r="AO18">
-        <v>0.99845791964146047</v>
+        <v>0.99653588726932718</v>
       </c>
       <c r="AP18">
-        <v>28.2714732398913</v>
+        <v>63.508733395668145</v>
       </c>
       <c r="AR18" t="s">
         <v>243</v>
@@ -8470,13 +8470,13 @@
         <v>419</v>
       </c>
       <c r="BB18" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="BC18">
-        <v>0.99353721168226494</v>
+        <v>0.99608994650263638</v>
       </c>
       <c r="BD18">
-        <v>780.55486105754892</v>
+        <v>589.950661136485</v>
       </c>
     </row>
     <row r="19" spans="2:56">
@@ -8541,16 +8541,16 @@
         <v>262</v>
       </c>
       <c r="Y19" t="s">
-        <v>229</v>
+        <v>241</v>
       </c>
       <c r="Z19" t="s">
         <v>296</v>
       </c>
       <c r="AA19">
-        <v>0.99693515631487983</v>
+        <v>0.99881801309037566</v>
       </c>
       <c r="AB19">
-        <v>56.188800893869058</v>
+        <v>21.669760009780138</v>
       </c>
       <c r="AD19" t="s">
         <v>243</v>
@@ -8583,10 +8583,10 @@
         <v>365</v>
       </c>
       <c r="AO19">
-        <v>0.99641308487583879</v>
+        <v>0.99871360797890252</v>
       </c>
       <c r="AP19">
-        <v>65.760110609622657</v>
+        <v>23.583853720120768</v>
       </c>
       <c r="AR19" t="s">
         <v>243</v>
@@ -8613,16 +8613,16 @@
         <v>403</v>
       </c>
       <c r="BA19" t="s">
+        <v>420</v>
+      </c>
+      <c r="BB19" t="s">
         <v>421</v>
       </c>
-      <c r="BB19" t="s">
-        <v>422</v>
-      </c>
       <c r="BC19">
-        <v>0.99383352379209899</v>
+        <v>0.99399682431672776</v>
       </c>
       <c r="BD19">
-        <v>758.43022352327353</v>
+        <v>746.2371176843244</v>
       </c>
     </row>
     <row r="20" spans="2:56">
@@ -8687,16 +8687,16 @@
         <v>264</v>
       </c>
       <c r="Y20" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="Z20" t="s">
         <v>297</v>
       </c>
       <c r="AA20">
-        <v>0.99515616506526205</v>
+        <v>0.99730738889353909</v>
       </c>
       <c r="AB20">
-        <v>88.803640470195262</v>
+        <v>49.364536951784054</v>
       </c>
       <c r="AD20" t="s">
         <v>243</v>
@@ -8729,10 +8729,10 @@
         <v>367</v>
       </c>
       <c r="AO20">
-        <v>0.99449756685866841</v>
+        <v>0.99883902037019667</v>
       </c>
       <c r="AP20">
-        <v>100.87794092441324</v>
+        <v>21.284626546395259</v>
       </c>
       <c r="AR20" t="s">
         <v>243</v>
@@ -8759,16 +8759,16 @@
         <v>405</v>
       </c>
       <c r="BA20" t="s">
+        <v>422</v>
+      </c>
+      <c r="BB20" t="s">
         <v>423</v>
       </c>
-      <c r="BB20" t="s">
-        <v>413</v>
-      </c>
       <c r="BC20">
-        <v>0.99603306101923861</v>
+        <v>0.99255663966463281</v>
       </c>
       <c r="BD20">
-        <v>594.19811056351818</v>
+        <v>853.77090504074806</v>
       </c>
     </row>
     <row r="21" spans="2:56">
@@ -8833,16 +8833,16 @@
         <v>266</v>
       </c>
       <c r="Y21" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="Z21" t="s">
         <v>298</v>
       </c>
       <c r="AA21">
-        <v>0.99728872234103139</v>
+        <v>0.99481478101166732</v>
       </c>
       <c r="AB21">
-        <v>49.70675708109188</v>
+        <v>95.062348119433295</v>
       </c>
       <c r="AD21" t="s">
         <v>243</v>
@@ -8875,10 +8875,10 @@
         <v>369</v>
       </c>
       <c r="AO21">
-        <v>0.99730422320290779</v>
+        <v>0.99521984547821263</v>
       </c>
       <c r="AP21">
-        <v>49.422574613357185</v>
+        <v>87.636166232768815</v>
       </c>
     </row>
     <row r="22" spans="2:56">
@@ -8943,16 +8943,16 @@
         <v>268</v>
       </c>
       <c r="Y22" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="Z22" t="s">
         <v>299</v>
       </c>
       <c r="AA22">
-        <v>0.99583567586599486</v>
+        <v>0.99681878296180493</v>
       </c>
       <c r="AB22">
-        <v>76.34594245676044</v>
+        <v>58.322312366909152</v>
       </c>
       <c r="AD22" t="s">
         <v>243</v>
@@ -8985,10 +8985,10 @@
         <v>371</v>
       </c>
       <c r="AO22">
-        <v>0.99805709209211746</v>
+        <v>0.99802303154782224</v>
       </c>
       <c r="AP22">
-        <v>35.619978311179104</v>
+        <v>36.244421623259619</v>
       </c>
     </row>
     <row r="23" spans="2:56">
@@ -9053,16 +9053,16 @@
         <v>270</v>
       </c>
       <c r="Y23" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="Z23" t="s">
         <v>300</v>
       </c>
       <c r="AA23">
-        <v>0.99785589517057005</v>
+        <v>0.99693515631487983</v>
       </c>
       <c r="AB23">
-        <v>39.308588539549028</v>
+        <v>56.188800893869058</v>
       </c>
       <c r="AD23" t="s">
         <v>243</v>
@@ -9095,10 +9095,10 @@
         <v>373</v>
       </c>
       <c r="AO23">
-        <v>0.99883902037019667</v>
+        <v>0.99714358927215652</v>
       </c>
       <c r="AP23">
-        <v>21.284626546395259</v>
+        <v>52.367530010463909</v>
       </c>
     </row>
     <row r="24" spans="2:56">
@@ -9163,16 +9163,16 @@
         <v>272</v>
       </c>
       <c r="Y24" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="Z24" t="s">
         <v>301</v>
       </c>
       <c r="AA24">
-        <v>0.99770934816564383</v>
+        <v>0.99707401400885998</v>
       </c>
       <c r="AB24">
-        <v>41.995283629862939</v>
+        <v>53.643076504234422</v>
       </c>
       <c r="AD24" t="s">
         <v>243</v>
@@ -9205,10 +9205,10 @@
         <v>375</v>
       </c>
       <c r="AO24">
-        <v>0.99521984547821263</v>
+        <v>0.99827231256984739</v>
       </c>
       <c r="AP24">
-        <v>87.636166232768815</v>
+        <v>31.674269552798414</v>
       </c>
     </row>
     <row r="25" spans="2:56">
@@ -9273,16 +9273,16 @@
         <v>274</v>
       </c>
       <c r="Y25" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="Z25" t="s">
         <v>302</v>
       </c>
       <c r="AA25">
-        <v>0.9970292559096442</v>
+        <v>0.99826037700975512</v>
       </c>
       <c r="AB25">
-        <v>54.463641656523762</v>
+        <v>31.893088154488542</v>
       </c>
       <c r="AD25" t="s">
         <v>243</v>
@@ -9315,10 +9315,10 @@
         <v>377</v>
       </c>
       <c r="AO25">
-        <v>0.99871360797890252</v>
+        <v>0.99635146162488653</v>
       </c>
       <c r="AP25">
-        <v>23.583853720120768</v>
+        <v>66.889870210414614</v>
       </c>
     </row>
     <row r="26" spans="2:56">
@@ -9383,16 +9383,16 @@
         <v>276</v>
       </c>
       <c r="Y26" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="Z26" t="s">
         <v>303</v>
       </c>
       <c r="AA26">
-        <v>0.9982126095160021</v>
+        <v>0.99922515067657613</v>
       </c>
       <c r="AB26">
-        <v>32.768825539961391</v>
+        <v>14.205570929438155</v>
       </c>
       <c r="AD26" t="s">
         <v>243</v>
@@ -9422,13 +9422,13 @@
         <v>378</v>
       </c>
       <c r="AN26" t="s">
-        <v>379</v>
+        <v>294</v>
       </c>
       <c r="AO26">
-        <v>0.99802303154782224</v>
+        <v>0.99586212495478665</v>
       </c>
       <c r="AP26">
-        <v>36.244421623259619</v>
+        <v>75.861042495577635</v>
       </c>
     </row>
     <row r="27" spans="2:56">
@@ -9493,16 +9493,16 @@
         <v>278</v>
       </c>
       <c r="Y27" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="Z27" t="s">
         <v>304</v>
       </c>
       <c r="AA27">
-        <v>0.99658775492800411</v>
+        <v>0.99515616506526205</v>
       </c>
       <c r="AB27">
-        <v>62.557826319923819</v>
+        <v>88.803640470195262</v>
       </c>
       <c r="AD27" t="s">
         <v>243</v>
@@ -9529,16 +9529,16 @@
         <v>340</v>
       </c>
       <c r="AM27" t="s">
+        <v>379</v>
+      </c>
+      <c r="AN27" t="s">
         <v>380</v>
       </c>
-      <c r="AN27" t="s">
-        <v>381</v>
-      </c>
       <c r="AO27">
-        <v>0.99714358927215652</v>
+        <v>0.99622969699231045</v>
       </c>
       <c r="AP27">
-        <v>52.367530010463909</v>
+        <v>69.122221807641537</v>
       </c>
     </row>
     <row r="28" spans="2:56">
@@ -9603,16 +9603,16 @@
         <v>280</v>
       </c>
       <c r="Y28" t="s">
-        <v>231</v>
+        <v>240</v>
       </c>
       <c r="Z28" t="s">
         <v>305</v>
       </c>
       <c r="AA28">
-        <v>0.99510886326373238</v>
+        <v>0.99728872234103139</v>
       </c>
       <c r="AB28">
-        <v>89.670840164906522</v>
+        <v>49.70675708109188</v>
       </c>
       <c r="AD28" t="s">
         <v>243</v>
@@ -9639,16 +9639,16 @@
         <v>342</v>
       </c>
       <c r="AM28" t="s">
+        <v>381</v>
+      </c>
+      <c r="AN28" t="s">
         <v>382</v>
       </c>
-      <c r="AN28" t="s">
-        <v>383</v>
-      </c>
       <c r="AO28">
-        <v>0.99827231256984739</v>
+        <v>0.99730422320290779</v>
       </c>
       <c r="AP28">
-        <v>31.674269552798414</v>
+        <v>49.422574613357185</v>
       </c>
     </row>
     <row r="29" spans="2:56">
@@ -9713,16 +9713,16 @@
         <v>282</v>
       </c>
       <c r="Y29" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="Z29" t="s">
         <v>306</v>
       </c>
       <c r="AA29">
-        <v>0.99930490342600053</v>
+        <v>0.99583567586599486</v>
       </c>
       <c r="AB29">
-        <v>12.743437189989784</v>
+        <v>76.34594245676044</v>
       </c>
       <c r="AD29" t="s">
         <v>243</v>
@@ -9749,16 +9749,16 @@
         <v>344</v>
       </c>
       <c r="AM29" t="s">
+        <v>383</v>
+      </c>
+      <c r="AN29" t="s">
         <v>384</v>
       </c>
-      <c r="AN29" t="s">
-        <v>385</v>
-      </c>
       <c r="AO29">
-        <v>0.99635146162488653</v>
+        <v>0.99805709209211746</v>
       </c>
       <c r="AP29">
-        <v>66.889870210414614</v>
+        <v>35.619978311179104</v>
       </c>
     </row>
     <row r="30" spans="2:56">
@@ -9823,16 +9823,16 @@
         <v>284</v>
       </c>
       <c r="Y30" t="s">
-        <v>241</v>
+        <v>225</v>
       </c>
       <c r="Z30" t="s">
         <v>307</v>
       </c>
       <c r="AA30">
-        <v>0.99881801309037566</v>
+        <v>0.99785589517057005</v>
       </c>
       <c r="AB30">
-        <v>21.669760009780138</v>
+        <v>39.308588539549028</v>
       </c>
       <c r="AD30" t="s">
         <v>243</v>
@@ -9859,16 +9859,16 @@
         <v>346</v>
       </c>
       <c r="AM30" t="s">
+        <v>385</v>
+      </c>
+      <c r="AN30" t="s">
         <v>386</v>
       </c>
-      <c r="AN30" t="s">
-        <v>288</v>
-      </c>
       <c r="AO30">
-        <v>0.99586212495478665</v>
+        <v>0.99845791964146047</v>
       </c>
       <c r="AP30">
-        <v>75.861042495577635</v>
+        <v>28.2714732398913</v>
       </c>
     </row>
   </sheetData>
@@ -9877,7 +9877,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FECED44C-8F32-4276-ACE2-86D89654F16A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{828691EB-3C00-483B-97C4-DA5CEB24E96F}">
   <dimension ref="B9:Z30"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -9989,7 +9989,7 @@
         <v>424</v>
       </c>
       <c r="K11" t="s">
-        <v>376</v>
+        <v>364</v>
       </c>
       <c r="L11">
         <v>0.30278350605008381</v>
@@ -10022,7 +10022,7 @@
         <v>464</v>
       </c>
       <c r="X11" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="Y11">
         <v>0.83925000000000005</v>
@@ -10057,7 +10057,7 @@
         <v>426</v>
       </c>
       <c r="K12" t="s">
-        <v>362</v>
+        <v>385</v>
       </c>
       <c r="L12">
         <v>0.42035497786033621</v>
@@ -10090,7 +10090,7 @@
         <v>466</v>
       </c>
       <c r="X12" t="s">
-        <v>419</v>
+        <v>407</v>
       </c>
       <c r="Y12">
         <v>16.887</v>
@@ -10125,7 +10125,7 @@
         <v>428</v>
       </c>
       <c r="K13" t="s">
-        <v>360</v>
+        <v>354</v>
       </c>
       <c r="L13">
         <v>1.6077871713950227</v>
@@ -10158,7 +10158,7 @@
         <v>468</v>
       </c>
       <c r="X13" t="s">
-        <v>407</v>
+        <v>414</v>
       </c>
       <c r="Y13">
         <v>11.2965</v>
@@ -10193,7 +10193,7 @@
         <v>430</v>
       </c>
       <c r="K14" t="s">
-        <v>386</v>
+        <v>378</v>
       </c>
       <c r="L14">
         <v>2.531891424764753</v>
@@ -10226,7 +10226,7 @@
         <v>470</v>
       </c>
       <c r="X14" t="s">
-        <v>416</v>
+        <v>422</v>
       </c>
       <c r="Y14">
         <v>6.6577500000000001</v>
@@ -10261,7 +10261,7 @@
         <v>432</v>
       </c>
       <c r="K15" t="s">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="L15">
         <v>7.6497810049421515</v>
@@ -10294,7 +10294,7 @@
         <v>472</v>
       </c>
       <c r="X15" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="Y15">
         <v>17.089500000000001</v>
@@ -10329,7 +10329,7 @@
         <v>434</v>
       </c>
       <c r="K16" t="s">
-        <v>382</v>
+        <v>374</v>
       </c>
       <c r="L16">
         <v>0.60733325583919984</v>
@@ -10362,7 +10362,7 @@
         <v>474</v>
       </c>
       <c r="X16" t="s">
-        <v>418</v>
+        <v>409</v>
       </c>
       <c r="Y16">
         <v>8.8230000000000004</v>
@@ -10397,7 +10397,7 @@
         <v>436</v>
       </c>
       <c r="K17" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="L17">
         <v>0.78389041837100704</v>
@@ -10430,7 +10430,7 @@
         <v>476</v>
       </c>
       <c r="X17" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
       <c r="Y17">
         <v>0.22650000000000001</v>
@@ -10465,7 +10465,7 @@
         <v>438</v>
       </c>
       <c r="K18" t="s">
-        <v>374</v>
+        <v>368</v>
       </c>
       <c r="L18">
         <v>3.0365724666245324</v>
@@ -10498,7 +10498,7 @@
         <v>478</v>
       </c>
       <c r="X18" t="s">
-        <v>421</v>
+        <v>415</v>
       </c>
       <c r="Y18">
         <v>9.5062499999999996</v>
@@ -10533,7 +10533,7 @@
         <v>440</v>
       </c>
       <c r="K19" t="s">
-        <v>384</v>
+        <v>376</v>
       </c>
       <c r="L19">
         <v>0.22970161230087291</v>
@@ -10566,7 +10566,7 @@
         <v>480</v>
       </c>
       <c r="X19" t="s">
-        <v>414</v>
+        <v>420</v>
       </c>
       <c r="Y19">
         <v>13.37175</v>
@@ -10601,7 +10601,7 @@
         <v>442</v>
       </c>
       <c r="K20" t="s">
-        <v>380</v>
+        <v>372</v>
       </c>
       <c r="L20">
         <v>0.27066515065379043</v>
@@ -10634,7 +10634,7 @@
         <v>482</v>
       </c>
       <c r="X20" t="s">
-        <v>412</v>
+        <v>419</v>
       </c>
       <c r="Y20">
         <v>3.9427500000000002</v>
@@ -10669,7 +10669,7 @@
         <v>444</v>
       </c>
       <c r="K21" t="s">
-        <v>378</v>
+        <v>370</v>
       </c>
       <c r="L21">
         <v>0.32193208719379746</v>
@@ -10704,7 +10704,7 @@
         <v>446</v>
       </c>
       <c r="K22" t="s">
-        <v>358</v>
+        <v>352</v>
       </c>
       <c r="L22">
         <v>0.6573344927201471</v>
@@ -10739,7 +10739,7 @@
         <v>448</v>
       </c>
       <c r="K23" t="s">
-        <v>372</v>
+        <v>366</v>
       </c>
       <c r="L23">
         <v>0.28992997651770519</v>
@@ -10774,7 +10774,7 @@
         <v>450</v>
       </c>
       <c r="K24" t="s">
-        <v>368</v>
+        <v>381</v>
       </c>
       <c r="L24">
         <v>0.74609319967150689</v>
@@ -10809,7 +10809,7 @@
         <v>452</v>
       </c>
       <c r="K25" t="s">
-        <v>364</v>
+        <v>356</v>
       </c>
       <c r="L25">
         <v>0.35328950844501877</v>
@@ -10844,7 +10844,7 @@
         <v>454</v>
       </c>
       <c r="K26" t="s">
-        <v>366</v>
+        <v>358</v>
       </c>
       <c r="L26">
         <v>0.7924639655878376</v>
@@ -10879,7 +10879,7 @@
         <v>456</v>
       </c>
       <c r="K27" t="s">
-        <v>356</v>
+        <v>350</v>
       </c>
       <c r="L27">
         <v>0.55411362221124194</v>
@@ -10914,7 +10914,7 @@
         <v>458</v>
       </c>
       <c r="K28" t="s">
-        <v>350</v>
+        <v>379</v>
       </c>
       <c r="L28">
         <v>1.4327274230737423</v>
@@ -10949,7 +10949,7 @@
         <v>460</v>
       </c>
       <c r="K29" t="s">
-        <v>354</v>
+        <v>348</v>
       </c>
       <c r="L29">
         <v>0.56742801517356967</v>
@@ -10984,7 +10984,7 @@
         <v>462</v>
       </c>
       <c r="K30" t="s">
-        <v>370</v>
+        <v>383</v>
       </c>
       <c r="L30">
         <v>0.35405891742987328</v>
@@ -10999,7 +10999,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26280F15-5A85-4F23-B9C2-DF2F79DB26B8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F7365AA-67AF-4B2E-9065-C9887E1C1080}">
   <dimension ref="B9:U116"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -14483,7 +14483,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ED918156-C30A-418D-A997-C70692C605AA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D7063D2-4675-47D6-9EF0-98FED37960F6}">
   <dimension ref="B9:T88"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_POL_grids_kan50/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_POL_grids_kan50/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1E649D9-A650-4891-8316-C91CD15B4158}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F87F2F73-0947-4E2B-B0D3-6675D08BBE27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -862,24 +862,102 @@
     <t>pre</t>
   </si>
   <si>
+    <t>distr_solelc_spv_POL_013</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>NRGI</t>
+  </si>
+  <si>
+    <t>daynite</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_004</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_014</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_017</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_020</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_002</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_019</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_009</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 9</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_POL_006</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 6</t>
   </si>
   <si>
-    <t>NRGI</t>
-  </si>
-  <si>
-    <t>daynite</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_POL_010</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 10</t>
   </si>
   <si>
+    <t>distr_solelc_spv_POL_001</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_015</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_018</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_005</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_008</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 8</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_POL_003</t>
   </si>
   <si>
@@ -898,36 +976,6 @@
     <t>connecting solar to buses in cluster 16</t>
   </si>
   <si>
-    <t>distr_solelc_spv_POL_014</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_013</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_017</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_020</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_005</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 5</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_POL_012</t>
   </si>
   <si>
@@ -940,66 +988,57 @@
     <t>connecting solar to buses in cluster 11</t>
   </si>
   <si>
-    <t>distr_solelc_spv_POL_008</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_001</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_015</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_018</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_002</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_019</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_009</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_004</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 4</t>
-  </si>
-  <si>
     <t>comm-in</t>
   </si>
   <si>
     <t>ncap_cost~USD21_alt</t>
   </si>
   <si>
+    <t>e_Rzeszow_POL,e_Zamosc_POL,e_Pulawy_POL,e_Chelm_POL</t>
+  </si>
+  <si>
+    <t>e_GorzowWielkopolski_POL,e_Szczecin_POL,e_Police_POL</t>
+  </si>
+  <si>
+    <t>e_BielskoBiala_POL,e_Katowice_POL,e_Krakow_POL,e_Tarnow_POL</t>
+  </si>
+  <si>
+    <t>e_Konin_POL,e_Bydgoszcz_POL,e_Wloclawek_POL,e_Kwidzyn_POL,e_Plock_POL</t>
+  </si>
+  <si>
+    <t>e_OstrowiecSwietokrz_POL,e_Pulawy_POL,e_Warsaw_POL</t>
+  </si>
+  <si>
+    <t>e_Legnica_POL,e_Swidnica_POL,e_KedzierzynKozle_POL,e_Opole_POL</t>
+  </si>
+  <si>
+    <t>e_Kielce_POL,e_Warsaw_POL,e_OstrowiecSwietokrz_POL</t>
+  </si>
+  <si>
+    <t>e_Pulawy_POL,e_Bialystok_POL,e_Chelm_POL</t>
+  </si>
+  <si>
     <t>e_Plock_POL,e_Olsztyn_POL,e_Warsaw_POL</t>
   </si>
   <si>
     <t>e_Elk_POL,e_Grajewo_POL</t>
   </si>
   <si>
+    <t>e_Boleslawiec_POL,e_ZielonaGora_POL</t>
+  </si>
+  <si>
+    <t>e_Sosnowiec_POL,e_KedzierzynKozle_POL,e_Olesnica_POL,e_Gliwice_POL,e_Czestochowa_POL,e_Radomsko_POL,e_PiotrkowTrybunalsk_POL,e_Kielce_POL</t>
+  </si>
+  <si>
+    <t>e_Warsaw_POL,e_Lomza_POL</t>
+  </si>
+  <si>
+    <t>e_Lubin_POL,e_Poznan_POL,e_Koszalin_POL,e_Bydgoszcz_POL</t>
+  </si>
+  <si>
+    <t>e_Bydgoszcz_POL,e_Gdansk_POL,e_Grudziadz_POL,e_Kwidzyn_POL</t>
+  </si>
+  <si>
     <t>e_Lubin_POL,e_Swidnica_POL,e_Wroclaw_POL,e_Poznan_POL,e_Olesnica_POL</t>
   </si>
   <si>
@@ -1009,49 +1048,100 @@
     <t>e_Olesnica_POL,e_Konin_POL,e_PiotrkowTrybunalsk_POL,e_Plock_POL</t>
   </si>
   <si>
-    <t>e_BielskoBiala_POL,e_Katowice_POL,e_Krakow_POL,e_Tarnow_POL</t>
-  </si>
-  <si>
-    <t>e_Rzeszow_POL,e_Zamosc_POL,e_Pulawy_POL,e_Chelm_POL</t>
-  </si>
-  <si>
-    <t>e_Konin_POL,e_Bydgoszcz_POL,e_Wloclawek_POL,e_Kwidzyn_POL,e_Plock_POL</t>
-  </si>
-  <si>
-    <t>e_OstrowiecSwietokrz_POL,e_Pulawy_POL,e_Warsaw_POL</t>
-  </si>
-  <si>
-    <t>e_Lubin_POL,e_Poznan_POL,e_Koszalin_POL,e_Bydgoszcz_POL</t>
-  </si>
-  <si>
     <t>e_Krosno_POL,e_Mielec_POL,e_Debica_POL,e_Zamosc_POL</t>
   </si>
   <si>
     <t>e_Lomza_POL,e_Elk_POL,e_Bialystok_POL,e_Grajewo_POL</t>
   </si>
   <si>
-    <t>e_Bydgoszcz_POL,e_Gdansk_POL,e_Grudziadz_POL,e_Kwidzyn_POL</t>
-  </si>
-  <si>
-    <t>e_Boleslawiec_POL,e_ZielonaGora_POL</t>
-  </si>
-  <si>
-    <t>e_Sosnowiec_POL,e_KedzierzynKozle_POL,e_Olesnica_POL,e_Gliwice_POL,e_Czestochowa_POL,e_Radomsko_POL,e_PiotrkowTrybunalsk_POL,e_Kielce_POL</t>
-  </si>
-  <si>
-    <t>e_Warsaw_POL,e_Lomza_POL</t>
-  </si>
-  <si>
-    <t>e_Legnica_POL,e_Swidnica_POL,e_KedzierzynKozle_POL,e_Opole_POL</t>
-  </si>
-  <si>
-    <t>e_Kielce_POL,e_Warsaw_POL,e_OstrowiecSwietokrz_POL</t>
-  </si>
-  <si>
-    <t>e_Pulawy_POL,e_Bialystok_POL,e_Chelm_POL</t>
-  </si>
-  <si>
-    <t>e_GorzowWielkopolski_POL,e_Szczecin_POL,e_Police_POL</t>
+    <t>distr_wonelc_won_POL_007</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_002</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_014</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_020</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_006</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_009</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_004</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_001</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_013</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_008</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_012</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_003</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_018</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_015</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_016</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 16</t>
   </si>
   <si>
     <t>distr_wonelc_won_POL_019</t>
@@ -1066,60 +1156,12 @@
     <t>connecting wind onshore to buses in cluster 17</t>
   </si>
   <si>
-    <t>distr_wonelc_won_POL_012</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_003</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_015</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_016</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 16</t>
-  </si>
-  <si>
     <t>distr_wonelc_won_POL_005</t>
   </si>
   <si>
     <t>connecting wind onshore to buses in cluster 5</t>
   </si>
   <si>
-    <t>distr_wonelc_won_POL_007</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_001</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_013</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_008</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 8</t>
-  </si>
-  <si>
     <t>distr_wonelc_won_POL_011</t>
   </si>
   <si>
@@ -1132,46 +1174,91 @@
     <t>connecting wind onshore to buses in cluster 10</t>
   </si>
   <si>
-    <t>distr_wonelc_won_POL_006</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_009</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_004</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_018</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_014</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_020</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_002</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 2</t>
+    <t>elc_won_POL_007</t>
+  </si>
+  <si>
+    <t>e_Warsaw_POL,e_Plock_POL,e_Olsztyn_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_002</t>
+  </si>
+  <si>
+    <t>e_Tarnow_POL,e_Kielce_POL,e_OstrowiecSwietokrz_POL,e_Mielec_POL,e_Pulawy_POL,e_Rzeszow_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_014</t>
+  </si>
+  <si>
+    <t>e_Lubin_POL,e_Poznan_POL,e_Bydgoszcz_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_020</t>
+  </si>
+  <si>
+    <t>e_Sosnowiec_POL,e_KedzierzynKozle_POL,e_Olesnica_POL,e_Gliwice_POL,e_Czestochowa_POL,e_Radomsko_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_006</t>
+  </si>
+  <si>
+    <t>e_Olesnica_POL,e_Konin_POL,e_Bydgoszcz_POL,e_Wloclawek_POL,e_Kwidzyn_POL,e_Plock_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_009</t>
+  </si>
+  <si>
+    <t>e_Gdansk_POL,e_Grudziadz_POL,e_Kwidzyn_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_004</t>
+  </si>
+  <si>
+    <t>elc_won_POL_001</t>
+  </si>
+  <si>
+    <t>e_PiotrkowTrybunalsk_POL,e_Kielce_POL,e_Warsaw_POL,e_OstrowiecSwietokrz_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_013</t>
+  </si>
+  <si>
+    <t>e_Lubin_POL,e_Wroclaw_POL,e_Poznan_POL,e_Olesnica_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_008</t>
+  </si>
+  <si>
+    <t>e_Olsztyn_POL,e_Elk_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_012</t>
+  </si>
+  <si>
+    <t>e_ZielonaGora_POL,e_GorzowWielkopolski_POL,e_Szczecin_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_003</t>
+  </si>
+  <si>
+    <t>e_Warsaw_POL,e_Lomza_POL,e_Pulawy_POL,e_Bialystok_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_018</t>
+  </si>
+  <si>
+    <t>e_Boleslawiec_POL,e_Legnica_POL,e_Swidnica_POL,e_KedzierzynKozle_POL,e_Opole_POL,e_Olesnica_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_015</t>
+  </si>
+  <si>
+    <t>e_BielskoBiala_POL,e_Krakow_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_016</t>
+  </si>
+  <si>
+    <t>e_Krosno_POL,e_Debica_POL</t>
   </si>
   <si>
     <t>elc_won_POL_019</t>
@@ -1186,60 +1273,12 @@
     <t>e_Tarnow_POL,e_Krosno_POL</t>
   </si>
   <si>
-    <t>elc_won_POL_012</t>
-  </si>
-  <si>
-    <t>e_ZielonaGora_POL,e_GorzowWielkopolski_POL,e_Szczecin_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_003</t>
-  </si>
-  <si>
-    <t>e_Warsaw_POL,e_Lomza_POL,e_Pulawy_POL,e_Bialystok_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_015</t>
-  </si>
-  <si>
-    <t>e_BielskoBiala_POL,e_Krakow_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_016</t>
-  </si>
-  <si>
-    <t>e_Krosno_POL,e_Debica_POL</t>
-  </si>
-  <si>
     <t>elc_won_POL_005</t>
   </si>
   <si>
     <t>e_Lomza_POL,e_Elk_POL,e_Grajewo_POL,e_Bialystok_POL,e_Chelm_POL</t>
   </si>
   <si>
-    <t>elc_won_POL_007</t>
-  </si>
-  <si>
-    <t>e_Warsaw_POL,e_Plock_POL,e_Olsztyn_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_001</t>
-  </si>
-  <si>
-    <t>e_PiotrkowTrybunalsk_POL,e_Kielce_POL,e_Warsaw_POL,e_OstrowiecSwietokrz_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_013</t>
-  </si>
-  <si>
-    <t>e_Lubin_POL,e_Wroclaw_POL,e_Poznan_POL,e_Olesnica_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_008</t>
-  </si>
-  <si>
-    <t>e_Olsztyn_POL,e_Elk_POL</t>
-  </si>
-  <si>
     <t>elc_won_POL_011</t>
   </si>
   <si>
@@ -1252,43 +1291,52 @@
     <t>e_Police_POL,e_Koszalin_POL,e_Poznan_POL,e_Ustka_POL,e_Bydgoszcz_POL,e_Slupsk_POL,e_Gdansk_POL</t>
   </si>
   <si>
-    <t>elc_won_POL_006</t>
-  </si>
-  <si>
-    <t>e_Olesnica_POL,e_Konin_POL,e_Bydgoszcz_POL,e_Wloclawek_POL,e_Kwidzyn_POL,e_Plock_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_009</t>
-  </si>
-  <si>
-    <t>e_Gdansk_POL,e_Grudziadz_POL,e_Kwidzyn_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_004</t>
-  </si>
-  <si>
-    <t>elc_won_POL_018</t>
-  </si>
-  <si>
-    <t>e_Boleslawiec_POL,e_Legnica_POL,e_Swidnica_POL,e_KedzierzynKozle_POL,e_Opole_POL,e_Olesnica_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_014</t>
-  </si>
-  <si>
-    <t>e_Lubin_POL,e_Poznan_POL,e_Bydgoszcz_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_020</t>
-  </si>
-  <si>
-    <t>e_Sosnowiec_POL,e_KedzierzynKozle_POL,e_Olesnica_POL,e_Gliwice_POL,e_Czestochowa_POL,e_Radomsko_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_002</t>
-  </si>
-  <si>
-    <t>e_Tarnow_POL,e_Kielce_POL,e_OstrowiecSwietokrz_POL,e_Mielec_POL,e_Pulawy_POL,e_Rzeszow_POL</t>
+    <t>distr_wofelc_wof_POL_008</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_POL_007</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_POL_005</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_POL_001</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_POL_006</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_POL_003</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_POL_010</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_POL_009</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 9</t>
   </si>
   <si>
     <t>distr_wofelc_wof_POL_002</t>
@@ -1297,103 +1345,55 @@
     <t>connecting wind offshore to buses in cluster 2</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_POL_006</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_POL_005</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_POL_001</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_POL_003</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_POL_008</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_POL_007</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_POL_010</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_POL_009</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 9</t>
-  </si>
-  <si>
     <t>distr_wofelc_wof_POL_004</t>
   </si>
   <si>
     <t>connecting wind offshore to buses in cluster 4</t>
   </si>
   <si>
+    <t>elc_wof_POL_008</t>
+  </si>
+  <si>
+    <t>e_Police_POL,e_Koszalin_POL</t>
+  </si>
+  <si>
+    <t>elc_wof_POL_007</t>
+  </si>
+  <si>
+    <t>e_Koszalin_POL</t>
+  </si>
+  <si>
+    <t>elc_wof_POL_005</t>
+  </si>
+  <si>
+    <t>e_Gdynia_POL</t>
+  </si>
+  <si>
+    <t>elc_wof_POL_001</t>
+  </si>
+  <si>
+    <t>e_Gdansk_POL</t>
+  </si>
+  <si>
+    <t>elc_wof_POL_006</t>
+  </si>
+  <si>
+    <t>elc_wof_POL_003</t>
+  </si>
+  <si>
+    <t>elc_wof_POL_010</t>
+  </si>
+  <si>
+    <t>elc_wof_POL_009</t>
+  </si>
+  <si>
+    <t>e_Koszalin_POL,e_Ustka_POL</t>
+  </si>
+  <si>
     <t>elc_wof_POL_002</t>
   </si>
   <si>
     <t>e_Gdynia_POL,e_Gdansk_POL</t>
-  </si>
-  <si>
-    <t>elc_wof_POL_006</t>
-  </si>
-  <si>
-    <t>e_Gdynia_POL</t>
-  </si>
-  <si>
-    <t>elc_wof_POL_005</t>
-  </si>
-  <si>
-    <t>elc_wof_POL_001</t>
-  </si>
-  <si>
-    <t>e_Gdansk_POL</t>
-  </si>
-  <si>
-    <t>elc_wof_POL_003</t>
-  </si>
-  <si>
-    <t>elc_wof_POL_008</t>
-  </si>
-  <si>
-    <t>e_Police_POL,e_Koszalin_POL</t>
-  </si>
-  <si>
-    <t>elc_wof_POL_007</t>
-  </si>
-  <si>
-    <t>e_Koszalin_POL</t>
-  </si>
-  <si>
-    <t>elc_wof_POL_010</t>
-  </si>
-  <si>
-    <t>elc_wof_POL_009</t>
-  </si>
-  <si>
-    <t>e_Koszalin_POL,e_Ustka_POL</t>
   </si>
   <si>
     <t>elc_wof_POL_004</t>
@@ -7135,7 +7135,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2CE08A0-6DFC-47C4-B0DC-4A99B678EFFC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{645172D3-8486-41EC-92F7-C63B80E30FD9}">
   <dimension ref="B9:BD30"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -7373,16 +7373,16 @@
         <v>244</v>
       </c>
       <c r="Y11" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="Z11" t="s">
         <v>288</v>
       </c>
       <c r="AA11">
-        <v>0.99658775492800411</v>
+        <v>0.99606480786442353</v>
       </c>
       <c r="AB11">
-        <v>62.557826319923819</v>
+        <v>72.145189152235062</v>
       </c>
       <c r="AD11" t="s">
         <v>243</v>
@@ -7415,10 +7415,10 @@
         <v>349</v>
       </c>
       <c r="AO11">
-        <v>0.99872641243407079</v>
+        <v>0.99653588726932718</v>
       </c>
       <c r="AP11">
-        <v>23.349105375368897</v>
+        <v>63.508733395668145</v>
       </c>
       <c r="AR11" t="s">
         <v>243</v>
@@ -7451,10 +7451,10 @@
         <v>408</v>
       </c>
       <c r="BC11">
-        <v>0.99353721168226494</v>
+        <v>0.99383352379209899</v>
       </c>
       <c r="BD11">
-        <v>780.55486105754892</v>
+        <v>758.43022352327353</v>
       </c>
     </row>
     <row r="12" spans="2:56">
@@ -7519,16 +7519,16 @@
         <v>248</v>
       </c>
       <c r="Y12" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="Z12" t="s">
         <v>289</v>
       </c>
       <c r="AA12">
-        <v>0.99510886326373238</v>
+        <v>0.99785589517057005</v>
       </c>
       <c r="AB12">
-        <v>89.670840164906522</v>
+        <v>39.308588539549028</v>
       </c>
       <c r="AD12" t="s">
         <v>243</v>
@@ -7561,10 +7561,10 @@
         <v>351</v>
       </c>
       <c r="AO12">
-        <v>0.99776911581804295</v>
+        <v>0.99845791964146047</v>
       </c>
       <c r="AP12">
-        <v>40.899543335879912</v>
+        <v>28.2714732398913</v>
       </c>
       <c r="AR12" t="s">
         <v>243</v>
@@ -7597,10 +7597,10 @@
         <v>410</v>
       </c>
       <c r="BC12">
-        <v>0.99615739524125424</v>
+        <v>0.99603306101923861</v>
       </c>
       <c r="BD12">
-        <v>584.91448865302027</v>
+        <v>594.19811056351818</v>
       </c>
     </row>
     <row r="13" spans="2:56">
@@ -7665,16 +7665,16 @@
         <v>250</v>
       </c>
       <c r="Y13" t="s">
-        <v>224</v>
+        <v>235</v>
       </c>
       <c r="Z13" t="s">
         <v>290</v>
       </c>
       <c r="AA13">
-        <v>0.99770934816564383</v>
+        <v>0.99790408176624201</v>
       </c>
       <c r="AB13">
-        <v>41.995283629862939</v>
+        <v>38.425167618896296</v>
       </c>
       <c r="AD13" t="s">
         <v>243</v>
@@ -7707,10 +7707,10 @@
         <v>353</v>
       </c>
       <c r="AO13">
-        <v>0.99749126227646956</v>
+        <v>0.99730422320290779</v>
       </c>
       <c r="AP13">
-        <v>45.993524931390482</v>
+        <v>49.422574613357185</v>
       </c>
       <c r="AR13" t="s">
         <v>243</v>
@@ -7740,7 +7740,7 @@
         <v>411</v>
       </c>
       <c r="BB13" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="BC13">
         <v>0.99328660064428831</v>
@@ -7811,16 +7811,16 @@
         <v>252</v>
       </c>
       <c r="Y14" t="s">
-        <v>228</v>
+        <v>238</v>
       </c>
       <c r="Z14" t="s">
         <v>291</v>
       </c>
       <c r="AA14">
-        <v>0.9970292559096442</v>
+        <v>0.99930490342600053</v>
       </c>
       <c r="AB14">
-        <v>54.463641656523762</v>
+        <v>12.743437189989784</v>
       </c>
       <c r="AD14" t="s">
         <v>243</v>
@@ -7853,10 +7853,10 @@
         <v>355</v>
       </c>
       <c r="AO14">
-        <v>0.99807543246352515</v>
+        <v>0.99805709209211746</v>
       </c>
       <c r="AP14">
-        <v>35.283738168705199</v>
+        <v>35.619978311179104</v>
       </c>
       <c r="AR14" t="s">
         <v>243</v>
@@ -7883,10 +7883,10 @@
         <v>393</v>
       </c>
       <c r="BA14" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="BB14" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="BC14">
         <v>0.99644441082752833</v>
@@ -7957,16 +7957,16 @@
         <v>254</v>
       </c>
       <c r="Y15" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="Z15" t="s">
         <v>292</v>
       </c>
       <c r="AA15">
-        <v>0.9982126095160021</v>
+        <v>0.99881801309037566</v>
       </c>
       <c r="AB15">
-        <v>32.768825539961391</v>
+        <v>21.669760009780138</v>
       </c>
       <c r="AD15" t="s">
         <v>243</v>
@@ -7999,10 +7999,10 @@
         <v>357</v>
       </c>
       <c r="AO15">
-        <v>0.99641308487583879</v>
+        <v>0.99827231256984739</v>
       </c>
       <c r="AP15">
-        <v>65.760110609622657</v>
+        <v>31.674269552798414</v>
       </c>
       <c r="AR15" t="s">
         <v>243</v>
@@ -8029,16 +8029,16 @@
         <v>395</v>
       </c>
       <c r="BA15" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="BB15" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="BC15">
-        <v>0.99564787435456037</v>
+        <v>0.99615739524125424</v>
       </c>
       <c r="BD15">
-        <v>622.95871485949408</v>
+        <v>584.91448865302027</v>
       </c>
     </row>
     <row r="16" spans="2:56">
@@ -8103,16 +8103,16 @@
         <v>256</v>
       </c>
       <c r="Y16" t="s">
-        <v>235</v>
+        <v>223</v>
       </c>
       <c r="Z16" t="s">
         <v>293</v>
       </c>
       <c r="AA16">
-        <v>0.99790408176624201</v>
+        <v>0.99515616506526205</v>
       </c>
       <c r="AB16">
-        <v>38.425167618896296</v>
+        <v>88.803640470195262</v>
       </c>
       <c r="AD16" t="s">
         <v>243</v>
@@ -8145,10 +8145,10 @@
         <v>359</v>
       </c>
       <c r="AO16">
-        <v>0.99449756685866841</v>
+        <v>0.99635146162488653</v>
       </c>
       <c r="AP16">
-        <v>100.87794092441324</v>
+        <v>66.889870210414614</v>
       </c>
       <c r="AR16" t="s">
         <v>243</v>
@@ -8175,16 +8175,16 @@
         <v>397</v>
       </c>
       <c r="BA16" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="BB16" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="BC16">
-        <v>0.99383352379209899</v>
+        <v>0.99564787435456037</v>
       </c>
       <c r="BD16">
-        <v>758.43022352327353</v>
+        <v>622.95871485949408</v>
       </c>
     </row>
     <row r="17" spans="2:56">
@@ -8249,16 +8249,16 @@
         <v>258</v>
       </c>
       <c r="Y17" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="Z17" t="s">
         <v>294</v>
       </c>
       <c r="AA17">
-        <v>0.99606480786442353</v>
+        <v>0.99728872234103139</v>
       </c>
       <c r="AB17">
-        <v>72.145189152235062</v>
+        <v>49.70675708109188</v>
       </c>
       <c r="AD17" t="s">
         <v>243</v>
@@ -8288,13 +8288,13 @@
         <v>360</v>
       </c>
       <c r="AN17" t="s">
-        <v>361</v>
+        <v>288</v>
       </c>
       <c r="AO17">
-        <v>0.9963019969989696</v>
+        <v>0.99586212495478665</v>
       </c>
       <c r="AP17">
-        <v>67.796721685557472</v>
+        <v>75.861042495577635</v>
       </c>
       <c r="AR17" t="s">
         <v>243</v>
@@ -8324,13 +8324,13 @@
         <v>417</v>
       </c>
       <c r="BB17" t="s">
-        <v>418</v>
+        <v>410</v>
       </c>
       <c r="BC17">
-        <v>0.99603306101923861</v>
+        <v>0.99608994650263638</v>
       </c>
       <c r="BD17">
-        <v>594.19811056351818</v>
+        <v>589.950661136485</v>
       </c>
     </row>
     <row r="18" spans="2:56">
@@ -8395,16 +8395,16 @@
         <v>260</v>
       </c>
       <c r="Y18" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="Z18" t="s">
         <v>295</v>
       </c>
       <c r="AA18">
-        <v>0.99930490342600053</v>
+        <v>0.99583567586599486</v>
       </c>
       <c r="AB18">
-        <v>12.743437189989784</v>
+        <v>76.34594245676044</v>
       </c>
       <c r="AD18" t="s">
         <v>243</v>
@@ -8431,16 +8431,16 @@
         <v>322</v>
       </c>
       <c r="AM18" t="s">
+        <v>361</v>
+      </c>
+      <c r="AN18" t="s">
         <v>362</v>
       </c>
-      <c r="AN18" t="s">
-        <v>363</v>
-      </c>
       <c r="AO18">
-        <v>0.99653588726932718</v>
+        <v>0.99871360797890252</v>
       </c>
       <c r="AP18">
-        <v>63.508733395668145</v>
+        <v>23.583853720120768</v>
       </c>
       <c r="AR18" t="s">
         <v>243</v>
@@ -8467,16 +8467,16 @@
         <v>401</v>
       </c>
       <c r="BA18" t="s">
+        <v>418</v>
+      </c>
+      <c r="BB18" t="s">
         <v>419</v>
       </c>
-      <c r="BB18" t="s">
-        <v>418</v>
-      </c>
       <c r="BC18">
-        <v>0.99608994650263638</v>
+        <v>0.99399682431672776</v>
       </c>
       <c r="BD18">
-        <v>589.950661136485</v>
+        <v>746.2371176843244</v>
       </c>
     </row>
     <row r="19" spans="2:56">
@@ -8541,16 +8541,16 @@
         <v>262</v>
       </c>
       <c r="Y19" t="s">
-        <v>241</v>
+        <v>227</v>
       </c>
       <c r="Z19" t="s">
         <v>296</v>
       </c>
       <c r="AA19">
-        <v>0.99881801309037566</v>
+        <v>0.99658775492800411</v>
       </c>
       <c r="AB19">
-        <v>21.669760009780138</v>
+        <v>62.557826319923819</v>
       </c>
       <c r="AD19" t="s">
         <v>243</v>
@@ -8577,16 +8577,16 @@
         <v>324</v>
       </c>
       <c r="AM19" t="s">
+        <v>363</v>
+      </c>
+      <c r="AN19" t="s">
         <v>364</v>
       </c>
-      <c r="AN19" t="s">
-        <v>365</v>
-      </c>
       <c r="AO19">
-        <v>0.99871360797890252</v>
+        <v>0.99883902037019667</v>
       </c>
       <c r="AP19">
-        <v>23.583853720120768</v>
+        <v>21.284626546395259</v>
       </c>
       <c r="AR19" t="s">
         <v>243</v>
@@ -8619,10 +8619,10 @@
         <v>421</v>
       </c>
       <c r="BC19">
-        <v>0.99399682431672776</v>
+        <v>0.99353721168226494</v>
       </c>
       <c r="BD19">
-        <v>746.2371176843244</v>
+        <v>780.55486105754892</v>
       </c>
     </row>
     <row r="20" spans="2:56">
@@ -8687,16 +8687,16 @@
         <v>264</v>
       </c>
       <c r="Y20" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="Z20" t="s">
         <v>297</v>
       </c>
       <c r="AA20">
-        <v>0.99730738889353909</v>
+        <v>0.99510886326373238</v>
       </c>
       <c r="AB20">
-        <v>49.364536951784054</v>
+        <v>89.670840164906522</v>
       </c>
       <c r="AD20" t="s">
         <v>243</v>
@@ -8723,16 +8723,16 @@
         <v>326</v>
       </c>
       <c r="AM20" t="s">
+        <v>365</v>
+      </c>
+      <c r="AN20" t="s">
         <v>366</v>
       </c>
-      <c r="AN20" t="s">
-        <v>367</v>
-      </c>
       <c r="AO20">
-        <v>0.99883902037019667</v>
+        <v>0.99521984547821263</v>
       </c>
       <c r="AP20">
-        <v>21.284626546395259</v>
+        <v>87.636166232768815</v>
       </c>
       <c r="AR20" t="s">
         <v>243</v>
@@ -8833,16 +8833,16 @@
         <v>266</v>
       </c>
       <c r="Y21" t="s">
-        <v>233</v>
+        <v>222</v>
       </c>
       <c r="Z21" t="s">
         <v>298</v>
       </c>
       <c r="AA21">
-        <v>0.99481478101166732</v>
+        <v>0.99707401400885998</v>
       </c>
       <c r="AB21">
-        <v>95.062348119433295</v>
+        <v>53.643076504234422</v>
       </c>
       <c r="AD21" t="s">
         <v>243</v>
@@ -8869,16 +8869,16 @@
         <v>328</v>
       </c>
       <c r="AM21" t="s">
+        <v>367</v>
+      </c>
+      <c r="AN21" t="s">
         <v>368</v>
       </c>
-      <c r="AN21" t="s">
-        <v>369</v>
-      </c>
       <c r="AO21">
-        <v>0.99521984547821263</v>
+        <v>0.99749126227646956</v>
       </c>
       <c r="AP21">
-        <v>87.636166232768815</v>
+        <v>45.993524931390482</v>
       </c>
     </row>
     <row r="22" spans="2:56">
@@ -8943,16 +8943,16 @@
         <v>268</v>
       </c>
       <c r="Y22" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="Z22" t="s">
         <v>299</v>
       </c>
       <c r="AA22">
-        <v>0.99681878296180493</v>
+        <v>0.99826037700975512</v>
       </c>
       <c r="AB22">
-        <v>58.322312366909152</v>
+        <v>31.893088154488542</v>
       </c>
       <c r="AD22" t="s">
         <v>243</v>
@@ -8979,16 +8979,16 @@
         <v>330</v>
       </c>
       <c r="AM22" t="s">
+        <v>369</v>
+      </c>
+      <c r="AN22" t="s">
         <v>370</v>
       </c>
-      <c r="AN22" t="s">
-        <v>371</v>
-      </c>
       <c r="AO22">
-        <v>0.99802303154782224</v>
+        <v>0.99807543246352515</v>
       </c>
       <c r="AP22">
-        <v>36.244421623259619</v>
+        <v>35.283738168705199</v>
       </c>
     </row>
     <row r="23" spans="2:56">
@@ -9053,16 +9053,16 @@
         <v>270</v>
       </c>
       <c r="Y23" t="s">
-        <v>229</v>
+        <v>239</v>
       </c>
       <c r="Z23" t="s">
         <v>300</v>
       </c>
       <c r="AA23">
-        <v>0.99693515631487983</v>
+        <v>0.99922515067657613</v>
       </c>
       <c r="AB23">
-        <v>56.188800893869058</v>
+        <v>14.205570929438155</v>
       </c>
       <c r="AD23" t="s">
         <v>243</v>
@@ -9089,16 +9089,16 @@
         <v>332</v>
       </c>
       <c r="AM23" t="s">
+        <v>371</v>
+      </c>
+      <c r="AN23" t="s">
         <v>372</v>
       </c>
-      <c r="AN23" t="s">
-        <v>373</v>
-      </c>
       <c r="AO23">
-        <v>0.99714358927215652</v>
+        <v>0.99622969699231045</v>
       </c>
       <c r="AP23">
-        <v>52.367530010463909</v>
+        <v>69.122221807641537</v>
       </c>
     </row>
     <row r="24" spans="2:56">
@@ -9163,16 +9163,16 @@
         <v>272</v>
       </c>
       <c r="Y24" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="Z24" t="s">
         <v>301</v>
       </c>
       <c r="AA24">
-        <v>0.99707401400885998</v>
+        <v>0.99730738889353909</v>
       </c>
       <c r="AB24">
-        <v>53.643076504234422</v>
+        <v>49.364536951784054</v>
       </c>
       <c r="AD24" t="s">
         <v>243</v>
@@ -9199,16 +9199,16 @@
         <v>334</v>
       </c>
       <c r="AM24" t="s">
+        <v>373</v>
+      </c>
+      <c r="AN24" t="s">
         <v>374</v>
       </c>
-      <c r="AN24" t="s">
-        <v>375</v>
-      </c>
       <c r="AO24">
-        <v>0.99827231256984739</v>
+        <v>0.99641308487583879</v>
       </c>
       <c r="AP24">
-        <v>31.674269552798414</v>
+        <v>65.760110609622657</v>
       </c>
     </row>
     <row r="25" spans="2:56">
@@ -9273,16 +9273,16 @@
         <v>274</v>
       </c>
       <c r="Y25" t="s">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="Z25" t="s">
         <v>302</v>
       </c>
       <c r="AA25">
-        <v>0.99826037700975512</v>
+        <v>0.99693515631487983</v>
       </c>
       <c r="AB25">
-        <v>31.893088154488542</v>
+        <v>56.188800893869058</v>
       </c>
       <c r="AD25" t="s">
         <v>243</v>
@@ -9309,16 +9309,16 @@
         <v>336</v>
       </c>
       <c r="AM25" t="s">
+        <v>375</v>
+      </c>
+      <c r="AN25" t="s">
         <v>376</v>
       </c>
-      <c r="AN25" t="s">
-        <v>377</v>
-      </c>
       <c r="AO25">
-        <v>0.99635146162488653</v>
+        <v>0.99449756685866841</v>
       </c>
       <c r="AP25">
-        <v>66.889870210414614</v>
+        <v>100.87794092441324</v>
       </c>
     </row>
     <row r="26" spans="2:56">
@@ -9383,16 +9383,16 @@
         <v>276</v>
       </c>
       <c r="Y26" t="s">
-        <v>239</v>
+        <v>224</v>
       </c>
       <c r="Z26" t="s">
         <v>303</v>
       </c>
       <c r="AA26">
-        <v>0.99922515067657613</v>
+        <v>0.99770934816564383</v>
       </c>
       <c r="AB26">
-        <v>14.205570929438155</v>
+        <v>41.995283629862939</v>
       </c>
       <c r="AD26" t="s">
         <v>243</v>
@@ -9419,16 +9419,16 @@
         <v>338</v>
       </c>
       <c r="AM26" t="s">
+        <v>377</v>
+      </c>
+      <c r="AN26" t="s">
         <v>378</v>
       </c>
-      <c r="AN26" t="s">
-        <v>294</v>
-      </c>
       <c r="AO26">
-        <v>0.99586212495478665</v>
+        <v>0.99872641243407079</v>
       </c>
       <c r="AP26">
-        <v>75.861042495577635</v>
+        <v>23.349105375368897</v>
       </c>
     </row>
     <row r="27" spans="2:56">
@@ -9493,16 +9493,16 @@
         <v>278</v>
       </c>
       <c r="Y27" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="Z27" t="s">
         <v>304</v>
       </c>
       <c r="AA27">
-        <v>0.99515616506526205</v>
+        <v>0.9970292559096442</v>
       </c>
       <c r="AB27">
-        <v>88.803640470195262</v>
+        <v>54.463641656523762</v>
       </c>
       <c r="AD27" t="s">
         <v>243</v>
@@ -9535,10 +9535,10 @@
         <v>380</v>
       </c>
       <c r="AO27">
-        <v>0.99622969699231045</v>
+        <v>0.99776911581804295</v>
       </c>
       <c r="AP27">
-        <v>69.122221807641537</v>
+        <v>40.899543335879912</v>
       </c>
     </row>
     <row r="28" spans="2:56">
@@ -9603,16 +9603,16 @@
         <v>280</v>
       </c>
       <c r="Y28" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="Z28" t="s">
         <v>305</v>
       </c>
       <c r="AA28">
-        <v>0.99728872234103139</v>
+        <v>0.9982126095160021</v>
       </c>
       <c r="AB28">
-        <v>49.70675708109188</v>
+        <v>32.768825539961391</v>
       </c>
       <c r="AD28" t="s">
         <v>243</v>
@@ -9645,10 +9645,10 @@
         <v>382</v>
       </c>
       <c r="AO28">
-        <v>0.99730422320290779</v>
+        <v>0.9963019969989696</v>
       </c>
       <c r="AP28">
-        <v>49.422574613357185</v>
+        <v>67.796721685557472</v>
       </c>
     </row>
     <row r="29" spans="2:56">
@@ -9713,16 +9713,16 @@
         <v>282</v>
       </c>
       <c r="Y29" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="Z29" t="s">
         <v>306</v>
       </c>
       <c r="AA29">
-        <v>0.99583567586599486</v>
+        <v>0.99481478101166732</v>
       </c>
       <c r="AB29">
-        <v>76.34594245676044</v>
+        <v>95.062348119433295</v>
       </c>
       <c r="AD29" t="s">
         <v>243</v>
@@ -9755,10 +9755,10 @@
         <v>384</v>
       </c>
       <c r="AO29">
-        <v>0.99805709209211746</v>
+        <v>0.99802303154782224</v>
       </c>
       <c r="AP29">
-        <v>35.619978311179104</v>
+        <v>36.244421623259619</v>
       </c>
     </row>
     <row r="30" spans="2:56">
@@ -9823,16 +9823,16 @@
         <v>284</v>
       </c>
       <c r="Y30" t="s">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="Z30" t="s">
         <v>307</v>
       </c>
       <c r="AA30">
-        <v>0.99785589517057005</v>
+        <v>0.99681878296180493</v>
       </c>
       <c r="AB30">
-        <v>39.308588539549028</v>
+        <v>58.322312366909152</v>
       </c>
       <c r="AD30" t="s">
         <v>243</v>
@@ -9865,10 +9865,10 @@
         <v>386</v>
       </c>
       <c r="AO30">
-        <v>0.99845791964146047</v>
+        <v>0.99714358927215652</v>
       </c>
       <c r="AP30">
-        <v>28.2714732398913</v>
+        <v>52.367530010463909</v>
       </c>
     </row>
   </sheetData>
@@ -9877,7 +9877,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{828691EB-3C00-483B-97C4-DA5CEB24E96F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77E1D973-D2C1-4533-BCF9-C3E250BAF64F}">
   <dimension ref="B9:Z30"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -9989,7 +9989,7 @@
         <v>424</v>
       </c>
       <c r="K11" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="L11">
         <v>0.30278350605008381</v>
@@ -10022,7 +10022,7 @@
         <v>464</v>
       </c>
       <c r="X11" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="Y11">
         <v>0.83925000000000005</v>
@@ -10057,7 +10057,7 @@
         <v>426</v>
       </c>
       <c r="K12" t="s">
-        <v>385</v>
+        <v>350</v>
       </c>
       <c r="L12">
         <v>0.42035497786033621</v>
@@ -10090,7 +10090,7 @@
         <v>466</v>
       </c>
       <c r="X12" t="s">
-        <v>407</v>
+        <v>420</v>
       </c>
       <c r="Y12">
         <v>16.887</v>
@@ -10125,7 +10125,7 @@
         <v>428</v>
       </c>
       <c r="K13" t="s">
-        <v>354</v>
+        <v>369</v>
       </c>
       <c r="L13">
         <v>1.6077871713950227</v>
@@ -10158,7 +10158,7 @@
         <v>468</v>
       </c>
       <c r="X13" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="Y13">
         <v>11.2965</v>
@@ -10193,7 +10193,7 @@
         <v>430</v>
       </c>
       <c r="K14" t="s">
-        <v>378</v>
+        <v>360</v>
       </c>
       <c r="L14">
         <v>2.531891424764753</v>
@@ -10261,7 +10261,7 @@
         <v>432</v>
       </c>
       <c r="K15" t="s">
-        <v>360</v>
+        <v>381</v>
       </c>
       <c r="L15">
         <v>7.6497810049421515</v>
@@ -10329,7 +10329,7 @@
         <v>434</v>
       </c>
       <c r="K16" t="s">
-        <v>374</v>
+        <v>356</v>
       </c>
       <c r="L16">
         <v>0.60733325583919984</v>
@@ -10362,7 +10362,7 @@
         <v>474</v>
       </c>
       <c r="X16" t="s">
-        <v>409</v>
+        <v>415</v>
       </c>
       <c r="Y16">
         <v>8.8230000000000004</v>
@@ -10397,7 +10397,7 @@
         <v>436</v>
       </c>
       <c r="K17" t="s">
-        <v>362</v>
+        <v>348</v>
       </c>
       <c r="L17">
         <v>0.78389041837100704</v>
@@ -10430,7 +10430,7 @@
         <v>476</v>
       </c>
       <c r="X17" t="s">
-        <v>417</v>
+        <v>409</v>
       </c>
       <c r="Y17">
         <v>0.22650000000000001</v>
@@ -10465,7 +10465,7 @@
         <v>438</v>
       </c>
       <c r="K18" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="L18">
         <v>3.0365724666245324</v>
@@ -10498,7 +10498,7 @@
         <v>478</v>
       </c>
       <c r="X18" t="s">
-        <v>415</v>
+        <v>407</v>
       </c>
       <c r="Y18">
         <v>9.5062499999999996</v>
@@ -10533,7 +10533,7 @@
         <v>440</v>
       </c>
       <c r="K19" t="s">
-        <v>376</v>
+        <v>358</v>
       </c>
       <c r="L19">
         <v>0.22970161230087291</v>
@@ -10566,7 +10566,7 @@
         <v>480</v>
       </c>
       <c r="X19" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="Y19">
         <v>13.37175</v>
@@ -10601,7 +10601,7 @@
         <v>442</v>
       </c>
       <c r="K20" t="s">
-        <v>372</v>
+        <v>385</v>
       </c>
       <c r="L20">
         <v>0.27066515065379043</v>
@@ -10634,7 +10634,7 @@
         <v>482</v>
       </c>
       <c r="X20" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="Y20">
         <v>3.9427500000000002</v>
@@ -10669,7 +10669,7 @@
         <v>444</v>
       </c>
       <c r="K21" t="s">
-        <v>370</v>
+        <v>383</v>
       </c>
       <c r="L21">
         <v>0.32193208719379746</v>
@@ -10704,7 +10704,7 @@
         <v>446</v>
       </c>
       <c r="K22" t="s">
-        <v>352</v>
+        <v>367</v>
       </c>
       <c r="L22">
         <v>0.6573344927201471</v>
@@ -10739,7 +10739,7 @@
         <v>448</v>
       </c>
       <c r="K23" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="L23">
         <v>0.28992997651770519</v>
@@ -10774,7 +10774,7 @@
         <v>450</v>
       </c>
       <c r="K24" t="s">
-        <v>381</v>
+        <v>352</v>
       </c>
       <c r="L24">
         <v>0.74609319967150689</v>
@@ -10809,7 +10809,7 @@
         <v>452</v>
       </c>
       <c r="K25" t="s">
-        <v>356</v>
+        <v>373</v>
       </c>
       <c r="L25">
         <v>0.35328950844501877</v>
@@ -10844,7 +10844,7 @@
         <v>454</v>
       </c>
       <c r="K26" t="s">
-        <v>358</v>
+        <v>375</v>
       </c>
       <c r="L26">
         <v>0.7924639655878376</v>
@@ -10879,7 +10879,7 @@
         <v>456</v>
       </c>
       <c r="K27" t="s">
-        <v>350</v>
+        <v>379</v>
       </c>
       <c r="L27">
         <v>0.55411362221124194</v>
@@ -10914,7 +10914,7 @@
         <v>458</v>
       </c>
       <c r="K28" t="s">
-        <v>379</v>
+        <v>371</v>
       </c>
       <c r="L28">
         <v>1.4327274230737423</v>
@@ -10949,7 +10949,7 @@
         <v>460</v>
       </c>
       <c r="K29" t="s">
-        <v>348</v>
+        <v>377</v>
       </c>
       <c r="L29">
         <v>0.56742801517356967</v>
@@ -10984,7 +10984,7 @@
         <v>462</v>
       </c>
       <c r="K30" t="s">
-        <v>383</v>
+        <v>354</v>
       </c>
       <c r="L30">
         <v>0.35405891742987328</v>
@@ -10999,7 +10999,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F7365AA-67AF-4B2E-9065-C9887E1C1080}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D459FDB5-3A76-45FC-AFE1-881EBB3CB04D}">
   <dimension ref="B9:U116"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -14483,7 +14483,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D7063D2-4675-47D6-9EF0-98FED37960F6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59D27BC0-282E-4EC5-BF5B-F4EB2EC1ED26}">
   <dimension ref="B9:T88"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_POL_grids_kan50/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_POL_grids_kan50/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F87F2F73-0947-4E2B-B0D3-6675D08BBE27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E51FB54F-7EAD-48B6-B6C8-086902FAFCA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -862,42 +862,114 @@
     <t>pre</t>
   </si>
   <si>
+    <t>distr_solelc_spv_POL_001</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>NRGI</t>
+  </si>
+  <si>
+    <t>daynite</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_015</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_018</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_005</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_008</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_012</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_011</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_003</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_007</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_016</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_006</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_010</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_014</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_004</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_017</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_020</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 20</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_POL_013</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 13</t>
   </si>
   <si>
-    <t>NRGI</t>
-  </si>
-  <si>
-    <t>daynite</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_004</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_014</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_017</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_020</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 20</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_POL_002</t>
   </si>
   <si>
@@ -916,99 +988,63 @@
     <t>connecting solar to buses in cluster 9</t>
   </si>
   <si>
-    <t>distr_solelc_spv_POL_006</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_010</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_001</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_015</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_018</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_005</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_008</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_003</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_007</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_016</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_012</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_011</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 11</t>
-  </si>
-  <si>
     <t>comm-in</t>
   </si>
   <si>
     <t>ncap_cost~USD21_alt</t>
   </si>
   <si>
+    <t>e_Boleslawiec_POL,e_ZielonaGora_POL</t>
+  </si>
+  <si>
+    <t>e_Sosnowiec_POL,e_KedzierzynKozle_POL,e_Olesnica_POL,e_Gliwice_POL,e_Czestochowa_POL,e_Radomsko_POL,e_PiotrkowTrybunalsk_POL,e_Kielce_POL</t>
+  </si>
+  <si>
+    <t>e_Warsaw_POL,e_Lomza_POL</t>
+  </si>
+  <si>
+    <t>e_Lubin_POL,e_Poznan_POL,e_Koszalin_POL,e_Bydgoszcz_POL</t>
+  </si>
+  <si>
+    <t>e_Bydgoszcz_POL,e_Gdansk_POL,e_Grudziadz_POL,e_Kwidzyn_POL</t>
+  </si>
+  <si>
+    <t>e_Krosno_POL,e_Mielec_POL,e_Debica_POL,e_Zamosc_POL</t>
+  </si>
+  <si>
+    <t>e_Lomza_POL,e_Elk_POL,e_Bialystok_POL,e_Grajewo_POL</t>
+  </si>
+  <si>
+    <t>e_Lubin_POL,e_Swidnica_POL,e_Wroclaw_POL,e_Poznan_POL,e_Olesnica_POL</t>
+  </si>
+  <si>
+    <t>e_Koszalin_POL,e_Ustka_POL,e_Slupsk_POL</t>
+  </si>
+  <si>
+    <t>e_Olesnica_POL,e_Konin_POL,e_PiotrkowTrybunalsk_POL,e_Plock_POL</t>
+  </si>
+  <si>
+    <t>e_Plock_POL,e_Olsztyn_POL,e_Warsaw_POL</t>
+  </si>
+  <si>
+    <t>e_Elk_POL,e_Grajewo_POL</t>
+  </si>
+  <si>
+    <t>e_BielskoBiala_POL,e_Katowice_POL,e_Krakow_POL,e_Tarnow_POL</t>
+  </si>
+  <si>
+    <t>e_GorzowWielkopolski_POL,e_Szczecin_POL,e_Police_POL</t>
+  </si>
+  <si>
+    <t>e_Konin_POL,e_Bydgoszcz_POL,e_Wloclawek_POL,e_Kwidzyn_POL,e_Plock_POL</t>
+  </si>
+  <si>
+    <t>e_OstrowiecSwietokrz_POL,e_Pulawy_POL,e_Warsaw_POL</t>
+  </si>
+  <si>
     <t>e_Rzeszow_POL,e_Zamosc_POL,e_Pulawy_POL,e_Chelm_POL</t>
   </si>
   <si>
-    <t>e_GorzowWielkopolski_POL,e_Szczecin_POL,e_Police_POL</t>
-  </si>
-  <si>
-    <t>e_BielskoBiala_POL,e_Katowice_POL,e_Krakow_POL,e_Tarnow_POL</t>
-  </si>
-  <si>
-    <t>e_Konin_POL,e_Bydgoszcz_POL,e_Wloclawek_POL,e_Kwidzyn_POL,e_Plock_POL</t>
-  </si>
-  <si>
-    <t>e_OstrowiecSwietokrz_POL,e_Pulawy_POL,e_Warsaw_POL</t>
-  </si>
-  <si>
     <t>e_Legnica_POL,e_Swidnica_POL,e_KedzierzynKozle_POL,e_Opole_POL</t>
   </si>
   <si>
@@ -1018,54 +1054,102 @@
     <t>e_Pulawy_POL,e_Bialystok_POL,e_Chelm_POL</t>
   </si>
   <si>
-    <t>e_Plock_POL,e_Olsztyn_POL,e_Warsaw_POL</t>
-  </si>
-  <si>
-    <t>e_Elk_POL,e_Grajewo_POL</t>
-  </si>
-  <si>
-    <t>e_Boleslawiec_POL,e_ZielonaGora_POL</t>
-  </si>
-  <si>
-    <t>e_Sosnowiec_POL,e_KedzierzynKozle_POL,e_Olesnica_POL,e_Gliwice_POL,e_Czestochowa_POL,e_Radomsko_POL,e_PiotrkowTrybunalsk_POL,e_Kielce_POL</t>
-  </si>
-  <si>
-    <t>e_Warsaw_POL,e_Lomza_POL</t>
-  </si>
-  <si>
-    <t>e_Lubin_POL,e_Poznan_POL,e_Koszalin_POL,e_Bydgoszcz_POL</t>
-  </si>
-  <si>
-    <t>e_Bydgoszcz_POL,e_Gdansk_POL,e_Grudziadz_POL,e_Kwidzyn_POL</t>
-  </si>
-  <si>
-    <t>e_Lubin_POL,e_Swidnica_POL,e_Wroclaw_POL,e_Poznan_POL,e_Olesnica_POL</t>
-  </si>
-  <si>
-    <t>e_Koszalin_POL,e_Ustka_POL,e_Slupsk_POL</t>
-  </si>
-  <si>
-    <t>e_Olesnica_POL,e_Konin_POL,e_PiotrkowTrybunalsk_POL,e_Plock_POL</t>
-  </si>
-  <si>
-    <t>e_Krosno_POL,e_Mielec_POL,e_Debica_POL,e_Zamosc_POL</t>
-  </si>
-  <si>
-    <t>e_Lomza_POL,e_Elk_POL,e_Bialystok_POL,e_Grajewo_POL</t>
-  </si>
-  <si>
     <t>distr_wonelc_won_POL_007</t>
   </si>
   <si>
     <t>connecting wind onshore to buses in cluster 7</t>
   </si>
   <si>
+    <t>distr_wonelc_won_POL_005</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_001</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_018</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_015</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_016</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_013</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_008</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 8</t>
+  </si>
+  <si>
     <t>distr_wonelc_won_POL_002</t>
   </si>
   <si>
     <t>connecting wind onshore to buses in cluster 2</t>
   </si>
   <si>
+    <t>distr_wonelc_won_POL_019</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_017</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_006</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_009</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_004</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_012</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_003</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 3</t>
+  </si>
+  <si>
     <t>distr_wonelc_won_POL_014</t>
   </si>
   <si>
@@ -1078,90 +1162,6 @@
     <t>connecting wind onshore to buses in cluster 20</t>
   </si>
   <si>
-    <t>distr_wonelc_won_POL_006</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_009</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_004</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_001</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_013</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_008</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_012</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_003</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_018</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_015</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_016</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_019</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_017</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_005</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 5</t>
-  </si>
-  <si>
     <t>distr_wonelc_won_POL_011</t>
   </si>
   <si>
@@ -1180,12 +1180,93 @@
     <t>e_Warsaw_POL,e_Plock_POL,e_Olsztyn_POL</t>
   </si>
   <si>
+    <t>elc_won_POL_005</t>
+  </si>
+  <si>
+    <t>e_Lomza_POL,e_Elk_POL,e_Grajewo_POL,e_Bialystok_POL,e_Chelm_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_001</t>
+  </si>
+  <si>
+    <t>e_PiotrkowTrybunalsk_POL,e_Kielce_POL,e_Warsaw_POL,e_OstrowiecSwietokrz_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_018</t>
+  </si>
+  <si>
+    <t>e_Boleslawiec_POL,e_Legnica_POL,e_Swidnica_POL,e_KedzierzynKozle_POL,e_Opole_POL,e_Olesnica_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_015</t>
+  </si>
+  <si>
+    <t>e_BielskoBiala_POL,e_Krakow_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_016</t>
+  </si>
+  <si>
+    <t>e_Krosno_POL,e_Debica_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_013</t>
+  </si>
+  <si>
+    <t>e_Lubin_POL,e_Wroclaw_POL,e_Poznan_POL,e_Olesnica_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_008</t>
+  </si>
+  <si>
+    <t>e_Olsztyn_POL,e_Elk_POL</t>
+  </si>
+  <si>
     <t>elc_won_POL_002</t>
   </si>
   <si>
     <t>e_Tarnow_POL,e_Kielce_POL,e_OstrowiecSwietokrz_POL,e_Mielec_POL,e_Pulawy_POL,e_Rzeszow_POL</t>
   </si>
   <si>
+    <t>elc_won_POL_019</t>
+  </si>
+  <si>
+    <t>e_Katowice_POL,e_Czestochowa_POL,e_Krakow_POL,e_Kielce_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_017</t>
+  </si>
+  <si>
+    <t>e_Tarnow_POL,e_Krosno_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_006</t>
+  </si>
+  <si>
+    <t>e_Olesnica_POL,e_Konin_POL,e_Bydgoszcz_POL,e_Wloclawek_POL,e_Kwidzyn_POL,e_Plock_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_009</t>
+  </si>
+  <si>
+    <t>e_Gdansk_POL,e_Grudziadz_POL,e_Kwidzyn_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_004</t>
+  </si>
+  <si>
+    <t>elc_won_POL_012</t>
+  </si>
+  <si>
+    <t>e_ZielonaGora_POL,e_GorzowWielkopolski_POL,e_Szczecin_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_003</t>
+  </si>
+  <si>
+    <t>e_Warsaw_POL,e_Lomza_POL,e_Pulawy_POL,e_Bialystok_POL</t>
+  </si>
+  <si>
     <t>elc_won_POL_014</t>
   </si>
   <si>
@@ -1198,87 +1279,6 @@
     <t>e_Sosnowiec_POL,e_KedzierzynKozle_POL,e_Olesnica_POL,e_Gliwice_POL,e_Czestochowa_POL,e_Radomsko_POL</t>
   </si>
   <si>
-    <t>elc_won_POL_006</t>
-  </si>
-  <si>
-    <t>e_Olesnica_POL,e_Konin_POL,e_Bydgoszcz_POL,e_Wloclawek_POL,e_Kwidzyn_POL,e_Plock_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_009</t>
-  </si>
-  <si>
-    <t>e_Gdansk_POL,e_Grudziadz_POL,e_Kwidzyn_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_004</t>
-  </si>
-  <si>
-    <t>elc_won_POL_001</t>
-  </si>
-  <si>
-    <t>e_PiotrkowTrybunalsk_POL,e_Kielce_POL,e_Warsaw_POL,e_OstrowiecSwietokrz_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_013</t>
-  </si>
-  <si>
-    <t>e_Lubin_POL,e_Wroclaw_POL,e_Poznan_POL,e_Olesnica_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_008</t>
-  </si>
-  <si>
-    <t>e_Olsztyn_POL,e_Elk_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_012</t>
-  </si>
-  <si>
-    <t>e_ZielonaGora_POL,e_GorzowWielkopolski_POL,e_Szczecin_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_003</t>
-  </si>
-  <si>
-    <t>e_Warsaw_POL,e_Lomza_POL,e_Pulawy_POL,e_Bialystok_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_018</t>
-  </si>
-  <si>
-    <t>e_Boleslawiec_POL,e_Legnica_POL,e_Swidnica_POL,e_KedzierzynKozle_POL,e_Opole_POL,e_Olesnica_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_015</t>
-  </si>
-  <si>
-    <t>e_BielskoBiala_POL,e_Krakow_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_016</t>
-  </si>
-  <si>
-    <t>e_Krosno_POL,e_Debica_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_019</t>
-  </si>
-  <si>
-    <t>e_Katowice_POL,e_Czestochowa_POL,e_Krakow_POL,e_Kielce_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_017</t>
-  </si>
-  <si>
-    <t>e_Tarnow_POL,e_Krosno_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_005</t>
-  </si>
-  <si>
-    <t>e_Lomza_POL,e_Elk_POL,e_Grajewo_POL,e_Bialystok_POL,e_Chelm_POL</t>
-  </si>
-  <si>
     <t>elc_won_POL_011</t>
   </si>
   <si>
@@ -1291,6 +1291,42 @@
     <t>e_Police_POL,e_Koszalin_POL,e_Poznan_POL,e_Ustka_POL,e_Bydgoszcz_POL,e_Slupsk_POL,e_Gdansk_POL</t>
   </si>
   <si>
+    <t>distr_wofelc_wof_POL_006</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_POL_002</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_POL_005</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_POL_001</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_POL_003</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_POL_004</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 4</t>
+  </si>
+  <si>
     <t>distr_wofelc_wof_POL_008</t>
   </si>
   <si>
@@ -1303,30 +1339,6 @@
     <t>connecting wind offshore to buses in cluster 7</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_POL_005</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_POL_001</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_POL_006</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_POL_003</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 3</t>
-  </si>
-  <si>
     <t>distr_wofelc_wof_POL_010</t>
   </si>
   <si>
@@ -1339,16 +1351,34 @@
     <t>connecting wind offshore to buses in cluster 9</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_POL_002</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_POL_004</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 4</t>
+    <t>elc_wof_POL_006</t>
+  </si>
+  <si>
+    <t>e_Gdynia_POL</t>
+  </si>
+  <si>
+    <t>elc_wof_POL_002</t>
+  </si>
+  <si>
+    <t>e_Gdynia_POL,e_Gdansk_POL</t>
+  </si>
+  <si>
+    <t>elc_wof_POL_005</t>
+  </si>
+  <si>
+    <t>elc_wof_POL_001</t>
+  </si>
+  <si>
+    <t>e_Gdansk_POL</t>
+  </si>
+  <si>
+    <t>elc_wof_POL_003</t>
+  </si>
+  <si>
+    <t>elc_wof_POL_004</t>
+  </si>
+  <si>
+    <t>e_Ustka_POL,e_Gdynia_POL</t>
   </si>
   <si>
     <t>elc_wof_POL_008</t>
@@ -1363,24 +1393,6 @@
     <t>e_Koszalin_POL</t>
   </si>
   <si>
-    <t>elc_wof_POL_005</t>
-  </si>
-  <si>
-    <t>e_Gdynia_POL</t>
-  </si>
-  <si>
-    <t>elc_wof_POL_001</t>
-  </si>
-  <si>
-    <t>e_Gdansk_POL</t>
-  </si>
-  <si>
-    <t>elc_wof_POL_006</t>
-  </si>
-  <si>
-    <t>elc_wof_POL_003</t>
-  </si>
-  <si>
     <t>elc_wof_POL_010</t>
   </si>
   <si>
@@ -1388,18 +1400,6 @@
   </si>
   <si>
     <t>e_Koszalin_POL,e_Ustka_POL</t>
-  </si>
-  <si>
-    <t>elc_wof_POL_002</t>
-  </si>
-  <si>
-    <t>e_Gdynia_POL,e_Gdansk_POL</t>
-  </si>
-  <si>
-    <t>elc_wof_POL_004</t>
-  </si>
-  <si>
-    <t>e_Ustka_POL,e_Gdynia_POL</t>
   </si>
   <si>
     <t>e_won_POL_001</t>
@@ -7135,7 +7135,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{645172D3-8486-41EC-92F7-C63B80E30FD9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8AE2C5E8-BE0A-4671-9D3B-EB04D62CB92C}">
   <dimension ref="B9:BD30"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -7373,16 +7373,16 @@
         <v>244</v>
       </c>
       <c r="Y11" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="Z11" t="s">
         <v>288</v>
       </c>
       <c r="AA11">
-        <v>0.99606480786442353</v>
+        <v>0.99707401400885998</v>
       </c>
       <c r="AB11">
-        <v>72.145189152235062</v>
+        <v>53.643076504234422</v>
       </c>
       <c r="AD11" t="s">
         <v>243</v>
@@ -7451,10 +7451,10 @@
         <v>408</v>
       </c>
       <c r="BC11">
-        <v>0.99383352379209899</v>
+        <v>0.99615739524125424</v>
       </c>
       <c r="BD11">
-        <v>758.43022352327353</v>
+        <v>584.91448865302027</v>
       </c>
     </row>
     <row r="12" spans="2:56">
@@ -7519,16 +7519,16 @@
         <v>248</v>
       </c>
       <c r="Y12" t="s">
-        <v>225</v>
+        <v>236</v>
       </c>
       <c r="Z12" t="s">
         <v>289</v>
       </c>
       <c r="AA12">
-        <v>0.99785589517057005</v>
+        <v>0.99826037700975512</v>
       </c>
       <c r="AB12">
-        <v>39.308588539549028</v>
+        <v>31.893088154488542</v>
       </c>
       <c r="AD12" t="s">
         <v>243</v>
@@ -7561,10 +7561,10 @@
         <v>351</v>
       </c>
       <c r="AO12">
-        <v>0.99845791964146047</v>
+        <v>0.9963019969989696</v>
       </c>
       <c r="AP12">
-        <v>28.2714732398913</v>
+        <v>67.796721685557472</v>
       </c>
       <c r="AR12" t="s">
         <v>243</v>
@@ -7597,10 +7597,10 @@
         <v>410</v>
       </c>
       <c r="BC12">
-        <v>0.99603306101923861</v>
+        <v>0.99353721168226494</v>
       </c>
       <c r="BD12">
-        <v>594.19811056351818</v>
+        <v>780.55486105754892</v>
       </c>
     </row>
     <row r="13" spans="2:56">
@@ -7665,16 +7665,16 @@
         <v>250</v>
       </c>
       <c r="Y13" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="Z13" t="s">
         <v>290</v>
       </c>
       <c r="AA13">
-        <v>0.99790408176624201</v>
+        <v>0.99922515067657613</v>
       </c>
       <c r="AB13">
-        <v>38.425167618896296</v>
+        <v>14.205570929438155</v>
       </c>
       <c r="AD13" t="s">
         <v>243</v>
@@ -7707,10 +7707,10 @@
         <v>353</v>
       </c>
       <c r="AO13">
-        <v>0.99730422320290779</v>
+        <v>0.99871360797890252</v>
       </c>
       <c r="AP13">
-        <v>49.422574613357185</v>
+        <v>23.583853720120768</v>
       </c>
       <c r="AR13" t="s">
         <v>243</v>
@@ -7740,7 +7740,7 @@
         <v>411</v>
       </c>
       <c r="BB13" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="BC13">
         <v>0.99328660064428831</v>
@@ -7811,16 +7811,16 @@
         <v>252</v>
       </c>
       <c r="Y14" t="s">
-        <v>238</v>
+        <v>226</v>
       </c>
       <c r="Z14" t="s">
         <v>291</v>
       </c>
       <c r="AA14">
-        <v>0.99930490342600053</v>
+        <v>0.99730738889353909</v>
       </c>
       <c r="AB14">
-        <v>12.743437189989784</v>
+        <v>49.364536951784054</v>
       </c>
       <c r="AD14" t="s">
         <v>243</v>
@@ -7853,10 +7853,10 @@
         <v>355</v>
       </c>
       <c r="AO14">
-        <v>0.99805709209211746</v>
+        <v>0.99622969699231045</v>
       </c>
       <c r="AP14">
-        <v>35.619978311179104</v>
+        <v>69.122221807641537</v>
       </c>
       <c r="AR14" t="s">
         <v>243</v>
@@ -7883,10 +7883,10 @@
         <v>393</v>
       </c>
       <c r="BA14" t="s">
+        <v>412</v>
+      </c>
+      <c r="BB14" t="s">
         <v>413</v>
-      </c>
-      <c r="BB14" t="s">
-        <v>414</v>
       </c>
       <c r="BC14">
         <v>0.99644441082752833</v>
@@ -7957,16 +7957,16 @@
         <v>254</v>
       </c>
       <c r="Y15" t="s">
-        <v>241</v>
+        <v>229</v>
       </c>
       <c r="Z15" t="s">
         <v>292</v>
       </c>
       <c r="AA15">
-        <v>0.99881801309037566</v>
+        <v>0.99693515631487983</v>
       </c>
       <c r="AB15">
-        <v>21.669760009780138</v>
+        <v>56.188800893869058</v>
       </c>
       <c r="AD15" t="s">
         <v>243</v>
@@ -7999,10 +7999,10 @@
         <v>357</v>
       </c>
       <c r="AO15">
-        <v>0.99827231256984739</v>
+        <v>0.99641308487583879</v>
       </c>
       <c r="AP15">
-        <v>31.674269552798414</v>
+        <v>65.760110609622657</v>
       </c>
       <c r="AR15" t="s">
         <v>243</v>
@@ -8029,16 +8029,16 @@
         <v>395</v>
       </c>
       <c r="BA15" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="BB15" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="BC15">
-        <v>0.99615739524125424</v>
+        <v>0.99564787435456037</v>
       </c>
       <c r="BD15">
-        <v>584.91448865302027</v>
+        <v>622.95871485949408</v>
       </c>
     </row>
     <row r="16" spans="2:56">
@@ -8103,16 +8103,16 @@
         <v>256</v>
       </c>
       <c r="Y16" t="s">
-        <v>223</v>
+        <v>233</v>
       </c>
       <c r="Z16" t="s">
         <v>293</v>
       </c>
       <c r="AA16">
-        <v>0.99515616506526205</v>
+        <v>0.99481478101166732</v>
       </c>
       <c r="AB16">
-        <v>88.803640470195262</v>
+        <v>95.062348119433295</v>
       </c>
       <c r="AD16" t="s">
         <v>243</v>
@@ -8145,10 +8145,10 @@
         <v>359</v>
       </c>
       <c r="AO16">
-        <v>0.99635146162488653</v>
+        <v>0.99449756685866841</v>
       </c>
       <c r="AP16">
-        <v>66.889870210414614</v>
+        <v>100.87794092441324</v>
       </c>
       <c r="AR16" t="s">
         <v>243</v>
@@ -8175,16 +8175,16 @@
         <v>397</v>
       </c>
       <c r="BA16" t="s">
+        <v>415</v>
+      </c>
+      <c r="BB16" t="s">
         <v>416</v>
       </c>
-      <c r="BB16" t="s">
-        <v>414</v>
-      </c>
       <c r="BC16">
-        <v>0.99564787435456037</v>
+        <v>0.99255663966463281</v>
       </c>
       <c r="BD16">
-        <v>622.95871485949408</v>
+        <v>853.77090504074806</v>
       </c>
     </row>
     <row r="17" spans="2:56">
@@ -8249,16 +8249,16 @@
         <v>258</v>
       </c>
       <c r="Y17" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="Z17" t="s">
         <v>294</v>
       </c>
       <c r="AA17">
-        <v>0.99728872234103139</v>
+        <v>0.99681878296180493</v>
       </c>
       <c r="AB17">
-        <v>49.70675708109188</v>
+        <v>58.322312366909152</v>
       </c>
       <c r="AD17" t="s">
         <v>243</v>
@@ -8288,13 +8288,13 @@
         <v>360</v>
       </c>
       <c r="AN17" t="s">
-        <v>288</v>
+        <v>361</v>
       </c>
       <c r="AO17">
-        <v>0.99586212495478665</v>
+        <v>0.99883902037019667</v>
       </c>
       <c r="AP17">
-        <v>75.861042495577635</v>
+        <v>21.284626546395259</v>
       </c>
       <c r="AR17" t="s">
         <v>243</v>
@@ -8324,13 +8324,13 @@
         <v>417</v>
       </c>
       <c r="BB17" t="s">
-        <v>410</v>
+        <v>418</v>
       </c>
       <c r="BC17">
-        <v>0.99608994650263638</v>
+        <v>0.99383352379209899</v>
       </c>
       <c r="BD17">
-        <v>589.950661136485</v>
+        <v>758.43022352327353</v>
       </c>
     </row>
     <row r="18" spans="2:56">
@@ -8395,16 +8395,16 @@
         <v>260</v>
       </c>
       <c r="Y18" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="Z18" t="s">
         <v>295</v>
       </c>
       <c r="AA18">
-        <v>0.99583567586599486</v>
+        <v>0.99770934816564383</v>
       </c>
       <c r="AB18">
-        <v>76.34594245676044</v>
+        <v>41.995283629862939</v>
       </c>
       <c r="AD18" t="s">
         <v>243</v>
@@ -8431,16 +8431,16 @@
         <v>322</v>
       </c>
       <c r="AM18" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AN18" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AO18">
-        <v>0.99871360797890252</v>
+        <v>0.99521984547821263</v>
       </c>
       <c r="AP18">
-        <v>23.583853720120768</v>
+        <v>87.636166232768815</v>
       </c>
       <c r="AR18" t="s">
         <v>243</v>
@@ -8467,16 +8467,16 @@
         <v>401</v>
       </c>
       <c r="BA18" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="BB18" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="BC18">
-        <v>0.99399682431672776</v>
+        <v>0.99603306101923861</v>
       </c>
       <c r="BD18">
-        <v>746.2371176843244</v>
+        <v>594.19811056351818</v>
       </c>
     </row>
     <row r="19" spans="2:56">
@@ -8541,16 +8541,16 @@
         <v>262</v>
       </c>
       <c r="Y19" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Z19" t="s">
         <v>296</v>
       </c>
       <c r="AA19">
-        <v>0.99658775492800411</v>
+        <v>0.9970292559096442</v>
       </c>
       <c r="AB19">
-        <v>62.557826319923819</v>
+        <v>54.463641656523762</v>
       </c>
       <c r="AD19" t="s">
         <v>243</v>
@@ -8577,16 +8577,16 @@
         <v>324</v>
       </c>
       <c r="AM19" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AN19" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AO19">
-        <v>0.99883902037019667</v>
+        <v>0.99845791964146047</v>
       </c>
       <c r="AP19">
-        <v>21.284626546395259</v>
+        <v>28.2714732398913</v>
       </c>
       <c r="AR19" t="s">
         <v>243</v>
@@ -8613,16 +8613,16 @@
         <v>403</v>
       </c>
       <c r="BA19" t="s">
+        <v>421</v>
+      </c>
+      <c r="BB19" t="s">
         <v>420</v>
       </c>
-      <c r="BB19" t="s">
-        <v>421</v>
-      </c>
       <c r="BC19">
-        <v>0.99353721168226494</v>
+        <v>0.99608994650263638</v>
       </c>
       <c r="BD19">
-        <v>780.55486105754892</v>
+        <v>589.950661136485</v>
       </c>
     </row>
     <row r="20" spans="2:56">
@@ -8687,16 +8687,16 @@
         <v>264</v>
       </c>
       <c r="Y20" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="Z20" t="s">
         <v>297</v>
       </c>
       <c r="AA20">
-        <v>0.99510886326373238</v>
+        <v>0.9982126095160021</v>
       </c>
       <c r="AB20">
-        <v>89.670840164906522</v>
+        <v>32.768825539961391</v>
       </c>
       <c r="AD20" t="s">
         <v>243</v>
@@ -8723,16 +8723,16 @@
         <v>326</v>
       </c>
       <c r="AM20" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AN20" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AO20">
-        <v>0.99521984547821263</v>
+        <v>0.99872641243407079</v>
       </c>
       <c r="AP20">
-        <v>87.636166232768815</v>
+        <v>23.349105375368897</v>
       </c>
       <c r="AR20" t="s">
         <v>243</v>
@@ -8765,10 +8765,10 @@
         <v>423</v>
       </c>
       <c r="BC20">
-        <v>0.99255663966463281</v>
+        <v>0.99399682431672776</v>
       </c>
       <c r="BD20">
-        <v>853.77090504074806</v>
+        <v>746.2371176843244</v>
       </c>
     </row>
     <row r="21" spans="2:56">
@@ -8833,16 +8833,16 @@
         <v>266</v>
       </c>
       <c r="Y21" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="Z21" t="s">
         <v>298</v>
       </c>
       <c r="AA21">
-        <v>0.99707401400885998</v>
+        <v>0.99658775492800411</v>
       </c>
       <c r="AB21">
-        <v>53.643076504234422</v>
+        <v>62.557826319923819</v>
       </c>
       <c r="AD21" t="s">
         <v>243</v>
@@ -8869,16 +8869,16 @@
         <v>328</v>
       </c>
       <c r="AM21" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AN21" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AO21">
-        <v>0.99749126227646956</v>
+        <v>0.99776911581804295</v>
       </c>
       <c r="AP21">
-        <v>45.993524931390482</v>
+        <v>40.899543335879912</v>
       </c>
     </row>
     <row r="22" spans="2:56">
@@ -8943,16 +8943,16 @@
         <v>268</v>
       </c>
       <c r="Y22" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="Z22" t="s">
         <v>299</v>
       </c>
       <c r="AA22">
-        <v>0.99826037700975512</v>
+        <v>0.99510886326373238</v>
       </c>
       <c r="AB22">
-        <v>31.893088154488542</v>
+        <v>89.670840164906522</v>
       </c>
       <c r="AD22" t="s">
         <v>243</v>
@@ -8979,16 +8979,16 @@
         <v>330</v>
       </c>
       <c r="AM22" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AN22" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AO22">
-        <v>0.99807543246352515</v>
+        <v>0.99827231256984739</v>
       </c>
       <c r="AP22">
-        <v>35.283738168705199</v>
+        <v>31.674269552798414</v>
       </c>
     </row>
     <row r="23" spans="2:56">
@@ -9053,16 +9053,16 @@
         <v>270</v>
       </c>
       <c r="Y23" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="Z23" t="s">
         <v>300</v>
       </c>
       <c r="AA23">
-        <v>0.99922515067657613</v>
+        <v>0.99790408176624201</v>
       </c>
       <c r="AB23">
-        <v>14.205570929438155</v>
+        <v>38.425167618896296</v>
       </c>
       <c r="AD23" t="s">
         <v>243</v>
@@ -9089,16 +9089,16 @@
         <v>332</v>
       </c>
       <c r="AM23" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AN23" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AO23">
-        <v>0.99622969699231045</v>
+        <v>0.99635146162488653</v>
       </c>
       <c r="AP23">
-        <v>69.122221807641537</v>
+        <v>66.889870210414614</v>
       </c>
     </row>
     <row r="24" spans="2:56">
@@ -9163,16 +9163,16 @@
         <v>272</v>
       </c>
       <c r="Y24" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="Z24" t="s">
         <v>301</v>
       </c>
       <c r="AA24">
-        <v>0.99730738889353909</v>
+        <v>0.99785589517057005</v>
       </c>
       <c r="AB24">
-        <v>49.364536951784054</v>
+        <v>39.308588539549028</v>
       </c>
       <c r="AD24" t="s">
         <v>243</v>
@@ -9199,16 +9199,16 @@
         <v>334</v>
       </c>
       <c r="AM24" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AN24" t="s">
-        <v>374</v>
+        <v>304</v>
       </c>
       <c r="AO24">
-        <v>0.99641308487583879</v>
+        <v>0.99586212495478665</v>
       </c>
       <c r="AP24">
-        <v>65.760110609622657</v>
+        <v>75.861042495577635</v>
       </c>
     </row>
     <row r="25" spans="2:56">
@@ -9273,16 +9273,16 @@
         <v>274</v>
       </c>
       <c r="Y25" t="s">
-        <v>229</v>
+        <v>238</v>
       </c>
       <c r="Z25" t="s">
         <v>302</v>
       </c>
       <c r="AA25">
-        <v>0.99693515631487983</v>
+        <v>0.99930490342600053</v>
       </c>
       <c r="AB25">
-        <v>56.188800893869058</v>
+        <v>12.743437189989784</v>
       </c>
       <c r="AD25" t="s">
         <v>243</v>
@@ -9315,10 +9315,10 @@
         <v>376</v>
       </c>
       <c r="AO25">
-        <v>0.99449756685866841</v>
+        <v>0.99749126227646956</v>
       </c>
       <c r="AP25">
-        <v>100.87794092441324</v>
+        <v>45.993524931390482</v>
       </c>
     </row>
     <row r="26" spans="2:56">
@@ -9383,16 +9383,16 @@
         <v>276</v>
       </c>
       <c r="Y26" t="s">
-        <v>224</v>
+        <v>241</v>
       </c>
       <c r="Z26" t="s">
         <v>303</v>
       </c>
       <c r="AA26">
-        <v>0.99770934816564383</v>
+        <v>0.99881801309037566</v>
       </c>
       <c r="AB26">
-        <v>41.995283629862939</v>
+        <v>21.669760009780138</v>
       </c>
       <c r="AD26" t="s">
         <v>243</v>
@@ -9425,10 +9425,10 @@
         <v>378</v>
       </c>
       <c r="AO26">
-        <v>0.99872641243407079</v>
+        <v>0.99807543246352515</v>
       </c>
       <c r="AP26">
-        <v>23.349105375368897</v>
+        <v>35.283738168705199</v>
       </c>
     </row>
     <row r="27" spans="2:56">
@@ -9493,16 +9493,16 @@
         <v>278</v>
       </c>
       <c r="Y27" t="s">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="Z27" t="s">
         <v>304</v>
       </c>
       <c r="AA27">
-        <v>0.9970292559096442</v>
+        <v>0.99606480786442353</v>
       </c>
       <c r="AB27">
-        <v>54.463641656523762</v>
+        <v>72.145189152235062</v>
       </c>
       <c r="AD27" t="s">
         <v>243</v>
@@ -9535,10 +9535,10 @@
         <v>380</v>
       </c>
       <c r="AO27">
-        <v>0.99776911581804295</v>
+        <v>0.99730422320290779</v>
       </c>
       <c r="AP27">
-        <v>40.899543335879912</v>
+        <v>49.422574613357185</v>
       </c>
     </row>
     <row r="28" spans="2:56">
@@ -9603,16 +9603,16 @@
         <v>280</v>
       </c>
       <c r="Y28" t="s">
-        <v>237</v>
+        <v>223</v>
       </c>
       <c r="Z28" t="s">
         <v>305</v>
       </c>
       <c r="AA28">
-        <v>0.9982126095160021</v>
+        <v>0.99515616506526205</v>
       </c>
       <c r="AB28">
-        <v>32.768825539961391</v>
+        <v>88.803640470195262</v>
       </c>
       <c r="AD28" t="s">
         <v>243</v>
@@ -9645,10 +9645,10 @@
         <v>382</v>
       </c>
       <c r="AO28">
-        <v>0.9963019969989696</v>
+        <v>0.99805709209211746</v>
       </c>
       <c r="AP28">
-        <v>67.796721685557472</v>
+        <v>35.619978311179104</v>
       </c>
     </row>
     <row r="29" spans="2:56">
@@ -9713,16 +9713,16 @@
         <v>282</v>
       </c>
       <c r="Y29" t="s">
-        <v>233</v>
+        <v>240</v>
       </c>
       <c r="Z29" t="s">
         <v>306</v>
       </c>
       <c r="AA29">
-        <v>0.99481478101166732</v>
+        <v>0.99728872234103139</v>
       </c>
       <c r="AB29">
-        <v>95.062348119433295</v>
+        <v>49.70675708109188</v>
       </c>
       <c r="AD29" t="s">
         <v>243</v>
@@ -9823,16 +9823,16 @@
         <v>284</v>
       </c>
       <c r="Y30" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="Z30" t="s">
         <v>307</v>
       </c>
       <c r="AA30">
-        <v>0.99681878296180493</v>
+        <v>0.99583567586599486</v>
       </c>
       <c r="AB30">
-        <v>58.322312366909152</v>
+        <v>76.34594245676044</v>
       </c>
       <c r="AD30" t="s">
         <v>243</v>
@@ -9877,7 +9877,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77E1D973-D2C1-4533-BCF9-C3E250BAF64F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B614BAE-7B6E-4ADF-AB76-C7AA6081215F}">
   <dimension ref="B9:Z30"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -9989,7 +9989,7 @@
         <v>424</v>
       </c>
       <c r="K11" t="s">
-        <v>361</v>
+        <v>352</v>
       </c>
       <c r="L11">
         <v>0.30278350605008381</v>
@@ -10022,7 +10022,7 @@
         <v>464</v>
       </c>
       <c r="X11" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="Y11">
         <v>0.83925000000000005</v>
@@ -10057,7 +10057,7 @@
         <v>426</v>
       </c>
       <c r="K12" t="s">
-        <v>350</v>
+        <v>364</v>
       </c>
       <c r="L12">
         <v>0.42035497786033621</v>
@@ -10090,7 +10090,7 @@
         <v>466</v>
       </c>
       <c r="X12" t="s">
-        <v>420</v>
+        <v>409</v>
       </c>
       <c r="Y12">
         <v>16.887</v>
@@ -10125,7 +10125,7 @@
         <v>428</v>
       </c>
       <c r="K13" t="s">
-        <v>369</v>
+        <v>377</v>
       </c>
       <c r="L13">
         <v>1.6077871713950227</v>
@@ -10158,7 +10158,7 @@
         <v>468</v>
       </c>
       <c r="X13" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="Y13">
         <v>11.2965</v>
@@ -10193,7 +10193,7 @@
         <v>430</v>
       </c>
       <c r="K14" t="s">
-        <v>360</v>
+        <v>374</v>
       </c>
       <c r="L14">
         <v>2.531891424764753</v>
@@ -10226,7 +10226,7 @@
         <v>470</v>
       </c>
       <c r="X14" t="s">
-        <v>422</v>
+        <v>415</v>
       </c>
       <c r="Y14">
         <v>6.6577500000000001</v>
@@ -10261,7 +10261,7 @@
         <v>432</v>
       </c>
       <c r="K15" t="s">
-        <v>381</v>
+        <v>350</v>
       </c>
       <c r="L15">
         <v>7.6497810049421515</v>
@@ -10329,7 +10329,7 @@
         <v>434</v>
       </c>
       <c r="K16" t="s">
-        <v>356</v>
+        <v>370</v>
       </c>
       <c r="L16">
         <v>0.60733325583919984</v>
@@ -10362,7 +10362,7 @@
         <v>474</v>
       </c>
       <c r="X16" t="s">
-        <v>415</v>
+        <v>407</v>
       </c>
       <c r="Y16">
         <v>8.8230000000000004</v>
@@ -10430,7 +10430,7 @@
         <v>476</v>
       </c>
       <c r="X17" t="s">
-        <v>409</v>
+        <v>419</v>
       </c>
       <c r="Y17">
         <v>0.22650000000000001</v>
@@ -10465,7 +10465,7 @@
         <v>438</v>
       </c>
       <c r="K18" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="L18">
         <v>3.0365724666245324</v>
@@ -10498,7 +10498,7 @@
         <v>478</v>
       </c>
       <c r="X18" t="s">
-        <v>407</v>
+        <v>417</v>
       </c>
       <c r="Y18">
         <v>9.5062499999999996</v>
@@ -10533,7 +10533,7 @@
         <v>440</v>
       </c>
       <c r="K19" t="s">
-        <v>358</v>
+        <v>372</v>
       </c>
       <c r="L19">
         <v>0.22970161230087291</v>
@@ -10566,7 +10566,7 @@
         <v>480</v>
       </c>
       <c r="X19" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="Y19">
         <v>13.37175</v>
@@ -10634,7 +10634,7 @@
         <v>482</v>
       </c>
       <c r="X20" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="Y20">
         <v>3.9427500000000002</v>
@@ -10704,7 +10704,7 @@
         <v>446</v>
       </c>
       <c r="K22" t="s">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c r="L22">
         <v>0.6573344927201471</v>
@@ -10739,7 +10739,7 @@
         <v>448</v>
       </c>
       <c r="K23" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="L23">
         <v>0.28992997651770519</v>
@@ -10774,7 +10774,7 @@
         <v>450</v>
       </c>
       <c r="K24" t="s">
-        <v>352</v>
+        <v>379</v>
       </c>
       <c r="L24">
         <v>0.74609319967150689</v>
@@ -10809,7 +10809,7 @@
         <v>452</v>
       </c>
       <c r="K25" t="s">
-        <v>373</v>
+        <v>356</v>
       </c>
       <c r="L25">
         <v>0.35328950844501877</v>
@@ -10844,7 +10844,7 @@
         <v>454</v>
       </c>
       <c r="K26" t="s">
-        <v>375</v>
+        <v>358</v>
       </c>
       <c r="L26">
         <v>0.7924639655878376</v>
@@ -10879,7 +10879,7 @@
         <v>456</v>
       </c>
       <c r="K27" t="s">
-        <v>379</v>
+        <v>368</v>
       </c>
       <c r="L27">
         <v>0.55411362221124194</v>
@@ -10914,7 +10914,7 @@
         <v>458</v>
       </c>
       <c r="K28" t="s">
-        <v>371</v>
+        <v>354</v>
       </c>
       <c r="L28">
         <v>1.4327274230737423</v>
@@ -10949,7 +10949,7 @@
         <v>460</v>
       </c>
       <c r="K29" t="s">
-        <v>377</v>
+        <v>366</v>
       </c>
       <c r="L29">
         <v>0.56742801517356967</v>
@@ -10984,7 +10984,7 @@
         <v>462</v>
       </c>
       <c r="K30" t="s">
-        <v>354</v>
+        <v>381</v>
       </c>
       <c r="L30">
         <v>0.35405891742987328</v>
@@ -10999,7 +10999,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D459FDB5-3A76-45FC-AFE1-881EBB3CB04D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75D303FB-CC57-44E2-8733-2773CDA1D973}">
   <dimension ref="B9:U116"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -14483,7 +14483,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59D27BC0-282E-4EC5-BF5B-F4EB2EC1ED26}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0404747-6D62-48FB-84D0-DCCC10793260}">
   <dimension ref="B9:T88"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_POL_grids_kan50/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_POL_grids_kan50/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E51FB54F-7EAD-48B6-B6C8-086902FAFCA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A8F182B-F6D7-4866-B01D-7AA7638694B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -886,28 +886,70 @@
     <t>connecting solar to buses in cluster 18</t>
   </si>
   <si>
+    <t>distr_solelc_spv_POL_014</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_008</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_012</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_011</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_002</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_019</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_009</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_006</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_010</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 10</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_POL_005</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 5</t>
   </si>
   <si>
-    <t>distr_solelc_spv_POL_008</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_012</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_011</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 11</t>
+    <t>distr_solelc_spv_POL_004</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 4</t>
   </si>
   <si>
     <t>distr_solelc_spv_POL_003</t>
@@ -928,30 +970,6 @@
     <t>connecting solar to buses in cluster 16</t>
   </si>
   <si>
-    <t>distr_solelc_spv_POL_006</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_010</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_014</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_004</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 4</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_POL_017</t>
   </si>
   <si>
@@ -970,24 +988,6 @@
     <t>connecting solar to buses in cluster 13</t>
   </si>
   <si>
-    <t>distr_solelc_spv_POL_002</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_019</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_009</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 9</t>
-  </si>
-  <si>
     <t>comm-in</t>
   </si>
   <si>
@@ -1003,16 +1003,37 @@
     <t>e_Warsaw_POL,e_Lomza_POL</t>
   </si>
   <si>
+    <t>e_BielskoBiala_POL,e_Katowice_POL,e_Krakow_POL,e_Tarnow_POL</t>
+  </si>
+  <si>
+    <t>e_Bydgoszcz_POL,e_Gdansk_POL,e_Grudziadz_POL,e_Kwidzyn_POL</t>
+  </si>
+  <si>
+    <t>e_Krosno_POL,e_Mielec_POL,e_Debica_POL,e_Zamosc_POL</t>
+  </si>
+  <si>
+    <t>e_Lomza_POL,e_Elk_POL,e_Bialystok_POL,e_Grajewo_POL</t>
+  </si>
+  <si>
+    <t>e_Legnica_POL,e_Swidnica_POL,e_KedzierzynKozle_POL,e_Opole_POL</t>
+  </si>
+  <si>
+    <t>e_Kielce_POL,e_Warsaw_POL,e_OstrowiecSwietokrz_POL</t>
+  </si>
+  <si>
+    <t>e_Pulawy_POL,e_Bialystok_POL,e_Chelm_POL</t>
+  </si>
+  <si>
+    <t>e_Plock_POL,e_Olsztyn_POL,e_Warsaw_POL</t>
+  </si>
+  <si>
+    <t>e_Elk_POL,e_Grajewo_POL</t>
+  </si>
+  <si>
     <t>e_Lubin_POL,e_Poznan_POL,e_Koszalin_POL,e_Bydgoszcz_POL</t>
   </si>
   <si>
-    <t>e_Bydgoszcz_POL,e_Gdansk_POL,e_Grudziadz_POL,e_Kwidzyn_POL</t>
-  </si>
-  <si>
-    <t>e_Krosno_POL,e_Mielec_POL,e_Debica_POL,e_Zamosc_POL</t>
-  </si>
-  <si>
-    <t>e_Lomza_POL,e_Elk_POL,e_Bialystok_POL,e_Grajewo_POL</t>
+    <t>e_GorzowWielkopolski_POL,e_Szczecin_POL,e_Police_POL</t>
   </si>
   <si>
     <t>e_Lubin_POL,e_Swidnica_POL,e_Wroclaw_POL,e_Poznan_POL,e_Olesnica_POL</t>
@@ -1024,18 +1045,6 @@
     <t>e_Olesnica_POL,e_Konin_POL,e_PiotrkowTrybunalsk_POL,e_Plock_POL</t>
   </si>
   <si>
-    <t>e_Plock_POL,e_Olsztyn_POL,e_Warsaw_POL</t>
-  </si>
-  <si>
-    <t>e_Elk_POL,e_Grajewo_POL</t>
-  </si>
-  <si>
-    <t>e_BielskoBiala_POL,e_Katowice_POL,e_Krakow_POL,e_Tarnow_POL</t>
-  </si>
-  <si>
-    <t>e_GorzowWielkopolski_POL,e_Szczecin_POL,e_Police_POL</t>
-  </si>
-  <si>
     <t>e_Konin_POL,e_Bydgoszcz_POL,e_Wloclawek_POL,e_Kwidzyn_POL,e_Plock_POL</t>
   </si>
   <si>
@@ -1045,13 +1054,94 @@
     <t>e_Rzeszow_POL,e_Zamosc_POL,e_Pulawy_POL,e_Chelm_POL</t>
   </si>
   <si>
-    <t>e_Legnica_POL,e_Swidnica_POL,e_KedzierzynKozle_POL,e_Opole_POL</t>
-  </si>
-  <si>
-    <t>e_Kielce_POL,e_Warsaw_POL,e_OstrowiecSwietokrz_POL</t>
-  </si>
-  <si>
-    <t>e_Pulawy_POL,e_Bialystok_POL,e_Chelm_POL</t>
+    <t>distr_wonelc_won_POL_014</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_020</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_001</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_015</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_016</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_011</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_010</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_005</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_006</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_009</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_004</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_002</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_018</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_019</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_017</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 17</t>
   </si>
   <si>
     <t>distr_wonelc_won_POL_007</t>
@@ -1060,36 +1150,6 @@
     <t>connecting wind onshore to buses in cluster 7</t>
   </si>
   <si>
-    <t>distr_wonelc_won_POL_005</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_001</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_018</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_015</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_016</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 16</t>
-  </si>
-  <si>
     <t>distr_wonelc_won_POL_013</t>
   </si>
   <si>
@@ -1102,42 +1162,6 @@
     <t>connecting wind onshore to buses in cluster 8</t>
   </si>
   <si>
-    <t>distr_wonelc_won_POL_002</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_019</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_017</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_006</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_009</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_004</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 4</t>
-  </si>
-  <si>
     <t>distr_wonelc_won_POL_012</t>
   </si>
   <si>
@@ -1150,28 +1174,91 @@
     <t>connecting wind onshore to buses in cluster 3</t>
   </si>
   <si>
-    <t>distr_wonelc_won_POL_014</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_020</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_011</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_010</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 10</t>
+    <t>elc_won_POL_014</t>
+  </si>
+  <si>
+    <t>e_Lubin_POL,e_Poznan_POL,e_Bydgoszcz_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_020</t>
+  </si>
+  <si>
+    <t>e_Sosnowiec_POL,e_KedzierzynKozle_POL,e_Olesnica_POL,e_Gliwice_POL,e_Czestochowa_POL,e_Radomsko_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_001</t>
+  </si>
+  <si>
+    <t>e_PiotrkowTrybunalsk_POL,e_Kielce_POL,e_Warsaw_POL,e_OstrowiecSwietokrz_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_015</t>
+  </si>
+  <si>
+    <t>e_BielskoBiala_POL,e_Krakow_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_016</t>
+  </si>
+  <si>
+    <t>e_Krosno_POL,e_Debica_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_011</t>
+  </si>
+  <si>
+    <t>e_Boleslawiec_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_010</t>
+  </si>
+  <si>
+    <t>e_Police_POL,e_Koszalin_POL,e_Poznan_POL,e_Ustka_POL,e_Bydgoszcz_POL,e_Slupsk_POL,e_Gdansk_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_005</t>
+  </si>
+  <si>
+    <t>e_Lomza_POL,e_Elk_POL,e_Grajewo_POL,e_Bialystok_POL,e_Chelm_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_006</t>
+  </si>
+  <si>
+    <t>e_Olesnica_POL,e_Konin_POL,e_Bydgoszcz_POL,e_Wloclawek_POL,e_Kwidzyn_POL,e_Plock_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_009</t>
+  </si>
+  <si>
+    <t>e_Gdansk_POL,e_Grudziadz_POL,e_Kwidzyn_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_004</t>
+  </si>
+  <si>
+    <t>elc_won_POL_002</t>
+  </si>
+  <si>
+    <t>e_Tarnow_POL,e_Kielce_POL,e_OstrowiecSwietokrz_POL,e_Mielec_POL,e_Pulawy_POL,e_Rzeszow_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_018</t>
+  </si>
+  <si>
+    <t>e_Boleslawiec_POL,e_Legnica_POL,e_Swidnica_POL,e_KedzierzynKozle_POL,e_Opole_POL,e_Olesnica_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_019</t>
+  </si>
+  <si>
+    <t>e_Katowice_POL,e_Czestochowa_POL,e_Krakow_POL,e_Kielce_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_017</t>
+  </si>
+  <si>
+    <t>e_Tarnow_POL,e_Krosno_POL</t>
   </si>
   <si>
     <t>elc_won_POL_007</t>
@@ -1180,36 +1267,6 @@
     <t>e_Warsaw_POL,e_Plock_POL,e_Olsztyn_POL</t>
   </si>
   <si>
-    <t>elc_won_POL_005</t>
-  </si>
-  <si>
-    <t>e_Lomza_POL,e_Elk_POL,e_Grajewo_POL,e_Bialystok_POL,e_Chelm_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_001</t>
-  </si>
-  <si>
-    <t>e_PiotrkowTrybunalsk_POL,e_Kielce_POL,e_Warsaw_POL,e_OstrowiecSwietokrz_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_018</t>
-  </si>
-  <si>
-    <t>e_Boleslawiec_POL,e_Legnica_POL,e_Swidnica_POL,e_KedzierzynKozle_POL,e_Opole_POL,e_Olesnica_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_015</t>
-  </si>
-  <si>
-    <t>e_BielskoBiala_POL,e_Krakow_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_016</t>
-  </si>
-  <si>
-    <t>e_Krosno_POL,e_Debica_POL</t>
-  </si>
-  <si>
     <t>elc_won_POL_013</t>
   </si>
   <si>
@@ -1222,39 +1279,6 @@
     <t>e_Olsztyn_POL,e_Elk_POL</t>
   </si>
   <si>
-    <t>elc_won_POL_002</t>
-  </si>
-  <si>
-    <t>e_Tarnow_POL,e_Kielce_POL,e_OstrowiecSwietokrz_POL,e_Mielec_POL,e_Pulawy_POL,e_Rzeszow_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_019</t>
-  </si>
-  <si>
-    <t>e_Katowice_POL,e_Czestochowa_POL,e_Krakow_POL,e_Kielce_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_017</t>
-  </si>
-  <si>
-    <t>e_Tarnow_POL,e_Krosno_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_006</t>
-  </si>
-  <si>
-    <t>e_Olesnica_POL,e_Konin_POL,e_Bydgoszcz_POL,e_Wloclawek_POL,e_Kwidzyn_POL,e_Plock_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_009</t>
-  </si>
-  <si>
-    <t>e_Gdansk_POL,e_Grudziadz_POL,e_Kwidzyn_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_004</t>
-  </si>
-  <si>
     <t>elc_won_POL_012</t>
   </si>
   <si>
@@ -1267,30 +1291,6 @@
     <t>e_Warsaw_POL,e_Lomza_POL,e_Pulawy_POL,e_Bialystok_POL</t>
   </si>
   <si>
-    <t>elc_won_POL_014</t>
-  </si>
-  <si>
-    <t>e_Lubin_POL,e_Poznan_POL,e_Bydgoszcz_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_020</t>
-  </si>
-  <si>
-    <t>e_Sosnowiec_POL,e_KedzierzynKozle_POL,e_Olesnica_POL,e_Gliwice_POL,e_Czestochowa_POL,e_Radomsko_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_011</t>
-  </si>
-  <si>
-    <t>e_Boleslawiec_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_010</t>
-  </si>
-  <si>
-    <t>e_Police_POL,e_Koszalin_POL,e_Poznan_POL,e_Ustka_POL,e_Bydgoszcz_POL,e_Slupsk_POL,e_Gdansk_POL</t>
-  </si>
-  <si>
     <t>distr_wofelc_wof_POL_006</t>
   </si>
   <si>
@@ -1303,6 +1303,12 @@
     <t>connecting wind offshore to buses in cluster 2</t>
   </si>
   <si>
+    <t>distr_wofelc_wof_POL_003</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 3</t>
+  </si>
+  <si>
     <t>distr_wofelc_wof_POL_005</t>
   </si>
   <si>
@@ -1315,10 +1321,16 @@
     <t>connecting wind offshore to buses in cluster 1</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_POL_003</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 3</t>
+    <t>distr_wofelc_wof_POL_008</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_POL_007</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 7</t>
   </si>
   <si>
     <t>distr_wofelc_wof_POL_004</t>
@@ -1327,18 +1339,6 @@
     <t>connecting wind offshore to buses in cluster 4</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_POL_008</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_POL_007</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 7</t>
-  </si>
-  <si>
     <t>distr_wofelc_wof_POL_010</t>
   </si>
   <si>
@@ -1363,34 +1363,34 @@
     <t>e_Gdynia_POL,e_Gdansk_POL</t>
   </si>
   <si>
+    <t>elc_wof_POL_003</t>
+  </si>
+  <si>
+    <t>e_Gdansk_POL</t>
+  </si>
+  <si>
     <t>elc_wof_POL_005</t>
   </si>
   <si>
     <t>elc_wof_POL_001</t>
   </si>
   <si>
-    <t>e_Gdansk_POL</t>
-  </si>
-  <si>
-    <t>elc_wof_POL_003</t>
+    <t>elc_wof_POL_008</t>
+  </si>
+  <si>
+    <t>e_Police_POL,e_Koszalin_POL</t>
+  </si>
+  <si>
+    <t>elc_wof_POL_007</t>
+  </si>
+  <si>
+    <t>e_Koszalin_POL</t>
   </si>
   <si>
     <t>elc_wof_POL_004</t>
   </si>
   <si>
     <t>e_Ustka_POL,e_Gdynia_POL</t>
-  </si>
-  <si>
-    <t>elc_wof_POL_008</t>
-  </si>
-  <si>
-    <t>e_Police_POL,e_Koszalin_POL</t>
-  </si>
-  <si>
-    <t>elc_wof_POL_007</t>
-  </si>
-  <si>
-    <t>e_Koszalin_POL</t>
   </si>
   <si>
     <t>elc_wof_POL_010</t>
@@ -7135,7 +7135,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8AE2C5E8-BE0A-4671-9D3B-EB04D62CB92C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27508DC0-66DD-414F-BDC7-00722E819C4C}">
   <dimension ref="B9:BD30"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -7415,10 +7415,10 @@
         <v>349</v>
       </c>
       <c r="AO11">
-        <v>0.99653588726932718</v>
+        <v>0.99730422320290779</v>
       </c>
       <c r="AP11">
-        <v>63.508733395668145</v>
+        <v>49.422574613357185</v>
       </c>
       <c r="AR11" t="s">
         <v>243</v>
@@ -7561,10 +7561,10 @@
         <v>351</v>
       </c>
       <c r="AO12">
-        <v>0.9963019969989696</v>
+        <v>0.99805709209211746</v>
       </c>
       <c r="AP12">
-        <v>67.796721685557472</v>
+        <v>35.619978311179104</v>
       </c>
       <c r="AR12" t="s">
         <v>243</v>
@@ -7740,13 +7740,13 @@
         <v>411</v>
       </c>
       <c r="BB13" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="BC13">
-        <v>0.99328660064428831</v>
+        <v>0.99564787435456037</v>
       </c>
       <c r="BD13">
-        <v>799.26715189313825</v>
+        <v>622.95871485949408</v>
       </c>
     </row>
     <row r="14" spans="2:56">
@@ -7811,16 +7811,16 @@
         <v>252</v>
       </c>
       <c r="Y14" t="s">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="Z14" t="s">
         <v>291</v>
       </c>
       <c r="AA14">
-        <v>0.99730738889353909</v>
+        <v>0.99790408176624201</v>
       </c>
       <c r="AB14">
-        <v>49.364536951784054</v>
+        <v>38.425167618896296</v>
       </c>
       <c r="AD14" t="s">
         <v>243</v>
@@ -7853,10 +7853,10 @@
         <v>355</v>
       </c>
       <c r="AO14">
-        <v>0.99622969699231045</v>
+        <v>0.99641308487583879</v>
       </c>
       <c r="AP14">
-        <v>69.122221807641537</v>
+        <v>65.760110609622657</v>
       </c>
       <c r="AR14" t="s">
         <v>243</v>
@@ -7883,16 +7883,16 @@
         <v>393</v>
       </c>
       <c r="BA14" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="BB14" t="s">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="BC14">
-        <v>0.99644441082752833</v>
+        <v>0.99328660064428831</v>
       </c>
       <c r="BD14">
-        <v>563.48399154455342</v>
+        <v>799.26715189313825</v>
       </c>
     </row>
     <row r="15" spans="2:56">
@@ -7999,10 +7999,10 @@
         <v>357</v>
       </c>
       <c r="AO15">
-        <v>0.99641308487583879</v>
+        <v>0.99449756685866841</v>
       </c>
       <c r="AP15">
-        <v>65.760110609622657</v>
+        <v>100.87794092441324</v>
       </c>
       <c r="AR15" t="s">
         <v>243</v>
@@ -8032,13 +8032,13 @@
         <v>414</v>
       </c>
       <c r="BB15" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="BC15">
-        <v>0.99564787435456037</v>
+        <v>0.99644441082752833</v>
       </c>
       <c r="BD15">
-        <v>622.95871485949408</v>
+        <v>563.48399154455342</v>
       </c>
     </row>
     <row r="16" spans="2:56">
@@ -8145,10 +8145,10 @@
         <v>359</v>
       </c>
       <c r="AO16">
-        <v>0.99449756685866841</v>
+        <v>0.99802303154782224</v>
       </c>
       <c r="AP16">
-        <v>100.87794092441324</v>
+        <v>36.244421623259619</v>
       </c>
       <c r="AR16" t="s">
         <v>243</v>
@@ -8181,10 +8181,10 @@
         <v>416</v>
       </c>
       <c r="BC16">
-        <v>0.99255663966463281</v>
+        <v>0.99383352379209899</v>
       </c>
       <c r="BD16">
-        <v>853.77090504074806</v>
+        <v>758.43022352327353</v>
       </c>
     </row>
     <row r="17" spans="2:56">
@@ -8291,10 +8291,10 @@
         <v>361</v>
       </c>
       <c r="AO17">
-        <v>0.99883902037019667</v>
+        <v>0.99714358927215652</v>
       </c>
       <c r="AP17">
-        <v>21.284626546395259</v>
+        <v>52.367530010463909</v>
       </c>
       <c r="AR17" t="s">
         <v>243</v>
@@ -8327,10 +8327,10 @@
         <v>418</v>
       </c>
       <c r="BC17">
-        <v>0.99383352379209899</v>
+        <v>0.99603306101923861</v>
       </c>
       <c r="BD17">
-        <v>758.43022352327353</v>
+        <v>594.19811056351818</v>
       </c>
     </row>
     <row r="18" spans="2:56">
@@ -8395,16 +8395,16 @@
         <v>260</v>
       </c>
       <c r="Y18" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="Z18" t="s">
         <v>295</v>
       </c>
       <c r="AA18">
-        <v>0.99770934816564383</v>
+        <v>0.99515616506526205</v>
       </c>
       <c r="AB18">
-        <v>41.995283629862939</v>
+        <v>88.803640470195262</v>
       </c>
       <c r="AD18" t="s">
         <v>243</v>
@@ -8437,10 +8437,10 @@
         <v>363</v>
       </c>
       <c r="AO18">
-        <v>0.99521984547821263</v>
+        <v>0.9963019969989696</v>
       </c>
       <c r="AP18">
-        <v>87.636166232768815</v>
+        <v>67.796721685557472</v>
       </c>
       <c r="AR18" t="s">
         <v>243</v>
@@ -8473,10 +8473,10 @@
         <v>420</v>
       </c>
       <c r="BC18">
-        <v>0.99603306101923861</v>
+        <v>0.99255663966463281</v>
       </c>
       <c r="BD18">
-        <v>594.19811056351818</v>
+        <v>853.77090504074806</v>
       </c>
     </row>
     <row r="19" spans="2:56">
@@ -8541,16 +8541,16 @@
         <v>262</v>
       </c>
       <c r="Y19" t="s">
-        <v>228</v>
+        <v>240</v>
       </c>
       <c r="Z19" t="s">
         <v>296</v>
       </c>
       <c r="AA19">
-        <v>0.9970292559096442</v>
+        <v>0.99728872234103139</v>
       </c>
       <c r="AB19">
-        <v>54.463641656523762</v>
+        <v>49.70675708109188</v>
       </c>
       <c r="AD19" t="s">
         <v>243</v>
@@ -8583,10 +8583,10 @@
         <v>365</v>
       </c>
       <c r="AO19">
-        <v>0.99845791964146047</v>
+        <v>0.99827231256984739</v>
       </c>
       <c r="AP19">
-        <v>28.2714732398913</v>
+        <v>31.674269552798414</v>
       </c>
       <c r="AR19" t="s">
         <v>243</v>
@@ -8616,7 +8616,7 @@
         <v>421</v>
       </c>
       <c r="BB19" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="BC19">
         <v>0.99608994650263638</v>
@@ -8687,16 +8687,16 @@
         <v>264</v>
       </c>
       <c r="Y20" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="Z20" t="s">
         <v>297</v>
       </c>
       <c r="AA20">
-        <v>0.9982126095160021</v>
+        <v>0.99583567586599486</v>
       </c>
       <c r="AB20">
-        <v>32.768825539961391</v>
+        <v>76.34594245676044</v>
       </c>
       <c r="AD20" t="s">
         <v>243</v>
@@ -8729,10 +8729,10 @@
         <v>367</v>
       </c>
       <c r="AO20">
-        <v>0.99872641243407079</v>
+        <v>0.99635146162488653</v>
       </c>
       <c r="AP20">
-        <v>23.349105375368897</v>
+        <v>66.889870210414614</v>
       </c>
       <c r="AR20" t="s">
         <v>243</v>
@@ -8872,13 +8872,13 @@
         <v>368</v>
       </c>
       <c r="AN21" t="s">
-        <v>369</v>
+        <v>307</v>
       </c>
       <c r="AO21">
-        <v>0.99776911581804295</v>
+        <v>0.99586212495478665</v>
       </c>
       <c r="AP21">
-        <v>40.899543335879912</v>
+        <v>75.861042495577635</v>
       </c>
     </row>
     <row r="22" spans="2:56">
@@ -8979,16 +8979,16 @@
         <v>330</v>
       </c>
       <c r="AM22" t="s">
+        <v>369</v>
+      </c>
+      <c r="AN22" t="s">
         <v>370</v>
       </c>
-      <c r="AN22" t="s">
-        <v>371</v>
-      </c>
       <c r="AO22">
-        <v>0.99827231256984739</v>
+        <v>0.99845791964146047</v>
       </c>
       <c r="AP22">
-        <v>31.674269552798414</v>
+        <v>28.2714732398913</v>
       </c>
     </row>
     <row r="23" spans="2:56">
@@ -9053,16 +9053,16 @@
         <v>270</v>
       </c>
       <c r="Y23" t="s">
-        <v>235</v>
+        <v>226</v>
       </c>
       <c r="Z23" t="s">
         <v>300</v>
       </c>
       <c r="AA23">
-        <v>0.99790408176624201</v>
+        <v>0.99730738889353909</v>
       </c>
       <c r="AB23">
-        <v>38.425167618896296</v>
+        <v>49.364536951784054</v>
       </c>
       <c r="AD23" t="s">
         <v>243</v>
@@ -9089,16 +9089,16 @@
         <v>332</v>
       </c>
       <c r="AM23" t="s">
+        <v>371</v>
+      </c>
+      <c r="AN23" t="s">
         <v>372</v>
       </c>
-      <c r="AN23" t="s">
-        <v>373</v>
-      </c>
       <c r="AO23">
-        <v>0.99635146162488653</v>
+        <v>0.99622969699231045</v>
       </c>
       <c r="AP23">
-        <v>66.889870210414614</v>
+        <v>69.122221807641537</v>
       </c>
     </row>
     <row r="24" spans="2:56">
@@ -9199,16 +9199,16 @@
         <v>334</v>
       </c>
       <c r="AM24" t="s">
+        <v>373</v>
+      </c>
+      <c r="AN24" t="s">
         <v>374</v>
       </c>
-      <c r="AN24" t="s">
-        <v>304</v>
-      </c>
       <c r="AO24">
-        <v>0.99586212495478665</v>
+        <v>0.99872641243407079</v>
       </c>
       <c r="AP24">
-        <v>75.861042495577635</v>
+        <v>23.349105375368897</v>
       </c>
     </row>
     <row r="25" spans="2:56">
@@ -9273,16 +9273,16 @@
         <v>274</v>
       </c>
       <c r="Y25" t="s">
-        <v>238</v>
+        <v>224</v>
       </c>
       <c r="Z25" t="s">
         <v>302</v>
       </c>
       <c r="AA25">
-        <v>0.99930490342600053</v>
+        <v>0.99770934816564383</v>
       </c>
       <c r="AB25">
-        <v>12.743437189989784</v>
+        <v>41.995283629862939</v>
       </c>
       <c r="AD25" t="s">
         <v>243</v>
@@ -9315,10 +9315,10 @@
         <v>376</v>
       </c>
       <c r="AO25">
-        <v>0.99749126227646956</v>
+        <v>0.99776911581804295</v>
       </c>
       <c r="AP25">
-        <v>45.993524931390482</v>
+        <v>40.899543335879912</v>
       </c>
     </row>
     <row r="26" spans="2:56">
@@ -9383,16 +9383,16 @@
         <v>276</v>
       </c>
       <c r="Y26" t="s">
-        <v>241</v>
+        <v>228</v>
       </c>
       <c r="Z26" t="s">
         <v>303</v>
       </c>
       <c r="AA26">
-        <v>0.99881801309037566</v>
+        <v>0.9970292559096442</v>
       </c>
       <c r="AB26">
-        <v>21.669760009780138</v>
+        <v>54.463641656523762</v>
       </c>
       <c r="AD26" t="s">
         <v>243</v>
@@ -9425,10 +9425,10 @@
         <v>378</v>
       </c>
       <c r="AO26">
-        <v>0.99807543246352515</v>
+        <v>0.99653588726932718</v>
       </c>
       <c r="AP26">
-        <v>35.283738168705199</v>
+        <v>63.508733395668145</v>
       </c>
     </row>
     <row r="27" spans="2:56">
@@ -9493,16 +9493,16 @@
         <v>278</v>
       </c>
       <c r="Y27" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="Z27" t="s">
         <v>304</v>
       </c>
       <c r="AA27">
-        <v>0.99606480786442353</v>
+        <v>0.9982126095160021</v>
       </c>
       <c r="AB27">
-        <v>72.145189152235062</v>
+        <v>32.768825539961391</v>
       </c>
       <c r="AD27" t="s">
         <v>243</v>
@@ -9535,10 +9535,10 @@
         <v>380</v>
       </c>
       <c r="AO27">
-        <v>0.99730422320290779</v>
+        <v>0.99883902037019667</v>
       </c>
       <c r="AP27">
-        <v>49.422574613357185</v>
+        <v>21.284626546395259</v>
       </c>
     </row>
     <row r="28" spans="2:56">
@@ -9603,16 +9603,16 @@
         <v>280</v>
       </c>
       <c r="Y28" t="s">
-        <v>223</v>
+        <v>238</v>
       </c>
       <c r="Z28" t="s">
         <v>305</v>
       </c>
       <c r="AA28">
-        <v>0.99515616506526205</v>
+        <v>0.99930490342600053</v>
       </c>
       <c r="AB28">
-        <v>88.803640470195262</v>
+        <v>12.743437189989784</v>
       </c>
       <c r="AD28" t="s">
         <v>243</v>
@@ -9645,10 +9645,10 @@
         <v>382</v>
       </c>
       <c r="AO28">
-        <v>0.99805709209211746</v>
+        <v>0.99521984547821263</v>
       </c>
       <c r="AP28">
-        <v>35.619978311179104</v>
+        <v>87.636166232768815</v>
       </c>
     </row>
     <row r="29" spans="2:56">
@@ -9713,16 +9713,16 @@
         <v>282</v>
       </c>
       <c r="Y29" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Z29" t="s">
         <v>306</v>
       </c>
       <c r="AA29">
-        <v>0.99728872234103139</v>
+        <v>0.99881801309037566</v>
       </c>
       <c r="AB29">
-        <v>49.70675708109188</v>
+        <v>21.669760009780138</v>
       </c>
       <c r="AD29" t="s">
         <v>243</v>
@@ -9755,10 +9755,10 @@
         <v>384</v>
       </c>
       <c r="AO29">
-        <v>0.99802303154782224</v>
+        <v>0.99749126227646956</v>
       </c>
       <c r="AP29">
-        <v>36.244421623259619</v>
+        <v>45.993524931390482</v>
       </c>
     </row>
     <row r="30" spans="2:56">
@@ -9823,16 +9823,16 @@
         <v>284</v>
       </c>
       <c r="Y30" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="Z30" t="s">
         <v>307</v>
       </c>
       <c r="AA30">
-        <v>0.99583567586599486</v>
+        <v>0.99606480786442353</v>
       </c>
       <c r="AB30">
-        <v>76.34594245676044</v>
+        <v>72.145189152235062</v>
       </c>
       <c r="AD30" t="s">
         <v>243</v>
@@ -9865,10 +9865,10 @@
         <v>386</v>
       </c>
       <c r="AO30">
-        <v>0.99714358927215652</v>
+        <v>0.99807543246352515</v>
       </c>
       <c r="AP30">
-        <v>52.367530010463909</v>
+        <v>35.283738168705199</v>
       </c>
     </row>
   </sheetData>
@@ -9877,7 +9877,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B614BAE-7B6E-4ADF-AB76-C7AA6081215F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7C23A4B-4E1B-4EE9-9618-EEBEA7A40911}">
   <dimension ref="B9:Z30"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -10022,7 +10022,7 @@
         <v>464</v>
       </c>
       <c r="X11" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="Y11">
         <v>0.83925000000000005</v>
@@ -10057,7 +10057,7 @@
         <v>426</v>
       </c>
       <c r="K12" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="L12">
         <v>0.42035497786033621</v>
@@ -10125,7 +10125,7 @@
         <v>428</v>
       </c>
       <c r="K13" t="s">
-        <v>377</v>
+        <v>385</v>
       </c>
       <c r="L13">
         <v>1.6077871713950227</v>
@@ -10158,7 +10158,7 @@
         <v>468</v>
       </c>
       <c r="X13" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="Y13">
         <v>11.2965</v>
@@ -10193,7 +10193,7 @@
         <v>430</v>
       </c>
       <c r="K14" t="s">
-        <v>374</v>
+        <v>368</v>
       </c>
       <c r="L14">
         <v>2.531891424764753</v>
@@ -10226,7 +10226,7 @@
         <v>470</v>
       </c>
       <c r="X14" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="Y14">
         <v>6.6577500000000001</v>
@@ -10261,7 +10261,7 @@
         <v>432</v>
       </c>
       <c r="K15" t="s">
-        <v>350</v>
+        <v>362</v>
       </c>
       <c r="L15">
         <v>7.6497810049421515</v>
@@ -10294,7 +10294,7 @@
         <v>472</v>
       </c>
       <c r="X15" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="Y15">
         <v>17.089500000000001</v>
@@ -10329,7 +10329,7 @@
         <v>434</v>
       </c>
       <c r="K16" t="s">
-        <v>370</v>
+        <v>364</v>
       </c>
       <c r="L16">
         <v>0.60733325583919984</v>
@@ -10397,7 +10397,7 @@
         <v>436</v>
       </c>
       <c r="K17" t="s">
-        <v>348</v>
+        <v>377</v>
       </c>
       <c r="L17">
         <v>0.78389041837100704</v>
@@ -10430,7 +10430,7 @@
         <v>476</v>
       </c>
       <c r="X17" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="Y17">
         <v>0.22650000000000001</v>
@@ -10465,7 +10465,7 @@
         <v>438</v>
       </c>
       <c r="K18" t="s">
-        <v>362</v>
+        <v>381</v>
       </c>
       <c r="L18">
         <v>3.0365724666245324</v>
@@ -10498,7 +10498,7 @@
         <v>478</v>
       </c>
       <c r="X18" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="Y18">
         <v>9.5062499999999996</v>
@@ -10533,7 +10533,7 @@
         <v>440</v>
       </c>
       <c r="K19" t="s">
-        <v>372</v>
+        <v>366</v>
       </c>
       <c r="L19">
         <v>0.22970161230087291</v>
@@ -10601,7 +10601,7 @@
         <v>442</v>
       </c>
       <c r="K20" t="s">
-        <v>385</v>
+        <v>360</v>
       </c>
       <c r="L20">
         <v>0.27066515065379043</v>
@@ -10669,7 +10669,7 @@
         <v>444</v>
       </c>
       <c r="K21" t="s">
-        <v>383</v>
+        <v>358</v>
       </c>
       <c r="L21">
         <v>0.32193208719379746</v>
@@ -10704,7 +10704,7 @@
         <v>446</v>
       </c>
       <c r="K22" t="s">
-        <v>375</v>
+        <v>383</v>
       </c>
       <c r="L22">
         <v>0.6573344927201471</v>
@@ -10739,7 +10739,7 @@
         <v>448</v>
       </c>
       <c r="K23" t="s">
-        <v>360</v>
+        <v>379</v>
       </c>
       <c r="L23">
         <v>0.28992997651770519</v>
@@ -10774,7 +10774,7 @@
         <v>450</v>
       </c>
       <c r="K24" t="s">
-        <v>379</v>
+        <v>348</v>
       </c>
       <c r="L24">
         <v>0.74609319967150689</v>
@@ -10809,7 +10809,7 @@
         <v>452</v>
       </c>
       <c r="K25" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="L25">
         <v>0.35328950844501877</v>
@@ -10844,7 +10844,7 @@
         <v>454</v>
       </c>
       <c r="K26" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="L26">
         <v>0.7924639655878376</v>
@@ -10879,7 +10879,7 @@
         <v>456</v>
       </c>
       <c r="K27" t="s">
-        <v>368</v>
+        <v>375</v>
       </c>
       <c r="L27">
         <v>0.55411362221124194</v>
@@ -10914,7 +10914,7 @@
         <v>458</v>
       </c>
       <c r="K28" t="s">
-        <v>354</v>
+        <v>371</v>
       </c>
       <c r="L28">
         <v>1.4327274230737423</v>
@@ -10949,7 +10949,7 @@
         <v>460</v>
       </c>
       <c r="K29" t="s">
-        <v>366</v>
+        <v>373</v>
       </c>
       <c r="L29">
         <v>0.56742801517356967</v>
@@ -10984,7 +10984,7 @@
         <v>462</v>
       </c>
       <c r="K30" t="s">
-        <v>381</v>
+        <v>350</v>
       </c>
       <c r="L30">
         <v>0.35405891742987328</v>
@@ -10999,7 +10999,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75D303FB-CC57-44E2-8733-2773CDA1D973}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{229762F6-D211-430E-A843-5287F019D45C}">
   <dimension ref="B9:U116"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -14483,7 +14483,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0404747-6D62-48FB-84D0-DCCC10793260}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ADA7E36C-5808-44D3-B950-B101A5D199F2}">
   <dimension ref="B9:T88"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_POL_grids_kan50/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_POL_grids_kan50/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A8F182B-F6D7-4866-B01D-7AA7638694B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B813692-D8A7-4003-92DE-A9412075EAAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2843" uniqueCount="745">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2831" uniqueCount="745">
   <si>
     <t>~FI_Process</t>
   </si>
@@ -862,18 +862,54 @@
     <t>pre</t>
   </si>
   <si>
+    <t>distr_solelc_spv_POL_003</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>NRGI</t>
+  </si>
+  <si>
+    <t>daynite</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_007</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_016</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_008</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_017</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_020</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 20</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_POL_001</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 1</t>
   </si>
   <si>
-    <t>NRGI</t>
-  </si>
-  <si>
-    <t>daynite</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_POL_015</t>
   </si>
   <si>
@@ -886,16 +922,52 @@
     <t>connecting solar to buses in cluster 18</t>
   </si>
   <si>
+    <t>distr_solelc_spv_POL_013</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_005</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_002</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_019</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_009</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 9</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_POL_014</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 14</t>
   </si>
   <si>
-    <t>distr_solelc_spv_POL_008</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 8</t>
+    <t>distr_solelc_spv_POL_006</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_010</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 10</t>
   </si>
   <si>
     <t>distr_solelc_spv_POL_012</t>
@@ -910,90 +982,36 @@
     <t>connecting solar to buses in cluster 11</t>
   </si>
   <si>
-    <t>distr_solelc_spv_POL_002</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_019</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_009</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_006</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_010</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_005</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 5</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_POL_004</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 4</t>
   </si>
   <si>
-    <t>distr_solelc_spv_POL_003</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_007</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_016</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_017</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_020</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_013</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 13</t>
-  </si>
-  <si>
     <t>comm-in</t>
   </si>
   <si>
     <t>ncap_cost~USD21_alt</t>
   </si>
   <si>
+    <t>e_Lubin_POL,e_Swidnica_POL,e_Wroclaw_POL,e_Poznan_POL,e_Olesnica_POL</t>
+  </si>
+  <si>
+    <t>e_Koszalin_POL,e_Ustka_POL,e_Slupsk_POL</t>
+  </si>
+  <si>
+    <t>e_Olesnica_POL,e_Konin_POL,e_PiotrkowTrybunalsk_POL,e_Plock_POL</t>
+  </si>
+  <si>
+    <t>e_Bydgoszcz_POL,e_Gdansk_POL,e_Grudziadz_POL,e_Kwidzyn_POL</t>
+  </si>
+  <si>
+    <t>e_Konin_POL,e_Bydgoszcz_POL,e_Wloclawek_POL,e_Kwidzyn_POL,e_Plock_POL</t>
+  </si>
+  <si>
+    <t>e_OstrowiecSwietokrz_POL,e_Pulawy_POL,e_Warsaw_POL</t>
+  </si>
+  <si>
     <t>e_Boleslawiec_POL,e_ZielonaGora_POL</t>
   </si>
   <si>
@@ -1003,10 +1021,28 @@
     <t>e_Warsaw_POL,e_Lomza_POL</t>
   </si>
   <si>
+    <t>e_Rzeszow_POL,e_Zamosc_POL,e_Pulawy_POL,e_Chelm_POL</t>
+  </si>
+  <si>
+    <t>e_Lubin_POL,e_Poznan_POL,e_Koszalin_POL,e_Bydgoszcz_POL</t>
+  </si>
+  <si>
+    <t>e_Legnica_POL,e_Swidnica_POL,e_KedzierzynKozle_POL,e_Opole_POL</t>
+  </si>
+  <si>
+    <t>e_Kielce_POL,e_Warsaw_POL,e_OstrowiecSwietokrz_POL</t>
+  </si>
+  <si>
+    <t>e_Pulawy_POL,e_Bialystok_POL,e_Chelm_POL</t>
+  </si>
+  <si>
     <t>e_BielskoBiala_POL,e_Katowice_POL,e_Krakow_POL,e_Tarnow_POL</t>
   </si>
   <si>
-    <t>e_Bydgoszcz_POL,e_Gdansk_POL,e_Grudziadz_POL,e_Kwidzyn_POL</t>
+    <t>e_Plock_POL,e_Olsztyn_POL,e_Warsaw_POL</t>
+  </si>
+  <si>
+    <t>e_Elk_POL,e_Grajewo_POL</t>
   </si>
   <si>
     <t>e_Krosno_POL,e_Mielec_POL,e_Debica_POL,e_Zamosc_POL</t>
@@ -1015,45 +1051,9 @@
     <t>e_Lomza_POL,e_Elk_POL,e_Bialystok_POL,e_Grajewo_POL</t>
   </si>
   <si>
-    <t>e_Legnica_POL,e_Swidnica_POL,e_KedzierzynKozle_POL,e_Opole_POL</t>
-  </si>
-  <si>
-    <t>e_Kielce_POL,e_Warsaw_POL,e_OstrowiecSwietokrz_POL</t>
-  </si>
-  <si>
-    <t>e_Pulawy_POL,e_Bialystok_POL,e_Chelm_POL</t>
-  </si>
-  <si>
-    <t>e_Plock_POL,e_Olsztyn_POL,e_Warsaw_POL</t>
-  </si>
-  <si>
-    <t>e_Elk_POL,e_Grajewo_POL</t>
-  </si>
-  <si>
-    <t>e_Lubin_POL,e_Poznan_POL,e_Koszalin_POL,e_Bydgoszcz_POL</t>
-  </si>
-  <si>
     <t>e_GorzowWielkopolski_POL,e_Szczecin_POL,e_Police_POL</t>
   </si>
   <si>
-    <t>e_Lubin_POL,e_Swidnica_POL,e_Wroclaw_POL,e_Poznan_POL,e_Olesnica_POL</t>
-  </si>
-  <si>
-    <t>e_Koszalin_POL,e_Ustka_POL,e_Slupsk_POL</t>
-  </si>
-  <si>
-    <t>e_Olesnica_POL,e_Konin_POL,e_PiotrkowTrybunalsk_POL,e_Plock_POL</t>
-  </si>
-  <si>
-    <t>e_Konin_POL,e_Bydgoszcz_POL,e_Wloclawek_POL,e_Kwidzyn_POL,e_Plock_POL</t>
-  </si>
-  <si>
-    <t>e_OstrowiecSwietokrz_POL,e_Pulawy_POL,e_Warsaw_POL</t>
-  </si>
-  <si>
-    <t>e_Rzeszow_POL,e_Zamosc_POL,e_Pulawy_POL,e_Chelm_POL</t>
-  </si>
-  <si>
     <t>distr_wonelc_won_POL_014</t>
   </si>
   <si>
@@ -1066,114 +1066,114 @@
     <t>connecting wind onshore to buses in cluster 20</t>
   </si>
   <si>
+    <t>distr_wonelc_won_POL_013</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_008</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_002</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_018</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_015</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_016</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_019</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_017</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_005</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_006</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_009</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_004</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_011</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_010</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_007</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_012</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_003</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 3</t>
+  </si>
+  <si>
     <t>distr_wonelc_won_POL_001</t>
   </si>
   <si>
     <t>connecting wind onshore to buses in cluster 1</t>
   </si>
   <si>
-    <t>distr_wonelc_won_POL_015</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_016</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_011</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_010</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_005</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_006</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_009</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_004</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_002</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_018</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_019</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_017</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_007</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_013</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_008</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_012</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_003</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 3</t>
-  </si>
-  <si>
     <t>elc_won_POL_014</t>
   </si>
   <si>
@@ -1186,109 +1186,133 @@
     <t>e_Sosnowiec_POL,e_KedzierzynKozle_POL,e_Olesnica_POL,e_Gliwice_POL,e_Czestochowa_POL,e_Radomsko_POL</t>
   </si>
   <si>
+    <t>elc_won_POL_013</t>
+  </si>
+  <si>
+    <t>e_Lubin_POL,e_Wroclaw_POL,e_Poznan_POL,e_Olesnica_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_008</t>
+  </si>
+  <si>
+    <t>e_Olsztyn_POL,e_Elk_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_002</t>
+  </si>
+  <si>
+    <t>e_Tarnow_POL,e_Kielce_POL,e_OstrowiecSwietokrz_POL,e_Mielec_POL,e_Pulawy_POL,e_Rzeszow_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_018</t>
+  </si>
+  <si>
+    <t>e_Boleslawiec_POL,e_Legnica_POL,e_Swidnica_POL,e_KedzierzynKozle_POL,e_Opole_POL,e_Olesnica_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_015</t>
+  </si>
+  <si>
+    <t>e_BielskoBiala_POL,e_Krakow_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_016</t>
+  </si>
+  <si>
+    <t>e_Krosno_POL,e_Debica_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_019</t>
+  </si>
+  <si>
+    <t>e_Katowice_POL,e_Czestochowa_POL,e_Krakow_POL,e_Kielce_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_017</t>
+  </si>
+  <si>
+    <t>e_Tarnow_POL,e_Krosno_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_005</t>
+  </si>
+  <si>
+    <t>e_Lomza_POL,e_Elk_POL,e_Grajewo_POL,e_Bialystok_POL,e_Chelm_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_006</t>
+  </si>
+  <si>
+    <t>e_Olesnica_POL,e_Konin_POL,e_Bydgoszcz_POL,e_Wloclawek_POL,e_Kwidzyn_POL,e_Plock_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_009</t>
+  </si>
+  <si>
+    <t>e_Gdansk_POL,e_Grudziadz_POL,e_Kwidzyn_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_004</t>
+  </si>
+  <si>
+    <t>elc_won_POL_011</t>
+  </si>
+  <si>
+    <t>e_Boleslawiec_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_010</t>
+  </si>
+  <si>
+    <t>e_Police_POL,e_Koszalin_POL,e_Poznan_POL,e_Ustka_POL,e_Bydgoszcz_POL,e_Slupsk_POL,e_Gdansk_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_007</t>
+  </si>
+  <si>
+    <t>e_Warsaw_POL,e_Plock_POL,e_Olsztyn_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_012</t>
+  </si>
+  <si>
+    <t>e_ZielonaGora_POL,e_GorzowWielkopolski_POL,e_Szczecin_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_003</t>
+  </si>
+  <si>
+    <t>e_Warsaw_POL,e_Lomza_POL,e_Pulawy_POL,e_Bialystok_POL</t>
+  </si>
+  <si>
     <t>elc_won_POL_001</t>
   </si>
   <si>
     <t>e_PiotrkowTrybunalsk_POL,e_Kielce_POL,e_Warsaw_POL,e_OstrowiecSwietokrz_POL</t>
   </si>
   <si>
-    <t>elc_won_POL_015</t>
-  </si>
-  <si>
-    <t>e_BielskoBiala_POL,e_Krakow_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_016</t>
-  </si>
-  <si>
-    <t>e_Krosno_POL,e_Debica_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_011</t>
-  </si>
-  <si>
-    <t>e_Boleslawiec_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_010</t>
-  </si>
-  <si>
-    <t>e_Police_POL,e_Koszalin_POL,e_Poznan_POL,e_Ustka_POL,e_Bydgoszcz_POL,e_Slupsk_POL,e_Gdansk_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_005</t>
-  </si>
-  <si>
-    <t>e_Lomza_POL,e_Elk_POL,e_Grajewo_POL,e_Bialystok_POL,e_Chelm_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_006</t>
-  </si>
-  <si>
-    <t>e_Olesnica_POL,e_Konin_POL,e_Bydgoszcz_POL,e_Wloclawek_POL,e_Kwidzyn_POL,e_Plock_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_009</t>
-  </si>
-  <si>
-    <t>e_Gdansk_POL,e_Grudziadz_POL,e_Kwidzyn_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_004</t>
-  </si>
-  <si>
-    <t>elc_won_POL_002</t>
-  </si>
-  <si>
-    <t>e_Tarnow_POL,e_Kielce_POL,e_OstrowiecSwietokrz_POL,e_Mielec_POL,e_Pulawy_POL,e_Rzeszow_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_018</t>
-  </si>
-  <si>
-    <t>e_Boleslawiec_POL,e_Legnica_POL,e_Swidnica_POL,e_KedzierzynKozle_POL,e_Opole_POL,e_Olesnica_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_019</t>
-  </si>
-  <si>
-    <t>e_Katowice_POL,e_Czestochowa_POL,e_Krakow_POL,e_Kielce_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_017</t>
-  </si>
-  <si>
-    <t>e_Tarnow_POL,e_Krosno_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_007</t>
-  </si>
-  <si>
-    <t>e_Warsaw_POL,e_Plock_POL,e_Olsztyn_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_013</t>
-  </si>
-  <si>
-    <t>e_Lubin_POL,e_Wroclaw_POL,e_Poznan_POL,e_Olesnica_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_008</t>
-  </si>
-  <si>
-    <t>e_Olsztyn_POL,e_Elk_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_012</t>
-  </si>
-  <si>
-    <t>e_ZielonaGora_POL,e_GorzowWielkopolski_POL,e_Szczecin_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_003</t>
-  </si>
-  <si>
-    <t>e_Warsaw_POL,e_Lomza_POL,e_Pulawy_POL,e_Bialystok_POL</t>
+    <t>distr_wofelc_wof_POL_008</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_POL_007</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_POL_005</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_POL_001</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 1</t>
   </si>
   <si>
     <t>distr_wofelc_wof_POL_006</t>
@@ -1309,30 +1333,6 @@
     <t>connecting wind offshore to buses in cluster 3</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_POL_005</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_POL_001</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_POL_008</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_POL_007</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 7</t>
-  </si>
-  <si>
     <t>distr_wofelc_wof_POL_004</t>
   </si>
   <si>
@@ -1351,12 +1351,33 @@
     <t>connecting wind offshore to buses in cluster 9</t>
   </si>
   <si>
+    <t>elc_wof_POL_008</t>
+  </si>
+  <si>
+    <t>e_Police_POL,e_Koszalin_POL</t>
+  </si>
+  <si>
+    <t>elc_wof_POL_007</t>
+  </si>
+  <si>
+    <t>e_Koszalin_POL</t>
+  </si>
+  <si>
+    <t>elc_wof_POL_005</t>
+  </si>
+  <si>
+    <t>e_Gdynia_POL</t>
+  </si>
+  <si>
+    <t>elc_wof_POL_001</t>
+  </si>
+  <si>
+    <t>e_Gdansk_POL</t>
+  </si>
+  <si>
     <t>elc_wof_POL_006</t>
   </si>
   <si>
-    <t>e_Gdynia_POL</t>
-  </si>
-  <si>
     <t>elc_wof_POL_002</t>
   </si>
   <si>
@@ -1364,27 +1385,6 @@
   </si>
   <si>
     <t>elc_wof_POL_003</t>
-  </si>
-  <si>
-    <t>e_Gdansk_POL</t>
-  </si>
-  <si>
-    <t>elc_wof_POL_005</t>
-  </si>
-  <si>
-    <t>elc_wof_POL_001</t>
-  </si>
-  <si>
-    <t>elc_wof_POL_008</t>
-  </si>
-  <si>
-    <t>e_Police_POL,e_Koszalin_POL</t>
-  </si>
-  <si>
-    <t>elc_wof_POL_007</t>
-  </si>
-  <si>
-    <t>e_Koszalin_POL</t>
   </si>
   <si>
     <t>elc_wof_POL_004</t>
@@ -7135,7 +7135,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27508DC0-66DD-414F-BDC7-00722E819C4C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B57F7170-5D0A-43B5-B761-B700C5E67318}">
   <dimension ref="B9:BD30"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -7373,16 +7373,16 @@
         <v>244</v>
       </c>
       <c r="Y11" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="Z11" t="s">
         <v>288</v>
       </c>
       <c r="AA11">
-        <v>0.99707401400885998</v>
+        <v>0.99770934816564383</v>
       </c>
       <c r="AB11">
-        <v>53.643076504234422</v>
+        <v>41.995283629862939</v>
       </c>
       <c r="AD11" t="s">
         <v>243</v>
@@ -7451,10 +7451,10 @@
         <v>408</v>
       </c>
       <c r="BC11">
-        <v>0.99615739524125424</v>
+        <v>0.99383352379209899</v>
       </c>
       <c r="BD11">
-        <v>584.91448865302027</v>
+        <v>758.43022352327353</v>
       </c>
     </row>
     <row r="12" spans="2:56">
@@ -7519,16 +7519,16 @@
         <v>248</v>
       </c>
       <c r="Y12" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="Z12" t="s">
         <v>289</v>
       </c>
       <c r="AA12">
-        <v>0.99826037700975512</v>
+        <v>0.9970292559096442</v>
       </c>
       <c r="AB12">
-        <v>31.893088154488542</v>
+        <v>54.463641656523762</v>
       </c>
       <c r="AD12" t="s">
         <v>243</v>
@@ -7597,10 +7597,10 @@
         <v>410</v>
       </c>
       <c r="BC12">
-        <v>0.99353721168226494</v>
+        <v>0.99603306101923861</v>
       </c>
       <c r="BD12">
-        <v>780.55486105754892</v>
+        <v>594.19811056351818</v>
       </c>
     </row>
     <row r="13" spans="2:56">
@@ -7665,16 +7665,16 @@
         <v>250</v>
       </c>
       <c r="Y13" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="Z13" t="s">
         <v>290</v>
       </c>
       <c r="AA13">
-        <v>0.99922515067657613</v>
+        <v>0.9982126095160021</v>
       </c>
       <c r="AB13">
-        <v>14.205570929438155</v>
+        <v>32.768825539961391</v>
       </c>
       <c r="AD13" t="s">
         <v>243</v>
@@ -7707,10 +7707,10 @@
         <v>353</v>
       </c>
       <c r="AO13">
-        <v>0.99871360797890252</v>
+        <v>0.99883902037019667</v>
       </c>
       <c r="AP13">
-        <v>23.583853720120768</v>
+        <v>21.284626546395259</v>
       </c>
       <c r="AR13" t="s">
         <v>243</v>
@@ -7743,10 +7743,10 @@
         <v>412</v>
       </c>
       <c r="BC13">
-        <v>0.99564787435456037</v>
+        <v>0.99328660064428831</v>
       </c>
       <c r="BD13">
-        <v>622.95871485949408</v>
+        <v>799.26715189313825</v>
       </c>
     </row>
     <row r="14" spans="2:56">
@@ -7811,16 +7811,16 @@
         <v>252</v>
       </c>
       <c r="Y14" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="Z14" t="s">
         <v>291</v>
       </c>
       <c r="AA14">
-        <v>0.99790408176624201</v>
+        <v>0.99693515631487983</v>
       </c>
       <c r="AB14">
-        <v>38.425167618896296</v>
+        <v>56.188800893869058</v>
       </c>
       <c r="AD14" t="s">
         <v>243</v>
@@ -7853,10 +7853,10 @@
         <v>355</v>
       </c>
       <c r="AO14">
-        <v>0.99641308487583879</v>
+        <v>0.99521984547821263</v>
       </c>
       <c r="AP14">
-        <v>65.760110609622657</v>
+        <v>87.636166232768815</v>
       </c>
       <c r="AR14" t="s">
         <v>243</v>
@@ -7886,13 +7886,13 @@
         <v>413</v>
       </c>
       <c r="BB14" t="s">
-        <v>408</v>
+        <v>414</v>
       </c>
       <c r="BC14">
-        <v>0.99328660064428831</v>
+        <v>0.99644441082752833</v>
       </c>
       <c r="BD14">
-        <v>799.26715189313825</v>
+        <v>563.48399154455342</v>
       </c>
     </row>
     <row r="15" spans="2:56">
@@ -7957,16 +7957,16 @@
         <v>254</v>
       </c>
       <c r="Y15" t="s">
-        <v>229</v>
+        <v>238</v>
       </c>
       <c r="Z15" t="s">
         <v>292</v>
       </c>
       <c r="AA15">
-        <v>0.99693515631487983</v>
+        <v>0.99930490342600053</v>
       </c>
       <c r="AB15">
-        <v>56.188800893869058</v>
+        <v>12.743437189989784</v>
       </c>
       <c r="AD15" t="s">
         <v>243</v>
@@ -7999,10 +7999,10 @@
         <v>357</v>
       </c>
       <c r="AO15">
-        <v>0.99449756685866841</v>
+        <v>0.99845791964146047</v>
       </c>
       <c r="AP15">
-        <v>100.87794092441324</v>
+        <v>28.2714732398913</v>
       </c>
       <c r="AR15" t="s">
         <v>243</v>
@@ -8029,16 +8029,16 @@
         <v>395</v>
       </c>
       <c r="BA15" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="BB15" t="s">
         <v>412</v>
       </c>
       <c r="BC15">
-        <v>0.99644441082752833</v>
+        <v>0.99615739524125424</v>
       </c>
       <c r="BD15">
-        <v>563.48399154455342</v>
+        <v>584.91448865302027</v>
       </c>
     </row>
     <row r="16" spans="2:56">
@@ -8103,16 +8103,16 @@
         <v>256</v>
       </c>
       <c r="Y16" t="s">
-        <v>233</v>
+        <v>241</v>
       </c>
       <c r="Z16" t="s">
         <v>293</v>
       </c>
       <c r="AA16">
-        <v>0.99481478101166732</v>
+        <v>0.99881801309037566</v>
       </c>
       <c r="AB16">
-        <v>95.062348119433295</v>
+        <v>21.669760009780138</v>
       </c>
       <c r="AD16" t="s">
         <v>243</v>
@@ -8145,10 +8145,10 @@
         <v>359</v>
       </c>
       <c r="AO16">
-        <v>0.99802303154782224</v>
+        <v>0.99622969699231045</v>
       </c>
       <c r="AP16">
-        <v>36.244421623259619</v>
+        <v>69.122221807641537</v>
       </c>
       <c r="AR16" t="s">
         <v>243</v>
@@ -8175,16 +8175,16 @@
         <v>397</v>
       </c>
       <c r="BA16" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="BB16" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="BC16">
-        <v>0.99383352379209899</v>
+        <v>0.99353721168226494</v>
       </c>
       <c r="BD16">
-        <v>758.43022352327353</v>
+        <v>780.55486105754892</v>
       </c>
     </row>
     <row r="17" spans="2:56">
@@ -8249,16 +8249,16 @@
         <v>258</v>
       </c>
       <c r="Y17" t="s">
-        <v>232</v>
+        <v>222</v>
       </c>
       <c r="Z17" t="s">
         <v>294</v>
       </c>
       <c r="AA17">
-        <v>0.99681878296180493</v>
+        <v>0.99707401400885998</v>
       </c>
       <c r="AB17">
-        <v>58.322312366909152</v>
+        <v>53.643076504234422</v>
       </c>
       <c r="AD17" t="s">
         <v>243</v>
@@ -8291,10 +8291,10 @@
         <v>361</v>
       </c>
       <c r="AO17">
-        <v>0.99714358927215652</v>
+        <v>0.99641308487583879</v>
       </c>
       <c r="AP17">
-        <v>52.367530010463909</v>
+        <v>65.760110609622657</v>
       </c>
       <c r="AR17" t="s">
         <v>243</v>
@@ -8321,16 +8321,16 @@
         <v>399</v>
       </c>
       <c r="BA17" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="BB17" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="BC17">
-        <v>0.99603306101923861</v>
+        <v>0.99564787435456037</v>
       </c>
       <c r="BD17">
-        <v>594.19811056351818</v>
+        <v>622.95871485949408</v>
       </c>
     </row>
     <row r="18" spans="2:56">
@@ -8395,16 +8395,16 @@
         <v>260</v>
       </c>
       <c r="Y18" t="s">
-        <v>223</v>
+        <v>236</v>
       </c>
       <c r="Z18" t="s">
         <v>295</v>
       </c>
       <c r="AA18">
-        <v>0.99515616506526205</v>
+        <v>0.99826037700975512</v>
       </c>
       <c r="AB18">
-        <v>88.803640470195262</v>
+        <v>31.893088154488542</v>
       </c>
       <c r="AD18" t="s">
         <v>243</v>
@@ -8437,10 +8437,10 @@
         <v>363</v>
       </c>
       <c r="AO18">
-        <v>0.9963019969989696</v>
+        <v>0.99449756685866841</v>
       </c>
       <c r="AP18">
-        <v>67.796721685557472</v>
+        <v>100.87794092441324</v>
       </c>
       <c r="AR18" t="s">
         <v>243</v>
@@ -8541,16 +8541,16 @@
         <v>262</v>
       </c>
       <c r="Y19" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="Z19" t="s">
         <v>296</v>
       </c>
       <c r="AA19">
-        <v>0.99728872234103139</v>
+        <v>0.99922515067657613</v>
       </c>
       <c r="AB19">
-        <v>49.70675708109188</v>
+        <v>14.205570929438155</v>
       </c>
       <c r="AD19" t="s">
         <v>243</v>
@@ -8583,10 +8583,10 @@
         <v>365</v>
       </c>
       <c r="AO19">
-        <v>0.99827231256984739</v>
+        <v>0.99872641243407079</v>
       </c>
       <c r="AP19">
-        <v>31.674269552798414</v>
+        <v>23.349105375368897</v>
       </c>
       <c r="AR19" t="s">
         <v>243</v>
@@ -8616,7 +8616,7 @@
         <v>421</v>
       </c>
       <c r="BB19" t="s">
-        <v>418</v>
+        <v>410</v>
       </c>
       <c r="BC19">
         <v>0.99608994650263638</v>
@@ -8687,16 +8687,16 @@
         <v>264</v>
       </c>
       <c r="Y20" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="Z20" t="s">
         <v>297</v>
       </c>
       <c r="AA20">
-        <v>0.99583567586599486</v>
+        <v>0.99606480786442353</v>
       </c>
       <c r="AB20">
-        <v>76.34594245676044</v>
+        <v>72.145189152235062</v>
       </c>
       <c r="AD20" t="s">
         <v>243</v>
@@ -8729,10 +8729,10 @@
         <v>367</v>
       </c>
       <c r="AO20">
-        <v>0.99635146162488653</v>
+        <v>0.99776911581804295</v>
       </c>
       <c r="AP20">
-        <v>66.889870210414614</v>
+        <v>40.899543335879912</v>
       </c>
       <c r="AR20" t="s">
         <v>243</v>
@@ -8833,16 +8833,16 @@
         <v>266</v>
       </c>
       <c r="Y21" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="Z21" t="s">
         <v>298</v>
       </c>
       <c r="AA21">
-        <v>0.99658775492800411</v>
+        <v>0.99730738889353909</v>
       </c>
       <c r="AB21">
-        <v>62.557826319923819</v>
+        <v>49.364536951784054</v>
       </c>
       <c r="AD21" t="s">
         <v>243</v>
@@ -8872,13 +8872,13 @@
         <v>368</v>
       </c>
       <c r="AN21" t="s">
-        <v>307</v>
+        <v>369</v>
       </c>
       <c r="AO21">
-        <v>0.99586212495478665</v>
+        <v>0.9963019969989696</v>
       </c>
       <c r="AP21">
-        <v>75.861042495577635</v>
+        <v>67.796721685557472</v>
       </c>
     </row>
     <row r="22" spans="2:56">
@@ -8943,16 +8943,16 @@
         <v>268</v>
       </c>
       <c r="Y22" t="s">
-        <v>231</v>
+        <v>223</v>
       </c>
       <c r="Z22" t="s">
         <v>299</v>
       </c>
       <c r="AA22">
-        <v>0.99510886326373238</v>
+        <v>0.99515616506526205</v>
       </c>
       <c r="AB22">
-        <v>89.670840164906522</v>
+        <v>88.803640470195262</v>
       </c>
       <c r="AD22" t="s">
         <v>243</v>
@@ -8979,16 +8979,16 @@
         <v>330</v>
       </c>
       <c r="AM22" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AN22" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AO22">
-        <v>0.99845791964146047</v>
+        <v>0.99827231256984739</v>
       </c>
       <c r="AP22">
-        <v>28.2714732398913</v>
+        <v>31.674269552798414</v>
       </c>
     </row>
     <row r="23" spans="2:56">
@@ -9053,16 +9053,16 @@
         <v>270</v>
       </c>
       <c r="Y23" t="s">
-        <v>226</v>
+        <v>240</v>
       </c>
       <c r="Z23" t="s">
         <v>300</v>
       </c>
       <c r="AA23">
-        <v>0.99730738889353909</v>
+        <v>0.99728872234103139</v>
       </c>
       <c r="AB23">
-        <v>49.364536951784054</v>
+        <v>49.70675708109188</v>
       </c>
       <c r="AD23" t="s">
         <v>243</v>
@@ -9089,16 +9089,16 @@
         <v>332</v>
       </c>
       <c r="AM23" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AN23" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AO23">
-        <v>0.99622969699231045</v>
+        <v>0.99635146162488653</v>
       </c>
       <c r="AP23">
-        <v>69.122221807641537</v>
+        <v>66.889870210414614</v>
       </c>
     </row>
     <row r="24" spans="2:56">
@@ -9163,16 +9163,16 @@
         <v>272</v>
       </c>
       <c r="Y24" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="Z24" t="s">
         <v>301</v>
       </c>
       <c r="AA24">
-        <v>0.99785589517057005</v>
+        <v>0.99583567586599486</v>
       </c>
       <c r="AB24">
-        <v>39.308588539549028</v>
+        <v>76.34594245676044</v>
       </c>
       <c r="AD24" t="s">
         <v>243</v>
@@ -9199,16 +9199,16 @@
         <v>334</v>
       </c>
       <c r="AM24" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AN24" t="s">
-        <v>374</v>
+        <v>297</v>
       </c>
       <c r="AO24">
-        <v>0.99872641243407079</v>
+        <v>0.99586212495478665</v>
       </c>
       <c r="AP24">
-        <v>23.349105375368897</v>
+        <v>75.861042495577635</v>
       </c>
     </row>
     <row r="25" spans="2:56">
@@ -9273,16 +9273,16 @@
         <v>274</v>
       </c>
       <c r="Y25" t="s">
-        <v>224</v>
+        <v>235</v>
       </c>
       <c r="Z25" t="s">
         <v>302</v>
       </c>
       <c r="AA25">
-        <v>0.99770934816564383</v>
+        <v>0.99790408176624201</v>
       </c>
       <c r="AB25">
-        <v>41.995283629862939</v>
+        <v>38.425167618896296</v>
       </c>
       <c r="AD25" t="s">
         <v>243</v>
@@ -9315,10 +9315,10 @@
         <v>376</v>
       </c>
       <c r="AO25">
-        <v>0.99776911581804295</v>
+        <v>0.99802303154782224</v>
       </c>
       <c r="AP25">
-        <v>40.899543335879912</v>
+        <v>36.244421623259619</v>
       </c>
     </row>
     <row r="26" spans="2:56">
@@ -9383,16 +9383,16 @@
         <v>276</v>
       </c>
       <c r="Y26" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="Z26" t="s">
         <v>303</v>
       </c>
       <c r="AA26">
-        <v>0.9970292559096442</v>
+        <v>0.99658775492800411</v>
       </c>
       <c r="AB26">
-        <v>54.463641656523762</v>
+        <v>62.557826319923819</v>
       </c>
       <c r="AD26" t="s">
         <v>243</v>
@@ -9425,10 +9425,10 @@
         <v>378</v>
       </c>
       <c r="AO26">
-        <v>0.99653588726932718</v>
+        <v>0.99714358927215652</v>
       </c>
       <c r="AP26">
-        <v>63.508733395668145</v>
+        <v>52.367530010463909</v>
       </c>
     </row>
     <row r="27" spans="2:56">
@@ -9493,16 +9493,16 @@
         <v>278</v>
       </c>
       <c r="Y27" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="Z27" t="s">
         <v>304</v>
       </c>
       <c r="AA27">
-        <v>0.9982126095160021</v>
+        <v>0.99510886326373238</v>
       </c>
       <c r="AB27">
-        <v>32.768825539961391</v>
+        <v>89.670840164906522</v>
       </c>
       <c r="AD27" t="s">
         <v>243</v>
@@ -9535,10 +9535,10 @@
         <v>380</v>
       </c>
       <c r="AO27">
-        <v>0.99883902037019667</v>
+        <v>0.99653588726932718</v>
       </c>
       <c r="AP27">
-        <v>21.284626546395259</v>
+        <v>63.508733395668145</v>
       </c>
     </row>
     <row r="28" spans="2:56">
@@ -9603,16 +9603,16 @@
         <v>280</v>
       </c>
       <c r="Y28" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="Z28" t="s">
         <v>305</v>
       </c>
       <c r="AA28">
-        <v>0.99930490342600053</v>
+        <v>0.99481478101166732</v>
       </c>
       <c r="AB28">
-        <v>12.743437189989784</v>
+        <v>95.062348119433295</v>
       </c>
       <c r="AD28" t="s">
         <v>243</v>
@@ -9645,10 +9645,10 @@
         <v>382</v>
       </c>
       <c r="AO28">
-        <v>0.99521984547821263</v>
+        <v>0.99749126227646956</v>
       </c>
       <c r="AP28">
-        <v>87.636166232768815</v>
+        <v>45.993524931390482</v>
       </c>
     </row>
     <row r="29" spans="2:56">
@@ -9713,16 +9713,16 @@
         <v>282</v>
       </c>
       <c r="Y29" t="s">
-        <v>241</v>
+        <v>232</v>
       </c>
       <c r="Z29" t="s">
         <v>306</v>
       </c>
       <c r="AA29">
-        <v>0.99881801309037566</v>
+        <v>0.99681878296180493</v>
       </c>
       <c r="AB29">
-        <v>21.669760009780138</v>
+        <v>58.322312366909152</v>
       </c>
       <c r="AD29" t="s">
         <v>243</v>
@@ -9755,10 +9755,10 @@
         <v>384</v>
       </c>
       <c r="AO29">
-        <v>0.99749126227646956</v>
+        <v>0.99807543246352515</v>
       </c>
       <c r="AP29">
-        <v>45.993524931390482</v>
+        <v>35.283738168705199</v>
       </c>
     </row>
     <row r="30" spans="2:56">
@@ -9823,16 +9823,16 @@
         <v>284</v>
       </c>
       <c r="Y30" t="s">
-        <v>234</v>
+        <v>225</v>
       </c>
       <c r="Z30" t="s">
         <v>307</v>
       </c>
       <c r="AA30">
-        <v>0.99606480786442353</v>
+        <v>0.99785589517057005</v>
       </c>
       <c r="AB30">
-        <v>72.145189152235062</v>
+        <v>39.308588539549028</v>
       </c>
       <c r="AD30" t="s">
         <v>243</v>
@@ -9865,10 +9865,10 @@
         <v>386</v>
       </c>
       <c r="AO30">
-        <v>0.99807543246352515</v>
+        <v>0.99871360797890252</v>
       </c>
       <c r="AP30">
-        <v>35.283738168705199</v>
+        <v>23.583853720120768</v>
       </c>
     </row>
   </sheetData>
@@ -9877,7 +9877,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7C23A4B-4E1B-4EE9-9618-EEBEA7A40911}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26482C15-15A6-45C8-AADF-A88379AB76DF}">
   <dimension ref="B9:Z30"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -9989,7 +9989,7 @@
         <v>424</v>
       </c>
       <c r="K11" t="s">
-        <v>352</v>
+        <v>385</v>
       </c>
       <c r="L11">
         <v>0.30278350605008381</v>
@@ -10022,7 +10022,7 @@
         <v>464</v>
       </c>
       <c r="X11" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="Y11">
         <v>0.83925000000000005</v>
@@ -10057,7 +10057,7 @@
         <v>426</v>
       </c>
       <c r="K12" t="s">
-        <v>369</v>
+        <v>356</v>
       </c>
       <c r="L12">
         <v>0.42035497786033621</v>
@@ -10090,7 +10090,7 @@
         <v>466</v>
       </c>
       <c r="X12" t="s">
-        <v>409</v>
+        <v>416</v>
       </c>
       <c r="Y12">
         <v>16.887</v>
@@ -10125,7 +10125,7 @@
         <v>428</v>
       </c>
       <c r="K13" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="L13">
         <v>1.6077871713950227</v>
@@ -10158,7 +10158,7 @@
         <v>468</v>
       </c>
       <c r="X13" t="s">
-        <v>411</v>
+        <v>418</v>
       </c>
       <c r="Y13">
         <v>11.2965</v>
@@ -10193,7 +10193,7 @@
         <v>430</v>
       </c>
       <c r="K14" t="s">
-        <v>368</v>
+        <v>374</v>
       </c>
       <c r="L14">
         <v>2.531891424764753</v>
@@ -10261,7 +10261,7 @@
         <v>432</v>
       </c>
       <c r="K15" t="s">
-        <v>362</v>
+        <v>368</v>
       </c>
       <c r="L15">
         <v>7.6497810049421515</v>
@@ -10294,7 +10294,7 @@
         <v>472</v>
       </c>
       <c r="X15" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="Y15">
         <v>17.089500000000001</v>
@@ -10329,7 +10329,7 @@
         <v>434</v>
       </c>
       <c r="K16" t="s">
-        <v>364</v>
+        <v>370</v>
       </c>
       <c r="L16">
         <v>0.60733325583919984</v>
@@ -10362,7 +10362,7 @@
         <v>474</v>
       </c>
       <c r="X16" t="s">
-        <v>407</v>
+        <v>415</v>
       </c>
       <c r="Y16">
         <v>8.8230000000000004</v>
@@ -10397,7 +10397,7 @@
         <v>436</v>
       </c>
       <c r="K17" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="L17">
         <v>0.78389041837100704</v>
@@ -10430,7 +10430,7 @@
         <v>476</v>
       </c>
       <c r="X17" t="s">
-        <v>417</v>
+        <v>409</v>
       </c>
       <c r="Y17">
         <v>0.22650000000000001</v>
@@ -10465,7 +10465,7 @@
         <v>438</v>
       </c>
       <c r="K18" t="s">
-        <v>381</v>
+        <v>354</v>
       </c>
       <c r="L18">
         <v>3.0365724666245324</v>
@@ -10498,7 +10498,7 @@
         <v>478</v>
       </c>
       <c r="X18" t="s">
-        <v>415</v>
+        <v>407</v>
       </c>
       <c r="Y18">
         <v>9.5062499999999996</v>
@@ -10533,7 +10533,7 @@
         <v>440</v>
       </c>
       <c r="K19" t="s">
-        <v>366</v>
+        <v>372</v>
       </c>
       <c r="L19">
         <v>0.22970161230087291</v>
@@ -10601,7 +10601,7 @@
         <v>442</v>
       </c>
       <c r="K20" t="s">
-        <v>360</v>
+        <v>377</v>
       </c>
       <c r="L20">
         <v>0.27066515065379043</v>
@@ -10669,7 +10669,7 @@
         <v>444</v>
       </c>
       <c r="K21" t="s">
-        <v>358</v>
+        <v>375</v>
       </c>
       <c r="L21">
         <v>0.32193208719379746</v>
@@ -10704,7 +10704,7 @@
         <v>446</v>
       </c>
       <c r="K22" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="L22">
         <v>0.6573344927201471</v>
@@ -10739,7 +10739,7 @@
         <v>448</v>
       </c>
       <c r="K23" t="s">
-        <v>379</v>
+        <v>352</v>
       </c>
       <c r="L23">
         <v>0.28992997651770519</v>
@@ -10809,7 +10809,7 @@
         <v>452</v>
       </c>
       <c r="K25" t="s">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="L25">
         <v>0.35328950844501877</v>
@@ -10844,7 +10844,7 @@
         <v>454</v>
       </c>
       <c r="K26" t="s">
-        <v>356</v>
+        <v>362</v>
       </c>
       <c r="L26">
         <v>0.7924639655878376</v>
@@ -10879,7 +10879,7 @@
         <v>456</v>
       </c>
       <c r="K27" t="s">
-        <v>375</v>
+        <v>366</v>
       </c>
       <c r="L27">
         <v>0.55411362221124194</v>
@@ -10914,7 +10914,7 @@
         <v>458</v>
       </c>
       <c r="K28" t="s">
-        <v>371</v>
+        <v>358</v>
       </c>
       <c r="L28">
         <v>1.4327274230737423</v>
@@ -10949,7 +10949,7 @@
         <v>460</v>
       </c>
       <c r="K29" t="s">
-        <v>373</v>
+        <v>364</v>
       </c>
       <c r="L29">
         <v>0.56742801517356967</v>
@@ -10999,7 +10999,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{229762F6-D211-430E-A843-5287F019D45C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{054D1DD9-6C63-451C-A696-99D7476CB73A}">
   <dimension ref="B9:U116"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -11163,13 +11163,13 @@
         <v>19</v>
       </c>
       <c r="F13">
-        <v>0.58899999999999997</v>
+        <v>2.1204000000000001</v>
       </c>
       <c r="I13">
-        <v>0.54400000000000004</v>
+        <v>1.9583999999999999</v>
       </c>
       <c r="L13">
-        <v>0.497</v>
+        <v>1.7891999999999999</v>
       </c>
       <c r="M13" t="s">
         <v>488</v>
@@ -11439,13 +11439,13 @@
         <v>19</v>
       </c>
       <c r="F19">
-        <v>1.9279999999999999</v>
+        <v>6.9408000000000003</v>
       </c>
       <c r="I19">
-        <v>1.9279999999999999</v>
+        <v>6.9408000000000003</v>
       </c>
       <c r="L19">
-        <v>1.9279999999999999</v>
+        <v>6.9408000000000003</v>
       </c>
       <c r="M19" t="s">
         <v>488</v>
@@ -11715,13 +11715,13 @@
         <v>493</v>
       </c>
       <c r="E25">
-        <v>1.3</v>
+        <v>4.68</v>
       </c>
       <c r="H25">
-        <v>1.3</v>
+        <v>4.68</v>
       </c>
       <c r="L25">
-        <v>1.2</v>
+        <v>4.32</v>
       </c>
       <c r="M25" t="s">
         <v>488</v>
@@ -11739,7 +11739,7 @@
         <v>21</v>
       </c>
       <c r="T25" t="s">
-        <v>247</v>
+        <v>516</v>
       </c>
       <c r="U25" t="s">
         <v>513</v>
@@ -11780,7 +11780,7 @@
         <v>21</v>
       </c>
       <c r="T26" t="s">
-        <v>247</v>
+        <v>516</v>
       </c>
       <c r="U26" t="s">
         <v>513</v>
@@ -11983,13 +11983,13 @@
         <v>497</v>
       </c>
       <c r="F33">
-        <v>1.294</v>
+        <v>4.6584000000000003</v>
       </c>
       <c r="I33">
-        <v>1.1060000000000001</v>
+        <v>3.9815999999999998</v>
       </c>
       <c r="L33">
-        <v>0.98899999999999999</v>
+        <v>3.5604</v>
       </c>
       <c r="M33" t="s">
         <v>488</v>
@@ -12151,13 +12151,13 @@
         <v>19</v>
       </c>
       <c r="F39">
-        <v>2.3610000000000002</v>
+        <v>8.4995999999999992</v>
       </c>
       <c r="I39">
-        <v>2.3610000000000002</v>
+        <v>8.4995999999999992</v>
       </c>
       <c r="L39">
-        <v>2.3610000000000002</v>
+        <v>8.4995999999999992</v>
       </c>
       <c r="M39" t="s">
         <v>488</v>
@@ -12319,13 +12319,13 @@
         <v>19</v>
       </c>
       <c r="F45">
-        <v>2.5499999999999998</v>
+        <v>9.18</v>
       </c>
       <c r="I45">
-        <v>2.4420000000000002</v>
+        <v>8.7911999999999999</v>
       </c>
       <c r="L45">
-        <v>2.3170000000000002</v>
+        <v>8.3412000000000006</v>
       </c>
       <c r="M45" t="s">
         <v>488</v>
@@ -12487,13 +12487,13 @@
         <v>19</v>
       </c>
       <c r="F51">
-        <v>2.6389999999999998</v>
+        <v>9.5004000000000008</v>
       </c>
       <c r="I51">
-        <v>2.6389999999999998</v>
+        <v>9.5004000000000008</v>
       </c>
       <c r="L51">
-        <v>2.6389999999999998</v>
+        <v>9.5004000000000008</v>
       </c>
       <c r="M51" t="s">
         <v>488</v>
@@ -12800,10 +12800,10 @@
         <v>19</v>
       </c>
       <c r="I62">
-        <v>0.77800000000000002</v>
+        <v>2.8008000000000002</v>
       </c>
       <c r="L62">
-        <v>0.77800000000000002</v>
+        <v>2.8008000000000002</v>
       </c>
       <c r="M62" t="s">
         <v>488</v>
@@ -12954,19 +12954,19 @@
         <v>19</v>
       </c>
       <c r="H67">
-        <v>0.72199999999999998</v>
+        <v>2.5992000000000002</v>
       </c>
       <c r="I67">
-        <v>0.72199999999999998</v>
+        <v>2.5992000000000002</v>
       </c>
       <c r="J67">
-        <v>0.72199999999999998</v>
+        <v>2.5992000000000002</v>
       </c>
       <c r="K67">
-        <v>0.72199999999999998</v>
+        <v>2.5992000000000002</v>
       </c>
       <c r="L67">
-        <v>0.72199999999999998</v>
+        <v>2.5992000000000002</v>
       </c>
       <c r="M67" t="s">
         <v>488</v>
@@ -13105,13 +13105,13 @@
         <v>19</v>
       </c>
       <c r="F72">
-        <v>1.4570000000000001</v>
+        <v>5.2451999999999996</v>
       </c>
       <c r="I72">
-        <v>1.4570000000000001</v>
+        <v>5.2451999999999996</v>
       </c>
       <c r="L72">
-        <v>1.4570000000000001</v>
+        <v>5.2451999999999996</v>
       </c>
       <c r="M72" t="s">
         <v>488</v>
@@ -13296,13 +13296,13 @@
         <v>493</v>
       </c>
       <c r="E79">
-        <v>0.8</v>
+        <v>2.88</v>
       </c>
       <c r="H79">
-        <v>0.8</v>
+        <v>2.88</v>
       </c>
       <c r="L79">
-        <v>0.8</v>
+        <v>2.88</v>
       </c>
       <c r="M79" t="s">
         <v>488</v>
@@ -13510,13 +13510,13 @@
         <v>493</v>
       </c>
       <c r="E87">
-        <v>0.3</v>
+        <v>1.08</v>
       </c>
       <c r="H87">
-        <v>0.3</v>
+        <v>1.08</v>
       </c>
       <c r="L87">
-        <v>0.3</v>
+        <v>1.08</v>
       </c>
       <c r="M87" t="s">
         <v>488</v>
@@ -13678,13 +13678,13 @@
         <v>493</v>
       </c>
       <c r="E93">
-        <v>0.4</v>
+        <v>1.44</v>
       </c>
       <c r="H93">
-        <v>0.4</v>
+        <v>1.44</v>
       </c>
       <c r="L93">
-        <v>0.4</v>
+        <v>1.44</v>
       </c>
       <c r="M93" t="s">
         <v>488</v>
@@ -13793,9 +13793,6 @@
       <c r="B97" t="s">
         <v>509</v>
       </c>
-      <c r="C97" t="s">
-        <v>19</v>
-      </c>
       <c r="D97" t="s">
         <v>493</v>
       </c>
@@ -13822,9 +13819,6 @@
       <c r="B98" t="s">
         <v>509</v>
       </c>
-      <c r="C98" t="s">
-        <v>19</v>
-      </c>
       <c r="D98" t="s">
         <v>493</v>
       </c>
@@ -13851,26 +13845,23 @@
       <c r="B99" t="s">
         <v>509</v>
       </c>
-      <c r="C99" t="s">
-        <v>19</v>
-      </c>
       <c r="D99" t="s">
         <v>493</v>
       </c>
       <c r="G99">
-        <v>0.2</v>
+        <v>0.72</v>
       </c>
       <c r="H99">
-        <v>0.2</v>
+        <v>0.72</v>
       </c>
       <c r="I99">
-        <v>0.2</v>
+        <v>0.72</v>
       </c>
       <c r="J99">
-        <v>0.2</v>
+        <v>0.72</v>
       </c>
       <c r="L99">
-        <v>0.2</v>
+        <v>0.72</v>
       </c>
       <c r="M99" t="s">
         <v>488</v>
@@ -13880,9 +13871,6 @@
       <c r="B100" t="s">
         <v>509</v>
       </c>
-      <c r="C100" t="s">
-        <v>19</v>
-      </c>
       <c r="D100" t="s">
         <v>493</v>
       </c>
@@ -13909,9 +13897,6 @@
       <c r="B101" t="s">
         <v>509</v>
       </c>
-      <c r="C101" t="s">
-        <v>19</v>
-      </c>
       <c r="D101" t="s">
         <v>493</v>
       </c>
@@ -13947,9 +13932,6 @@
       <c r="B102" t="s">
         <v>509</v>
       </c>
-      <c r="C102" t="s">
-        <v>19</v>
-      </c>
       <c r="D102" t="s">
         <v>493</v>
       </c>
@@ -13985,9 +13967,6 @@
       <c r="B103" t="s">
         <v>510</v>
       </c>
-      <c r="C103" t="s">
-        <v>19</v>
-      </c>
       <c r="D103" t="s">
         <v>493</v>
       </c>
@@ -14014,9 +13993,6 @@
       <c r="B104" t="s">
         <v>510</v>
       </c>
-      <c r="C104" t="s">
-        <v>19</v>
-      </c>
       <c r="D104" t="s">
         <v>493</v>
       </c>
@@ -14043,26 +14019,23 @@
       <c r="B105" t="s">
         <v>510</v>
       </c>
-      <c r="C105" t="s">
-        <v>19</v>
-      </c>
       <c r="D105" t="s">
         <v>493</v>
       </c>
       <c r="G105">
-        <v>0.2</v>
+        <v>0.72</v>
       </c>
       <c r="H105">
-        <v>0.2</v>
+        <v>0.72</v>
       </c>
       <c r="I105">
-        <v>0.2</v>
+        <v>0.72</v>
       </c>
       <c r="J105">
-        <v>0.2</v>
+        <v>0.72</v>
       </c>
       <c r="L105">
-        <v>0.2</v>
+        <v>0.72</v>
       </c>
       <c r="M105" t="s">
         <v>488</v>
@@ -14072,9 +14045,6 @@
       <c r="B106" t="s">
         <v>510</v>
       </c>
-      <c r="C106" t="s">
-        <v>19</v>
-      </c>
       <c r="D106" t="s">
         <v>493</v>
       </c>
@@ -14101,9 +14071,6 @@
       <c r="B107" t="s">
         <v>510</v>
       </c>
-      <c r="C107" t="s">
-        <v>19</v>
-      </c>
       <c r="D107" t="s">
         <v>493</v>
       </c>
@@ -14139,9 +14106,6 @@
       <c r="B108" t="s">
         <v>510</v>
       </c>
-      <c r="C108" t="s">
-        <v>19</v>
-      </c>
       <c r="D108" t="s">
         <v>493</v>
       </c>
@@ -14298,28 +14262,28 @@
         <v>512</v>
       </c>
       <c r="E112">
-        <v>1.3</v>
+        <v>4.68</v>
       </c>
       <c r="F112">
-        <v>1.3</v>
+        <v>4.68</v>
       </c>
       <c r="G112">
-        <v>1.3</v>
+        <v>4.68</v>
       </c>
       <c r="H112">
-        <v>1.3</v>
+        <v>4.68</v>
       </c>
       <c r="I112">
-        <v>1.3</v>
+        <v>4.68</v>
       </c>
       <c r="J112">
-        <v>1.3</v>
+        <v>4.68</v>
       </c>
       <c r="K112">
-        <v>1.3</v>
+        <v>4.68</v>
       </c>
       <c r="L112">
-        <v>1.3</v>
+        <v>4.68</v>
       </c>
       <c r="M112" t="s">
         <v>488</v>
@@ -14483,7 +14447,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ADA7E36C-5808-44D3-B950-B101A5D199F2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89D212D2-B450-405B-8DE1-0BC7DCD77741}">
   <dimension ref="B9:T88"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_POL_grids_kan50/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_POL_grids_kan50/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B813692-D8A7-4003-92DE-A9412075EAAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0AFC72A-A955-49A5-9942-31179FBB336B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -862,18 +862,60 @@
     <t>pre</t>
   </si>
   <si>
+    <t>distr_solelc_spv_POL_001</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>NRGI</t>
+  </si>
+  <si>
+    <t>daynite</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_015</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_018</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_005</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_008</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_013</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_004</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 4</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_POL_003</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 3</t>
   </si>
   <si>
-    <t>NRGI</t>
-  </si>
-  <si>
-    <t>daynite</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_POL_007</t>
   </si>
   <si>
@@ -886,10 +928,22 @@
     <t>connecting solar to buses in cluster 16</t>
   </si>
   <si>
-    <t>distr_solelc_spv_POL_008</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 8</t>
+    <t>distr_solelc_spv_POL_006</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_010</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_014</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 14</t>
   </si>
   <si>
     <t>distr_solelc_spv_POL_017</t>
@@ -904,34 +958,16 @@
     <t>connecting solar to buses in cluster 20</t>
   </si>
   <si>
-    <t>distr_solelc_spv_POL_001</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_015</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_018</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_013</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_005</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 5</t>
+    <t>distr_solelc_spv_POL_012</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_011</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 11</t>
   </si>
   <si>
     <t>distr_solelc_spv_POL_002</t>
@@ -952,48 +988,33 @@
     <t>connecting solar to buses in cluster 9</t>
   </si>
   <si>
-    <t>distr_solelc_spv_POL_014</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_006</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_010</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_012</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_011</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_004</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 4</t>
-  </si>
-  <si>
     <t>comm-in</t>
   </si>
   <si>
     <t>ncap_cost~USD21_alt</t>
   </si>
   <si>
+    <t>e_Boleslawiec_POL,e_ZielonaGora_POL</t>
+  </si>
+  <si>
+    <t>e_Sosnowiec_POL,e_KedzierzynKozle_POL,e_Olesnica_POL,e_Gliwice_POL,e_Czestochowa_POL,e_Radomsko_POL,e_PiotrkowTrybunalsk_POL,e_Kielce_POL</t>
+  </si>
+  <si>
+    <t>e_Warsaw_POL,e_Lomza_POL</t>
+  </si>
+  <si>
+    <t>e_Lubin_POL,e_Poznan_POL,e_Koszalin_POL,e_Bydgoszcz_POL</t>
+  </si>
+  <si>
+    <t>e_Bydgoszcz_POL,e_Gdansk_POL,e_Grudziadz_POL,e_Kwidzyn_POL</t>
+  </si>
+  <si>
+    <t>e_Rzeszow_POL,e_Zamosc_POL,e_Pulawy_POL,e_Chelm_POL</t>
+  </si>
+  <si>
+    <t>e_GorzowWielkopolski_POL,e_Szczecin_POL,e_Police_POL</t>
+  </si>
+  <si>
     <t>e_Lubin_POL,e_Swidnica_POL,e_Wroclaw_POL,e_Poznan_POL,e_Olesnica_POL</t>
   </si>
   <si>
@@ -1003,7 +1024,13 @@
     <t>e_Olesnica_POL,e_Konin_POL,e_PiotrkowTrybunalsk_POL,e_Plock_POL</t>
   </si>
   <si>
-    <t>e_Bydgoszcz_POL,e_Gdansk_POL,e_Grudziadz_POL,e_Kwidzyn_POL</t>
+    <t>e_Plock_POL,e_Olsztyn_POL,e_Warsaw_POL</t>
+  </si>
+  <si>
+    <t>e_Elk_POL,e_Grajewo_POL</t>
+  </si>
+  <si>
+    <t>e_BielskoBiala_POL,e_Katowice_POL,e_Krakow_POL,e_Tarnow_POL</t>
   </si>
   <si>
     <t>e_Konin_POL,e_Bydgoszcz_POL,e_Wloclawek_POL,e_Kwidzyn_POL,e_Plock_POL</t>
@@ -1012,19 +1039,10 @@
     <t>e_OstrowiecSwietokrz_POL,e_Pulawy_POL,e_Warsaw_POL</t>
   </si>
   <si>
-    <t>e_Boleslawiec_POL,e_ZielonaGora_POL</t>
-  </si>
-  <si>
-    <t>e_Sosnowiec_POL,e_KedzierzynKozle_POL,e_Olesnica_POL,e_Gliwice_POL,e_Czestochowa_POL,e_Radomsko_POL,e_PiotrkowTrybunalsk_POL,e_Kielce_POL</t>
-  </si>
-  <si>
-    <t>e_Warsaw_POL,e_Lomza_POL</t>
-  </si>
-  <si>
-    <t>e_Rzeszow_POL,e_Zamosc_POL,e_Pulawy_POL,e_Chelm_POL</t>
-  </si>
-  <si>
-    <t>e_Lubin_POL,e_Poznan_POL,e_Koszalin_POL,e_Bydgoszcz_POL</t>
+    <t>e_Krosno_POL,e_Mielec_POL,e_Debica_POL,e_Zamosc_POL</t>
+  </si>
+  <si>
+    <t>e_Lomza_POL,e_Elk_POL,e_Bialystok_POL,e_Grajewo_POL</t>
   </si>
   <si>
     <t>e_Legnica_POL,e_Swidnica_POL,e_KedzierzynKozle_POL,e_Opole_POL</t>
@@ -1036,22 +1054,76 @@
     <t>e_Pulawy_POL,e_Bialystok_POL,e_Chelm_POL</t>
   </si>
   <si>
-    <t>e_BielskoBiala_POL,e_Katowice_POL,e_Krakow_POL,e_Tarnow_POL</t>
-  </si>
-  <si>
-    <t>e_Plock_POL,e_Olsztyn_POL,e_Warsaw_POL</t>
-  </si>
-  <si>
-    <t>e_Elk_POL,e_Grajewo_POL</t>
-  </si>
-  <si>
-    <t>e_Krosno_POL,e_Mielec_POL,e_Debica_POL,e_Zamosc_POL</t>
-  </si>
-  <si>
-    <t>e_Lomza_POL,e_Elk_POL,e_Bialystok_POL,e_Grajewo_POL</t>
-  </si>
-  <si>
-    <t>e_GorzowWielkopolski_POL,e_Szczecin_POL,e_Police_POL</t>
+    <t>distr_wonelc_won_POL_015</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_016</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_005</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_006</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_009</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_004</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_012</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_003</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_019</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_017</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_011</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_010</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 10</t>
   </si>
   <si>
     <t>distr_wonelc_won_POL_014</t>
@@ -1084,94 +1156,91 @@
     <t>connecting wind onshore to buses in cluster 2</t>
   </si>
   <si>
+    <t>distr_wonelc_won_POL_007</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_001</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 1</t>
+  </si>
+  <si>
     <t>distr_wonelc_won_POL_018</t>
   </si>
   <si>
     <t>connecting wind onshore to buses in cluster 18</t>
   </si>
   <si>
-    <t>distr_wonelc_won_POL_015</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_016</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_019</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_017</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_005</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_006</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_009</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_004</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_011</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_010</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_007</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_012</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_003</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_001</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 1</t>
+    <t>elc_won_POL_015</t>
+  </si>
+  <si>
+    <t>e_BielskoBiala_POL,e_Krakow_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_016</t>
+  </si>
+  <si>
+    <t>e_Krosno_POL,e_Debica_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_005</t>
+  </si>
+  <si>
+    <t>e_Lomza_POL,e_Elk_POL,e_Grajewo_POL,e_Bialystok_POL,e_Chelm_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_006</t>
+  </si>
+  <si>
+    <t>e_Olesnica_POL,e_Konin_POL,e_Bydgoszcz_POL,e_Wloclawek_POL,e_Kwidzyn_POL,e_Plock_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_009</t>
+  </si>
+  <si>
+    <t>e_Gdansk_POL,e_Grudziadz_POL,e_Kwidzyn_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_004</t>
+  </si>
+  <si>
+    <t>elc_won_POL_012</t>
+  </si>
+  <si>
+    <t>e_ZielonaGora_POL,e_GorzowWielkopolski_POL,e_Szczecin_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_003</t>
+  </si>
+  <si>
+    <t>e_Warsaw_POL,e_Lomza_POL,e_Pulawy_POL,e_Bialystok_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_019</t>
+  </si>
+  <si>
+    <t>e_Katowice_POL,e_Czestochowa_POL,e_Krakow_POL,e_Kielce_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_017</t>
+  </si>
+  <si>
+    <t>e_Tarnow_POL,e_Krosno_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_011</t>
+  </si>
+  <si>
+    <t>e_Boleslawiec_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_010</t>
+  </si>
+  <si>
+    <t>e_Police_POL,e_Koszalin_POL,e_Poznan_POL,e_Ustka_POL,e_Bydgoszcz_POL,e_Slupsk_POL,e_Gdansk_POL</t>
   </si>
   <si>
     <t>elc_won_POL_014</t>
@@ -1204,91 +1273,70 @@
     <t>e_Tarnow_POL,e_Kielce_POL,e_OstrowiecSwietokrz_POL,e_Mielec_POL,e_Pulawy_POL,e_Rzeszow_POL</t>
   </si>
   <si>
+    <t>elc_won_POL_007</t>
+  </si>
+  <si>
+    <t>e_Warsaw_POL,e_Plock_POL,e_Olsztyn_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_001</t>
+  </si>
+  <si>
+    <t>e_PiotrkowTrybunalsk_POL,e_Kielce_POL,e_Warsaw_POL,e_OstrowiecSwietokrz_POL</t>
+  </si>
+  <si>
     <t>elc_won_POL_018</t>
   </si>
   <si>
     <t>e_Boleslawiec_POL,e_Legnica_POL,e_Swidnica_POL,e_KedzierzynKozle_POL,e_Opole_POL,e_Olesnica_POL</t>
   </si>
   <si>
-    <t>elc_won_POL_015</t>
-  </si>
-  <si>
-    <t>e_BielskoBiala_POL,e_Krakow_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_016</t>
-  </si>
-  <si>
-    <t>e_Krosno_POL,e_Debica_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_019</t>
-  </si>
-  <si>
-    <t>e_Katowice_POL,e_Czestochowa_POL,e_Krakow_POL,e_Kielce_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_017</t>
-  </si>
-  <si>
-    <t>e_Tarnow_POL,e_Krosno_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_005</t>
-  </si>
-  <si>
-    <t>e_Lomza_POL,e_Elk_POL,e_Grajewo_POL,e_Bialystok_POL,e_Chelm_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_006</t>
-  </si>
-  <si>
-    <t>e_Olesnica_POL,e_Konin_POL,e_Bydgoszcz_POL,e_Wloclawek_POL,e_Kwidzyn_POL,e_Plock_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_009</t>
-  </si>
-  <si>
-    <t>e_Gdansk_POL,e_Grudziadz_POL,e_Kwidzyn_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_004</t>
-  </si>
-  <si>
-    <t>elc_won_POL_011</t>
-  </si>
-  <si>
-    <t>e_Boleslawiec_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_010</t>
-  </si>
-  <si>
-    <t>e_Police_POL,e_Koszalin_POL,e_Poznan_POL,e_Ustka_POL,e_Bydgoszcz_POL,e_Slupsk_POL,e_Gdansk_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_007</t>
-  </si>
-  <si>
-    <t>e_Warsaw_POL,e_Plock_POL,e_Olsztyn_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_012</t>
-  </si>
-  <si>
-    <t>e_ZielonaGora_POL,e_GorzowWielkopolski_POL,e_Szczecin_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_003</t>
-  </si>
-  <si>
-    <t>e_Warsaw_POL,e_Lomza_POL,e_Pulawy_POL,e_Bialystok_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_001</t>
-  </si>
-  <si>
-    <t>e_PiotrkowTrybunalsk_POL,e_Kielce_POL,e_Warsaw_POL,e_OstrowiecSwietokrz_POL</t>
+    <t>distr_wofelc_wof_POL_003</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_POL_005</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_POL_001</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_POL_006</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_POL_002</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_POL_004</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_POL_010</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_POL_009</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 9</t>
   </si>
   <si>
     <t>distr_wofelc_wof_POL_008</t>
@@ -1303,52 +1351,46 @@
     <t>connecting wind offshore to buses in cluster 7</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_POL_005</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_POL_001</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_POL_006</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_POL_002</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_POL_003</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_POL_004</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_POL_010</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_POL_009</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 9</t>
+    <t>elc_wof_POL_003</t>
+  </si>
+  <si>
+    <t>e_Gdansk_POL</t>
+  </si>
+  <si>
+    <t>elc_wof_POL_005</t>
+  </si>
+  <si>
+    <t>e_Gdynia_POL</t>
+  </si>
+  <si>
+    <t>elc_wof_POL_001</t>
+  </si>
+  <si>
+    <t>elc_wof_POL_006</t>
+  </si>
+  <si>
+    <t>elc_wof_POL_002</t>
+  </si>
+  <si>
+    <t>e_Gdynia_POL,e_Gdansk_POL</t>
+  </si>
+  <si>
+    <t>elc_wof_POL_004</t>
+  </si>
+  <si>
+    <t>e_Ustka_POL,e_Gdynia_POL</t>
+  </si>
+  <si>
+    <t>elc_wof_POL_010</t>
+  </si>
+  <si>
+    <t>e_Koszalin_POL</t>
+  </si>
+  <si>
+    <t>elc_wof_POL_009</t>
+  </si>
+  <si>
+    <t>e_Koszalin_POL,e_Ustka_POL</t>
   </si>
   <si>
     <t>elc_wof_POL_008</t>
@@ -1358,48 +1400,6 @@
   </si>
   <si>
     <t>elc_wof_POL_007</t>
-  </si>
-  <si>
-    <t>e_Koszalin_POL</t>
-  </si>
-  <si>
-    <t>elc_wof_POL_005</t>
-  </si>
-  <si>
-    <t>e_Gdynia_POL</t>
-  </si>
-  <si>
-    <t>elc_wof_POL_001</t>
-  </si>
-  <si>
-    <t>e_Gdansk_POL</t>
-  </si>
-  <si>
-    <t>elc_wof_POL_006</t>
-  </si>
-  <si>
-    <t>elc_wof_POL_002</t>
-  </si>
-  <si>
-    <t>e_Gdynia_POL,e_Gdansk_POL</t>
-  </si>
-  <si>
-    <t>elc_wof_POL_003</t>
-  </si>
-  <si>
-    <t>elc_wof_POL_004</t>
-  </si>
-  <si>
-    <t>e_Ustka_POL,e_Gdynia_POL</t>
-  </si>
-  <si>
-    <t>elc_wof_POL_010</t>
-  </si>
-  <si>
-    <t>elc_wof_POL_009</t>
-  </si>
-  <si>
-    <t>e_Koszalin_POL,e_Ustka_POL</t>
   </si>
   <si>
     <t>e_won_POL_001</t>
@@ -7135,7 +7135,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B57F7170-5D0A-43B5-B761-B700C5E67318}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{40DA0342-EF45-45DF-996D-024CA02BFD88}">
   <dimension ref="B9:BD30"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -7373,16 +7373,16 @@
         <v>244</v>
       </c>
       <c r="Y11" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="Z11" t="s">
         <v>288</v>
       </c>
       <c r="AA11">
-        <v>0.99770934816564383</v>
+        <v>0.99707401400885998</v>
       </c>
       <c r="AB11">
-        <v>41.995283629862939</v>
+        <v>53.643076504234422</v>
       </c>
       <c r="AD11" t="s">
         <v>243</v>
@@ -7415,10 +7415,10 @@
         <v>349</v>
       </c>
       <c r="AO11">
-        <v>0.99730422320290779</v>
+        <v>0.99641308487583879</v>
       </c>
       <c r="AP11">
-        <v>49.422574613357185</v>
+        <v>65.760110609622657</v>
       </c>
       <c r="AR11" t="s">
         <v>243</v>
@@ -7451,10 +7451,10 @@
         <v>408</v>
       </c>
       <c r="BC11">
-        <v>0.99383352379209899</v>
+        <v>0.99564787435456037</v>
       </c>
       <c r="BD11">
-        <v>758.43022352327353</v>
+        <v>622.95871485949408</v>
       </c>
     </row>
     <row r="12" spans="2:56">
@@ -7519,16 +7519,16 @@
         <v>248</v>
       </c>
       <c r="Y12" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="Z12" t="s">
         <v>289</v>
       </c>
       <c r="AA12">
-        <v>0.9970292559096442</v>
+        <v>0.99826037700975512</v>
       </c>
       <c r="AB12">
-        <v>54.463641656523762</v>
+        <v>31.893088154488542</v>
       </c>
       <c r="AD12" t="s">
         <v>243</v>
@@ -7561,10 +7561,10 @@
         <v>351</v>
       </c>
       <c r="AO12">
-        <v>0.99805709209211746</v>
+        <v>0.99449756685866841</v>
       </c>
       <c r="AP12">
-        <v>35.619978311179104</v>
+        <v>100.87794092441324</v>
       </c>
       <c r="AR12" t="s">
         <v>243</v>
@@ -7597,10 +7597,10 @@
         <v>410</v>
       </c>
       <c r="BC12">
-        <v>0.99603306101923861</v>
+        <v>0.99328660064428831</v>
       </c>
       <c r="BD12">
-        <v>594.19811056351818</v>
+        <v>799.26715189313825</v>
       </c>
     </row>
     <row r="13" spans="2:56">
@@ -7665,16 +7665,16 @@
         <v>250</v>
       </c>
       <c r="Y13" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="Z13" t="s">
         <v>290</v>
       </c>
       <c r="AA13">
-        <v>0.9982126095160021</v>
+        <v>0.99922515067657613</v>
       </c>
       <c r="AB13">
-        <v>32.768825539961391</v>
+        <v>14.205570929438155</v>
       </c>
       <c r="AD13" t="s">
         <v>243</v>
@@ -7707,10 +7707,10 @@
         <v>353</v>
       </c>
       <c r="AO13">
-        <v>0.99883902037019667</v>
+        <v>0.9963019969989696</v>
       </c>
       <c r="AP13">
-        <v>21.284626546395259</v>
+        <v>67.796721685557472</v>
       </c>
       <c r="AR13" t="s">
         <v>243</v>
@@ -7740,13 +7740,13 @@
         <v>411</v>
       </c>
       <c r="BB13" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="BC13">
-        <v>0.99328660064428831</v>
+        <v>0.99644441082752833</v>
       </c>
       <c r="BD13">
-        <v>799.26715189313825</v>
+        <v>563.48399154455342</v>
       </c>
     </row>
     <row r="14" spans="2:56">
@@ -7811,16 +7811,16 @@
         <v>252</v>
       </c>
       <c r="Y14" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="Z14" t="s">
         <v>291</v>
       </c>
       <c r="AA14">
-        <v>0.99693515631487983</v>
+        <v>0.99730738889353909</v>
       </c>
       <c r="AB14">
-        <v>56.188800893869058</v>
+        <v>49.364536951784054</v>
       </c>
       <c r="AD14" t="s">
         <v>243</v>
@@ -7853,10 +7853,10 @@
         <v>355</v>
       </c>
       <c r="AO14">
-        <v>0.99521984547821263</v>
+        <v>0.99827231256984739</v>
       </c>
       <c r="AP14">
-        <v>87.636166232768815</v>
+        <v>31.674269552798414</v>
       </c>
       <c r="AR14" t="s">
         <v>243</v>
@@ -7883,16 +7883,16 @@
         <v>393</v>
       </c>
       <c r="BA14" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="BB14" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="BC14">
-        <v>0.99644441082752833</v>
+        <v>0.99615739524125424</v>
       </c>
       <c r="BD14">
-        <v>563.48399154455342</v>
+        <v>584.91448865302027</v>
       </c>
     </row>
     <row r="15" spans="2:56">
@@ -7957,16 +7957,16 @@
         <v>254</v>
       </c>
       <c r="Y15" t="s">
-        <v>238</v>
+        <v>229</v>
       </c>
       <c r="Z15" t="s">
         <v>292</v>
       </c>
       <c r="AA15">
-        <v>0.99930490342600053</v>
+        <v>0.99693515631487983</v>
       </c>
       <c r="AB15">
-        <v>12.743437189989784</v>
+        <v>56.188800893869058</v>
       </c>
       <c r="AD15" t="s">
         <v>243</v>
@@ -7999,10 +7999,10 @@
         <v>357</v>
       </c>
       <c r="AO15">
-        <v>0.99845791964146047</v>
+        <v>0.99635146162488653</v>
       </c>
       <c r="AP15">
-        <v>28.2714732398913</v>
+        <v>66.889870210414614</v>
       </c>
       <c r="AR15" t="s">
         <v>243</v>
@@ -8029,16 +8029,16 @@
         <v>395</v>
       </c>
       <c r="BA15" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="BB15" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="BC15">
-        <v>0.99615739524125424</v>
+        <v>0.99353721168226494</v>
       </c>
       <c r="BD15">
-        <v>584.91448865302027</v>
+        <v>780.55486105754892</v>
       </c>
     </row>
     <row r="16" spans="2:56">
@@ -8103,16 +8103,16 @@
         <v>256</v>
       </c>
       <c r="Y16" t="s">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="Z16" t="s">
         <v>293</v>
       </c>
       <c r="AA16">
-        <v>0.99881801309037566</v>
+        <v>0.99606480786442353</v>
       </c>
       <c r="AB16">
-        <v>21.669760009780138</v>
+        <v>72.145189152235062</v>
       </c>
       <c r="AD16" t="s">
         <v>243</v>
@@ -8142,13 +8142,13 @@
         <v>358</v>
       </c>
       <c r="AN16" t="s">
-        <v>359</v>
+        <v>293</v>
       </c>
       <c r="AO16">
-        <v>0.99622969699231045</v>
+        <v>0.99586212495478665</v>
       </c>
       <c r="AP16">
-        <v>69.122221807641537</v>
+        <v>75.861042495577635</v>
       </c>
       <c r="AR16" t="s">
         <v>243</v>
@@ -8175,16 +8175,16 @@
         <v>397</v>
       </c>
       <c r="BA16" t="s">
+        <v>415</v>
+      </c>
+      <c r="BB16" t="s">
         <v>416</v>
       </c>
-      <c r="BB16" t="s">
-        <v>417</v>
-      </c>
       <c r="BC16">
-        <v>0.99353721168226494</v>
+        <v>0.99255663966463281</v>
       </c>
       <c r="BD16">
-        <v>780.55486105754892</v>
+        <v>853.77090504074806</v>
       </c>
     </row>
     <row r="17" spans="2:56">
@@ -8249,16 +8249,16 @@
         <v>258</v>
       </c>
       <c r="Y17" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="Z17" t="s">
         <v>294</v>
       </c>
       <c r="AA17">
-        <v>0.99707401400885998</v>
+        <v>0.99785589517057005</v>
       </c>
       <c r="AB17">
-        <v>53.643076504234422</v>
+        <v>39.308588539549028</v>
       </c>
       <c r="AD17" t="s">
         <v>243</v>
@@ -8285,16 +8285,16 @@
         <v>320</v>
       </c>
       <c r="AM17" t="s">
+        <v>359</v>
+      </c>
+      <c r="AN17" t="s">
         <v>360</v>
       </c>
-      <c r="AN17" t="s">
-        <v>361</v>
-      </c>
       <c r="AO17">
-        <v>0.99641308487583879</v>
+        <v>0.99749126227646956</v>
       </c>
       <c r="AP17">
-        <v>65.760110609622657</v>
+        <v>45.993524931390482</v>
       </c>
       <c r="AR17" t="s">
         <v>243</v>
@@ -8321,16 +8321,16 @@
         <v>399</v>
       </c>
       <c r="BA17" t="s">
+        <v>417</v>
+      </c>
+      <c r="BB17" t="s">
         <v>418</v>
       </c>
-      <c r="BB17" t="s">
-        <v>414</v>
-      </c>
       <c r="BC17">
-        <v>0.99564787435456037</v>
+        <v>0.99608994650263638</v>
       </c>
       <c r="BD17">
-        <v>622.95871485949408</v>
+        <v>589.950661136485</v>
       </c>
     </row>
     <row r="18" spans="2:56">
@@ -8395,16 +8395,16 @@
         <v>260</v>
       </c>
       <c r="Y18" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="Z18" t="s">
         <v>295</v>
       </c>
       <c r="AA18">
-        <v>0.99826037700975512</v>
+        <v>0.99770934816564383</v>
       </c>
       <c r="AB18">
-        <v>31.893088154488542</v>
+        <v>41.995283629862939</v>
       </c>
       <c r="AD18" t="s">
         <v>243</v>
@@ -8431,16 +8431,16 @@
         <v>322</v>
       </c>
       <c r="AM18" t="s">
+        <v>361</v>
+      </c>
+      <c r="AN18" t="s">
         <v>362</v>
       </c>
-      <c r="AN18" t="s">
-        <v>363</v>
-      </c>
       <c r="AO18">
-        <v>0.99449756685866841</v>
+        <v>0.99807543246352515</v>
       </c>
       <c r="AP18">
-        <v>100.87794092441324</v>
+        <v>35.283738168705199</v>
       </c>
       <c r="AR18" t="s">
         <v>243</v>
@@ -8473,10 +8473,10 @@
         <v>420</v>
       </c>
       <c r="BC18">
-        <v>0.99255663966463281</v>
+        <v>0.99399682431672776</v>
       </c>
       <c r="BD18">
-        <v>853.77090504074806</v>
+        <v>746.2371176843244</v>
       </c>
     </row>
     <row r="19" spans="2:56">
@@ -8541,16 +8541,16 @@
         <v>262</v>
       </c>
       <c r="Y19" t="s">
-        <v>239</v>
+        <v>228</v>
       </c>
       <c r="Z19" t="s">
         <v>296</v>
       </c>
       <c r="AA19">
-        <v>0.99922515067657613</v>
+        <v>0.9970292559096442</v>
       </c>
       <c r="AB19">
-        <v>14.205570929438155</v>
+        <v>54.463641656523762</v>
       </c>
       <c r="AD19" t="s">
         <v>243</v>
@@ -8577,10 +8577,10 @@
         <v>324</v>
       </c>
       <c r="AM19" t="s">
+        <v>363</v>
+      </c>
+      <c r="AN19" t="s">
         <v>364</v>
-      </c>
-      <c r="AN19" t="s">
-        <v>365</v>
       </c>
       <c r="AO19">
         <v>0.99872641243407079</v>
@@ -8616,13 +8616,13 @@
         <v>421</v>
       </c>
       <c r="BB19" t="s">
-        <v>410</v>
+        <v>422</v>
       </c>
       <c r="BC19">
-        <v>0.99608994650263638</v>
+        <v>0.99383352379209899</v>
       </c>
       <c r="BD19">
-        <v>589.950661136485</v>
+        <v>758.43022352327353</v>
       </c>
     </row>
     <row r="20" spans="2:56">
@@ -8687,16 +8687,16 @@
         <v>264</v>
       </c>
       <c r="Y20" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="Z20" t="s">
         <v>297</v>
       </c>
       <c r="AA20">
-        <v>0.99606480786442353</v>
+        <v>0.9982126095160021</v>
       </c>
       <c r="AB20">
-        <v>72.145189152235062</v>
+        <v>32.768825539961391</v>
       </c>
       <c r="AD20" t="s">
         <v>243</v>
@@ -8723,10 +8723,10 @@
         <v>326</v>
       </c>
       <c r="AM20" t="s">
+        <v>365</v>
+      </c>
+      <c r="AN20" t="s">
         <v>366</v>
-      </c>
-      <c r="AN20" t="s">
-        <v>367</v>
       </c>
       <c r="AO20">
         <v>0.99776911581804295</v>
@@ -8759,16 +8759,16 @@
         <v>405</v>
       </c>
       <c r="BA20" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="BB20" t="s">
-        <v>423</v>
+        <v>418</v>
       </c>
       <c r="BC20">
-        <v>0.99399682431672776</v>
+        <v>0.99603306101923861</v>
       </c>
       <c r="BD20">
-        <v>746.2371176843244</v>
+        <v>594.19811056351818</v>
       </c>
     </row>
     <row r="21" spans="2:56">
@@ -8833,16 +8833,16 @@
         <v>266</v>
       </c>
       <c r="Y21" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Z21" t="s">
         <v>298</v>
       </c>
       <c r="AA21">
-        <v>0.99730738889353909</v>
+        <v>0.99658775492800411</v>
       </c>
       <c r="AB21">
-        <v>49.364536951784054</v>
+        <v>62.557826319923819</v>
       </c>
       <c r="AD21" t="s">
         <v>243</v>
@@ -8869,16 +8869,16 @@
         <v>328</v>
       </c>
       <c r="AM21" t="s">
+        <v>367</v>
+      </c>
+      <c r="AN21" t="s">
         <v>368</v>
       </c>
-      <c r="AN21" t="s">
-        <v>369</v>
-      </c>
       <c r="AO21">
-        <v>0.9963019969989696</v>
+        <v>0.99802303154782224</v>
       </c>
       <c r="AP21">
-        <v>67.796721685557472</v>
+        <v>36.244421623259619</v>
       </c>
     </row>
     <row r="22" spans="2:56">
@@ -8943,16 +8943,16 @@
         <v>268</v>
       </c>
       <c r="Y22" t="s">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="Z22" t="s">
         <v>299</v>
       </c>
       <c r="AA22">
-        <v>0.99515616506526205</v>
+        <v>0.99510886326373238</v>
       </c>
       <c r="AB22">
-        <v>88.803640470195262</v>
+        <v>89.670840164906522</v>
       </c>
       <c r="AD22" t="s">
         <v>243</v>
@@ -8979,16 +8979,16 @@
         <v>330</v>
       </c>
       <c r="AM22" t="s">
+        <v>369</v>
+      </c>
+      <c r="AN22" t="s">
         <v>370</v>
       </c>
-      <c r="AN22" t="s">
-        <v>371</v>
-      </c>
       <c r="AO22">
-        <v>0.99827231256984739</v>
+        <v>0.99714358927215652</v>
       </c>
       <c r="AP22">
-        <v>31.674269552798414</v>
+        <v>52.367530010463909</v>
       </c>
     </row>
     <row r="23" spans="2:56">
@@ -9053,16 +9053,16 @@
         <v>270</v>
       </c>
       <c r="Y23" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="Z23" t="s">
         <v>300</v>
       </c>
       <c r="AA23">
-        <v>0.99728872234103139</v>
+        <v>0.99790408176624201</v>
       </c>
       <c r="AB23">
-        <v>49.70675708109188</v>
+        <v>38.425167618896296</v>
       </c>
       <c r="AD23" t="s">
         <v>243</v>
@@ -9089,16 +9089,16 @@
         <v>332</v>
       </c>
       <c r="AM23" t="s">
+        <v>371</v>
+      </c>
+      <c r="AN23" t="s">
         <v>372</v>
       </c>
-      <c r="AN23" t="s">
-        <v>373</v>
-      </c>
       <c r="AO23">
-        <v>0.99635146162488653</v>
+        <v>0.99730422320290779</v>
       </c>
       <c r="AP23">
-        <v>66.889870210414614</v>
+        <v>49.422574613357185</v>
       </c>
     </row>
     <row r="24" spans="2:56">
@@ -9163,16 +9163,16 @@
         <v>272</v>
       </c>
       <c r="Y24" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="Z24" t="s">
         <v>301</v>
       </c>
       <c r="AA24">
-        <v>0.99583567586599486</v>
+        <v>0.99930490342600053</v>
       </c>
       <c r="AB24">
-        <v>76.34594245676044</v>
+        <v>12.743437189989784</v>
       </c>
       <c r="AD24" t="s">
         <v>243</v>
@@ -9199,16 +9199,16 @@
         <v>334</v>
       </c>
       <c r="AM24" t="s">
+        <v>373</v>
+      </c>
+      <c r="AN24" t="s">
         <v>374</v>
       </c>
-      <c r="AN24" t="s">
-        <v>297</v>
-      </c>
       <c r="AO24">
-        <v>0.99586212495478665</v>
+        <v>0.99805709209211746</v>
       </c>
       <c r="AP24">
-        <v>75.861042495577635</v>
+        <v>35.619978311179104</v>
       </c>
     </row>
     <row r="25" spans="2:56">
@@ -9273,16 +9273,16 @@
         <v>274</v>
       </c>
       <c r="Y25" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="Z25" t="s">
         <v>302</v>
       </c>
       <c r="AA25">
-        <v>0.99790408176624201</v>
+        <v>0.99881801309037566</v>
       </c>
       <c r="AB25">
-        <v>38.425167618896296</v>
+        <v>21.669760009780138</v>
       </c>
       <c r="AD25" t="s">
         <v>243</v>
@@ -9315,10 +9315,10 @@
         <v>376</v>
       </c>
       <c r="AO25">
-        <v>0.99802303154782224</v>
+        <v>0.99883902037019667</v>
       </c>
       <c r="AP25">
-        <v>36.244421623259619</v>
+        <v>21.284626546395259</v>
       </c>
     </row>
     <row r="26" spans="2:56">
@@ -9383,16 +9383,16 @@
         <v>276</v>
       </c>
       <c r="Y26" t="s">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="Z26" t="s">
         <v>303</v>
       </c>
       <c r="AA26">
-        <v>0.99658775492800411</v>
+        <v>0.99481478101166732</v>
       </c>
       <c r="AB26">
-        <v>62.557826319923819</v>
+        <v>95.062348119433295</v>
       </c>
       <c r="AD26" t="s">
         <v>243</v>
@@ -9425,10 +9425,10 @@
         <v>378</v>
       </c>
       <c r="AO26">
-        <v>0.99714358927215652</v>
+        <v>0.99521984547821263</v>
       </c>
       <c r="AP26">
-        <v>52.367530010463909</v>
+        <v>87.636166232768815</v>
       </c>
     </row>
     <row r="27" spans="2:56">
@@ -9493,16 +9493,16 @@
         <v>278</v>
       </c>
       <c r="Y27" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Z27" t="s">
         <v>304</v>
       </c>
       <c r="AA27">
-        <v>0.99510886326373238</v>
+        <v>0.99681878296180493</v>
       </c>
       <c r="AB27">
-        <v>89.670840164906522</v>
+        <v>58.322312366909152</v>
       </c>
       <c r="AD27" t="s">
         <v>243</v>
@@ -9535,10 +9535,10 @@
         <v>380</v>
       </c>
       <c r="AO27">
-        <v>0.99653588726932718</v>
+        <v>0.99845791964146047</v>
       </c>
       <c r="AP27">
-        <v>63.508733395668145</v>
+        <v>28.2714732398913</v>
       </c>
     </row>
     <row r="28" spans="2:56">
@@ -9603,16 +9603,16 @@
         <v>280</v>
       </c>
       <c r="Y28" t="s">
-        <v>233</v>
+        <v>223</v>
       </c>
       <c r="Z28" t="s">
         <v>305</v>
       </c>
       <c r="AA28">
-        <v>0.99481478101166732</v>
+        <v>0.99515616506526205</v>
       </c>
       <c r="AB28">
-        <v>95.062348119433295</v>
+        <v>88.803640470195262</v>
       </c>
       <c r="AD28" t="s">
         <v>243</v>
@@ -9645,10 +9645,10 @@
         <v>382</v>
       </c>
       <c r="AO28">
-        <v>0.99749126227646956</v>
+        <v>0.99653588726932718</v>
       </c>
       <c r="AP28">
-        <v>45.993524931390482</v>
+        <v>63.508733395668145</v>
       </c>
     </row>
     <row r="29" spans="2:56">
@@ -9713,16 +9713,16 @@
         <v>282</v>
       </c>
       <c r="Y29" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="Z29" t="s">
         <v>306</v>
       </c>
       <c r="AA29">
-        <v>0.99681878296180493</v>
+        <v>0.99728872234103139</v>
       </c>
       <c r="AB29">
-        <v>58.322312366909152</v>
+        <v>49.70675708109188</v>
       </c>
       <c r="AD29" t="s">
         <v>243</v>
@@ -9755,10 +9755,10 @@
         <v>384</v>
       </c>
       <c r="AO29">
-        <v>0.99807543246352515</v>
+        <v>0.99871360797890252</v>
       </c>
       <c r="AP29">
-        <v>35.283738168705199</v>
+        <v>23.583853720120768</v>
       </c>
     </row>
     <row r="30" spans="2:56">
@@ -9823,16 +9823,16 @@
         <v>284</v>
       </c>
       <c r="Y30" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="Z30" t="s">
         <v>307</v>
       </c>
       <c r="AA30">
-        <v>0.99785589517057005</v>
+        <v>0.99583567586599486</v>
       </c>
       <c r="AB30">
-        <v>39.308588539549028</v>
+        <v>76.34594245676044</v>
       </c>
       <c r="AD30" t="s">
         <v>243</v>
@@ -9865,10 +9865,10 @@
         <v>386</v>
       </c>
       <c r="AO30">
-        <v>0.99871360797890252</v>
+        <v>0.99622969699231045</v>
       </c>
       <c r="AP30">
-        <v>23.583853720120768</v>
+        <v>69.122221807641537</v>
       </c>
     </row>
   </sheetData>
@@ -9877,7 +9877,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26482C15-15A6-45C8-AADF-A88379AB76DF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C7FE5C4-0098-464F-BFFD-C1BC75F7DE8D}">
   <dimension ref="B9:Z30"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -9989,7 +9989,7 @@
         <v>424</v>
       </c>
       <c r="K11" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="L11">
         <v>0.30278350605008381</v>
@@ -10022,7 +10022,7 @@
         <v>464</v>
       </c>
       <c r="X11" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="Y11">
         <v>0.83925000000000005</v>
@@ -10057,7 +10057,7 @@
         <v>426</v>
       </c>
       <c r="K12" t="s">
-        <v>356</v>
+        <v>379</v>
       </c>
       <c r="L12">
         <v>0.42035497786033621</v>
@@ -10090,7 +10090,7 @@
         <v>466</v>
       </c>
       <c r="X12" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="Y12">
         <v>16.887</v>
@@ -10125,7 +10125,7 @@
         <v>428</v>
       </c>
       <c r="K13" t="s">
-        <v>383</v>
+        <v>361</v>
       </c>
       <c r="L13">
         <v>1.6077871713950227</v>
@@ -10158,7 +10158,7 @@
         <v>468</v>
       </c>
       <c r="X13" t="s">
-        <v>418</v>
+        <v>407</v>
       </c>
       <c r="Y13">
         <v>11.2965</v>
@@ -10193,7 +10193,7 @@
         <v>430</v>
       </c>
       <c r="K14" t="s">
-        <v>374</v>
+        <v>358</v>
       </c>
       <c r="L14">
         <v>2.531891424764753</v>
@@ -10226,7 +10226,7 @@
         <v>470</v>
       </c>
       <c r="X14" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="Y14">
         <v>6.6577500000000001</v>
@@ -10261,7 +10261,7 @@
         <v>432</v>
       </c>
       <c r="K15" t="s">
-        <v>368</v>
+        <v>352</v>
       </c>
       <c r="L15">
         <v>7.6497810049421515</v>
@@ -10294,7 +10294,7 @@
         <v>472</v>
       </c>
       <c r="X15" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="Y15">
         <v>17.089500000000001</v>
@@ -10329,7 +10329,7 @@
         <v>434</v>
       </c>
       <c r="K16" t="s">
-        <v>370</v>
+        <v>354</v>
       </c>
       <c r="L16">
         <v>0.60733325583919984</v>
@@ -10362,7 +10362,7 @@
         <v>474</v>
       </c>
       <c r="X16" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="Y16">
         <v>8.8230000000000004</v>
@@ -10397,7 +10397,7 @@
         <v>436</v>
       </c>
       <c r="K17" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="L17">
         <v>0.78389041837100704</v>
@@ -10430,7 +10430,7 @@
         <v>476</v>
       </c>
       <c r="X17" t="s">
-        <v>409</v>
+        <v>423</v>
       </c>
       <c r="Y17">
         <v>0.22650000000000001</v>
@@ -10465,7 +10465,7 @@
         <v>438</v>
       </c>
       <c r="K18" t="s">
-        <v>354</v>
+        <v>377</v>
       </c>
       <c r="L18">
         <v>3.0365724666245324</v>
@@ -10498,7 +10498,7 @@
         <v>478</v>
       </c>
       <c r="X18" t="s">
-        <v>407</v>
+        <v>421</v>
       </c>
       <c r="Y18">
         <v>9.5062499999999996</v>
@@ -10533,7 +10533,7 @@
         <v>440</v>
       </c>
       <c r="K19" t="s">
-        <v>372</v>
+        <v>356</v>
       </c>
       <c r="L19">
         <v>0.22970161230087291</v>
@@ -10566,7 +10566,7 @@
         <v>480</v>
       </c>
       <c r="X19" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="Y19">
         <v>13.37175</v>
@@ -10601,7 +10601,7 @@
         <v>442</v>
       </c>
       <c r="K20" t="s">
-        <v>377</v>
+        <v>369</v>
       </c>
       <c r="L20">
         <v>0.27066515065379043</v>
@@ -10634,7 +10634,7 @@
         <v>482</v>
       </c>
       <c r="X20" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="Y20">
         <v>3.9427500000000002</v>
@@ -10669,7 +10669,7 @@
         <v>444</v>
       </c>
       <c r="K21" t="s">
-        <v>375</v>
+        <v>367</v>
       </c>
       <c r="L21">
         <v>0.32193208719379746</v>
@@ -10704,7 +10704,7 @@
         <v>446</v>
       </c>
       <c r="K22" t="s">
-        <v>381</v>
+        <v>359</v>
       </c>
       <c r="L22">
         <v>0.6573344927201471</v>
@@ -10739,7 +10739,7 @@
         <v>448</v>
       </c>
       <c r="K23" t="s">
-        <v>352</v>
+        <v>375</v>
       </c>
       <c r="L23">
         <v>0.28992997651770519</v>
@@ -10774,7 +10774,7 @@
         <v>450</v>
       </c>
       <c r="K24" t="s">
-        <v>348</v>
+        <v>371</v>
       </c>
       <c r="L24">
         <v>0.74609319967150689</v>
@@ -10809,7 +10809,7 @@
         <v>452</v>
       </c>
       <c r="K25" t="s">
-        <v>360</v>
+        <v>348</v>
       </c>
       <c r="L25">
         <v>0.35328950844501877</v>
@@ -10844,7 +10844,7 @@
         <v>454</v>
       </c>
       <c r="K26" t="s">
-        <v>362</v>
+        <v>350</v>
       </c>
       <c r="L26">
         <v>0.7924639655878376</v>
@@ -10879,7 +10879,7 @@
         <v>456</v>
       </c>
       <c r="K27" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="L27">
         <v>0.55411362221124194</v>
@@ -10914,7 +10914,7 @@
         <v>458</v>
       </c>
       <c r="K28" t="s">
-        <v>358</v>
+        <v>385</v>
       </c>
       <c r="L28">
         <v>1.4327274230737423</v>
@@ -10949,7 +10949,7 @@
         <v>460</v>
       </c>
       <c r="K29" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="L29">
         <v>0.56742801517356967</v>
@@ -10984,7 +10984,7 @@
         <v>462</v>
       </c>
       <c r="K30" t="s">
-        <v>350</v>
+        <v>373</v>
       </c>
       <c r="L30">
         <v>0.35405891742987328</v>
@@ -10999,7 +10999,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{054D1DD9-6C63-451C-A696-99D7476CB73A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F61CB38B-5814-4A86-86F9-8ED0DD3CC4E7}">
   <dimension ref="B9:U116"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -14447,7 +14447,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89D212D2-B450-405B-8DE1-0BC7DCD77741}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4BC157C-B24D-4829-9E0A-46EA44051D03}">
   <dimension ref="B9:T88"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_POL_grids_kan50/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_POL_grids_kan50/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95CD94EA-E715-4CD0-B8DA-8E3DEC52DF36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6886E1BB-D2D6-4A9C-AC34-BA4334CB1883}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2794" uniqueCount="725">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2816" uniqueCount="745">
   <si>
     <t>~FI_Process</t>
   </si>
@@ -711,18 +711,96 @@
     <t>pre</t>
   </si>
   <si>
+    <t>distr_solelc_spv_POL_008</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>NRGI</t>
+  </si>
+  <si>
+    <t>daynite</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_013</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_004</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_002</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_019</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_009</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_012</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_011</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_003</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_007</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_016</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_006</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_010</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 10</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_POL_001</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 1</t>
   </si>
   <si>
-    <t>NRGI</t>
-  </si>
-  <si>
-    <t>daynite</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_POL_015</t>
   </si>
   <si>
@@ -735,22 +813,10 @@
     <t>connecting solar to buses in cluster 18</t>
   </si>
   <si>
-    <t>distr_solelc_spv_POL_008</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_006</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_010</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 10</t>
+    <t>distr_solelc_spv_POL_005</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 5</t>
   </si>
   <si>
     <t>distr_solelc_spv_POL_014</t>
@@ -759,72 +825,6 @@
     <t>connecting solar to buses in cluster 14</t>
   </si>
   <si>
-    <t>distr_solelc_spv_POL_012</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_011</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_002</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_019</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_009</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_013</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_004</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_005</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_003</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_007</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_016</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 16</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_POL_017</t>
   </si>
   <si>
@@ -843,6 +843,45 @@
     <t>ncap_cost~USD21_alt</t>
   </si>
   <si>
+    <t>e_Bydgoszcz_POL,e_Gdansk_POL,e_Grudziadz_POL,e_Kwidzyn_POL</t>
+  </si>
+  <si>
+    <t>e_Rzeszow_POL,e_Zamosc_POL,e_Pulawy_POL,e_Chelm_POL</t>
+  </si>
+  <si>
+    <t>e_GorzowWielkopolski_POL,e_Szczecin_POL,e_Police_POL</t>
+  </si>
+  <si>
+    <t>e_Legnica_POL,e_Swidnica_POL,e_KedzierzynKozle_POL,e_Opole_POL</t>
+  </si>
+  <si>
+    <t>e_Kielce_POL,e_Warsaw_POL,e_OstrowiecSwietokrz_POL</t>
+  </si>
+  <si>
+    <t>e_Pulawy_POL,e_Bialystok_POL,e_Chelm_POL</t>
+  </si>
+  <si>
+    <t>e_Krosno_POL,e_Mielec_POL,e_Debica_POL,e_Zamosc_POL</t>
+  </si>
+  <si>
+    <t>e_Lomza_POL,e_Elk_POL,e_Bialystok_POL,e_Grajewo_POL</t>
+  </si>
+  <si>
+    <t>e_Lubin_POL,e_Swidnica_POL,e_Wroclaw_POL,e_Poznan_POL,e_Olesnica_POL</t>
+  </si>
+  <si>
+    <t>e_Koszalin_POL,e_Ustka_POL,e_Slupsk_POL</t>
+  </si>
+  <si>
+    <t>e_Olesnica_POL,e_Konin_POL,e_PiotrkowTrybunalsk_POL,e_Plock_POL</t>
+  </si>
+  <si>
+    <t>e_Plock_POL,e_Olsztyn_POL,e_Warsaw_POL</t>
+  </si>
+  <si>
+    <t>e_Elk_POL,e_Grajewo_POL</t>
+  </si>
+  <si>
     <t>e_Boleslawiec_POL,e_ZielonaGora_POL</t>
   </si>
   <si>
@@ -852,57 +891,42 @@
     <t>e_Warsaw_POL,e_Lomza_POL</t>
   </si>
   <si>
-    <t>e_Bydgoszcz_POL,e_Gdansk_POL,e_Grudziadz_POL,e_Kwidzyn_POL</t>
-  </si>
-  <si>
-    <t>e_Plock_POL,e_Olsztyn_POL,e_Warsaw_POL</t>
-  </si>
-  <si>
-    <t>e_Elk_POL,e_Grajewo_POL</t>
+    <t>e_Lubin_POL,e_Poznan_POL,e_Koszalin_POL,e_Bydgoszcz_POL</t>
   </si>
   <si>
     <t>e_BielskoBiala_POL,e_Katowice_POL,e_Krakow_POL,e_Tarnow_POL</t>
   </si>
   <si>
-    <t>e_Krosno_POL,e_Mielec_POL,e_Debica_POL,e_Zamosc_POL</t>
-  </si>
-  <si>
-    <t>e_Lomza_POL,e_Elk_POL,e_Bialystok_POL,e_Grajewo_POL</t>
-  </si>
-  <si>
-    <t>e_Legnica_POL,e_Swidnica_POL,e_KedzierzynKozle_POL,e_Opole_POL</t>
-  </si>
-  <si>
-    <t>e_Kielce_POL,e_Warsaw_POL,e_OstrowiecSwietokrz_POL</t>
-  </si>
-  <si>
-    <t>e_Pulawy_POL,e_Bialystok_POL,e_Chelm_POL</t>
-  </si>
-  <si>
-    <t>e_Rzeszow_POL,e_Zamosc_POL,e_Pulawy_POL,e_Chelm_POL</t>
-  </si>
-  <si>
-    <t>e_GorzowWielkopolski_POL,e_Szczecin_POL,e_Police_POL</t>
-  </si>
-  <si>
-    <t>e_Lubin_POL,e_Poznan_POL,e_Koszalin_POL,e_Bydgoszcz_POL</t>
-  </si>
-  <si>
-    <t>e_Lubin_POL,e_Swidnica_POL,e_Wroclaw_POL,e_Poznan_POL,e_Olesnica_POL</t>
-  </si>
-  <si>
-    <t>e_Koszalin_POL,e_Ustka_POL,e_Slupsk_POL</t>
-  </si>
-  <si>
-    <t>e_Olesnica_POL,e_Konin_POL,e_PiotrkowTrybunalsk_POL,e_Plock_POL</t>
-  </si>
-  <si>
     <t>e_Konin_POL,e_Bydgoszcz_POL,e_Wloclawek_POL,e_Kwidzyn_POL,e_Plock_POL</t>
   </si>
   <si>
     <t>e_OstrowiecSwietokrz_POL,e_Pulawy_POL,e_Warsaw_POL</t>
   </si>
   <si>
+    <t>distr_wonelc_won_POL_019</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_017</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_007</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_005</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 5</t>
+  </si>
+  <si>
     <t>distr_wonelc_won_POL_018</t>
   </si>
   <si>
@@ -921,12 +945,6 @@
     <t>connecting wind onshore to buses in cluster 10</t>
   </si>
   <si>
-    <t>distr_wonelc_won_POL_005</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 5</t>
-  </si>
-  <si>
     <t>distr_wonelc_won_POL_012</t>
   </si>
   <si>
@@ -939,6 +957,36 @@
     <t>connecting wind onshore to buses in cluster 3</t>
   </si>
   <si>
+    <t>distr_wonelc_won_POL_002</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_015</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_016</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_013</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_008</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 8</t>
+  </si>
+  <si>
     <t>distr_wonelc_won_POL_014</t>
   </si>
   <si>
@@ -951,76 +999,52 @@
     <t>connecting wind onshore to buses in cluster 20</t>
   </si>
   <si>
+    <t>distr_wonelc_won_POL_006</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_009</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_004</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 4</t>
+  </si>
+  <si>
     <t>distr_wonelc_won_POL_001</t>
   </si>
   <si>
     <t>connecting wind onshore to buses in cluster 1</t>
   </si>
   <si>
-    <t>distr_wonelc_won_POL_013</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_008</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_002</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_006</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_009</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_004</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_007</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_019</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_017</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_015</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_016</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 16</t>
+    <t>elc_won_POL_019</t>
+  </si>
+  <si>
+    <t>e_Katowice_POL,e_Czestochowa_POL,e_Krakow_POL,e_Kielce_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_017</t>
+  </si>
+  <si>
+    <t>e_Tarnow_POL,e_Krosno_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_007</t>
+  </si>
+  <si>
+    <t>e_Warsaw_POL,e_Plock_POL,e_Olsztyn_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_005</t>
+  </si>
+  <si>
+    <t>e_Lomza_POL,e_Elk_POL,e_Grajewo_POL,e_Bialystok_POL,e_Chelm_POL</t>
   </si>
   <si>
     <t>elc_won_POL_018</t>
@@ -1041,12 +1065,6 @@
     <t>e_Police_POL,e_Koszalin_POL,e_Poznan_POL,e_Ustka_POL,e_Bydgoszcz_POL,e_Slupsk_POL,e_Gdansk_POL</t>
   </si>
   <si>
-    <t>elc_won_POL_005</t>
-  </si>
-  <si>
-    <t>e_Lomza_POL,e_Elk_POL,e_Grajewo_POL,e_Bialystok_POL,e_Chelm_POL</t>
-  </si>
-  <si>
     <t>elc_won_POL_012</t>
   </si>
   <si>
@@ -1059,6 +1077,36 @@
     <t>e_Warsaw_POL,e_Lomza_POL,e_Pulawy_POL,e_Bialystok_POL</t>
   </si>
   <si>
+    <t>elc_won_POL_002</t>
+  </si>
+  <si>
+    <t>e_Tarnow_POL,e_Kielce_POL,e_OstrowiecSwietokrz_POL,e_Mielec_POL,e_Pulawy_POL,e_Rzeszow_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_015</t>
+  </si>
+  <si>
+    <t>e_BielskoBiala_POL,e_Krakow_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_016</t>
+  </si>
+  <si>
+    <t>e_Krosno_POL,e_Debica_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_013</t>
+  </si>
+  <si>
+    <t>e_Lubin_POL,e_Wroclaw_POL,e_Poznan_POL,e_Olesnica_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_008</t>
+  </si>
+  <si>
+    <t>e_Olsztyn_POL,e_Elk_POL</t>
+  </si>
+  <si>
     <t>elc_won_POL_014</t>
   </si>
   <si>
@@ -1071,75 +1119,27 @@
     <t>e_Sosnowiec_POL,e_KedzierzynKozle_POL,e_Olesnica_POL,e_Gliwice_POL,e_Czestochowa_POL,e_Radomsko_POL</t>
   </si>
   <si>
+    <t>elc_won_POL_006</t>
+  </si>
+  <si>
+    <t>e_Olesnica_POL,e_Konin_POL,e_Bydgoszcz_POL,e_Wloclawek_POL,e_Kwidzyn_POL,e_Plock_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_009</t>
+  </si>
+  <si>
+    <t>e_Gdansk_POL,e_Grudziadz_POL,e_Kwidzyn_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_004</t>
+  </si>
+  <si>
     <t>elc_won_POL_001</t>
   </si>
   <si>
     <t>e_PiotrkowTrybunalsk_POL,e_Kielce_POL,e_Warsaw_POL,e_OstrowiecSwietokrz_POL</t>
   </si>
   <si>
-    <t>elc_won_POL_013</t>
-  </si>
-  <si>
-    <t>e_Lubin_POL,e_Wroclaw_POL,e_Poznan_POL,e_Olesnica_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_008</t>
-  </si>
-  <si>
-    <t>e_Olsztyn_POL,e_Elk_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_002</t>
-  </si>
-  <si>
-    <t>e_Tarnow_POL,e_Kielce_POL,e_OstrowiecSwietokrz_POL,e_Mielec_POL,e_Pulawy_POL,e_Rzeszow_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_006</t>
-  </si>
-  <si>
-    <t>e_Olesnica_POL,e_Konin_POL,e_Bydgoszcz_POL,e_Wloclawek_POL,e_Kwidzyn_POL,e_Plock_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_009</t>
-  </si>
-  <si>
-    <t>e_Gdansk_POL,e_Grudziadz_POL,e_Kwidzyn_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_004</t>
-  </si>
-  <si>
-    <t>elc_won_POL_007</t>
-  </si>
-  <si>
-    <t>e_Warsaw_POL,e_Plock_POL,e_Olsztyn_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_019</t>
-  </si>
-  <si>
-    <t>e_Katowice_POL,e_Czestochowa_POL,e_Krakow_POL,e_Kielce_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_017</t>
-  </si>
-  <si>
-    <t>e_Tarnow_POL,e_Krosno_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_015</t>
-  </si>
-  <si>
-    <t>e_BielskoBiala_POL,e_Krakow_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_016</t>
-  </si>
-  <si>
-    <t>e_Krosno_POL,e_Debica_POL</t>
-  </si>
-  <si>
     <t>distr_wofelc_wof_POL_008</t>
   </si>
   <si>
@@ -1152,30 +1152,42 @@
     <t>connecting wind offshore to buses in cluster 7</t>
   </si>
   <si>
+    <t>distr_wofelc_wof_POL_002</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 2</t>
+  </si>
+  <si>
     <t>distr_wofelc_wof_POL_006</t>
   </si>
   <si>
     <t>connecting wind offshore to buses in cluster 6</t>
   </si>
   <si>
+    <t>distr_wofelc_wof_POL_004</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_POL_010</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_POL_009</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 9</t>
+  </si>
+  <si>
     <t>distr_wofelc_wof_POL_003</t>
   </si>
   <si>
     <t>connecting wind offshore to buses in cluster 3</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_POL_004</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_POL_002</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 2</t>
-  </si>
-  <si>
     <t>distr_wofelc_wof_POL_005</t>
   </si>
   <si>
@@ -1188,18 +1200,6 @@
     <t>connecting wind offshore to buses in cluster 1</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_POL_010</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_POL_009</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 9</t>
-  </si>
-  <si>
     <t>elc_wof_POL_008</t>
   </si>
   <si>
@@ -1212,45 +1212,45 @@
     <t>e_Koszalin_POL</t>
   </si>
   <si>
+    <t>elc_wof_POL_002</t>
+  </si>
+  <si>
+    <t>e_Gdynia_POL,e_Gdansk_POL</t>
+  </si>
+  <si>
     <t>elc_wof_POL_006</t>
   </si>
   <si>
     <t>e_Gdynia_POL</t>
   </si>
   <si>
+    <t>elc_wof_POL_004</t>
+  </si>
+  <si>
+    <t>e_Ustka_POL,e_Gdynia_POL</t>
+  </si>
+  <si>
+    <t>elc_wof_POL_010</t>
+  </si>
+  <si>
+    <t>elc_wof_POL_009</t>
+  </si>
+  <si>
+    <t>e_Koszalin_POL,e_Ustka_POL</t>
+  </si>
+  <si>
     <t>elc_wof_POL_003</t>
   </si>
   <si>
     <t>e_Gdansk_POL</t>
   </si>
   <si>
-    <t>elc_wof_POL_004</t>
-  </si>
-  <si>
-    <t>e_Ustka_POL,e_Gdynia_POL</t>
-  </si>
-  <si>
-    <t>elc_wof_POL_002</t>
-  </si>
-  <si>
-    <t>e_Gdynia_POL,e_Gdansk_POL</t>
-  </si>
-  <si>
     <t>elc_wof_POL_005</t>
   </si>
   <si>
     <t>elc_wof_POL_001</t>
   </si>
   <si>
-    <t>elc_wof_POL_010</t>
-  </si>
-  <si>
-    <t>elc_wof_POL_009</t>
-  </si>
-  <si>
-    <t>e_Koszalin_POL,e_Ustka_POL</t>
-  </si>
-  <si>
     <t>e_won_POL_001</t>
   </si>
   <si>
@@ -1548,16 +1548,76 @@
     <t>HET,CO2Cap</t>
   </si>
   <si>
+    <t>pcg</t>
+  </si>
+  <si>
+    <t>Natural gas combined cycle. IEA GEC</t>
+  </si>
+  <si>
     <t>yes</t>
   </si>
   <si>
+    <t>Natural gas open-cycle combustion turbine. IEA GEC</t>
+  </si>
+  <si>
     <t>CHP</t>
   </si>
   <si>
+    <t>Gas combined cycle CHP, steam extraction (large). DEA el&amp;dh 05</t>
+  </si>
+  <si>
+    <t>Natural gas CCGT with post-combustion CCS. IEA GEC</t>
+  </si>
+  <si>
+    <t>Coal subcritical steam cycle. IEA GEC</t>
+  </si>
+  <si>
+    <t>Coal supercritical steam cycle. IEA GEC</t>
+  </si>
+  <si>
+    <t>Coal ultra-supercritical steam cycle. IEA GEC</t>
+  </si>
+  <si>
+    <t>Coal integrated gasification combined cycle. IEA GEC</t>
+  </si>
+  <si>
+    <t>Nuclear large reactor (Gen III/III+). IEA GEC</t>
+  </si>
+  <si>
+    <t>Nuclear small modular reactor. ATB</t>
+  </si>
+  <si>
+    <t>Biomass dedicated large-scale. IEA GEC</t>
+  </si>
+  <si>
+    <t>Wood-chips CHP, steam extraction (large). DEA el&amp;dh 09a</t>
+  </si>
+  <si>
     <t>HPL</t>
   </si>
   <si>
+    <t>Natural gas DH boiler (medium). DEA el&amp;dh 44. Heat capacity basis</t>
+  </si>
+  <si>
     <t>season</t>
+  </si>
+  <si>
+    <t>Wood-chips DH boiler (large). DEA el&amp;dh 09a. Heat capacity basis</t>
+  </si>
+  <si>
+    <t>Electric DH boiler (large). DEA el&amp;dh 41. Heat capacity basis; region-uniform</t>
+  </si>
+  <si>
+    <t>Utility heat pump, air source, 10 MW, 70/35C DH. DEA el&amp;dh 40. heat_efficiency = COP; component split preserved</t>
+  </si>
+  <si>
+    <t>Utility-scale Li-ion battery, 4-hour duration. ATB</t>
+  </si>
+  <si>
+    <t>Utility-scale Li-ion battery, 8-hour duration. ATB</t>
+  </si>
+  <si>
+    <t>Gas combined cycle CHP with post-combustion CCS. Synthetic (DEA 05 + GEC gas CCS)</t>
   </si>
   <si>
     <t>e_BielskoBiala_POL,e_Elk_POL,e_Krosno_POL,e_Opole_POL,e_Rzeszow_POL,e_Sosnowiec_POL,e_Szczecin_POL,e_Zamosc_POL,e_w111615226-380_POL,e_w139452056-400_POL</t>
@@ -4122,7 +4182,7 @@
         <v>50</v>
       </c>
       <c r="V28" t="s">
-        <v>498</v>
+        <v>518</v>
       </c>
     </row>
     <row r="29" spans="2:22">
@@ -5784,7 +5844,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C52F2B83-4C0A-4435-B7C4-30B6B38BDCDC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02F0484B-22D0-4E0E-A716-2E666EF2C9D0}">
   <dimension ref="B9:BD30"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -6022,16 +6082,16 @@
         <v>215</v>
       </c>
       <c r="Y11" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="Z11" t="s">
         <v>259</v>
       </c>
       <c r="AA11">
-        <v>0.99707401400885998</v>
+        <v>0.99693515631487983</v>
       </c>
       <c r="AB11">
-        <v>53.643076504234422</v>
+        <v>56.188800893869058</v>
       </c>
       <c r="AD11" t="s">
         <v>214</v>
@@ -6064,10 +6124,10 @@
         <v>320</v>
       </c>
       <c r="AO11">
-        <v>0.99622969699231045</v>
+        <v>0.99872641243407079</v>
       </c>
       <c r="AP11">
-        <v>69.122221807641537</v>
+        <v>23.349105375368897</v>
       </c>
       <c r="AR11" t="s">
         <v>214</v>
@@ -6168,16 +6228,16 @@
         <v>219</v>
       </c>
       <c r="Y12" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="Z12" t="s">
         <v>260</v>
       </c>
       <c r="AA12">
-        <v>0.99826037700975512</v>
+        <v>0.99606480786442353</v>
       </c>
       <c r="AB12">
-        <v>31.893088154488542</v>
+        <v>72.145189152235062</v>
       </c>
       <c r="AD12" t="s">
         <v>214</v>
@@ -6210,10 +6270,10 @@
         <v>322</v>
       </c>
       <c r="AO12">
-        <v>0.99802303154782224</v>
+        <v>0.99776911581804295</v>
       </c>
       <c r="AP12">
-        <v>36.244421623259619</v>
+        <v>40.899543335879912</v>
       </c>
       <c r="AR12" t="s">
         <v>214</v>
@@ -6314,16 +6374,16 @@
         <v>221</v>
       </c>
       <c r="Y13" t="s">
-        <v>210</v>
+        <v>196</v>
       </c>
       <c r="Z13" t="s">
         <v>261</v>
       </c>
       <c r="AA13">
-        <v>0.99922515067657613</v>
+        <v>0.99785589517057005</v>
       </c>
       <c r="AB13">
-        <v>14.205570929438155</v>
+        <v>39.308588539549028</v>
       </c>
       <c r="AD13" t="s">
         <v>214</v>
@@ -6356,10 +6416,10 @@
         <v>324</v>
       </c>
       <c r="AO13">
-        <v>0.99714358927215652</v>
+        <v>0.99653588726932718</v>
       </c>
       <c r="AP13">
-        <v>52.367530010463909</v>
+        <v>63.508733395668145</v>
       </c>
       <c r="AR13" t="s">
         <v>214</v>
@@ -6392,10 +6452,10 @@
         <v>383</v>
       </c>
       <c r="BC13">
-        <v>0.99615739524125424</v>
+        <v>0.99353721168226494</v>
       </c>
       <c r="BD13">
-        <v>584.91448865302027</v>
+        <v>780.55486105754892</v>
       </c>
     </row>
     <row r="14" spans="2:56">
@@ -6460,16 +6520,16 @@
         <v>223</v>
       </c>
       <c r="Y14" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="Z14" t="s">
         <v>262</v>
       </c>
       <c r="AA14">
-        <v>0.99693515631487983</v>
+        <v>0.99515616506526205</v>
       </c>
       <c r="AB14">
-        <v>56.188800893869058</v>
+        <v>88.803640470195262</v>
       </c>
       <c r="AD14" t="s">
         <v>214</v>
@@ -6538,10 +6598,10 @@
         <v>385</v>
       </c>
       <c r="BC14">
-        <v>0.99564787435456037</v>
+        <v>0.99615739524125424</v>
       </c>
       <c r="BD14">
-        <v>622.95871485949408</v>
+        <v>584.91448865302027</v>
       </c>
     </row>
     <row r="15" spans="2:56">
@@ -6606,16 +6666,16 @@
         <v>225</v>
       </c>
       <c r="Y15" t="s">
-        <v>198</v>
+        <v>211</v>
       </c>
       <c r="Z15" t="s">
         <v>263</v>
       </c>
       <c r="AA15">
-        <v>0.99658775492800411</v>
+        <v>0.99728872234103139</v>
       </c>
       <c r="AB15">
-        <v>62.557826319923819</v>
+        <v>49.70675708109188</v>
       </c>
       <c r="AD15" t="s">
         <v>214</v>
@@ -6648,10 +6708,10 @@
         <v>328</v>
       </c>
       <c r="AO15">
-        <v>0.99749126227646956</v>
+        <v>0.99622969699231045</v>
       </c>
       <c r="AP15">
-        <v>45.993524931390482</v>
+        <v>69.122221807641537</v>
       </c>
       <c r="AR15" t="s">
         <v>214</v>
@@ -6752,16 +6812,16 @@
         <v>227</v>
       </c>
       <c r="Y16" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="Z16" t="s">
         <v>264</v>
       </c>
       <c r="AA16">
-        <v>0.99510886326373238</v>
+        <v>0.99583567586599486</v>
       </c>
       <c r="AB16">
-        <v>89.670840164906522</v>
+        <v>76.34594245676044</v>
       </c>
       <c r="AD16" t="s">
         <v>214</v>
@@ -6794,10 +6854,10 @@
         <v>330</v>
       </c>
       <c r="AO16">
-        <v>0.99807543246352515</v>
+        <v>0.99802303154782224</v>
       </c>
       <c r="AP16">
-        <v>35.283738168705199</v>
+        <v>36.244421623259619</v>
       </c>
       <c r="AR16" t="s">
         <v>214</v>
@@ -6827,13 +6887,13 @@
         <v>388</v>
       </c>
       <c r="BB16" t="s">
-        <v>389</v>
+        <v>381</v>
       </c>
       <c r="BC16">
-        <v>0.99353721168226494</v>
+        <v>0.99608994650263638</v>
       </c>
       <c r="BD16">
-        <v>780.55486105754892</v>
+        <v>589.950661136485</v>
       </c>
     </row>
     <row r="17" spans="2:56">
@@ -6898,16 +6958,16 @@
         <v>229</v>
       </c>
       <c r="Y17" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="Z17" t="s">
         <v>265</v>
       </c>
       <c r="AA17">
-        <v>0.99790408176624201</v>
+        <v>0.99481478101166732</v>
       </c>
       <c r="AB17">
-        <v>38.425167618896296</v>
+        <v>95.062348119433295</v>
       </c>
       <c r="AD17" t="s">
         <v>214</v>
@@ -6940,10 +7000,10 @@
         <v>332</v>
       </c>
       <c r="AO17">
-        <v>0.99730422320290779</v>
+        <v>0.99714358927215652</v>
       </c>
       <c r="AP17">
-        <v>49.422574613357185</v>
+        <v>52.367530010463909</v>
       </c>
       <c r="AR17" t="s">
         <v>214</v>
@@ -6970,16 +7030,16 @@
         <v>370</v>
       </c>
       <c r="BA17" t="s">
+        <v>389</v>
+      </c>
+      <c r="BB17" t="s">
         <v>390</v>
       </c>
-      <c r="BB17" t="s">
-        <v>383</v>
-      </c>
       <c r="BC17">
-        <v>0.99328660064428831</v>
+        <v>0.99399682431672776</v>
       </c>
       <c r="BD17">
-        <v>799.26715189313825</v>
+        <v>746.2371176843244</v>
       </c>
     </row>
     <row r="18" spans="2:56">
@@ -7044,16 +7104,16 @@
         <v>231</v>
       </c>
       <c r="Y18" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="Z18" t="s">
         <v>266</v>
       </c>
       <c r="AA18">
-        <v>0.99481478101166732</v>
+        <v>0.99681878296180493</v>
       </c>
       <c r="AB18">
-        <v>95.062348119433295</v>
+        <v>58.322312366909152</v>
       </c>
       <c r="AD18" t="s">
         <v>214</v>
@@ -7086,10 +7146,10 @@
         <v>334</v>
       </c>
       <c r="AO18">
-        <v>0.99805709209211746</v>
+        <v>0.99749126227646956</v>
       </c>
       <c r="AP18">
-        <v>35.619978311179104</v>
+        <v>45.993524931390482</v>
       </c>
       <c r="AR18" t="s">
         <v>214</v>
@@ -7119,13 +7179,13 @@
         <v>391</v>
       </c>
       <c r="BB18" t="s">
-        <v>385</v>
+        <v>392</v>
       </c>
       <c r="BC18">
-        <v>0.99644441082752833</v>
+        <v>0.99564787435456037</v>
       </c>
       <c r="BD18">
-        <v>563.48399154455342</v>
+        <v>622.95871485949408</v>
       </c>
     </row>
     <row r="19" spans="2:56">
@@ -7190,16 +7250,16 @@
         <v>233</v>
       </c>
       <c r="Y19" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="Z19" t="s">
         <v>267</v>
       </c>
       <c r="AA19">
-        <v>0.99681878296180493</v>
+        <v>0.99770934816564383</v>
       </c>
       <c r="AB19">
-        <v>58.322312366909152</v>
+        <v>41.995283629862939</v>
       </c>
       <c r="AD19" t="s">
         <v>214</v>
@@ -7232,10 +7292,10 @@
         <v>336</v>
       </c>
       <c r="AO19">
-        <v>0.99871360797890252</v>
+        <v>0.99807543246352515</v>
       </c>
       <c r="AP19">
-        <v>23.583853720120768</v>
+        <v>35.283738168705199</v>
       </c>
       <c r="AR19" t="s">
         <v>214</v>
@@ -7262,16 +7322,16 @@
         <v>374</v>
       </c>
       <c r="BA19" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="BB19" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="BC19">
-        <v>0.99608994650263638</v>
+        <v>0.99328660064428831</v>
       </c>
       <c r="BD19">
-        <v>589.950661136485</v>
+        <v>799.26715189313825</v>
       </c>
     </row>
     <row r="20" spans="2:56">
@@ -7336,16 +7396,16 @@
         <v>235</v>
       </c>
       <c r="Y20" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="Z20" t="s">
         <v>268</v>
       </c>
       <c r="AA20">
-        <v>0.99515616506526205</v>
+        <v>0.9970292559096442</v>
       </c>
       <c r="AB20">
-        <v>88.803640470195262</v>
+        <v>54.463641656523762</v>
       </c>
       <c r="AD20" t="s">
         <v>214</v>
@@ -7378,10 +7438,10 @@
         <v>338</v>
       </c>
       <c r="AO20">
-        <v>0.99883902037019667</v>
+        <v>0.99845791964146047</v>
       </c>
       <c r="AP20">
-        <v>21.284626546395259</v>
+        <v>28.2714732398913</v>
       </c>
       <c r="AR20" t="s">
         <v>214</v>
@@ -7408,16 +7468,16 @@
         <v>376</v>
       </c>
       <c r="BA20" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="BB20" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="BC20">
-        <v>0.99399682431672776</v>
+        <v>0.99644441082752833</v>
       </c>
       <c r="BD20">
-        <v>746.2371176843244</v>
+        <v>563.48399154455342</v>
       </c>
     </row>
     <row r="21" spans="2:56">
@@ -7482,16 +7542,16 @@
         <v>237</v>
       </c>
       <c r="Y21" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="Z21" t="s">
         <v>269</v>
       </c>
       <c r="AA21">
-        <v>0.99728872234103139</v>
+        <v>0.9982126095160021</v>
       </c>
       <c r="AB21">
-        <v>49.70675708109188</v>
+        <v>32.768825539961391</v>
       </c>
       <c r="AD21" t="s">
         <v>214</v>
@@ -7524,10 +7584,10 @@
         <v>340</v>
       </c>
       <c r="AO21">
-        <v>0.99521984547821263</v>
+        <v>0.99641308487583879</v>
       </c>
       <c r="AP21">
-        <v>87.636166232768815</v>
+        <v>65.760110609622657</v>
       </c>
     </row>
     <row r="22" spans="2:56">
@@ -7592,16 +7652,16 @@
         <v>239</v>
       </c>
       <c r="Y22" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="Z22" t="s">
         <v>270</v>
       </c>
       <c r="AA22">
-        <v>0.99583567586599486</v>
+        <v>0.99658775492800411</v>
       </c>
       <c r="AB22">
-        <v>76.34594245676044</v>
+        <v>62.557826319923819</v>
       </c>
       <c r="AD22" t="s">
         <v>214</v>
@@ -7634,10 +7694,10 @@
         <v>342</v>
       </c>
       <c r="AO22">
-        <v>0.99845791964146047</v>
+        <v>0.99449756685866841</v>
       </c>
       <c r="AP22">
-        <v>28.2714732398913</v>
+        <v>100.87794092441324</v>
       </c>
     </row>
     <row r="23" spans="2:56">
@@ -7702,16 +7762,16 @@
         <v>241</v>
       </c>
       <c r="Y23" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="Z23" t="s">
         <v>271</v>
       </c>
       <c r="AA23">
-        <v>0.99606480786442353</v>
+        <v>0.99510886326373238</v>
       </c>
       <c r="AB23">
-        <v>72.145189152235062</v>
+        <v>89.670840164906522</v>
       </c>
       <c r="AD23" t="s">
         <v>214</v>
@@ -7744,10 +7804,10 @@
         <v>344</v>
       </c>
       <c r="AO23">
-        <v>0.99827231256984739</v>
+        <v>0.99883902037019667</v>
       </c>
       <c r="AP23">
-        <v>31.674269552798414</v>
+        <v>21.284626546395259</v>
       </c>
     </row>
     <row r="24" spans="2:56">
@@ -7812,16 +7872,16 @@
         <v>243</v>
       </c>
       <c r="Y24" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="Z24" t="s">
         <v>272</v>
       </c>
       <c r="AA24">
-        <v>0.99785589517057005</v>
+        <v>0.99707401400885998</v>
       </c>
       <c r="AB24">
-        <v>39.308588539549028</v>
+        <v>53.643076504234422</v>
       </c>
       <c r="AD24" t="s">
         <v>214</v>
@@ -7854,10 +7914,10 @@
         <v>346</v>
       </c>
       <c r="AO24">
-        <v>0.99635146162488653</v>
+        <v>0.99521984547821263</v>
       </c>
       <c r="AP24">
-        <v>66.889870210414614</v>
+        <v>87.636166232768815</v>
       </c>
     </row>
     <row r="25" spans="2:56">
@@ -7922,16 +7982,16 @@
         <v>245</v>
       </c>
       <c r="Y25" t="s">
-        <v>197</v>
+        <v>207</v>
       </c>
       <c r="Z25" t="s">
         <v>273</v>
       </c>
       <c r="AA25">
-        <v>0.99730738889353909</v>
+        <v>0.99826037700975512</v>
       </c>
       <c r="AB25">
-        <v>49.364536951784054</v>
+        <v>31.893088154488542</v>
       </c>
       <c r="AD25" t="s">
         <v>214</v>
@@ -7961,13 +8021,13 @@
         <v>347</v>
       </c>
       <c r="AN25" t="s">
-        <v>271</v>
+        <v>348</v>
       </c>
       <c r="AO25">
-        <v>0.99586212495478665</v>
+        <v>0.99730422320290779</v>
       </c>
       <c r="AP25">
-        <v>75.861042495577635</v>
+        <v>49.422574613357185</v>
       </c>
     </row>
     <row r="26" spans="2:56">
@@ -8032,16 +8092,16 @@
         <v>247</v>
       </c>
       <c r="Y26" t="s">
-        <v>195</v>
+        <v>210</v>
       </c>
       <c r="Z26" t="s">
         <v>274</v>
       </c>
       <c r="AA26">
-        <v>0.99770934816564383</v>
+        <v>0.99922515067657613</v>
       </c>
       <c r="AB26">
-        <v>41.995283629862939</v>
+        <v>14.205570929438155</v>
       </c>
       <c r="AD26" t="s">
         <v>214</v>
@@ -8068,16 +8128,16 @@
         <v>309</v>
       </c>
       <c r="AM26" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AN26" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AO26">
-        <v>0.99653588726932718</v>
+        <v>0.99805709209211746</v>
       </c>
       <c r="AP26">
-        <v>63.508733395668145</v>
+        <v>35.619978311179104</v>
       </c>
     </row>
     <row r="27" spans="2:56">
@@ -8142,16 +8202,16 @@
         <v>249</v>
       </c>
       <c r="Y27" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="Z27" t="s">
         <v>275</v>
       </c>
       <c r="AA27">
-        <v>0.9970292559096442</v>
+        <v>0.99730738889353909</v>
       </c>
       <c r="AB27">
-        <v>54.463641656523762</v>
+        <v>49.364536951784054</v>
       </c>
       <c r="AD27" t="s">
         <v>214</v>
@@ -8178,16 +8238,16 @@
         <v>311</v>
       </c>
       <c r="AM27" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AN27" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AO27">
-        <v>0.99872641243407079</v>
+        <v>0.99827231256984739</v>
       </c>
       <c r="AP27">
-        <v>23.349105375368897</v>
+        <v>31.674269552798414</v>
       </c>
     </row>
     <row r="28" spans="2:56">
@@ -8252,16 +8312,16 @@
         <v>251</v>
       </c>
       <c r="Y28" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="Z28" t="s">
         <v>276</v>
       </c>
       <c r="AA28">
-        <v>0.9982126095160021</v>
+        <v>0.99790408176624201</v>
       </c>
       <c r="AB28">
-        <v>32.768825539961391</v>
+        <v>38.425167618896296</v>
       </c>
       <c r="AD28" t="s">
         <v>214</v>
@@ -8288,16 +8348,16 @@
         <v>313</v>
       </c>
       <c r="AM28" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AN28" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AO28">
-        <v>0.99776911581804295</v>
+        <v>0.99635146162488653</v>
       </c>
       <c r="AP28">
-        <v>40.899543335879912</v>
+        <v>66.889870210414614</v>
       </c>
     </row>
     <row r="29" spans="2:56">
@@ -8398,16 +8458,16 @@
         <v>315</v>
       </c>
       <c r="AM29" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AN29" t="s">
-        <v>355</v>
+        <v>260</v>
       </c>
       <c r="AO29">
-        <v>0.99641308487583879</v>
+        <v>0.99586212495478665</v>
       </c>
       <c r="AP29">
-        <v>65.760110609622657</v>
+        <v>75.861042495577635</v>
       </c>
     </row>
     <row r="30" spans="2:56">
@@ -8514,10 +8574,10 @@
         <v>357</v>
       </c>
       <c r="AO30">
-        <v>0.99449756685866841</v>
+        <v>0.99871360797890252</v>
       </c>
       <c r="AP30">
-        <v>100.87794092441324</v>
+        <v>23.583853720120768</v>
       </c>
     </row>
   </sheetData>
@@ -8526,7 +8586,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45B35996-1FD0-428E-823F-39CBAF1F4249}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59151317-8DD6-4792-A37C-CEF8C67A62EE}">
   <dimension ref="B9:Z30"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -8638,7 +8698,7 @@
         <v>395</v>
       </c>
       <c r="K11" t="s">
-        <v>335</v>
+        <v>356</v>
       </c>
       <c r="L11">
         <v>0.30278350605008381</v>
@@ -8671,7 +8731,7 @@
         <v>435</v>
       </c>
       <c r="X11" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="Y11">
         <v>0.83925000000000005</v>
@@ -8706,7 +8766,7 @@
         <v>397</v>
       </c>
       <c r="K12" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="L12">
         <v>0.42035497786033621</v>
@@ -8739,7 +8799,7 @@
         <v>437</v>
       </c>
       <c r="X12" t="s">
-        <v>388</v>
+        <v>382</v>
       </c>
       <c r="Y12">
         <v>16.887</v>
@@ -8774,7 +8834,7 @@
         <v>399</v>
       </c>
       <c r="K13" t="s">
-        <v>329</v>
+        <v>335</v>
       </c>
       <c r="L13">
         <v>1.6077871713950227</v>
@@ -8807,7 +8867,7 @@
         <v>439</v>
       </c>
       <c r="X13" t="s">
-        <v>384</v>
+        <v>391</v>
       </c>
       <c r="Y13">
         <v>11.2965</v>
@@ -8842,7 +8902,7 @@
         <v>401</v>
       </c>
       <c r="K14" t="s">
-        <v>347</v>
+        <v>355</v>
       </c>
       <c r="L14">
         <v>2.531891424764753</v>
@@ -8943,7 +9003,7 @@
         <v>443</v>
       </c>
       <c r="X15" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="Y15">
         <v>17.089500000000001</v>
@@ -8978,7 +9038,7 @@
         <v>405</v>
       </c>
       <c r="K16" t="s">
-        <v>343</v>
+        <v>351</v>
       </c>
       <c r="L16">
         <v>0.60733325583919984</v>
@@ -9011,7 +9071,7 @@
         <v>445</v>
       </c>
       <c r="X16" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="Y16">
         <v>8.8230000000000004</v>
@@ -9046,7 +9106,7 @@
         <v>407</v>
       </c>
       <c r="K17" t="s">
-        <v>348</v>
+        <v>323</v>
       </c>
       <c r="L17">
         <v>0.78389041837100704</v>
@@ -9114,7 +9174,7 @@
         <v>409</v>
       </c>
       <c r="K18" t="s">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="L18">
         <v>3.0365724666245324</v>
@@ -9182,7 +9242,7 @@
         <v>411</v>
       </c>
       <c r="K19" t="s">
-        <v>345</v>
+        <v>353</v>
       </c>
       <c r="L19">
         <v>0.22970161230087291</v>
@@ -9215,7 +9275,7 @@
         <v>451</v>
       </c>
       <c r="X19" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="Y19">
         <v>13.37175</v>
@@ -9250,7 +9310,7 @@
         <v>413</v>
       </c>
       <c r="K20" t="s">
-        <v>323</v>
+        <v>331</v>
       </c>
       <c r="L20">
         <v>0.27066515065379043</v>
@@ -9283,7 +9343,7 @@
         <v>453</v>
       </c>
       <c r="X20" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="Y20">
         <v>3.9427500000000002</v>
@@ -9318,7 +9378,7 @@
         <v>415</v>
       </c>
       <c r="K21" t="s">
-        <v>321</v>
+        <v>329</v>
       </c>
       <c r="L21">
         <v>0.32193208719379746</v>
@@ -9353,7 +9413,7 @@
         <v>417</v>
       </c>
       <c r="K22" t="s">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c r="L22">
         <v>0.6573344927201471</v>
@@ -9388,7 +9448,7 @@
         <v>419</v>
       </c>
       <c r="K23" t="s">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="L23">
         <v>0.28992997651770519</v>
@@ -9423,7 +9483,7 @@
         <v>421</v>
       </c>
       <c r="K24" t="s">
-        <v>331</v>
+        <v>347</v>
       </c>
       <c r="L24">
         <v>0.74609319967150689</v>
@@ -9458,7 +9518,7 @@
         <v>423</v>
       </c>
       <c r="K25" t="s">
-        <v>354</v>
+        <v>339</v>
       </c>
       <c r="L25">
         <v>0.35328950844501877</v>
@@ -9493,7 +9553,7 @@
         <v>425</v>
       </c>
       <c r="K26" t="s">
-        <v>356</v>
+        <v>341</v>
       </c>
       <c r="L26">
         <v>0.7924639655878376</v>
@@ -9528,7 +9588,7 @@
         <v>427</v>
       </c>
       <c r="K27" t="s">
-        <v>352</v>
+        <v>321</v>
       </c>
       <c r="L27">
         <v>0.55411362221124194</v>
@@ -9563,7 +9623,7 @@
         <v>429</v>
       </c>
       <c r="K28" t="s">
-        <v>319</v>
+        <v>327</v>
       </c>
       <c r="L28">
         <v>1.4327274230737423</v>
@@ -9598,7 +9658,7 @@
         <v>431</v>
       </c>
       <c r="K29" t="s">
-        <v>350</v>
+        <v>319</v>
       </c>
       <c r="L29">
         <v>0.56742801517356967</v>
@@ -9633,7 +9693,7 @@
         <v>433</v>
       </c>
       <c r="K30" t="s">
-        <v>333</v>
+        <v>349</v>
       </c>
       <c r="L30">
         <v>0.35405891742987328</v>
@@ -9648,11 +9708,11 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70501254-1258-4265-9E89-FC49F5AF90E8}">
-  <dimension ref="B9:X136"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{339FE14C-E19A-4BFE-A95A-E195613017B1}">
+  <dimension ref="B9:Y136"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
-    <row r="9" spans="2:24">
+    <row r="9" spans="2:25">
       <c r="B9" t="s">
         <v>455</v>
       </c>
@@ -9660,7 +9720,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="10" spans="2:24">
+    <row r="10" spans="2:25">
       <c r="B10" t="s">
         <v>140</v>
       </c>
@@ -9727,8 +9787,11 @@
       <c r="X10" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="11" spans="2:24">
+      <c r="Y10" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="11" spans="2:25">
       <c r="B11" t="s">
         <v>459</v>
       </c>
@@ -9756,6 +9819,9 @@
       <c r="S11" t="s">
         <v>459</v>
       </c>
+      <c r="T11" t="s">
+        <v>495</v>
+      </c>
       <c r="U11" t="s">
         <v>10</v>
       </c>
@@ -9766,10 +9832,10 @@
         <v>218</v>
       </c>
       <c r="X11" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="12" spans="2:24">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="12" spans="2:25">
       <c r="B12" t="s">
         <v>459</v>
       </c>
@@ -9797,6 +9863,9 @@
       <c r="S12" t="s">
         <v>465</v>
       </c>
+      <c r="T12" t="s">
+        <v>497</v>
+      </c>
       <c r="U12" t="s">
         <v>10</v>
       </c>
@@ -9807,10 +9876,10 @@
         <v>218</v>
       </c>
       <c r="X12" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="13" spans="2:24">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="13" spans="2:25">
       <c r="B13" t="s">
         <v>459</v>
       </c>
@@ -9833,11 +9902,14 @@
         <v>462</v>
       </c>
       <c r="R13" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="S13" t="s">
         <v>466</v>
       </c>
+      <c r="T13" t="s">
+        <v>499</v>
+      </c>
       <c r="U13" t="s">
         <v>10</v>
       </c>
@@ -9848,10 +9920,10 @@
         <v>218</v>
       </c>
       <c r="X13" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="14" spans="2:24">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="14" spans="2:25">
       <c r="B14" t="s">
         <v>459</v>
       </c>
@@ -9879,6 +9951,9 @@
       <c r="S14" t="s">
         <v>470</v>
       </c>
+      <c r="T14" t="s">
+        <v>500</v>
+      </c>
       <c r="U14" t="s">
         <v>10</v>
       </c>
@@ -9889,10 +9964,10 @@
         <v>218</v>
       </c>
       <c r="X14" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="15" spans="2:24">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="15" spans="2:25">
       <c r="B15" t="s">
         <v>459</v>
       </c>
@@ -9938,6 +10013,9 @@
       <c r="S15" t="s">
         <v>472</v>
       </c>
+      <c r="T15" t="s">
+        <v>501</v>
+      </c>
       <c r="U15" t="s">
         <v>10</v>
       </c>
@@ -9948,10 +10026,10 @@
         <v>218</v>
       </c>
       <c r="X15" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="16" spans="2:24">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="16" spans="2:25">
       <c r="B16" t="s">
         <v>459</v>
       </c>
@@ -9997,6 +10075,9 @@
       <c r="S16" t="s">
         <v>473</v>
       </c>
+      <c r="T16" t="s">
+        <v>502</v>
+      </c>
       <c r="U16" t="s">
         <v>10</v>
       </c>
@@ -10007,10 +10088,10 @@
         <v>218</v>
       </c>
       <c r="X16" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="17" spans="2:24">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="17" spans="2:25">
       <c r="B17" t="s">
         <v>465</v>
       </c>
@@ -10038,6 +10119,9 @@
       <c r="S17" t="s">
         <v>474</v>
       </c>
+      <c r="T17" t="s">
+        <v>503</v>
+      </c>
       <c r="U17" t="s">
         <v>10</v>
       </c>
@@ -10048,10 +10132,10 @@
         <v>218</v>
       </c>
       <c r="X17" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="18" spans="2:24">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="18" spans="2:25">
       <c r="B18" t="s">
         <v>465</v>
       </c>
@@ -10079,6 +10163,9 @@
       <c r="S18" t="s">
         <v>475</v>
       </c>
+      <c r="T18" t="s">
+        <v>504</v>
+      </c>
       <c r="U18" t="s">
         <v>10</v>
       </c>
@@ -10089,10 +10176,10 @@
         <v>218</v>
       </c>
       <c r="X18" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="19" spans="2:24">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="19" spans="2:25">
       <c r="B19" t="s">
         <v>465</v>
       </c>
@@ -10120,6 +10207,9 @@
       <c r="S19" t="s">
         <v>476</v>
       </c>
+      <c r="T19" t="s">
+        <v>505</v>
+      </c>
       <c r="U19" t="s">
         <v>10</v>
       </c>
@@ -10130,10 +10220,10 @@
         <v>218</v>
       </c>
       <c r="X19" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="20" spans="2:24">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="20" spans="2:25">
       <c r="B20" t="s">
         <v>465</v>
       </c>
@@ -10161,6 +10251,9 @@
       <c r="S20" t="s">
         <v>477</v>
       </c>
+      <c r="T20" t="s">
+        <v>506</v>
+      </c>
       <c r="U20" t="s">
         <v>10</v>
       </c>
@@ -10171,10 +10264,10 @@
         <v>218</v>
       </c>
       <c r="X20" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="21" spans="2:24">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="21" spans="2:25">
       <c r="B21" t="s">
         <v>465</v>
       </c>
@@ -10220,6 +10313,9 @@
       <c r="S21" t="s">
         <v>478</v>
       </c>
+      <c r="T21" t="s">
+        <v>507</v>
+      </c>
       <c r="U21" t="s">
         <v>10</v>
       </c>
@@ -10230,10 +10326,10 @@
         <v>218</v>
       </c>
       <c r="X21" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="22" spans="2:24">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="22" spans="2:25">
       <c r="B22" t="s">
         <v>465</v>
       </c>
@@ -10274,11 +10370,14 @@
         <v>464</v>
       </c>
       <c r="R22" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="S22" t="s">
         <v>480</v>
       </c>
+      <c r="T22" t="s">
+        <v>508</v>
+      </c>
       <c r="U22" t="s">
         <v>10</v>
       </c>
@@ -10289,10 +10388,10 @@
         <v>218</v>
       </c>
       <c r="X22" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="23" spans="2:24">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="23" spans="2:25">
       <c r="B23" t="s">
         <v>466</v>
       </c>
@@ -10315,11 +10414,14 @@
         <v>460</v>
       </c>
       <c r="R23" t="s">
-        <v>496</v>
+        <v>509</v>
       </c>
       <c r="S23" t="s">
         <v>481</v>
       </c>
+      <c r="T23" t="s">
+        <v>510</v>
+      </c>
       <c r="U23" t="s">
         <v>10</v>
       </c>
@@ -10327,13 +10429,13 @@
         <v>20</v>
       </c>
       <c r="W23" t="s">
-        <v>497</v>
+        <v>511</v>
       </c>
       <c r="X23" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="24" spans="2:24">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="24" spans="2:25">
       <c r="B24" t="s">
         <v>466</v>
       </c>
@@ -10356,11 +10458,14 @@
         <v>461</v>
       </c>
       <c r="R24" t="s">
-        <v>496</v>
+        <v>509</v>
       </c>
       <c r="S24" t="s">
         <v>482</v>
       </c>
+      <c r="T24" t="s">
+        <v>512</v>
+      </c>
       <c r="U24" t="s">
         <v>10</v>
       </c>
@@ -10368,13 +10473,13 @@
         <v>20</v>
       </c>
       <c r="W24" t="s">
-        <v>497</v>
+        <v>511</v>
       </c>
       <c r="X24" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="25" spans="2:24">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="25" spans="2:25">
       <c r="B25" t="s">
         <v>466</v>
       </c>
@@ -10397,11 +10502,14 @@
         <v>462</v>
       </c>
       <c r="R25" t="s">
-        <v>496</v>
+        <v>509</v>
       </c>
       <c r="S25" t="s">
         <v>483</v>
       </c>
+      <c r="T25" t="s">
+        <v>513</v>
+      </c>
       <c r="U25" t="s">
         <v>10</v>
       </c>
@@ -10409,13 +10517,13 @@
         <v>20</v>
       </c>
       <c r="W25" t="s">
-        <v>497</v>
+        <v>511</v>
       </c>
       <c r="X25" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="26" spans="2:24">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="26" spans="2:25">
       <c r="B26" t="s">
         <v>466</v>
       </c>
@@ -10438,11 +10546,14 @@
         <v>115</v>
       </c>
       <c r="R26" t="s">
-        <v>496</v>
+        <v>509</v>
       </c>
       <c r="S26" t="s">
         <v>484</v>
       </c>
+      <c r="T26" t="s">
+        <v>514</v>
+      </c>
       <c r="U26" t="s">
         <v>10</v>
       </c>
@@ -10450,13 +10561,13 @@
         <v>20</v>
       </c>
       <c r="W26" t="s">
-        <v>497</v>
+        <v>511</v>
       </c>
       <c r="X26" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="27" spans="2:24">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="27" spans="2:25">
       <c r="B27" t="s">
         <v>466</v>
       </c>
@@ -10502,6 +10613,9 @@
       <c r="S27" t="s">
         <v>485</v>
       </c>
+      <c r="T27" t="s">
+        <v>515</v>
+      </c>
       <c r="U27" t="s">
         <v>10</v>
       </c>
@@ -10512,10 +10626,13 @@
         <v>218</v>
       </c>
       <c r="X27" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="28" spans="2:24">
+        <v>496</v>
+      </c>
+      <c r="Y27" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="28" spans="2:25">
       <c r="B28" t="s">
         <v>466</v>
       </c>
@@ -10561,6 +10678,9 @@
       <c r="S28" t="s">
         <v>491</v>
       </c>
+      <c r="T28" t="s">
+        <v>516</v>
+      </c>
       <c r="U28" t="s">
         <v>10</v>
       </c>
@@ -10571,10 +10691,13 @@
         <v>218</v>
       </c>
       <c r="X28" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="29" spans="2:24">
+        <v>496</v>
+      </c>
+      <c r="Y28" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="29" spans="2:25">
       <c r="B29" t="s">
         <v>466</v>
       </c>
@@ -10597,11 +10720,14 @@
         <v>468</v>
       </c>
       <c r="R29" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="S29" t="s">
         <v>492</v>
       </c>
+      <c r="T29" t="s">
+        <v>517</v>
+      </c>
       <c r="U29" t="s">
         <v>10</v>
       </c>
@@ -10612,10 +10738,10 @@
         <v>218</v>
       </c>
       <c r="X29" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="30" spans="2:24">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="30" spans="2:25">
       <c r="B30" t="s">
         <v>466</v>
       </c>
@@ -10638,7 +10764,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="31" spans="2:24">
+    <row r="31" spans="2:25">
       <c r="B31" t="s">
         <v>470</v>
       </c>
@@ -10661,7 +10787,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="32" spans="2:24">
+    <row r="32" spans="2:25">
       <c r="B32" t="s">
         <v>470</v>
       </c>
@@ -12935,22 +13061,22 @@
         <v>2100.8000000000002</v>
       </c>
       <c r="H109">
-        <v>1711.4</v>
+        <v>1390.7</v>
       </c>
       <c r="I109">
-        <v>1451.3</v>
+        <v>1117.5999999999999</v>
       </c>
       <c r="J109">
-        <v>1347.4</v>
+        <v>1028.7</v>
       </c>
       <c r="K109">
-        <v>1243.5</v>
+        <v>939.8</v>
       </c>
       <c r="L109">
-        <v>1139.5999999999999</v>
+        <v>850.9</v>
       </c>
       <c r="M109">
-        <v>1035.8</v>
+        <v>762</v>
       </c>
       <c r="N109" t="s">
         <v>460</v>
@@ -12964,22 +13090,22 @@
         <v>48.2</v>
       </c>
       <c r="H110">
-        <v>38.799999999999997</v>
+        <v>31</v>
       </c>
       <c r="I110">
-        <v>32.5</v>
+        <v>24.5</v>
       </c>
       <c r="J110">
-        <v>30</v>
+        <v>22.3</v>
       </c>
       <c r="K110">
-        <v>27.5</v>
+        <v>20.2</v>
       </c>
       <c r="L110">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="M110">
-        <v>22.5</v>
+        <v>15.9</v>
       </c>
       <c r="N110" t="s">
         <v>461</v>
@@ -13276,22 +13402,22 @@
         <v>3721.6</v>
       </c>
       <c r="H119">
-        <v>2996.4</v>
+        <v>2436.3000000000002</v>
       </c>
       <c r="I119">
-        <v>2470</v>
+        <v>1940.6</v>
       </c>
       <c r="J119">
-        <v>2273.5</v>
+        <v>1780.6</v>
       </c>
       <c r="K119">
-        <v>2077.5</v>
+        <v>1617.6</v>
       </c>
       <c r="L119">
-        <v>1882.2</v>
+        <v>1457.5</v>
       </c>
       <c r="M119">
-        <v>1687.7</v>
+        <v>1297.5</v>
       </c>
       <c r="N119" t="s">
         <v>460</v>
@@ -13305,22 +13431,22 @@
         <v>87.3</v>
       </c>
       <c r="H120">
-        <v>69.8</v>
+        <v>56.3</v>
       </c>
       <c r="I120">
-        <v>57.1</v>
+        <v>44.3</v>
       </c>
       <c r="J120">
-        <v>52.3</v>
+        <v>40.4</v>
       </c>
       <c r="K120">
-        <v>47.6</v>
+        <v>36.5</v>
       </c>
       <c r="L120">
-        <v>42.9</v>
+        <v>32.700000000000003</v>
       </c>
       <c r="M120">
-        <v>38.200000000000003</v>
+        <v>28.8</v>
       </c>
       <c r="N120" t="s">
         <v>461</v>
@@ -13943,7 +14069,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0EF94235-1B5A-4740-BAA3-75407316041B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B9325FF-5D1B-41D3-B3B3-572D34CFCA51}">
   <dimension ref="B9:T88"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -13963,7 +14089,7 @@
         <v>140</v>
       </c>
       <c r="D10" t="s">
-        <v>499</v>
+        <v>519</v>
       </c>
       <c r="E10" t="s">
         <v>141</v>
@@ -13984,22 +14110,22 @@
         <v>140</v>
       </c>
       <c r="L10" t="s">
-        <v>499</v>
+        <v>519</v>
       </c>
       <c r="M10" t="s">
         <v>190</v>
       </c>
       <c r="N10" t="s">
-        <v>658</v>
+        <v>678</v>
       </c>
       <c r="O10" t="s">
         <v>52</v>
       </c>
       <c r="P10" t="s">
-        <v>659</v>
+        <v>679</v>
       </c>
       <c r="Q10" t="s">
-        <v>660</v>
+        <v>680</v>
       </c>
       <c r="R10" t="s">
         <v>462</v>
@@ -14016,19 +14142,19 @@
         <v>214</v>
       </c>
       <c r="C11" t="s">
-        <v>500</v>
+        <v>520</v>
       </c>
       <c r="D11" t="s">
-        <v>501</v>
+        <v>521</v>
       </c>
       <c r="E11" t="s">
-        <v>502</v>
+        <v>522</v>
       </c>
       <c r="F11" t="s">
-        <v>503</v>
+        <v>523</v>
       </c>
       <c r="G11" t="s">
-        <v>503</v>
+        <v>523</v>
       </c>
       <c r="H11" t="s">
         <v>149</v>
@@ -14037,13 +14163,13 @@
         <v>150</v>
       </c>
       <c r="K11" t="s">
-        <v>500</v>
+        <v>520</v>
       </c>
       <c r="L11" t="s">
-        <v>501</v>
+        <v>521</v>
       </c>
       <c r="M11" t="s">
-        <v>661</v>
+        <v>681</v>
       </c>
       <c r="N11">
         <v>319.327</v>
@@ -14061,7 +14187,7 @@
         <v>0.03</v>
       </c>
       <c r="T11" t="s">
-        <v>662</v>
+        <v>682</v>
       </c>
     </row>
     <row r="12" spans="2:20">
@@ -14069,19 +14195,19 @@
         <v>214</v>
       </c>
       <c r="C12" t="s">
-        <v>504</v>
+        <v>524</v>
       </c>
       <c r="D12" t="s">
-        <v>501</v>
+        <v>521</v>
       </c>
       <c r="E12" t="s">
-        <v>505</v>
+        <v>525</v>
       </c>
       <c r="F12" t="s">
-        <v>503</v>
+        <v>523</v>
       </c>
       <c r="G12" t="s">
-        <v>503</v>
+        <v>523</v>
       </c>
       <c r="H12" t="s">
         <v>149</v>
@@ -14090,13 +14216,13 @@
         <v>150</v>
       </c>
       <c r="K12" t="s">
-        <v>504</v>
+        <v>524</v>
       </c>
       <c r="L12" t="s">
-        <v>501</v>
+        <v>521</v>
       </c>
       <c r="M12" t="s">
-        <v>663</v>
+        <v>683</v>
       </c>
       <c r="N12">
         <v>882.43899999999996</v>
@@ -14114,7 +14240,7 @@
         <v>0.08</v>
       </c>
       <c r="T12" t="s">
-        <v>662</v>
+        <v>682</v>
       </c>
     </row>
     <row r="13" spans="2:20">
@@ -14122,19 +14248,19 @@
         <v>214</v>
       </c>
       <c r="C13" t="s">
-        <v>506</v>
+        <v>526</v>
       </c>
       <c r="D13" t="s">
-        <v>501</v>
+        <v>521</v>
       </c>
       <c r="E13" t="s">
-        <v>507</v>
+        <v>527</v>
       </c>
       <c r="F13" t="s">
-        <v>503</v>
+        <v>523</v>
       </c>
       <c r="G13" t="s">
-        <v>503</v>
+        <v>523</v>
       </c>
       <c r="H13" t="s">
         <v>149</v>
@@ -14143,13 +14269,13 @@
         <v>150</v>
       </c>
       <c r="K13" t="s">
-        <v>506</v>
+        <v>526</v>
       </c>
       <c r="L13" t="s">
-        <v>501</v>
+        <v>521</v>
       </c>
       <c r="M13" t="s">
-        <v>664</v>
+        <v>684</v>
       </c>
       <c r="N13">
         <v>861.25900000000001</v>
@@ -14167,7 +14293,7 @@
         <v>0.08</v>
       </c>
       <c r="T13" t="s">
-        <v>662</v>
+        <v>682</v>
       </c>
     </row>
     <row r="14" spans="2:20">
@@ -14175,19 +14301,19 @@
         <v>214</v>
       </c>
       <c r="C14" t="s">
-        <v>508</v>
+        <v>528</v>
       </c>
       <c r="D14" t="s">
-        <v>501</v>
+        <v>521</v>
       </c>
       <c r="E14" t="s">
-        <v>509</v>
+        <v>529</v>
       </c>
       <c r="F14" t="s">
-        <v>503</v>
+        <v>523</v>
       </c>
       <c r="G14" t="s">
-        <v>503</v>
+        <v>523</v>
       </c>
       <c r="H14" t="s">
         <v>149</v>
@@ -14196,13 +14322,13 @@
         <v>150</v>
       </c>
       <c r="K14" t="s">
-        <v>508</v>
+        <v>528</v>
       </c>
       <c r="L14" t="s">
-        <v>501</v>
+        <v>521</v>
       </c>
       <c r="M14" t="s">
-        <v>665</v>
+        <v>685</v>
       </c>
       <c r="N14">
         <v>304.55599999999998</v>
@@ -14220,7 +14346,7 @@
         <v>0.08</v>
       </c>
       <c r="T14" t="s">
-        <v>662</v>
+        <v>682</v>
       </c>
     </row>
     <row r="15" spans="2:20">
@@ -14228,19 +14354,19 @@
         <v>214</v>
       </c>
       <c r="C15" t="s">
-        <v>510</v>
+        <v>530</v>
       </c>
       <c r="D15" t="s">
-        <v>501</v>
+        <v>521</v>
       </c>
       <c r="E15" t="s">
-        <v>511</v>
+        <v>531</v>
       </c>
       <c r="F15" t="s">
-        <v>503</v>
+        <v>523</v>
       </c>
       <c r="G15" t="s">
-        <v>503</v>
+        <v>523</v>
       </c>
       <c r="H15" t="s">
         <v>149</v>
@@ -14249,13 +14375,13 @@
         <v>150</v>
       </c>
       <c r="K15" t="s">
-        <v>510</v>
+        <v>530</v>
       </c>
       <c r="L15" t="s">
-        <v>501</v>
+        <v>521</v>
       </c>
       <c r="M15" t="s">
-        <v>666</v>
+        <v>686</v>
       </c>
       <c r="N15">
         <v>3132.1019999999999</v>
@@ -14273,7 +14399,7 @@
         <v>0.08</v>
       </c>
       <c r="T15" t="s">
-        <v>662</v>
+        <v>682</v>
       </c>
     </row>
     <row r="16" spans="2:20">
@@ -14281,19 +14407,19 @@
         <v>214</v>
       </c>
       <c r="C16" t="s">
-        <v>512</v>
+        <v>532</v>
       </c>
       <c r="D16" t="s">
-        <v>501</v>
+        <v>521</v>
       </c>
       <c r="E16" t="s">
-        <v>513</v>
+        <v>533</v>
       </c>
       <c r="F16" t="s">
-        <v>503</v>
+        <v>523</v>
       </c>
       <c r="G16" t="s">
-        <v>503</v>
+        <v>523</v>
       </c>
       <c r="H16" t="s">
         <v>149</v>
@@ -14302,13 +14428,13 @@
         <v>150</v>
       </c>
       <c r="K16" t="s">
-        <v>512</v>
+        <v>532</v>
       </c>
       <c r="L16" t="s">
-        <v>501</v>
+        <v>521</v>
       </c>
       <c r="M16" t="s">
-        <v>667</v>
+        <v>687</v>
       </c>
       <c r="N16">
         <v>1600.077</v>
@@ -14326,7 +14452,7 @@
         <v>0.08</v>
       </c>
       <c r="T16" t="s">
-        <v>662</v>
+        <v>682</v>
       </c>
     </row>
     <row r="17" spans="2:20">
@@ -14334,19 +14460,19 @@
         <v>214</v>
       </c>
       <c r="C17" t="s">
-        <v>514</v>
+        <v>534</v>
       </c>
       <c r="D17" t="s">
-        <v>501</v>
+        <v>521</v>
       </c>
       <c r="E17" t="s">
-        <v>515</v>
+        <v>535</v>
       </c>
       <c r="F17" t="s">
-        <v>503</v>
+        <v>523</v>
       </c>
       <c r="G17" t="s">
-        <v>503</v>
+        <v>523</v>
       </c>
       <c r="H17" t="s">
         <v>149</v>
@@ -14355,13 +14481,13 @@
         <v>150</v>
       </c>
       <c r="K17" t="s">
-        <v>514</v>
+        <v>534</v>
       </c>
       <c r="L17" t="s">
-        <v>501</v>
+        <v>521</v>
       </c>
       <c r="M17" t="s">
-        <v>668</v>
+        <v>688</v>
       </c>
       <c r="N17">
         <v>1623.857</v>
@@ -14379,7 +14505,7 @@
         <v>0.08</v>
       </c>
       <c r="T17" t="s">
-        <v>662</v>
+        <v>682</v>
       </c>
     </row>
     <row r="18" spans="2:20">
@@ -14387,19 +14513,19 @@
         <v>214</v>
       </c>
       <c r="C18" t="s">
-        <v>516</v>
+        <v>536</v>
       </c>
       <c r="D18" t="s">
-        <v>501</v>
+        <v>521</v>
       </c>
       <c r="E18" t="s">
-        <v>517</v>
+        <v>537</v>
       </c>
       <c r="F18" t="s">
-        <v>503</v>
+        <v>523</v>
       </c>
       <c r="G18" t="s">
-        <v>503</v>
+        <v>523</v>
       </c>
       <c r="H18" t="s">
         <v>149</v>
@@ -14408,13 +14534,13 @@
         <v>150</v>
       </c>
       <c r="K18" t="s">
-        <v>516</v>
+        <v>536</v>
       </c>
       <c r="L18" t="s">
-        <v>501</v>
+        <v>521</v>
       </c>
       <c r="M18" t="s">
-        <v>669</v>
+        <v>689</v>
       </c>
       <c r="N18">
         <v>1552.307</v>
@@ -14432,7 +14558,7 @@
         <v>0.08</v>
       </c>
       <c r="T18" t="s">
-        <v>662</v>
+        <v>682</v>
       </c>
     </row>
     <row r="19" spans="2:20">
@@ -14440,19 +14566,19 @@
         <v>214</v>
       </c>
       <c r="C19" t="s">
-        <v>518</v>
+        <v>538</v>
       </c>
       <c r="D19" t="s">
-        <v>501</v>
+        <v>521</v>
       </c>
       <c r="E19" t="s">
-        <v>519</v>
+        <v>539</v>
       </c>
       <c r="F19" t="s">
-        <v>503</v>
+        <v>523</v>
       </c>
       <c r="G19" t="s">
-        <v>503</v>
+        <v>523</v>
       </c>
       <c r="H19" t="s">
         <v>149</v>
@@ -14461,13 +14587,13 @@
         <v>150</v>
       </c>
       <c r="K19" t="s">
-        <v>518</v>
+        <v>538</v>
       </c>
       <c r="L19" t="s">
-        <v>501</v>
+        <v>521</v>
       </c>
       <c r="M19" t="s">
-        <v>670</v>
+        <v>690</v>
       </c>
       <c r="N19">
         <v>493.09899999999999</v>
@@ -14485,7 +14611,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="T19" t="s">
-        <v>662</v>
+        <v>682</v>
       </c>
     </row>
     <row r="20" spans="2:20">
@@ -14493,19 +14619,19 @@
         <v>214</v>
       </c>
       <c r="C20" t="s">
-        <v>520</v>
+        <v>540</v>
       </c>
       <c r="D20" t="s">
-        <v>501</v>
+        <v>521</v>
       </c>
       <c r="E20" t="s">
-        <v>521</v>
+        <v>541</v>
       </c>
       <c r="F20" t="s">
-        <v>503</v>
+        <v>523</v>
       </c>
       <c r="G20" t="s">
-        <v>503</v>
+        <v>523</v>
       </c>
       <c r="H20" t="s">
         <v>149</v>
@@ -14514,13 +14640,13 @@
         <v>150</v>
       </c>
       <c r="K20" t="s">
-        <v>520</v>
+        <v>540</v>
       </c>
       <c r="L20" t="s">
-        <v>501</v>
+        <v>521</v>
       </c>
       <c r="M20" t="s">
-        <v>671</v>
+        <v>691</v>
       </c>
       <c r="N20">
         <v>131.52799999999999</v>
@@ -14538,7 +14664,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="T20" t="s">
-        <v>662</v>
+        <v>682</v>
       </c>
     </row>
     <row r="21" spans="2:20">
@@ -14546,19 +14672,19 @@
         <v>214</v>
       </c>
       <c r="C21" t="s">
-        <v>522</v>
+        <v>542</v>
       </c>
       <c r="D21" t="s">
-        <v>501</v>
+        <v>521</v>
       </c>
       <c r="E21" t="s">
+        <v>543</v>
+      </c>
+      <c r="F21" t="s">
         <v>523</v>
       </c>
-      <c r="F21" t="s">
-        <v>503</v>
-      </c>
       <c r="G21" t="s">
-        <v>503</v>
+        <v>523</v>
       </c>
       <c r="H21" t="s">
         <v>149</v>
@@ -14567,13 +14693,13 @@
         <v>150</v>
       </c>
       <c r="K21" t="s">
-        <v>522</v>
+        <v>542</v>
       </c>
       <c r="L21" t="s">
-        <v>501</v>
+        <v>521</v>
       </c>
       <c r="M21" t="s">
-        <v>666</v>
+        <v>686</v>
       </c>
       <c r="N21">
         <v>601.34699999999998</v>
@@ -14591,7 +14717,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="T21" t="s">
-        <v>662</v>
+        <v>682</v>
       </c>
     </row>
     <row r="22" spans="2:20">
@@ -14599,19 +14725,19 @@
         <v>214</v>
       </c>
       <c r="C22" t="s">
-        <v>524</v>
+        <v>544</v>
       </c>
       <c r="D22" t="s">
-        <v>501</v>
+        <v>521</v>
       </c>
       <c r="E22" t="s">
-        <v>525</v>
+        <v>545</v>
       </c>
       <c r="F22" t="s">
-        <v>503</v>
+        <v>523</v>
       </c>
       <c r="G22" t="s">
-        <v>503</v>
+        <v>523</v>
       </c>
       <c r="H22" t="s">
         <v>149</v>
@@ -14620,13 +14746,13 @@
         <v>150</v>
       </c>
       <c r="K22" t="s">
-        <v>524</v>
+        <v>544</v>
       </c>
       <c r="L22" t="s">
-        <v>501</v>
+        <v>521</v>
       </c>
       <c r="M22" t="s">
-        <v>672</v>
+        <v>692</v>
       </c>
       <c r="N22">
         <v>974.39300000000003</v>
@@ -14644,7 +14770,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="T22" t="s">
-        <v>662</v>
+        <v>682</v>
       </c>
     </row>
     <row r="23" spans="2:20">
@@ -14652,19 +14778,19 @@
         <v>214</v>
       </c>
       <c r="C23" t="s">
-        <v>526</v>
+        <v>546</v>
       </c>
       <c r="D23" t="s">
-        <v>501</v>
+        <v>521</v>
       </c>
       <c r="E23" t="s">
-        <v>527</v>
+        <v>547</v>
       </c>
       <c r="F23" t="s">
-        <v>503</v>
+        <v>523</v>
       </c>
       <c r="G23" t="s">
-        <v>503</v>
+        <v>523</v>
       </c>
       <c r="H23" t="s">
         <v>149</v>
@@ -14673,13 +14799,13 @@
         <v>150</v>
       </c>
       <c r="K23" t="s">
-        <v>526</v>
+        <v>546</v>
       </c>
       <c r="L23" t="s">
-        <v>501</v>
+        <v>521</v>
       </c>
       <c r="M23" t="s">
-        <v>673</v>
+        <v>693</v>
       </c>
       <c r="N23">
         <v>2487.9319999999998</v>
@@ -14697,7 +14823,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="T23" t="s">
-        <v>662</v>
+        <v>682</v>
       </c>
     </row>
     <row r="24" spans="2:20">
@@ -14705,19 +14831,19 @@
         <v>214</v>
       </c>
       <c r="C24" t="s">
-        <v>528</v>
+        <v>548</v>
       </c>
       <c r="D24" t="s">
-        <v>501</v>
+        <v>521</v>
       </c>
       <c r="E24" t="s">
-        <v>529</v>
+        <v>549</v>
       </c>
       <c r="F24" t="s">
-        <v>503</v>
+        <v>523</v>
       </c>
       <c r="G24" t="s">
-        <v>503</v>
+        <v>523</v>
       </c>
       <c r="H24" t="s">
         <v>149</v>
@@ -14726,13 +14852,13 @@
         <v>150</v>
       </c>
       <c r="K24" t="s">
-        <v>528</v>
+        <v>548</v>
       </c>
       <c r="L24" t="s">
-        <v>501</v>
+        <v>521</v>
       </c>
       <c r="M24" t="s">
-        <v>674</v>
+        <v>694</v>
       </c>
       <c r="N24">
         <v>831.85599999999999</v>
@@ -14750,7 +14876,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="T24" t="s">
-        <v>662</v>
+        <v>682</v>
       </c>
     </row>
     <row r="25" spans="2:20">
@@ -14758,19 +14884,19 @@
         <v>214</v>
       </c>
       <c r="C25" t="s">
-        <v>530</v>
+        <v>550</v>
       </c>
       <c r="D25" t="s">
-        <v>501</v>
+        <v>521</v>
       </c>
       <c r="E25" t="s">
-        <v>531</v>
+        <v>551</v>
       </c>
       <c r="F25" t="s">
-        <v>503</v>
+        <v>523</v>
       </c>
       <c r="G25" t="s">
-        <v>503</v>
+        <v>523</v>
       </c>
       <c r="H25" t="s">
         <v>149</v>
@@ -14779,13 +14905,13 @@
         <v>150</v>
       </c>
       <c r="K25" t="s">
-        <v>530</v>
+        <v>550</v>
       </c>
       <c r="L25" t="s">
-        <v>501</v>
+        <v>521</v>
       </c>
       <c r="M25" t="s">
-        <v>675</v>
+        <v>695</v>
       </c>
       <c r="N25">
         <v>1126.671</v>
@@ -14803,7 +14929,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="T25" t="s">
-        <v>662</v>
+        <v>682</v>
       </c>
     </row>
     <row r="26" spans="2:20">
@@ -14811,19 +14937,19 @@
         <v>214</v>
       </c>
       <c r="C26" t="s">
-        <v>532</v>
+        <v>552</v>
       </c>
       <c r="D26" t="s">
-        <v>501</v>
+        <v>521</v>
       </c>
       <c r="E26" t="s">
-        <v>533</v>
+        <v>553</v>
       </c>
       <c r="F26" t="s">
-        <v>503</v>
+        <v>523</v>
       </c>
       <c r="G26" t="s">
-        <v>503</v>
+        <v>523</v>
       </c>
       <c r="H26" t="s">
         <v>149</v>
@@ -14832,13 +14958,13 @@
         <v>150</v>
       </c>
       <c r="K26" t="s">
-        <v>532</v>
+        <v>552</v>
       </c>
       <c r="L26" t="s">
-        <v>501</v>
+        <v>521</v>
       </c>
       <c r="M26" t="s">
-        <v>665</v>
+        <v>685</v>
       </c>
       <c r="N26">
         <v>275.786</v>
@@ -14856,7 +14982,7 @@
         <v>0.09</v>
       </c>
       <c r="T26" t="s">
-        <v>662</v>
+        <v>682</v>
       </c>
     </row>
     <row r="27" spans="2:20">
@@ -14864,19 +14990,19 @@
         <v>214</v>
       </c>
       <c r="C27" t="s">
-        <v>534</v>
+        <v>554</v>
       </c>
       <c r="D27" t="s">
-        <v>501</v>
+        <v>521</v>
       </c>
       <c r="E27" t="s">
-        <v>535</v>
+        <v>555</v>
       </c>
       <c r="F27" t="s">
-        <v>503</v>
+        <v>523</v>
       </c>
       <c r="G27" t="s">
-        <v>503</v>
+        <v>523</v>
       </c>
       <c r="H27" t="s">
         <v>149</v>
@@ -14885,13 +15011,13 @@
         <v>150</v>
       </c>
       <c r="K27" t="s">
-        <v>534</v>
+        <v>554</v>
       </c>
       <c r="L27" t="s">
-        <v>501</v>
+        <v>521</v>
       </c>
       <c r="M27" t="s">
-        <v>676</v>
+        <v>696</v>
       </c>
       <c r="N27">
         <v>167.37799999999999</v>
@@ -14909,7 +15035,7 @@
         <v>0.09</v>
       </c>
       <c r="T27" t="s">
-        <v>662</v>
+        <v>682</v>
       </c>
     </row>
     <row r="28" spans="2:20">
@@ -14917,19 +15043,19 @@
         <v>214</v>
       </c>
       <c r="C28" t="s">
-        <v>536</v>
+        <v>556</v>
       </c>
       <c r="D28" t="s">
-        <v>501</v>
+        <v>521</v>
       </c>
       <c r="E28" t="s">
-        <v>537</v>
+        <v>557</v>
       </c>
       <c r="F28" t="s">
-        <v>503</v>
+        <v>523</v>
       </c>
       <c r="G28" t="s">
-        <v>503</v>
+        <v>523</v>
       </c>
       <c r="H28" t="s">
         <v>149</v>
@@ -14938,13 +15064,13 @@
         <v>150</v>
       </c>
       <c r="K28" t="s">
-        <v>536</v>
+        <v>556</v>
       </c>
       <c r="L28" t="s">
-        <v>501</v>
+        <v>521</v>
       </c>
       <c r="M28" t="s">
-        <v>670</v>
+        <v>690</v>
       </c>
       <c r="N28">
         <v>188.172</v>
@@ -14962,7 +15088,7 @@
         <v>0.09</v>
       </c>
       <c r="T28" t="s">
-        <v>662</v>
+        <v>682</v>
       </c>
     </row>
     <row r="29" spans="2:20">
@@ -14970,19 +15096,19 @@
         <v>214</v>
       </c>
       <c r="C29" t="s">
-        <v>538</v>
+        <v>558</v>
       </c>
       <c r="D29" t="s">
-        <v>501</v>
+        <v>521</v>
       </c>
       <c r="E29" t="s">
-        <v>539</v>
+        <v>559</v>
       </c>
       <c r="F29" t="s">
-        <v>503</v>
+        <v>523</v>
       </c>
       <c r="G29" t="s">
-        <v>503</v>
+        <v>523</v>
       </c>
       <c r="H29" t="s">
         <v>149</v>
@@ -14991,13 +15117,13 @@
         <v>150</v>
       </c>
       <c r="K29" t="s">
-        <v>538</v>
+        <v>558</v>
       </c>
       <c r="L29" t="s">
-        <v>501</v>
+        <v>521</v>
       </c>
       <c r="M29" t="s">
-        <v>677</v>
+        <v>697</v>
       </c>
       <c r="N29">
         <v>272.721</v>
@@ -15015,7 +15141,7 @@
         <v>0.09</v>
       </c>
       <c r="T29" t="s">
-        <v>662</v>
+        <v>682</v>
       </c>
     </row>
     <row r="30" spans="2:20">
@@ -15023,19 +15149,19 @@
         <v>214</v>
       </c>
       <c r="C30" t="s">
-        <v>540</v>
+        <v>560</v>
       </c>
       <c r="D30" t="s">
-        <v>501</v>
+        <v>521</v>
       </c>
       <c r="E30" t="s">
-        <v>541</v>
+        <v>561</v>
       </c>
       <c r="F30" t="s">
-        <v>503</v>
+        <v>523</v>
       </c>
       <c r="G30" t="s">
-        <v>503</v>
+        <v>523</v>
       </c>
       <c r="H30" t="s">
         <v>149</v>
@@ -15044,13 +15170,13 @@
         <v>150</v>
       </c>
       <c r="K30" t="s">
-        <v>540</v>
+        <v>560</v>
       </c>
       <c r="L30" t="s">
-        <v>501</v>
+        <v>521</v>
       </c>
       <c r="M30" t="s">
-        <v>663</v>
+        <v>683</v>
       </c>
       <c r="N30">
         <v>176.96699999999998</v>
@@ -15068,7 +15194,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="T30" t="s">
-        <v>662</v>
+        <v>682</v>
       </c>
     </row>
     <row r="31" spans="2:20">
@@ -15076,19 +15202,19 @@
         <v>214</v>
       </c>
       <c r="C31" t="s">
-        <v>542</v>
+        <v>562</v>
       </c>
       <c r="D31" t="s">
-        <v>501</v>
+        <v>521</v>
       </c>
       <c r="E31" t="s">
-        <v>543</v>
+        <v>563</v>
       </c>
       <c r="F31" t="s">
-        <v>503</v>
+        <v>523</v>
       </c>
       <c r="G31" t="s">
-        <v>503</v>
+        <v>523</v>
       </c>
       <c r="H31" t="s">
         <v>149</v>
@@ -15097,13 +15223,13 @@
         <v>150</v>
       </c>
       <c r="K31" t="s">
-        <v>542</v>
+        <v>562</v>
       </c>
       <c r="L31" t="s">
-        <v>501</v>
+        <v>521</v>
       </c>
       <c r="M31" t="s">
-        <v>665</v>
+        <v>685</v>
       </c>
       <c r="N31">
         <v>129.97499999999999</v>
@@ -15121,7 +15247,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="T31" t="s">
-        <v>662</v>
+        <v>682</v>
       </c>
     </row>
     <row r="32" spans="2:20">
@@ -15129,19 +15255,19 @@
         <v>214</v>
       </c>
       <c r="C32" t="s">
-        <v>544</v>
+        <v>564</v>
       </c>
       <c r="D32" t="s">
-        <v>501</v>
+        <v>521</v>
       </c>
       <c r="E32" t="s">
-        <v>545</v>
+        <v>565</v>
       </c>
       <c r="F32" t="s">
-        <v>503</v>
+        <v>523</v>
       </c>
       <c r="G32" t="s">
-        <v>503</v>
+        <v>523</v>
       </c>
       <c r="H32" t="s">
         <v>149</v>
@@ -15150,13 +15276,13 @@
         <v>150</v>
       </c>
       <c r="K32" t="s">
-        <v>544</v>
+        <v>564</v>
       </c>
       <c r="L32" t="s">
-        <v>501</v>
+        <v>521</v>
       </c>
       <c r="M32" t="s">
-        <v>666</v>
+        <v>686</v>
       </c>
       <c r="N32">
         <v>314.16899999999998</v>
@@ -15174,7 +15300,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="T32" t="s">
-        <v>662</v>
+        <v>682</v>
       </c>
     </row>
     <row r="33" spans="2:20">
@@ -15182,19 +15308,19 @@
         <v>214</v>
       </c>
       <c r="C33" t="s">
-        <v>546</v>
+        <v>566</v>
       </c>
       <c r="D33" t="s">
-        <v>501</v>
+        <v>521</v>
       </c>
       <c r="E33" t="s">
-        <v>547</v>
+        <v>567</v>
       </c>
       <c r="F33" t="s">
-        <v>503</v>
+        <v>523</v>
       </c>
       <c r="G33" t="s">
-        <v>503</v>
+        <v>523</v>
       </c>
       <c r="H33" t="s">
         <v>149</v>
@@ -15203,13 +15329,13 @@
         <v>150</v>
       </c>
       <c r="K33" t="s">
-        <v>546</v>
+        <v>566</v>
       </c>
       <c r="L33" t="s">
-        <v>501</v>
+        <v>521</v>
       </c>
       <c r="M33" t="s">
-        <v>667</v>
+        <v>687</v>
       </c>
       <c r="N33">
         <v>245.42599999999999</v>
@@ -15227,7 +15353,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="T33" t="s">
-        <v>662</v>
+        <v>682</v>
       </c>
     </row>
     <row r="34" spans="2:20">
@@ -15235,19 +15361,19 @@
         <v>214</v>
       </c>
       <c r="C34" t="s">
-        <v>548</v>
+        <v>568</v>
       </c>
       <c r="D34" t="s">
-        <v>501</v>
+        <v>521</v>
       </c>
       <c r="E34" t="s">
-        <v>549</v>
+        <v>569</v>
       </c>
       <c r="F34" t="s">
-        <v>503</v>
+        <v>523</v>
       </c>
       <c r="G34" t="s">
-        <v>503</v>
+        <v>523</v>
       </c>
       <c r="H34" t="s">
         <v>149</v>
@@ -15256,13 +15382,13 @@
         <v>150</v>
       </c>
       <c r="K34" t="s">
-        <v>548</v>
+        <v>568</v>
       </c>
       <c r="L34" t="s">
-        <v>501</v>
+        <v>521</v>
       </c>
       <c r="M34" t="s">
-        <v>668</v>
+        <v>688</v>
       </c>
       <c r="N34">
         <v>19.093</v>
@@ -15280,7 +15406,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="T34" t="s">
-        <v>662</v>
+        <v>682</v>
       </c>
     </row>
     <row r="35" spans="2:20">
@@ -15288,19 +15414,19 @@
         <v>214</v>
       </c>
       <c r="C35" t="s">
-        <v>550</v>
+        <v>570</v>
       </c>
       <c r="D35" t="s">
-        <v>501</v>
+        <v>521</v>
       </c>
       <c r="E35" t="s">
-        <v>551</v>
+        <v>571</v>
       </c>
       <c r="F35" t="s">
-        <v>503</v>
+        <v>523</v>
       </c>
       <c r="G35" t="s">
-        <v>503</v>
+        <v>523</v>
       </c>
       <c r="H35" t="s">
         <v>149</v>
@@ -15309,13 +15435,13 @@
         <v>150</v>
       </c>
       <c r="K35" t="s">
-        <v>550</v>
+        <v>570</v>
       </c>
       <c r="L35" t="s">
-        <v>501</v>
+        <v>521</v>
       </c>
       <c r="M35" t="s">
-        <v>678</v>
+        <v>698</v>
       </c>
       <c r="N35">
         <v>378.12299999999999</v>
@@ -15333,7 +15459,7 @@
         <v>0.09</v>
       </c>
       <c r="T35" t="s">
-        <v>662</v>
+        <v>682</v>
       </c>
     </row>
     <row r="36" spans="2:20">
@@ -15341,19 +15467,19 @@
         <v>214</v>
       </c>
       <c r="C36" t="s">
-        <v>552</v>
+        <v>572</v>
       </c>
       <c r="D36" t="s">
-        <v>501</v>
+        <v>521</v>
       </c>
       <c r="E36" t="s">
-        <v>553</v>
+        <v>573</v>
       </c>
       <c r="F36" t="s">
-        <v>503</v>
+        <v>523</v>
       </c>
       <c r="G36" t="s">
-        <v>503</v>
+        <v>523</v>
       </c>
       <c r="H36" t="s">
         <v>149</v>
@@ -15362,13 +15488,13 @@
         <v>150</v>
       </c>
       <c r="K36" t="s">
-        <v>552</v>
+        <v>572</v>
       </c>
       <c r="L36" t="s">
-        <v>501</v>
+        <v>521</v>
       </c>
       <c r="M36" t="s">
-        <v>670</v>
+        <v>690</v>
       </c>
       <c r="N36">
         <v>196.30600000000001</v>
@@ -15386,7 +15512,7 @@
         <v>0.09</v>
       </c>
       <c r="T36" t="s">
-        <v>662</v>
+        <v>682</v>
       </c>
     </row>
     <row r="37" spans="2:20">
@@ -15394,19 +15520,19 @@
         <v>214</v>
       </c>
       <c r="C37" t="s">
-        <v>554</v>
+        <v>574</v>
       </c>
       <c r="D37" t="s">
-        <v>501</v>
+        <v>521</v>
       </c>
       <c r="E37" t="s">
-        <v>555</v>
+        <v>575</v>
       </c>
       <c r="F37" t="s">
-        <v>503</v>
+        <v>523</v>
       </c>
       <c r="G37" t="s">
-        <v>503</v>
+        <v>523</v>
       </c>
       <c r="H37" t="s">
         <v>149</v>
@@ -15415,13 +15541,13 @@
         <v>150</v>
       </c>
       <c r="K37" t="s">
-        <v>554</v>
+        <v>574</v>
       </c>
       <c r="L37" t="s">
-        <v>501</v>
+        <v>521</v>
       </c>
       <c r="M37" t="s">
-        <v>671</v>
+        <v>691</v>
       </c>
       <c r="N37">
         <v>430.95600000000002</v>
@@ -15439,7 +15565,7 @@
         <v>0.09</v>
       </c>
       <c r="T37" t="s">
-        <v>662</v>
+        <v>682</v>
       </c>
     </row>
     <row r="38" spans="2:20">
@@ -15447,19 +15573,19 @@
         <v>214</v>
       </c>
       <c r="C38" t="s">
-        <v>556</v>
+        <v>576</v>
       </c>
       <c r="D38" t="s">
-        <v>501</v>
+        <v>521</v>
       </c>
       <c r="E38" t="s">
-        <v>557</v>
+        <v>577</v>
       </c>
       <c r="F38" t="s">
-        <v>503</v>
+        <v>523</v>
       </c>
       <c r="G38" t="s">
-        <v>503</v>
+        <v>523</v>
       </c>
       <c r="H38" t="s">
         <v>149</v>
@@ -15468,13 +15594,13 @@
         <v>150</v>
       </c>
       <c r="K38" t="s">
-        <v>556</v>
+        <v>576</v>
       </c>
       <c r="L38" t="s">
-        <v>501</v>
+        <v>521</v>
       </c>
       <c r="M38" t="s">
-        <v>679</v>
+        <v>699</v>
       </c>
       <c r="N38">
         <v>1037.6130000000001</v>
@@ -15492,7 +15618,7 @@
         <v>0.09</v>
       </c>
       <c r="T38" t="s">
-        <v>662</v>
+        <v>682</v>
       </c>
     </row>
     <row r="39" spans="2:20">
@@ -15500,19 +15626,19 @@
         <v>214</v>
       </c>
       <c r="C39" t="s">
-        <v>558</v>
+        <v>578</v>
       </c>
       <c r="D39" t="s">
-        <v>501</v>
+        <v>521</v>
       </c>
       <c r="E39" t="s">
-        <v>559</v>
+        <v>579</v>
       </c>
       <c r="F39" t="s">
-        <v>503</v>
+        <v>523</v>
       </c>
       <c r="G39" t="s">
-        <v>503</v>
+        <v>523</v>
       </c>
       <c r="H39" t="s">
         <v>149</v>
@@ -15521,13 +15647,13 @@
         <v>150</v>
       </c>
       <c r="K39" t="s">
-        <v>558</v>
+        <v>578</v>
       </c>
       <c r="L39" t="s">
-        <v>501</v>
+        <v>521</v>
       </c>
       <c r="M39" t="s">
-        <v>680</v>
+        <v>700</v>
       </c>
       <c r="N39">
         <v>2044.3420000000001</v>
@@ -15545,7 +15671,7 @@
         <v>0.06</v>
       </c>
       <c r="T39" t="s">
-        <v>662</v>
+        <v>682</v>
       </c>
     </row>
     <row r="40" spans="2:20">
@@ -15553,19 +15679,19 @@
         <v>214</v>
       </c>
       <c r="C40" t="s">
-        <v>560</v>
+        <v>580</v>
       </c>
       <c r="D40" t="s">
-        <v>501</v>
+        <v>521</v>
       </c>
       <c r="E40" t="s">
-        <v>561</v>
+        <v>581</v>
       </c>
       <c r="F40" t="s">
-        <v>503</v>
+        <v>523</v>
       </c>
       <c r="G40" t="s">
-        <v>503</v>
+        <v>523</v>
       </c>
       <c r="H40" t="s">
         <v>149</v>
@@ -15574,13 +15700,13 @@
         <v>150</v>
       </c>
       <c r="K40" t="s">
-        <v>560</v>
+        <v>580</v>
       </c>
       <c r="L40" t="s">
-        <v>501</v>
+        <v>521</v>
       </c>
       <c r="M40" t="s">
-        <v>670</v>
+        <v>690</v>
       </c>
       <c r="N40">
         <v>97.498999999999995</v>
@@ -15598,7 +15724,7 @@
         <v>0.06</v>
       </c>
       <c r="T40" t="s">
-        <v>662</v>
+        <v>682</v>
       </c>
     </row>
     <row r="41" spans="2:20">
@@ -15606,19 +15732,19 @@
         <v>214</v>
       </c>
       <c r="C41" t="s">
-        <v>562</v>
+        <v>582</v>
       </c>
       <c r="D41" t="s">
-        <v>501</v>
+        <v>521</v>
       </c>
       <c r="E41" t="s">
-        <v>563</v>
+        <v>583</v>
       </c>
       <c r="F41" t="s">
-        <v>503</v>
+        <v>523</v>
       </c>
       <c r="G41" t="s">
-        <v>503</v>
+        <v>523</v>
       </c>
       <c r="H41" t="s">
         <v>149</v>
@@ -15627,13 +15753,13 @@
         <v>150</v>
       </c>
       <c r="K41" t="s">
-        <v>562</v>
+        <v>582</v>
       </c>
       <c r="L41" t="s">
-        <v>501</v>
+        <v>521</v>
       </c>
       <c r="M41" t="s">
-        <v>681</v>
+        <v>701</v>
       </c>
       <c r="N41">
         <v>6984.4229999999998</v>
@@ -15651,7 +15777,7 @@
         <v>0.06</v>
       </c>
       <c r="T41" t="s">
-        <v>662</v>
+        <v>682</v>
       </c>
     </row>
     <row r="42" spans="2:20">
@@ -15659,19 +15785,19 @@
         <v>214</v>
       </c>
       <c r="C42" t="s">
-        <v>564</v>
+        <v>584</v>
       </c>
       <c r="D42" t="s">
-        <v>501</v>
+        <v>521</v>
       </c>
       <c r="E42" t="s">
-        <v>565</v>
+        <v>585</v>
       </c>
       <c r="F42" t="s">
-        <v>503</v>
+        <v>523</v>
       </c>
       <c r="G42" t="s">
-        <v>503</v>
+        <v>523</v>
       </c>
       <c r="H42" t="s">
         <v>149</v>
@@ -15680,13 +15806,13 @@
         <v>150</v>
       </c>
       <c r="K42" t="s">
-        <v>564</v>
+        <v>584</v>
       </c>
       <c r="L42" t="s">
-        <v>501</v>
+        <v>521</v>
       </c>
       <c r="M42" t="s">
-        <v>682</v>
+        <v>702</v>
       </c>
       <c r="N42">
         <v>109.327</v>
@@ -15704,7 +15830,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="T42" t="s">
-        <v>662</v>
+        <v>682</v>
       </c>
     </row>
     <row r="43" spans="2:20">
@@ -15712,19 +15838,19 @@
         <v>214</v>
       </c>
       <c r="C43" t="s">
-        <v>566</v>
+        <v>586</v>
       </c>
       <c r="D43" t="s">
-        <v>501</v>
+        <v>521</v>
       </c>
       <c r="E43" t="s">
-        <v>567</v>
+        <v>587</v>
       </c>
       <c r="F43" t="s">
-        <v>503</v>
+        <v>523</v>
       </c>
       <c r="G43" t="s">
-        <v>503</v>
+        <v>523</v>
       </c>
       <c r="H43" t="s">
         <v>149</v>
@@ -15733,13 +15859,13 @@
         <v>150</v>
       </c>
       <c r="K43" t="s">
-        <v>566</v>
+        <v>586</v>
       </c>
       <c r="L43" t="s">
-        <v>501</v>
+        <v>521</v>
       </c>
       <c r="M43" t="s">
-        <v>683</v>
+        <v>703</v>
       </c>
       <c r="N43">
         <v>360.57299999999998</v>
@@ -15757,7 +15883,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="T43" t="s">
-        <v>662</v>
+        <v>682</v>
       </c>
     </row>
     <row r="44" spans="2:20">
@@ -15765,19 +15891,19 @@
         <v>214</v>
       </c>
       <c r="C44" t="s">
-        <v>568</v>
+        <v>588</v>
       </c>
       <c r="D44" t="s">
-        <v>501</v>
+        <v>521</v>
       </c>
       <c r="E44" t="s">
-        <v>569</v>
+        <v>589</v>
       </c>
       <c r="F44" t="s">
-        <v>503</v>
+        <v>523</v>
       </c>
       <c r="G44" t="s">
-        <v>503</v>
+        <v>523</v>
       </c>
       <c r="H44" t="s">
         <v>149</v>
@@ -15786,13 +15912,13 @@
         <v>150</v>
       </c>
       <c r="K44" t="s">
-        <v>568</v>
+        <v>588</v>
       </c>
       <c r="L44" t="s">
-        <v>501</v>
+        <v>521</v>
       </c>
       <c r="M44" t="s">
-        <v>684</v>
+        <v>704</v>
       </c>
       <c r="N44">
         <v>1932.395</v>
@@ -15810,7 +15936,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="T44" t="s">
-        <v>662</v>
+        <v>682</v>
       </c>
     </row>
     <row r="45" spans="2:20">
@@ -15818,19 +15944,19 @@
         <v>214</v>
       </c>
       <c r="C45" t="s">
-        <v>570</v>
+        <v>590</v>
       </c>
       <c r="D45" t="s">
-        <v>501</v>
+        <v>521</v>
       </c>
       <c r="E45" t="s">
-        <v>571</v>
+        <v>591</v>
       </c>
       <c r="F45" t="s">
-        <v>503</v>
+        <v>523</v>
       </c>
       <c r="G45" t="s">
-        <v>503</v>
+        <v>523</v>
       </c>
       <c r="H45" t="s">
         <v>149</v>
@@ -15839,13 +15965,13 @@
         <v>150</v>
       </c>
       <c r="K45" t="s">
-        <v>570</v>
+        <v>590</v>
       </c>
       <c r="L45" t="s">
-        <v>501</v>
+        <v>521</v>
       </c>
       <c r="M45" t="s">
-        <v>685</v>
+        <v>705</v>
       </c>
       <c r="N45">
         <v>494.291</v>
@@ -15863,7 +15989,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="T45" t="s">
-        <v>662</v>
+        <v>682</v>
       </c>
     </row>
     <row r="46" spans="2:20">
@@ -15871,19 +15997,19 @@
         <v>214</v>
       </c>
       <c r="C46" t="s">
-        <v>572</v>
+        <v>592</v>
       </c>
       <c r="D46" t="s">
-        <v>501</v>
+        <v>521</v>
       </c>
       <c r="E46" t="s">
-        <v>573</v>
+        <v>593</v>
       </c>
       <c r="F46" t="s">
-        <v>503</v>
+        <v>523</v>
       </c>
       <c r="G46" t="s">
-        <v>503</v>
+        <v>523</v>
       </c>
       <c r="H46" t="s">
         <v>149</v>
@@ -15892,13 +16018,13 @@
         <v>150</v>
       </c>
       <c r="K46" t="s">
-        <v>572</v>
+        <v>592</v>
       </c>
       <c r="L46" t="s">
-        <v>501</v>
+        <v>521</v>
       </c>
       <c r="M46" t="s">
-        <v>663</v>
+        <v>683</v>
       </c>
       <c r="N46">
         <v>1545.7440000000001</v>
@@ -15916,7 +16042,7 @@
         <v>0.06</v>
       </c>
       <c r="T46" t="s">
-        <v>662</v>
+        <v>682</v>
       </c>
     </row>
     <row r="47" spans="2:20">
@@ -15924,19 +16050,19 @@
         <v>214</v>
       </c>
       <c r="C47" t="s">
-        <v>574</v>
+        <v>594</v>
       </c>
       <c r="D47" t="s">
-        <v>501</v>
+        <v>521</v>
       </c>
       <c r="E47" t="s">
-        <v>575</v>
+        <v>595</v>
       </c>
       <c r="F47" t="s">
-        <v>503</v>
+        <v>523</v>
       </c>
       <c r="G47" t="s">
-        <v>503</v>
+        <v>523</v>
       </c>
       <c r="H47" t="s">
         <v>149</v>
@@ -15945,13 +16071,13 @@
         <v>150</v>
       </c>
       <c r="K47" t="s">
-        <v>574</v>
+        <v>594</v>
       </c>
       <c r="L47" t="s">
-        <v>501</v>
+        <v>521</v>
       </c>
       <c r="M47" t="s">
-        <v>670</v>
+        <v>690</v>
       </c>
       <c r="N47">
         <v>7482.6549999999997</v>
@@ -15969,7 +16095,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="T47" t="s">
-        <v>662</v>
+        <v>682</v>
       </c>
     </row>
     <row r="48" spans="2:20">
@@ -15977,19 +16103,19 @@
         <v>214</v>
       </c>
       <c r="C48" t="s">
-        <v>576</v>
+        <v>596</v>
       </c>
       <c r="D48" t="s">
-        <v>501</v>
+        <v>521</v>
       </c>
       <c r="E48" t="s">
-        <v>577</v>
+        <v>597</v>
       </c>
       <c r="F48" t="s">
-        <v>503</v>
+        <v>523</v>
       </c>
       <c r="G48" t="s">
-        <v>503</v>
+        <v>523</v>
       </c>
       <c r="H48" t="s">
         <v>149</v>
@@ -15998,13 +16124,13 @@
         <v>150</v>
       </c>
       <c r="K48" t="s">
-        <v>576</v>
+        <v>596</v>
       </c>
       <c r="L48" t="s">
-        <v>501</v>
+        <v>521</v>
       </c>
       <c r="M48" t="s">
-        <v>686</v>
+        <v>706</v>
       </c>
       <c r="N48">
         <v>386.70000000000005</v>
@@ -16022,7 +16148,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="T48" t="s">
-        <v>662</v>
+        <v>682</v>
       </c>
     </row>
     <row r="49" spans="2:20">
@@ -16030,19 +16156,19 @@
         <v>214</v>
       </c>
       <c r="C49" t="s">
-        <v>578</v>
+        <v>598</v>
       </c>
       <c r="D49" t="s">
-        <v>501</v>
+        <v>521</v>
       </c>
       <c r="E49" t="s">
-        <v>579</v>
+        <v>599</v>
       </c>
       <c r="F49" t="s">
-        <v>503</v>
+        <v>523</v>
       </c>
       <c r="G49" t="s">
-        <v>503</v>
+        <v>523</v>
       </c>
       <c r="H49" t="s">
         <v>149</v>
@@ -16051,13 +16177,13 @@
         <v>150</v>
       </c>
       <c r="K49" t="s">
-        <v>578</v>
+        <v>598</v>
       </c>
       <c r="L49" t="s">
-        <v>501</v>
+        <v>521</v>
       </c>
       <c r="M49" t="s">
-        <v>668</v>
+        <v>688</v>
       </c>
       <c r="N49">
         <v>120.292</v>
@@ -16075,7 +16201,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="T49" t="s">
-        <v>662</v>
+        <v>682</v>
       </c>
     </row>
     <row r="50" spans="2:20">
@@ -16083,19 +16209,19 @@
         <v>214</v>
       </c>
       <c r="C50" t="s">
-        <v>580</v>
+        <v>600</v>
       </c>
       <c r="D50" t="s">
-        <v>501</v>
+        <v>521</v>
       </c>
       <c r="E50" t="s">
-        <v>581</v>
+        <v>601</v>
       </c>
       <c r="F50" t="s">
-        <v>503</v>
+        <v>523</v>
       </c>
       <c r="G50" t="s">
-        <v>503</v>
+        <v>523</v>
       </c>
       <c r="H50" t="s">
         <v>149</v>
@@ -16104,13 +16230,13 @@
         <v>150</v>
       </c>
       <c r="K50" t="s">
-        <v>580</v>
+        <v>600</v>
       </c>
       <c r="L50" t="s">
-        <v>501</v>
+        <v>521</v>
       </c>
       <c r="M50" t="s">
-        <v>687</v>
+        <v>707</v>
       </c>
       <c r="N50">
         <v>294.22699999999998</v>
@@ -16128,7 +16254,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="T50" t="s">
-        <v>662</v>
+        <v>682</v>
       </c>
     </row>
     <row r="51" spans="2:20">
@@ -16136,19 +16262,19 @@
         <v>214</v>
       </c>
       <c r="C51" t="s">
-        <v>582</v>
+        <v>602</v>
       </c>
       <c r="D51" t="s">
-        <v>501</v>
+        <v>521</v>
       </c>
       <c r="E51" t="s">
-        <v>583</v>
+        <v>603</v>
       </c>
       <c r="F51" t="s">
-        <v>503</v>
+        <v>523</v>
       </c>
       <c r="G51" t="s">
-        <v>503</v>
+        <v>523</v>
       </c>
       <c r="H51" t="s">
         <v>149</v>
@@ -16157,13 +16283,13 @@
         <v>150</v>
       </c>
       <c r="K51" t="s">
-        <v>582</v>
+        <v>602</v>
       </c>
       <c r="L51" t="s">
-        <v>501</v>
+        <v>521</v>
       </c>
       <c r="M51" t="s">
-        <v>688</v>
+        <v>708</v>
       </c>
       <c r="N51">
         <v>214.36099999999999</v>
@@ -16181,7 +16307,7 @@
         <v>0.08</v>
       </c>
       <c r="T51" t="s">
-        <v>662</v>
+        <v>682</v>
       </c>
     </row>
     <row r="52" spans="2:20">
@@ -16189,19 +16315,19 @@
         <v>214</v>
       </c>
       <c r="C52" t="s">
-        <v>584</v>
+        <v>604</v>
       </c>
       <c r="D52" t="s">
-        <v>501</v>
+        <v>521</v>
       </c>
       <c r="E52" t="s">
-        <v>585</v>
+        <v>605</v>
       </c>
       <c r="F52" t="s">
-        <v>503</v>
+        <v>523</v>
       </c>
       <c r="G52" t="s">
-        <v>503</v>
+        <v>523</v>
       </c>
       <c r="H52" t="s">
         <v>149</v>
@@ -16210,13 +16336,13 @@
         <v>150</v>
       </c>
       <c r="K52" t="s">
-        <v>584</v>
+        <v>604</v>
       </c>
       <c r="L52" t="s">
-        <v>501</v>
+        <v>521</v>
       </c>
       <c r="M52" t="s">
-        <v>689</v>
+        <v>709</v>
       </c>
       <c r="N52">
         <v>112.628</v>
@@ -16234,7 +16360,7 @@
         <v>0.08</v>
       </c>
       <c r="T52" t="s">
-        <v>662</v>
+        <v>682</v>
       </c>
     </row>
     <row r="53" spans="2:20">
@@ -16242,19 +16368,19 @@
         <v>214</v>
       </c>
       <c r="C53" t="s">
-        <v>586</v>
+        <v>606</v>
       </c>
       <c r="D53" t="s">
-        <v>501</v>
+        <v>521</v>
       </c>
       <c r="E53" t="s">
-        <v>587</v>
+        <v>607</v>
       </c>
       <c r="F53" t="s">
-        <v>503</v>
+        <v>523</v>
       </c>
       <c r="G53" t="s">
-        <v>503</v>
+        <v>523</v>
       </c>
       <c r="H53" t="s">
         <v>149</v>
@@ -16263,13 +16389,13 @@
         <v>150</v>
       </c>
       <c r="K53" t="s">
-        <v>586</v>
+        <v>606</v>
       </c>
       <c r="L53" t="s">
-        <v>501</v>
+        <v>521</v>
       </c>
       <c r="M53" t="s">
-        <v>667</v>
+        <v>687</v>
       </c>
       <c r="N53">
         <v>121.261</v>
@@ -16287,7 +16413,7 @@
         <v>0.08</v>
       </c>
       <c r="T53" t="s">
-        <v>662</v>
+        <v>682</v>
       </c>
     </row>
     <row r="54" spans="2:20">
@@ -16295,19 +16421,19 @@
         <v>214</v>
       </c>
       <c r="C54" t="s">
-        <v>588</v>
+        <v>608</v>
       </c>
       <c r="D54" t="s">
-        <v>501</v>
+        <v>521</v>
       </c>
       <c r="E54" t="s">
-        <v>589</v>
+        <v>609</v>
       </c>
       <c r="F54" t="s">
-        <v>503</v>
+        <v>523</v>
       </c>
       <c r="G54" t="s">
-        <v>503</v>
+        <v>523</v>
       </c>
       <c r="H54" t="s">
         <v>149</v>
@@ -16316,13 +16442,13 @@
         <v>150</v>
       </c>
       <c r="K54" t="s">
-        <v>588</v>
+        <v>608</v>
       </c>
       <c r="L54" t="s">
-        <v>501</v>
+        <v>521</v>
       </c>
       <c r="M54" t="s">
-        <v>690</v>
+        <v>710</v>
       </c>
       <c r="N54">
         <v>424.137</v>
@@ -16340,7 +16466,7 @@
         <v>0.08</v>
       </c>
       <c r="T54" t="s">
-        <v>662</v>
+        <v>682</v>
       </c>
     </row>
     <row r="55" spans="2:20">
@@ -16348,19 +16474,19 @@
         <v>214</v>
       </c>
       <c r="C55" t="s">
-        <v>590</v>
+        <v>610</v>
       </c>
       <c r="D55" t="s">
-        <v>501</v>
+        <v>521</v>
       </c>
       <c r="E55" t="s">
-        <v>591</v>
+        <v>611</v>
       </c>
       <c r="F55" t="s">
-        <v>503</v>
+        <v>523</v>
       </c>
       <c r="G55" t="s">
-        <v>503</v>
+        <v>523</v>
       </c>
       <c r="H55" t="s">
         <v>149</v>
@@ -16369,13 +16495,13 @@
         <v>150</v>
       </c>
       <c r="K55" t="s">
-        <v>590</v>
+        <v>610</v>
       </c>
       <c r="L55" t="s">
-        <v>501</v>
+        <v>521</v>
       </c>
       <c r="M55" t="s">
-        <v>691</v>
+        <v>711</v>
       </c>
       <c r="N55">
         <v>265.97300000000001</v>
@@ -16393,7 +16519,7 @@
         <v>0.08</v>
       </c>
       <c r="T55" t="s">
-        <v>662</v>
+        <v>682</v>
       </c>
     </row>
     <row r="56" spans="2:20">
@@ -16401,19 +16527,19 @@
         <v>214</v>
       </c>
       <c r="C56" t="s">
-        <v>592</v>
+        <v>612</v>
       </c>
       <c r="D56" t="s">
-        <v>501</v>
+        <v>521</v>
       </c>
       <c r="E56" t="s">
-        <v>593</v>
+        <v>613</v>
       </c>
       <c r="F56" t="s">
-        <v>503</v>
+        <v>523</v>
       </c>
       <c r="G56" t="s">
-        <v>503</v>
+        <v>523</v>
       </c>
       <c r="H56" t="s">
         <v>149</v>
@@ -16422,13 +16548,13 @@
         <v>150</v>
       </c>
       <c r="K56" t="s">
-        <v>592</v>
+        <v>612</v>
       </c>
       <c r="L56" t="s">
-        <v>501</v>
+        <v>521</v>
       </c>
       <c r="M56" t="s">
-        <v>692</v>
+        <v>712</v>
       </c>
       <c r="N56">
         <v>114.34099999999999</v>
@@ -16446,7 +16572,7 @@
         <v>0.08</v>
       </c>
       <c r="T56" t="s">
-        <v>662</v>
+        <v>682</v>
       </c>
     </row>
     <row r="57" spans="2:20">
@@ -16454,19 +16580,19 @@
         <v>214</v>
       </c>
       <c r="C57" t="s">
-        <v>594</v>
+        <v>614</v>
       </c>
       <c r="D57" t="s">
-        <v>501</v>
+        <v>521</v>
       </c>
       <c r="E57" t="s">
-        <v>595</v>
+        <v>615</v>
       </c>
       <c r="F57" t="s">
-        <v>503</v>
+        <v>523</v>
       </c>
       <c r="G57" t="s">
-        <v>503</v>
+        <v>523</v>
       </c>
       <c r="H57" t="s">
         <v>149</v>
@@ -16475,13 +16601,13 @@
         <v>150</v>
       </c>
       <c r="K57" t="s">
-        <v>594</v>
+        <v>614</v>
       </c>
       <c r="L57" t="s">
-        <v>501</v>
+        <v>521</v>
       </c>
       <c r="M57" t="s">
-        <v>693</v>
+        <v>713</v>
       </c>
       <c r="N57">
         <v>108.322</v>
@@ -16499,7 +16625,7 @@
         <v>0.08</v>
       </c>
       <c r="T57" t="s">
-        <v>662</v>
+        <v>682</v>
       </c>
     </row>
     <row r="58" spans="2:20">
@@ -16507,19 +16633,19 @@
         <v>214</v>
       </c>
       <c r="C58" t="s">
-        <v>596</v>
+        <v>616</v>
       </c>
       <c r="D58" t="s">
-        <v>501</v>
+        <v>521</v>
       </c>
       <c r="E58" t="s">
-        <v>597</v>
+        <v>617</v>
       </c>
       <c r="F58" t="s">
-        <v>503</v>
+        <v>523</v>
       </c>
       <c r="G58" t="s">
-        <v>503</v>
+        <v>523</v>
       </c>
       <c r="H58" t="s">
         <v>149</v>
@@ -16528,13 +16654,13 @@
         <v>150</v>
       </c>
       <c r="K58" t="s">
-        <v>596</v>
+        <v>616</v>
       </c>
       <c r="L58" t="s">
-        <v>501</v>
+        <v>521</v>
       </c>
       <c r="M58" t="s">
-        <v>694</v>
+        <v>714</v>
       </c>
       <c r="N58">
         <v>400.26300000000003</v>
@@ -16552,7 +16678,7 @@
         <v>0.08</v>
       </c>
       <c r="T58" t="s">
-        <v>662</v>
+        <v>682</v>
       </c>
     </row>
     <row r="59" spans="2:20">
@@ -16560,19 +16686,19 @@
         <v>214</v>
       </c>
       <c r="C59" t="s">
-        <v>598</v>
+        <v>618</v>
       </c>
       <c r="D59" t="s">
-        <v>501</v>
+        <v>521</v>
       </c>
       <c r="E59" t="s">
-        <v>599</v>
+        <v>619</v>
       </c>
       <c r="F59" t="s">
-        <v>503</v>
+        <v>523</v>
       </c>
       <c r="G59" t="s">
-        <v>503</v>
+        <v>523</v>
       </c>
       <c r="H59" t="s">
         <v>149</v>
@@ -16581,16 +16707,16 @@
         <v>150</v>
       </c>
       <c r="K59" t="s">
-        <v>598</v>
+        <v>618</v>
       </c>
       <c r="L59" t="s">
-        <v>501</v>
+        <v>521</v>
       </c>
       <c r="R59">
         <v>7.7499999999999999E-3</v>
       </c>
       <c r="S59" t="s">
-        <v>695</v>
+        <v>715</v>
       </c>
     </row>
     <row r="60" spans="2:20">
@@ -16598,19 +16724,19 @@
         <v>214</v>
       </c>
       <c r="C60" t="s">
-        <v>600</v>
+        <v>620</v>
       </c>
       <c r="D60" t="s">
-        <v>501</v>
+        <v>521</v>
       </c>
       <c r="E60" t="s">
-        <v>601</v>
+        <v>621</v>
       </c>
       <c r="F60" t="s">
-        <v>503</v>
+        <v>523</v>
       </c>
       <c r="G60" t="s">
-        <v>503</v>
+        <v>523</v>
       </c>
       <c r="H60" t="s">
         <v>149</v>
@@ -16619,16 +16745,16 @@
         <v>150</v>
       </c>
       <c r="K60" t="s">
-        <v>600</v>
+        <v>620</v>
       </c>
       <c r="L60" t="s">
-        <v>501</v>
+        <v>521</v>
       </c>
       <c r="R60">
         <v>7.7499999999999999E-3</v>
       </c>
       <c r="S60" t="s">
-        <v>696</v>
+        <v>716</v>
       </c>
     </row>
     <row r="61" spans="2:20">
@@ -16636,19 +16762,19 @@
         <v>214</v>
       </c>
       <c r="C61" t="s">
-        <v>602</v>
+        <v>622</v>
       </c>
       <c r="D61" t="s">
-        <v>501</v>
+        <v>521</v>
       </c>
       <c r="E61" t="s">
-        <v>603</v>
+        <v>623</v>
       </c>
       <c r="F61" t="s">
-        <v>503</v>
+        <v>523</v>
       </c>
       <c r="G61" t="s">
-        <v>503</v>
+        <v>523</v>
       </c>
       <c r="H61" t="s">
         <v>149</v>
@@ -16657,16 +16783,16 @@
         <v>150</v>
       </c>
       <c r="K61" t="s">
-        <v>602</v>
+        <v>622</v>
       </c>
       <c r="L61" t="s">
-        <v>501</v>
+        <v>521</v>
       </c>
       <c r="R61">
         <v>7.7499999999999999E-3</v>
       </c>
       <c r="S61" t="s">
-        <v>697</v>
+        <v>717</v>
       </c>
     </row>
     <row r="62" spans="2:20">
@@ -16674,19 +16800,19 @@
         <v>214</v>
       </c>
       <c r="C62" t="s">
-        <v>604</v>
+        <v>624</v>
       </c>
       <c r="D62" t="s">
-        <v>501</v>
+        <v>521</v>
       </c>
       <c r="E62" t="s">
-        <v>605</v>
+        <v>625</v>
       </c>
       <c r="F62" t="s">
-        <v>503</v>
+        <v>523</v>
       </c>
       <c r="G62" t="s">
-        <v>503</v>
+        <v>523</v>
       </c>
       <c r="H62" t="s">
         <v>149</v>
@@ -16695,16 +16821,16 @@
         <v>150</v>
       </c>
       <c r="K62" t="s">
-        <v>604</v>
+        <v>624</v>
       </c>
       <c r="L62" t="s">
-        <v>501</v>
+        <v>521</v>
       </c>
       <c r="R62">
         <v>7.7499999999999999E-3</v>
       </c>
       <c r="S62" t="s">
-        <v>698</v>
+        <v>718</v>
       </c>
     </row>
     <row r="63" spans="2:20">
@@ -16712,19 +16838,19 @@
         <v>214</v>
       </c>
       <c r="C63" t="s">
-        <v>606</v>
+        <v>626</v>
       </c>
       <c r="D63" t="s">
-        <v>501</v>
+        <v>521</v>
       </c>
       <c r="E63" t="s">
-        <v>607</v>
+        <v>627</v>
       </c>
       <c r="F63" t="s">
-        <v>503</v>
+        <v>523</v>
       </c>
       <c r="G63" t="s">
-        <v>503</v>
+        <v>523</v>
       </c>
       <c r="H63" t="s">
         <v>149</v>
@@ -16733,16 +16859,16 @@
         <v>150</v>
       </c>
       <c r="K63" t="s">
-        <v>606</v>
+        <v>626</v>
       </c>
       <c r="L63" t="s">
-        <v>501</v>
+        <v>521</v>
       </c>
       <c r="R63">
         <v>7.7499999999999999E-3</v>
       </c>
       <c r="S63" t="s">
-        <v>699</v>
+        <v>719</v>
       </c>
     </row>
     <row r="64" spans="2:20">
@@ -16750,19 +16876,19 @@
         <v>214</v>
       </c>
       <c r="C64" t="s">
-        <v>608</v>
+        <v>628</v>
       </c>
       <c r="D64" t="s">
-        <v>501</v>
+        <v>521</v>
       </c>
       <c r="E64" t="s">
-        <v>609</v>
+        <v>629</v>
       </c>
       <c r="F64" t="s">
-        <v>503</v>
+        <v>523</v>
       </c>
       <c r="G64" t="s">
-        <v>503</v>
+        <v>523</v>
       </c>
       <c r="H64" t="s">
         <v>149</v>
@@ -16771,16 +16897,16 @@
         <v>150</v>
       </c>
       <c r="K64" t="s">
-        <v>608</v>
+        <v>628</v>
       </c>
       <c r="L64" t="s">
-        <v>501</v>
+        <v>521</v>
       </c>
       <c r="R64">
         <v>7.7499999999999999E-3</v>
       </c>
       <c r="S64" t="s">
-        <v>700</v>
+        <v>720</v>
       </c>
     </row>
     <row r="65" spans="2:19">
@@ -16788,19 +16914,19 @@
         <v>214</v>
       </c>
       <c r="C65" t="s">
-        <v>610</v>
+        <v>630</v>
       </c>
       <c r="D65" t="s">
-        <v>501</v>
+        <v>521</v>
       </c>
       <c r="E65" t="s">
-        <v>611</v>
+        <v>631</v>
       </c>
       <c r="F65" t="s">
-        <v>503</v>
+        <v>523</v>
       </c>
       <c r="G65" t="s">
-        <v>503</v>
+        <v>523</v>
       </c>
       <c r="H65" t="s">
         <v>149</v>
@@ -16809,16 +16935,16 @@
         <v>150</v>
       </c>
       <c r="K65" t="s">
-        <v>610</v>
+        <v>630</v>
       </c>
       <c r="L65" t="s">
-        <v>501</v>
+        <v>521</v>
       </c>
       <c r="R65">
         <v>7.7499999999999999E-3</v>
       </c>
       <c r="S65" t="s">
-        <v>701</v>
+        <v>721</v>
       </c>
     </row>
     <row r="66" spans="2:19">
@@ -16826,19 +16952,19 @@
         <v>214</v>
       </c>
       <c r="C66" t="s">
-        <v>612</v>
+        <v>632</v>
       </c>
       <c r="D66" t="s">
-        <v>501</v>
+        <v>521</v>
       </c>
       <c r="E66" t="s">
-        <v>613</v>
+        <v>633</v>
       </c>
       <c r="F66" t="s">
-        <v>503</v>
+        <v>523</v>
       </c>
       <c r="G66" t="s">
-        <v>503</v>
+        <v>523</v>
       </c>
       <c r="H66" t="s">
         <v>149</v>
@@ -16847,16 +16973,16 @@
         <v>150</v>
       </c>
       <c r="K66" t="s">
-        <v>612</v>
+        <v>632</v>
       </c>
       <c r="L66" t="s">
-        <v>501</v>
+        <v>521</v>
       </c>
       <c r="R66">
         <v>7.7499999999999999E-3</v>
       </c>
       <c r="S66" t="s">
-        <v>702</v>
+        <v>722</v>
       </c>
     </row>
     <row r="67" spans="2:19">
@@ -16864,19 +16990,19 @@
         <v>214</v>
       </c>
       <c r="C67" t="s">
-        <v>614</v>
+        <v>634</v>
       </c>
       <c r="D67" t="s">
-        <v>501</v>
+        <v>521</v>
       </c>
       <c r="E67" t="s">
-        <v>615</v>
+        <v>635</v>
       </c>
       <c r="F67" t="s">
-        <v>503</v>
+        <v>523</v>
       </c>
       <c r="G67" t="s">
-        <v>503</v>
+        <v>523</v>
       </c>
       <c r="H67" t="s">
         <v>149</v>
@@ -16885,16 +17011,16 @@
         <v>150</v>
       </c>
       <c r="K67" t="s">
-        <v>614</v>
+        <v>634</v>
       </c>
       <c r="L67" t="s">
-        <v>501</v>
+        <v>521</v>
       </c>
       <c r="R67">
         <v>7.7499999999999999E-3</v>
       </c>
       <c r="S67" t="s">
-        <v>703</v>
+        <v>723</v>
       </c>
     </row>
     <row r="68" spans="2:19">
@@ -16902,19 +17028,19 @@
         <v>214</v>
       </c>
       <c r="C68" t="s">
-        <v>616</v>
+        <v>636</v>
       </c>
       <c r="D68" t="s">
-        <v>501</v>
+        <v>521</v>
       </c>
       <c r="E68" t="s">
-        <v>617</v>
+        <v>637</v>
       </c>
       <c r="F68" t="s">
-        <v>503</v>
+        <v>523</v>
       </c>
       <c r="G68" t="s">
-        <v>503</v>
+        <v>523</v>
       </c>
       <c r="H68" t="s">
         <v>149</v>
@@ -16923,16 +17049,16 @@
         <v>150</v>
       </c>
       <c r="K68" t="s">
-        <v>616</v>
+        <v>636</v>
       </c>
       <c r="L68" t="s">
-        <v>501</v>
+        <v>521</v>
       </c>
       <c r="R68">
         <v>7.7499999999999999E-3</v>
       </c>
       <c r="S68" t="s">
-        <v>704</v>
+        <v>724</v>
       </c>
     </row>
     <row r="69" spans="2:19">
@@ -16940,19 +17066,19 @@
         <v>214</v>
       </c>
       <c r="C69" t="s">
-        <v>618</v>
+        <v>638</v>
       </c>
       <c r="D69" t="s">
-        <v>501</v>
+        <v>521</v>
       </c>
       <c r="E69" t="s">
-        <v>619</v>
+        <v>639</v>
       </c>
       <c r="F69" t="s">
-        <v>503</v>
+        <v>523</v>
       </c>
       <c r="G69" t="s">
-        <v>503</v>
+        <v>523</v>
       </c>
       <c r="H69" t="s">
         <v>149</v>
@@ -16961,16 +17087,16 @@
         <v>150</v>
       </c>
       <c r="K69" t="s">
-        <v>618</v>
+        <v>638</v>
       </c>
       <c r="L69" t="s">
-        <v>501</v>
+        <v>521</v>
       </c>
       <c r="R69">
         <v>7.7499999999999999E-3</v>
       </c>
       <c r="S69" t="s">
-        <v>705</v>
+        <v>725</v>
       </c>
     </row>
     <row r="70" spans="2:19">
@@ -16978,19 +17104,19 @@
         <v>214</v>
       </c>
       <c r="C70" t="s">
-        <v>620</v>
+        <v>640</v>
       </c>
       <c r="D70" t="s">
-        <v>501</v>
+        <v>521</v>
       </c>
       <c r="E70" t="s">
-        <v>621</v>
+        <v>641</v>
       </c>
       <c r="F70" t="s">
-        <v>503</v>
+        <v>523</v>
       </c>
       <c r="G70" t="s">
-        <v>503</v>
+        <v>523</v>
       </c>
       <c r="H70" t="s">
         <v>149</v>
@@ -16999,16 +17125,16 @@
         <v>150</v>
       </c>
       <c r="K70" t="s">
-        <v>620</v>
+        <v>640</v>
       </c>
       <c r="L70" t="s">
-        <v>501</v>
+        <v>521</v>
       </c>
       <c r="R70">
         <v>7.7499999999999999E-3</v>
       </c>
       <c r="S70" t="s">
-        <v>706</v>
+        <v>726</v>
       </c>
     </row>
     <row r="71" spans="2:19">
@@ -17016,19 +17142,19 @@
         <v>214</v>
       </c>
       <c r="C71" t="s">
-        <v>622</v>
+        <v>642</v>
       </c>
       <c r="D71" t="s">
-        <v>501</v>
+        <v>521</v>
       </c>
       <c r="E71" t="s">
-        <v>623</v>
+        <v>643</v>
       </c>
       <c r="F71" t="s">
-        <v>503</v>
+        <v>523</v>
       </c>
       <c r="G71" t="s">
-        <v>503</v>
+        <v>523</v>
       </c>
       <c r="H71" t="s">
         <v>149</v>
@@ -17037,16 +17163,16 @@
         <v>150</v>
       </c>
       <c r="K71" t="s">
-        <v>622</v>
+        <v>642</v>
       </c>
       <c r="L71" t="s">
-        <v>501</v>
+        <v>521</v>
       </c>
       <c r="R71">
         <v>7.7499999999999999E-3</v>
       </c>
       <c r="S71" t="s">
-        <v>707</v>
+        <v>727</v>
       </c>
     </row>
     <row r="72" spans="2:19">
@@ -17054,19 +17180,19 @@
         <v>214</v>
       </c>
       <c r="C72" t="s">
-        <v>624</v>
+        <v>644</v>
       </c>
       <c r="D72" t="s">
-        <v>501</v>
+        <v>521</v>
       </c>
       <c r="E72" t="s">
-        <v>625</v>
+        <v>645</v>
       </c>
       <c r="F72" t="s">
-        <v>503</v>
+        <v>523</v>
       </c>
       <c r="G72" t="s">
-        <v>503</v>
+        <v>523</v>
       </c>
       <c r="H72" t="s">
         <v>149</v>
@@ -17075,16 +17201,16 @@
         <v>150</v>
       </c>
       <c r="K72" t="s">
-        <v>624</v>
+        <v>644</v>
       </c>
       <c r="L72" t="s">
-        <v>501</v>
+        <v>521</v>
       </c>
       <c r="R72">
         <v>7.7499999999999999E-3</v>
       </c>
       <c r="S72" t="s">
-        <v>708</v>
+        <v>728</v>
       </c>
     </row>
     <row r="73" spans="2:19">
@@ -17092,19 +17218,19 @@
         <v>214</v>
       </c>
       <c r="C73" t="s">
-        <v>626</v>
+        <v>646</v>
       </c>
       <c r="D73" t="s">
-        <v>501</v>
+        <v>521</v>
       </c>
       <c r="E73" t="s">
-        <v>627</v>
+        <v>647</v>
       </c>
       <c r="F73" t="s">
-        <v>503</v>
+        <v>523</v>
       </c>
       <c r="G73" t="s">
-        <v>503</v>
+        <v>523</v>
       </c>
       <c r="H73" t="s">
         <v>149</v>
@@ -17113,16 +17239,16 @@
         <v>150</v>
       </c>
       <c r="K73" t="s">
-        <v>626</v>
+        <v>646</v>
       </c>
       <c r="L73" t="s">
-        <v>501</v>
+        <v>521</v>
       </c>
       <c r="R73">
         <v>7.7499999999999999E-3</v>
       </c>
       <c r="S73" t="s">
-        <v>709</v>
+        <v>729</v>
       </c>
     </row>
     <row r="74" spans="2:19">
@@ -17130,19 +17256,19 @@
         <v>214</v>
       </c>
       <c r="C74" t="s">
-        <v>628</v>
+        <v>648</v>
       </c>
       <c r="D74" t="s">
-        <v>501</v>
+        <v>521</v>
       </c>
       <c r="E74" t="s">
-        <v>629</v>
+        <v>649</v>
       </c>
       <c r="F74" t="s">
-        <v>503</v>
+        <v>523</v>
       </c>
       <c r="G74" t="s">
-        <v>503</v>
+        <v>523</v>
       </c>
       <c r="H74" t="s">
         <v>149</v>
@@ -17151,16 +17277,16 @@
         <v>150</v>
       </c>
       <c r="K74" t="s">
-        <v>628</v>
+        <v>648</v>
       </c>
       <c r="L74" t="s">
-        <v>501</v>
+        <v>521</v>
       </c>
       <c r="R74">
         <v>7.7499999999999999E-3</v>
       </c>
       <c r="S74" t="s">
-        <v>710</v>
+        <v>730</v>
       </c>
     </row>
     <row r="75" spans="2:19">
@@ -17168,19 +17294,19 @@
         <v>214</v>
       </c>
       <c r="C75" t="s">
-        <v>630</v>
+        <v>650</v>
       </c>
       <c r="D75" t="s">
-        <v>501</v>
+        <v>521</v>
       </c>
       <c r="E75" t="s">
-        <v>631</v>
+        <v>651</v>
       </c>
       <c r="F75" t="s">
-        <v>503</v>
+        <v>523</v>
       </c>
       <c r="G75" t="s">
-        <v>503</v>
+        <v>523</v>
       </c>
       <c r="H75" t="s">
         <v>149</v>
@@ -17189,16 +17315,16 @@
         <v>150</v>
       </c>
       <c r="K75" t="s">
-        <v>630</v>
+        <v>650</v>
       </c>
       <c r="L75" t="s">
-        <v>501</v>
+        <v>521</v>
       </c>
       <c r="R75">
         <v>7.7499999999999999E-3</v>
       </c>
       <c r="S75" t="s">
-        <v>711</v>
+        <v>731</v>
       </c>
     </row>
     <row r="76" spans="2:19">
@@ -17206,19 +17332,19 @@
         <v>214</v>
       </c>
       <c r="C76" t="s">
-        <v>632</v>
+        <v>652</v>
       </c>
       <c r="D76" t="s">
-        <v>501</v>
+        <v>521</v>
       </c>
       <c r="E76" t="s">
-        <v>633</v>
+        <v>653</v>
       </c>
       <c r="F76" t="s">
-        <v>503</v>
+        <v>523</v>
       </c>
       <c r="G76" t="s">
-        <v>503</v>
+        <v>523</v>
       </c>
       <c r="H76" t="s">
         <v>149</v>
@@ -17227,16 +17353,16 @@
         <v>150</v>
       </c>
       <c r="K76" t="s">
-        <v>632</v>
+        <v>652</v>
       </c>
       <c r="L76" t="s">
-        <v>501</v>
+        <v>521</v>
       </c>
       <c r="R76">
         <v>7.7499999999999999E-3</v>
       </c>
       <c r="S76" t="s">
-        <v>712</v>
+        <v>732</v>
       </c>
     </row>
     <row r="77" spans="2:19">
@@ -17244,19 +17370,19 @@
         <v>214</v>
       </c>
       <c r="C77" t="s">
-        <v>634</v>
+        <v>654</v>
       </c>
       <c r="D77" t="s">
-        <v>501</v>
+        <v>521</v>
       </c>
       <c r="E77" t="s">
-        <v>635</v>
+        <v>655</v>
       </c>
       <c r="F77" t="s">
-        <v>503</v>
+        <v>523</v>
       </c>
       <c r="G77" t="s">
-        <v>503</v>
+        <v>523</v>
       </c>
       <c r="H77" t="s">
         <v>149</v>
@@ -17265,16 +17391,16 @@
         <v>150</v>
       </c>
       <c r="K77" t="s">
-        <v>634</v>
+        <v>654</v>
       </c>
       <c r="L77" t="s">
-        <v>501</v>
+        <v>521</v>
       </c>
       <c r="R77">
         <v>7.7499999999999999E-3</v>
       </c>
       <c r="S77" t="s">
-        <v>713</v>
+        <v>733</v>
       </c>
     </row>
     <row r="78" spans="2:19">
@@ -17282,19 +17408,19 @@
         <v>214</v>
       </c>
       <c r="C78" t="s">
-        <v>636</v>
+        <v>656</v>
       </c>
       <c r="D78" t="s">
-        <v>501</v>
+        <v>521</v>
       </c>
       <c r="E78" t="s">
-        <v>637</v>
+        <v>657</v>
       </c>
       <c r="F78" t="s">
-        <v>503</v>
+        <v>523</v>
       </c>
       <c r="G78" t="s">
-        <v>503</v>
+        <v>523</v>
       </c>
       <c r="H78" t="s">
         <v>149</v>
@@ -17303,16 +17429,16 @@
         <v>150</v>
       </c>
       <c r="K78" t="s">
-        <v>636</v>
+        <v>656</v>
       </c>
       <c r="L78" t="s">
-        <v>501</v>
+        <v>521</v>
       </c>
       <c r="R78">
         <v>7.7499999999999999E-3</v>
       </c>
       <c r="S78" t="s">
-        <v>714</v>
+        <v>734</v>
       </c>
     </row>
     <row r="79" spans="2:19">
@@ -17320,19 +17446,19 @@
         <v>214</v>
       </c>
       <c r="C79" t="s">
-        <v>638</v>
+        <v>658</v>
       </c>
       <c r="D79" t="s">
-        <v>501</v>
+        <v>521</v>
       </c>
       <c r="E79" t="s">
-        <v>639</v>
+        <v>659</v>
       </c>
       <c r="F79" t="s">
-        <v>503</v>
+        <v>523</v>
       </c>
       <c r="G79" t="s">
-        <v>503</v>
+        <v>523</v>
       </c>
       <c r="H79" t="s">
         <v>149</v>
@@ -17341,16 +17467,16 @@
         <v>150</v>
       </c>
       <c r="K79" t="s">
-        <v>638</v>
+        <v>658</v>
       </c>
       <c r="L79" t="s">
-        <v>501</v>
+        <v>521</v>
       </c>
       <c r="R79">
         <v>7.7499999999999999E-3</v>
       </c>
       <c r="S79" t="s">
-        <v>715</v>
+        <v>735</v>
       </c>
     </row>
     <row r="80" spans="2:19">
@@ -17358,19 +17484,19 @@
         <v>214</v>
       </c>
       <c r="C80" t="s">
-        <v>640</v>
+        <v>660</v>
       </c>
       <c r="D80" t="s">
-        <v>501</v>
+        <v>521</v>
       </c>
       <c r="E80" t="s">
-        <v>641</v>
+        <v>661</v>
       </c>
       <c r="F80" t="s">
-        <v>503</v>
+        <v>523</v>
       </c>
       <c r="G80" t="s">
-        <v>503</v>
+        <v>523</v>
       </c>
       <c r="H80" t="s">
         <v>149</v>
@@ -17379,16 +17505,16 @@
         <v>150</v>
       </c>
       <c r="K80" t="s">
-        <v>640</v>
+        <v>660</v>
       </c>
       <c r="L80" t="s">
-        <v>501</v>
+        <v>521</v>
       </c>
       <c r="R80">
         <v>7.7499999999999999E-3</v>
       </c>
       <c r="S80" t="s">
-        <v>716</v>
+        <v>736</v>
       </c>
     </row>
     <row r="81" spans="2:19">
@@ -17396,19 +17522,19 @@
         <v>214</v>
       </c>
       <c r="C81" t="s">
-        <v>642</v>
+        <v>662</v>
       </c>
       <c r="D81" t="s">
-        <v>501</v>
+        <v>521</v>
       </c>
       <c r="E81" t="s">
-        <v>643</v>
+        <v>663</v>
       </c>
       <c r="F81" t="s">
-        <v>503</v>
+        <v>523</v>
       </c>
       <c r="G81" t="s">
-        <v>503</v>
+        <v>523</v>
       </c>
       <c r="H81" t="s">
         <v>149</v>
@@ -17417,16 +17543,16 @@
         <v>150</v>
       </c>
       <c r="K81" t="s">
-        <v>642</v>
+        <v>662</v>
       </c>
       <c r="L81" t="s">
-        <v>501</v>
+        <v>521</v>
       </c>
       <c r="R81">
         <v>7.7499999999999999E-3</v>
       </c>
       <c r="S81" t="s">
-        <v>717</v>
+        <v>737</v>
       </c>
     </row>
     <row r="82" spans="2:19">
@@ -17434,19 +17560,19 @@
         <v>214</v>
       </c>
       <c r="C82" t="s">
-        <v>644</v>
+        <v>664</v>
       </c>
       <c r="D82" t="s">
-        <v>501</v>
+        <v>521</v>
       </c>
       <c r="E82" t="s">
-        <v>645</v>
+        <v>665</v>
       </c>
       <c r="F82" t="s">
-        <v>503</v>
+        <v>523</v>
       </c>
       <c r="G82" t="s">
-        <v>503</v>
+        <v>523</v>
       </c>
       <c r="H82" t="s">
         <v>149</v>
@@ -17455,16 +17581,16 @@
         <v>150</v>
       </c>
       <c r="K82" t="s">
-        <v>644</v>
+        <v>664</v>
       </c>
       <c r="L82" t="s">
-        <v>501</v>
+        <v>521</v>
       </c>
       <c r="R82">
         <v>7.7499999999999999E-3</v>
       </c>
       <c r="S82" t="s">
-        <v>718</v>
+        <v>738</v>
       </c>
     </row>
     <row r="83" spans="2:19">
@@ -17472,19 +17598,19 @@
         <v>214</v>
       </c>
       <c r="C83" t="s">
-        <v>646</v>
+        <v>666</v>
       </c>
       <c r="D83" t="s">
-        <v>501</v>
+        <v>521</v>
       </c>
       <c r="E83" t="s">
-        <v>647</v>
+        <v>667</v>
       </c>
       <c r="F83" t="s">
-        <v>503</v>
+        <v>523</v>
       </c>
       <c r="G83" t="s">
-        <v>503</v>
+        <v>523</v>
       </c>
       <c r="H83" t="s">
         <v>149</v>
@@ -17493,16 +17619,16 @@
         <v>150</v>
       </c>
       <c r="K83" t="s">
-        <v>646</v>
+        <v>666</v>
       </c>
       <c r="L83" t="s">
-        <v>501</v>
+        <v>521</v>
       </c>
       <c r="R83">
         <v>7.7499999999999999E-3</v>
       </c>
       <c r="S83" t="s">
-        <v>719</v>
+        <v>739</v>
       </c>
     </row>
     <row r="84" spans="2:19">
@@ -17510,19 +17636,19 @@
         <v>214</v>
       </c>
       <c r="C84" t="s">
-        <v>648</v>
+        <v>668</v>
       </c>
       <c r="D84" t="s">
-        <v>501</v>
+        <v>521</v>
       </c>
       <c r="E84" t="s">
-        <v>649</v>
+        <v>669</v>
       </c>
       <c r="F84" t="s">
-        <v>503</v>
+        <v>523</v>
       </c>
       <c r="G84" t="s">
-        <v>503</v>
+        <v>523</v>
       </c>
       <c r="H84" t="s">
         <v>149</v>
@@ -17531,16 +17657,16 @@
         <v>150</v>
       </c>
       <c r="K84" t="s">
-        <v>648</v>
+        <v>668</v>
       </c>
       <c r="L84" t="s">
-        <v>501</v>
+        <v>521</v>
       </c>
       <c r="R84">
         <v>7.7499999999999999E-3</v>
       </c>
       <c r="S84" t="s">
-        <v>720</v>
+        <v>740</v>
       </c>
     </row>
     <row r="85" spans="2:19">
@@ -17548,19 +17674,19 @@
         <v>214</v>
       </c>
       <c r="C85" t="s">
-        <v>650</v>
+        <v>670</v>
       </c>
       <c r="D85" t="s">
-        <v>501</v>
+        <v>521</v>
       </c>
       <c r="E85" t="s">
-        <v>651</v>
+        <v>671</v>
       </c>
       <c r="F85" t="s">
-        <v>503</v>
+        <v>523</v>
       </c>
       <c r="G85" t="s">
-        <v>503</v>
+        <v>523</v>
       </c>
       <c r="H85" t="s">
         <v>149</v>
@@ -17569,16 +17695,16 @@
         <v>150</v>
       </c>
       <c r="K85" t="s">
-        <v>650</v>
+        <v>670</v>
       </c>
       <c r="L85" t="s">
-        <v>501</v>
+        <v>521</v>
       </c>
       <c r="R85">
         <v>7.7499999999999999E-3</v>
       </c>
       <c r="S85" t="s">
-        <v>721</v>
+        <v>741</v>
       </c>
     </row>
     <row r="86" spans="2:19">
@@ -17586,19 +17712,19 @@
         <v>214</v>
       </c>
       <c r="C86" t="s">
-        <v>652</v>
+        <v>672</v>
       </c>
       <c r="D86" t="s">
-        <v>501</v>
+        <v>521</v>
       </c>
       <c r="E86" t="s">
-        <v>653</v>
+        <v>673</v>
       </c>
       <c r="F86" t="s">
-        <v>503</v>
+        <v>523</v>
       </c>
       <c r="G86" t="s">
-        <v>503</v>
+        <v>523</v>
       </c>
       <c r="H86" t="s">
         <v>149</v>
@@ -17607,16 +17733,16 @@
         <v>150</v>
       </c>
       <c r="K86" t="s">
-        <v>652</v>
+        <v>672</v>
       </c>
       <c r="L86" t="s">
-        <v>501</v>
+        <v>521</v>
       </c>
       <c r="R86">
         <v>7.7499999999999999E-3</v>
       </c>
       <c r="S86" t="s">
-        <v>722</v>
+        <v>742</v>
       </c>
     </row>
     <row r="87" spans="2:19">
@@ -17624,19 +17750,19 @@
         <v>214</v>
       </c>
       <c r="C87" t="s">
-        <v>654</v>
+        <v>674</v>
       </c>
       <c r="D87" t="s">
-        <v>501</v>
+        <v>521</v>
       </c>
       <c r="E87" t="s">
-        <v>655</v>
+        <v>675</v>
       </c>
       <c r="F87" t="s">
-        <v>503</v>
+        <v>523</v>
       </c>
       <c r="G87" t="s">
-        <v>503</v>
+        <v>523</v>
       </c>
       <c r="H87" t="s">
         <v>149</v>
@@ -17645,16 +17771,16 @@
         <v>150</v>
       </c>
       <c r="K87" t="s">
-        <v>654</v>
+        <v>674</v>
       </c>
       <c r="L87" t="s">
-        <v>501</v>
+        <v>521</v>
       </c>
       <c r="R87">
         <v>7.7499999999999999E-3</v>
       </c>
       <c r="S87" t="s">
-        <v>723</v>
+        <v>743</v>
       </c>
     </row>
     <row r="88" spans="2:19">
@@ -17662,19 +17788,19 @@
         <v>214</v>
       </c>
       <c r="C88" t="s">
-        <v>656</v>
+        <v>676</v>
       </c>
       <c r="D88" t="s">
-        <v>501</v>
+        <v>521</v>
       </c>
       <c r="E88" t="s">
-        <v>657</v>
+        <v>677</v>
       </c>
       <c r="F88" t="s">
-        <v>503</v>
+        <v>523</v>
       </c>
       <c r="G88" t="s">
-        <v>503</v>
+        <v>523</v>
       </c>
       <c r="H88" t="s">
         <v>149</v>
@@ -17683,16 +17809,16 @@
         <v>150</v>
       </c>
       <c r="K88" t="s">
-        <v>656</v>
+        <v>676</v>
       </c>
       <c r="L88" t="s">
-        <v>501</v>
+        <v>521</v>
       </c>
       <c r="R88">
         <v>7.7499999999999999E-3</v>
       </c>
       <c r="S88" t="s">
-        <v>724</v>
+        <v>744</v>
       </c>
     </row>
   </sheetData>

--- a/VerveStacks_POL_grids_kan50/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_POL_grids_kan50/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6886E1BB-D2D6-4A9C-AC34-BA4334CB1883}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1593261B-018E-42A2-8374-FD8809C3FAAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -711,196 +711,244 @@
     <t>pre</t>
   </si>
   <si>
+    <t>distr_solelc_spv_POL_005</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>NRGI</t>
+  </si>
+  <si>
+    <t>daynite</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_006</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_010</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_002</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_019</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_009</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_017</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_020</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_014</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_013</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_001</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_015</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_018</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_003</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_007</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_016</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_004</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_012</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_011</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 11</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_POL_008</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 8</t>
   </si>
   <si>
-    <t>NRGI</t>
-  </si>
-  <si>
-    <t>daynite</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_013</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_004</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_002</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_019</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_009</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_012</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_011</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_003</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_007</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_016</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_006</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_010</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_001</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_015</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_018</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_005</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_014</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_017</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_020</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 20</t>
-  </si>
-  <si>
     <t>comm-in</t>
   </si>
   <si>
     <t>ncap_cost~USD21_alt</t>
   </si>
   <si>
+    <t>e_Lubin_POL,e_Poznan_POL,e_Koszalin_POL,e_Bydgoszcz_POL</t>
+  </si>
+  <si>
+    <t>e_Plock_POL,e_Olsztyn_POL,e_Warsaw_POL</t>
+  </si>
+  <si>
+    <t>e_Elk_POL,e_Grajewo_POL</t>
+  </si>
+  <si>
+    <t>e_Legnica_POL,e_Swidnica_POL,e_KedzierzynKozle_POL,e_Opole_POL</t>
+  </si>
+  <si>
+    <t>e_Kielce_POL,e_Warsaw_POL,e_OstrowiecSwietokrz_POL</t>
+  </si>
+  <si>
+    <t>e_Pulawy_POL,e_Bialystok_POL,e_Chelm_POL</t>
+  </si>
+  <si>
+    <t>e_Konin_POL,e_Bydgoszcz_POL,e_Wloclawek_POL,e_Kwidzyn_POL,e_Plock_POL</t>
+  </si>
+  <si>
+    <t>e_OstrowiecSwietokrz_POL,e_Pulawy_POL,e_Warsaw_POL</t>
+  </si>
+  <si>
+    <t>e_BielskoBiala_POL,e_Katowice_POL,e_Krakow_POL,e_Tarnow_POL</t>
+  </si>
+  <si>
+    <t>e_Rzeszow_POL,e_Zamosc_POL,e_Pulawy_POL,e_Chelm_POL</t>
+  </si>
+  <si>
+    <t>e_Boleslawiec_POL,e_ZielonaGora_POL</t>
+  </si>
+  <si>
+    <t>e_Sosnowiec_POL,e_KedzierzynKozle_POL,e_Olesnica_POL,e_Gliwice_POL,e_Czestochowa_POL,e_Radomsko_POL,e_PiotrkowTrybunalsk_POL,e_Kielce_POL</t>
+  </si>
+  <si>
+    <t>e_Warsaw_POL,e_Lomza_POL</t>
+  </si>
+  <si>
+    <t>e_Lubin_POL,e_Swidnica_POL,e_Wroclaw_POL,e_Poznan_POL,e_Olesnica_POL</t>
+  </si>
+  <si>
+    <t>e_Koszalin_POL,e_Ustka_POL,e_Slupsk_POL</t>
+  </si>
+  <si>
+    <t>e_Olesnica_POL,e_Konin_POL,e_PiotrkowTrybunalsk_POL,e_Plock_POL</t>
+  </si>
+  <si>
+    <t>e_GorzowWielkopolski_POL,e_Szczecin_POL,e_Police_POL</t>
+  </si>
+  <si>
+    <t>e_Krosno_POL,e_Mielec_POL,e_Debica_POL,e_Zamosc_POL</t>
+  </si>
+  <si>
+    <t>e_Lomza_POL,e_Elk_POL,e_Bialystok_POL,e_Grajewo_POL</t>
+  </si>
+  <si>
     <t>e_Bydgoszcz_POL,e_Gdansk_POL,e_Grudziadz_POL,e_Kwidzyn_POL</t>
   </si>
   <si>
-    <t>e_Rzeszow_POL,e_Zamosc_POL,e_Pulawy_POL,e_Chelm_POL</t>
-  </si>
-  <si>
-    <t>e_GorzowWielkopolski_POL,e_Szczecin_POL,e_Police_POL</t>
-  </si>
-  <si>
-    <t>e_Legnica_POL,e_Swidnica_POL,e_KedzierzynKozle_POL,e_Opole_POL</t>
-  </si>
-  <si>
-    <t>e_Kielce_POL,e_Warsaw_POL,e_OstrowiecSwietokrz_POL</t>
-  </si>
-  <si>
-    <t>e_Pulawy_POL,e_Bialystok_POL,e_Chelm_POL</t>
-  </si>
-  <si>
-    <t>e_Krosno_POL,e_Mielec_POL,e_Debica_POL,e_Zamosc_POL</t>
-  </si>
-  <si>
-    <t>e_Lomza_POL,e_Elk_POL,e_Bialystok_POL,e_Grajewo_POL</t>
-  </si>
-  <si>
-    <t>e_Lubin_POL,e_Swidnica_POL,e_Wroclaw_POL,e_Poznan_POL,e_Olesnica_POL</t>
-  </si>
-  <si>
-    <t>e_Koszalin_POL,e_Ustka_POL,e_Slupsk_POL</t>
-  </si>
-  <si>
-    <t>e_Olesnica_POL,e_Konin_POL,e_PiotrkowTrybunalsk_POL,e_Plock_POL</t>
-  </si>
-  <si>
-    <t>e_Plock_POL,e_Olsztyn_POL,e_Warsaw_POL</t>
-  </si>
-  <si>
-    <t>e_Elk_POL,e_Grajewo_POL</t>
-  </si>
-  <si>
-    <t>e_Boleslawiec_POL,e_ZielonaGora_POL</t>
-  </si>
-  <si>
-    <t>e_Sosnowiec_POL,e_KedzierzynKozle_POL,e_Olesnica_POL,e_Gliwice_POL,e_Czestochowa_POL,e_Radomsko_POL,e_PiotrkowTrybunalsk_POL,e_Kielce_POL</t>
-  </si>
-  <si>
-    <t>e_Warsaw_POL,e_Lomza_POL</t>
-  </si>
-  <si>
-    <t>e_Lubin_POL,e_Poznan_POL,e_Koszalin_POL,e_Bydgoszcz_POL</t>
-  </si>
-  <si>
-    <t>e_BielskoBiala_POL,e_Katowice_POL,e_Krakow_POL,e_Tarnow_POL</t>
-  </si>
-  <si>
-    <t>e_Konin_POL,e_Bydgoszcz_POL,e_Wloclawek_POL,e_Kwidzyn_POL,e_Plock_POL</t>
-  </si>
-  <si>
-    <t>e_OstrowiecSwietokrz_POL,e_Pulawy_POL,e_Warsaw_POL</t>
+    <t>distr_wonelc_won_POL_014</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_020</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_018</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_006</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_009</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_004</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_012</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_003</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 3</t>
   </si>
   <si>
     <t>distr_wonelc_won_POL_019</t>
@@ -921,42 +969,24 @@
     <t>connecting wind onshore to buses in cluster 7</t>
   </si>
   <si>
+    <t>distr_wonelc_won_POL_011</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_010</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 10</t>
+  </si>
+  <si>
     <t>distr_wonelc_won_POL_005</t>
   </si>
   <si>
     <t>connecting wind onshore to buses in cluster 5</t>
   </si>
   <si>
-    <t>distr_wonelc_won_POL_018</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_011</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_010</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_012</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_003</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 3</t>
-  </si>
-  <si>
     <t>distr_wonelc_won_POL_002</t>
   </si>
   <si>
@@ -987,42 +1017,57 @@
     <t>connecting wind onshore to buses in cluster 8</t>
   </si>
   <si>
-    <t>distr_wonelc_won_POL_014</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_020</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_006</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_009</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_004</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 4</t>
-  </si>
-  <si>
     <t>distr_wonelc_won_POL_001</t>
   </si>
   <si>
     <t>connecting wind onshore to buses in cluster 1</t>
   </si>
   <si>
+    <t>elc_won_POL_014</t>
+  </si>
+  <si>
+    <t>e_Lubin_POL,e_Poznan_POL,e_Bydgoszcz_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_020</t>
+  </si>
+  <si>
+    <t>e_Sosnowiec_POL,e_KedzierzynKozle_POL,e_Olesnica_POL,e_Gliwice_POL,e_Czestochowa_POL,e_Radomsko_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_018</t>
+  </si>
+  <si>
+    <t>e_Boleslawiec_POL,e_Legnica_POL,e_Swidnica_POL,e_KedzierzynKozle_POL,e_Opole_POL,e_Olesnica_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_006</t>
+  </si>
+  <si>
+    <t>e_Olesnica_POL,e_Konin_POL,e_Bydgoszcz_POL,e_Wloclawek_POL,e_Kwidzyn_POL,e_Plock_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_009</t>
+  </si>
+  <si>
+    <t>e_Gdansk_POL,e_Grudziadz_POL,e_Kwidzyn_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_004</t>
+  </si>
+  <si>
+    <t>elc_won_POL_012</t>
+  </si>
+  <si>
+    <t>e_ZielonaGora_POL,e_GorzowWielkopolski_POL,e_Szczecin_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_003</t>
+  </si>
+  <si>
+    <t>e_Warsaw_POL,e_Lomza_POL,e_Pulawy_POL,e_Bialystok_POL</t>
+  </si>
+  <si>
     <t>elc_won_POL_019</t>
   </si>
   <si>
@@ -1041,42 +1086,24 @@
     <t>e_Warsaw_POL,e_Plock_POL,e_Olsztyn_POL</t>
   </si>
   <si>
+    <t>elc_won_POL_011</t>
+  </si>
+  <si>
+    <t>e_Boleslawiec_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_010</t>
+  </si>
+  <si>
+    <t>e_Police_POL,e_Koszalin_POL,e_Poznan_POL,e_Ustka_POL,e_Bydgoszcz_POL,e_Slupsk_POL,e_Gdansk_POL</t>
+  </si>
+  <si>
     <t>elc_won_POL_005</t>
   </si>
   <si>
     <t>e_Lomza_POL,e_Elk_POL,e_Grajewo_POL,e_Bialystok_POL,e_Chelm_POL</t>
   </si>
   <si>
-    <t>elc_won_POL_018</t>
-  </si>
-  <si>
-    <t>e_Boleslawiec_POL,e_Legnica_POL,e_Swidnica_POL,e_KedzierzynKozle_POL,e_Opole_POL,e_Olesnica_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_011</t>
-  </si>
-  <si>
-    <t>e_Boleslawiec_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_010</t>
-  </si>
-  <si>
-    <t>e_Police_POL,e_Koszalin_POL,e_Poznan_POL,e_Ustka_POL,e_Bydgoszcz_POL,e_Slupsk_POL,e_Gdansk_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_012</t>
-  </si>
-  <si>
-    <t>e_ZielonaGora_POL,e_GorzowWielkopolski_POL,e_Szczecin_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_003</t>
-  </si>
-  <si>
-    <t>e_Warsaw_POL,e_Lomza_POL,e_Pulawy_POL,e_Bialystok_POL</t>
-  </si>
-  <si>
     <t>elc_won_POL_002</t>
   </si>
   <si>
@@ -1107,33 +1134,6 @@
     <t>e_Olsztyn_POL,e_Elk_POL</t>
   </si>
   <si>
-    <t>elc_won_POL_014</t>
-  </si>
-  <si>
-    <t>e_Lubin_POL,e_Poznan_POL,e_Bydgoszcz_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_020</t>
-  </si>
-  <si>
-    <t>e_Sosnowiec_POL,e_KedzierzynKozle_POL,e_Olesnica_POL,e_Gliwice_POL,e_Czestochowa_POL,e_Radomsko_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_006</t>
-  </si>
-  <si>
-    <t>e_Olesnica_POL,e_Konin_POL,e_Bydgoszcz_POL,e_Wloclawek_POL,e_Kwidzyn_POL,e_Plock_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_009</t>
-  </si>
-  <si>
-    <t>e_Gdansk_POL,e_Grudziadz_POL,e_Kwidzyn_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_004</t>
-  </si>
-  <si>
     <t>elc_won_POL_001</t>
   </si>
   <si>
@@ -1152,34 +1152,46 @@
     <t>connecting wind offshore to buses in cluster 7</t>
   </si>
   <si>
+    <t>distr_wofelc_wof_POL_010</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_POL_009</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_POL_004</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_POL_006</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 6</t>
+  </si>
+  <si>
     <t>distr_wofelc_wof_POL_002</t>
   </si>
   <si>
     <t>connecting wind offshore to buses in cluster 2</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_POL_006</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_POL_004</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_POL_010</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_POL_009</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 9</t>
+    <t>distr_wofelc_wof_POL_005</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_POL_001</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 1</t>
   </si>
   <si>
     <t>distr_wofelc_wof_POL_003</t>
@@ -1188,18 +1200,6 @@
     <t>connecting wind offshore to buses in cluster 3</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_POL_005</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_POL_001</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 1</t>
-  </si>
-  <si>
     <t>elc_wof_POL_008</t>
   </si>
   <si>
@@ -1212,43 +1212,43 @@
     <t>e_Koszalin_POL</t>
   </si>
   <si>
+    <t>elc_wof_POL_010</t>
+  </si>
+  <si>
+    <t>elc_wof_POL_009</t>
+  </si>
+  <si>
+    <t>e_Koszalin_POL,e_Ustka_POL</t>
+  </si>
+  <si>
+    <t>elc_wof_POL_004</t>
+  </si>
+  <si>
+    <t>e_Ustka_POL,e_Gdynia_POL</t>
+  </si>
+  <si>
+    <t>elc_wof_POL_006</t>
+  </si>
+  <si>
+    <t>e_Gdynia_POL</t>
+  </si>
+  <si>
     <t>elc_wof_POL_002</t>
   </si>
   <si>
     <t>e_Gdynia_POL,e_Gdansk_POL</t>
   </si>
   <si>
-    <t>elc_wof_POL_006</t>
-  </si>
-  <si>
-    <t>e_Gdynia_POL</t>
-  </si>
-  <si>
-    <t>elc_wof_POL_004</t>
-  </si>
-  <si>
-    <t>e_Ustka_POL,e_Gdynia_POL</t>
-  </si>
-  <si>
-    <t>elc_wof_POL_010</t>
-  </si>
-  <si>
-    <t>elc_wof_POL_009</t>
-  </si>
-  <si>
-    <t>e_Koszalin_POL,e_Ustka_POL</t>
+    <t>elc_wof_POL_005</t>
+  </si>
+  <si>
+    <t>elc_wof_POL_001</t>
+  </si>
+  <si>
+    <t>e_Gdansk_POL</t>
   </si>
   <si>
     <t>elc_wof_POL_003</t>
-  </si>
-  <si>
-    <t>e_Gdansk_POL</t>
-  </si>
-  <si>
-    <t>elc_wof_POL_005</t>
-  </si>
-  <si>
-    <t>elc_wof_POL_001</t>
   </si>
   <si>
     <t>e_won_POL_001</t>
@@ -5844,7 +5844,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02F0484B-22D0-4E0E-A716-2E666EF2C9D0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0C0ECA9-2976-4949-BB23-4E467F422200}">
   <dimension ref="B9:BD30"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -6082,16 +6082,16 @@
         <v>215</v>
       </c>
       <c r="Y11" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="Z11" t="s">
         <v>259</v>
       </c>
       <c r="AA11">
-        <v>0.99693515631487983</v>
+        <v>0.99730738889353909</v>
       </c>
       <c r="AB11">
-        <v>56.188800893869058</v>
+        <v>49.364536951784054</v>
       </c>
       <c r="AD11" t="s">
         <v>214</v>
@@ -6124,10 +6124,10 @@
         <v>320</v>
       </c>
       <c r="AO11">
-        <v>0.99872641243407079</v>
+        <v>0.99730422320290779</v>
       </c>
       <c r="AP11">
-        <v>23.349105375368897</v>
+        <v>49.422574613357185</v>
       </c>
       <c r="AR11" t="s">
         <v>214</v>
@@ -6228,16 +6228,16 @@
         <v>219</v>
       </c>
       <c r="Y12" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="Z12" t="s">
         <v>260</v>
       </c>
       <c r="AA12">
-        <v>0.99606480786442353</v>
+        <v>0.99658775492800411</v>
       </c>
       <c r="AB12">
-        <v>72.145189152235062</v>
+        <v>62.557826319923819</v>
       </c>
       <c r="AD12" t="s">
         <v>214</v>
@@ -6270,10 +6270,10 @@
         <v>322</v>
       </c>
       <c r="AO12">
-        <v>0.99776911581804295</v>
+        <v>0.99805709209211746</v>
       </c>
       <c r="AP12">
-        <v>40.899543335879912</v>
+        <v>35.619978311179104</v>
       </c>
       <c r="AR12" t="s">
         <v>214</v>
@@ -6374,16 +6374,16 @@
         <v>221</v>
       </c>
       <c r="Y13" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="Z13" t="s">
         <v>261</v>
       </c>
       <c r="AA13">
-        <v>0.99785589517057005</v>
+        <v>0.99510886326373238</v>
       </c>
       <c r="AB13">
-        <v>39.308588539549028</v>
+        <v>89.670840164906522</v>
       </c>
       <c r="AD13" t="s">
         <v>214</v>
@@ -6416,10 +6416,10 @@
         <v>324</v>
       </c>
       <c r="AO13">
-        <v>0.99653588726932718</v>
+        <v>0.99622969699231045</v>
       </c>
       <c r="AP13">
-        <v>63.508733395668145</v>
+        <v>69.122221807641537</v>
       </c>
       <c r="AR13" t="s">
         <v>214</v>
@@ -6449,13 +6449,13 @@
         <v>382</v>
       </c>
       <c r="BB13" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="BC13">
-        <v>0.99353721168226494</v>
+        <v>0.99608994650263638</v>
       </c>
       <c r="BD13">
-        <v>780.55486105754892</v>
+        <v>589.950661136485</v>
       </c>
     </row>
     <row r="14" spans="2:56">
@@ -6562,10 +6562,10 @@
         <v>326</v>
       </c>
       <c r="AO14">
-        <v>0.9963019969989696</v>
+        <v>0.99827231256984739</v>
       </c>
       <c r="AP14">
-        <v>67.796721685557472</v>
+        <v>31.674269552798414</v>
       </c>
       <c r="AR14" t="s">
         <v>214</v>
@@ -6592,16 +6592,16 @@
         <v>364</v>
       </c>
       <c r="BA14" t="s">
+        <v>383</v>
+      </c>
+      <c r="BB14" t="s">
         <v>384</v>
       </c>
-      <c r="BB14" t="s">
-        <v>385</v>
-      </c>
       <c r="BC14">
-        <v>0.99615739524125424</v>
+        <v>0.99399682431672776</v>
       </c>
       <c r="BD14">
-        <v>584.91448865302027</v>
+        <v>746.2371176843244</v>
       </c>
     </row>
     <row r="15" spans="2:56">
@@ -6708,10 +6708,10 @@
         <v>328</v>
       </c>
       <c r="AO15">
-        <v>0.99622969699231045</v>
+        <v>0.99635146162488653</v>
       </c>
       <c r="AP15">
-        <v>69.122221807641537</v>
+        <v>66.889870210414614</v>
       </c>
       <c r="AR15" t="s">
         <v>214</v>
@@ -6738,10 +6738,10 @@
         <v>366</v>
       </c>
       <c r="BA15" t="s">
+        <v>385</v>
+      </c>
+      <c r="BB15" t="s">
         <v>386</v>
-      </c>
-      <c r="BB15" t="s">
-        <v>387</v>
       </c>
       <c r="BC15">
         <v>0.99255663966463281</v>
@@ -6851,13 +6851,13 @@
         <v>329</v>
       </c>
       <c r="AN16" t="s">
-        <v>330</v>
+        <v>268</v>
       </c>
       <c r="AO16">
-        <v>0.99802303154782224</v>
+        <v>0.99586212495478665</v>
       </c>
       <c r="AP16">
-        <v>36.244421623259619</v>
+        <v>75.861042495577635</v>
       </c>
       <c r="AR16" t="s">
         <v>214</v>
@@ -6884,16 +6884,16 @@
         <v>368</v>
       </c>
       <c r="BA16" t="s">
+        <v>387</v>
+      </c>
+      <c r="BB16" t="s">
         <v>388</v>
       </c>
-      <c r="BB16" t="s">
-        <v>381</v>
-      </c>
       <c r="BC16">
-        <v>0.99608994650263638</v>
+        <v>0.99615739524125424</v>
       </c>
       <c r="BD16">
-        <v>589.950661136485</v>
+        <v>584.91448865302027</v>
       </c>
     </row>
     <row r="17" spans="2:56">
@@ -6958,16 +6958,16 @@
         <v>229</v>
       </c>
       <c r="Y17" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="Z17" t="s">
         <v>265</v>
       </c>
       <c r="AA17">
-        <v>0.99481478101166732</v>
+        <v>0.99930490342600053</v>
       </c>
       <c r="AB17">
-        <v>95.062348119433295</v>
+        <v>12.743437189989784</v>
       </c>
       <c r="AD17" t="s">
         <v>214</v>
@@ -6994,16 +6994,16 @@
         <v>291</v>
       </c>
       <c r="AM17" t="s">
+        <v>330</v>
+      </c>
+      <c r="AN17" t="s">
         <v>331</v>
       </c>
-      <c r="AN17" t="s">
-        <v>332</v>
-      </c>
       <c r="AO17">
-        <v>0.99714358927215652</v>
+        <v>0.99749126227646956</v>
       </c>
       <c r="AP17">
-        <v>52.367530010463909</v>
+        <v>45.993524931390482</v>
       </c>
       <c r="AR17" t="s">
         <v>214</v>
@@ -7036,10 +7036,10 @@
         <v>390</v>
       </c>
       <c r="BC17">
-        <v>0.99399682431672776</v>
+        <v>0.99353721168226494</v>
       </c>
       <c r="BD17">
-        <v>746.2371176843244</v>
+        <v>780.55486105754892</v>
       </c>
     </row>
     <row r="18" spans="2:56">
@@ -7104,16 +7104,16 @@
         <v>231</v>
       </c>
       <c r="Y18" t="s">
-        <v>203</v>
+        <v>212</v>
       </c>
       <c r="Z18" t="s">
         <v>266</v>
       </c>
       <c r="AA18">
-        <v>0.99681878296180493</v>
+        <v>0.99881801309037566</v>
       </c>
       <c r="AB18">
-        <v>58.322312366909152</v>
+        <v>21.669760009780138</v>
       </c>
       <c r="AD18" t="s">
         <v>214</v>
@@ -7140,16 +7140,16 @@
         <v>293</v>
       </c>
       <c r="AM18" t="s">
+        <v>332</v>
+      </c>
+      <c r="AN18" t="s">
         <v>333</v>
       </c>
-      <c r="AN18" t="s">
-        <v>334</v>
-      </c>
       <c r="AO18">
-        <v>0.99749126227646956</v>
+        <v>0.99807543246352515</v>
       </c>
       <c r="AP18">
-        <v>45.993524931390482</v>
+        <v>35.283738168705199</v>
       </c>
       <c r="AR18" t="s">
         <v>214</v>
@@ -7179,13 +7179,13 @@
         <v>391</v>
       </c>
       <c r="BB18" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="BC18">
-        <v>0.99564787435456037</v>
+        <v>0.99328660064428831</v>
       </c>
       <c r="BD18">
-        <v>622.95871485949408</v>
+        <v>799.26715189313825</v>
       </c>
     </row>
     <row r="19" spans="2:56">
@@ -7250,16 +7250,16 @@
         <v>233</v>
       </c>
       <c r="Y19" t="s">
-        <v>195</v>
+        <v>206</v>
       </c>
       <c r="Z19" t="s">
         <v>267</v>
       </c>
       <c r="AA19">
-        <v>0.99770934816564383</v>
+        <v>0.99790408176624201</v>
       </c>
       <c r="AB19">
-        <v>41.995283629862939</v>
+        <v>38.425167618896296</v>
       </c>
       <c r="AD19" t="s">
         <v>214</v>
@@ -7286,16 +7286,16 @@
         <v>295</v>
       </c>
       <c r="AM19" t="s">
+        <v>334</v>
+      </c>
+      <c r="AN19" t="s">
         <v>335</v>
       </c>
-      <c r="AN19" t="s">
-        <v>336</v>
-      </c>
       <c r="AO19">
-        <v>0.99807543246352515</v>
+        <v>0.99872641243407079</v>
       </c>
       <c r="AP19">
-        <v>35.283738168705199</v>
+        <v>23.349105375368897</v>
       </c>
       <c r="AR19" t="s">
         <v>214</v>
@@ -7322,16 +7322,16 @@
         <v>374</v>
       </c>
       <c r="BA19" t="s">
+        <v>392</v>
+      </c>
+      <c r="BB19" t="s">
         <v>393</v>
       </c>
-      <c r="BB19" t="s">
-        <v>385</v>
-      </c>
       <c r="BC19">
-        <v>0.99328660064428831</v>
+        <v>0.99644441082752833</v>
       </c>
       <c r="BD19">
-        <v>799.26715189313825</v>
+        <v>563.48399154455342</v>
       </c>
     </row>
     <row r="20" spans="2:56">
@@ -7396,16 +7396,16 @@
         <v>235</v>
       </c>
       <c r="Y20" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="Z20" t="s">
         <v>268</v>
       </c>
       <c r="AA20">
-        <v>0.9970292559096442</v>
+        <v>0.99606480786442353</v>
       </c>
       <c r="AB20">
-        <v>54.463641656523762</v>
+        <v>72.145189152235062</v>
       </c>
       <c r="AD20" t="s">
         <v>214</v>
@@ -7432,16 +7432,16 @@
         <v>297</v>
       </c>
       <c r="AM20" t="s">
+        <v>336</v>
+      </c>
+      <c r="AN20" t="s">
         <v>337</v>
       </c>
-      <c r="AN20" t="s">
-        <v>338</v>
-      </c>
       <c r="AO20">
-        <v>0.99845791964146047</v>
+        <v>0.99776911581804295</v>
       </c>
       <c r="AP20">
-        <v>28.2714732398913</v>
+        <v>40.899543335879912</v>
       </c>
       <c r="AR20" t="s">
         <v>214</v>
@@ -7471,13 +7471,13 @@
         <v>394</v>
       </c>
       <c r="BB20" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="BC20">
-        <v>0.99644441082752833</v>
+        <v>0.99564787435456037</v>
       </c>
       <c r="BD20">
-        <v>563.48399154455342</v>
+        <v>622.95871485949408</v>
       </c>
     </row>
     <row r="21" spans="2:56">
@@ -7542,16 +7542,16 @@
         <v>237</v>
       </c>
       <c r="Y21" t="s">
-        <v>208</v>
+        <v>193</v>
       </c>
       <c r="Z21" t="s">
         <v>269</v>
       </c>
       <c r="AA21">
-        <v>0.9982126095160021</v>
+        <v>0.99707401400885998</v>
       </c>
       <c r="AB21">
-        <v>32.768825539961391</v>
+        <v>53.643076504234422</v>
       </c>
       <c r="AD21" t="s">
         <v>214</v>
@@ -7578,16 +7578,16 @@
         <v>299</v>
       </c>
       <c r="AM21" t="s">
+        <v>338</v>
+      </c>
+      <c r="AN21" t="s">
         <v>339</v>
       </c>
-      <c r="AN21" t="s">
-        <v>340</v>
-      </c>
       <c r="AO21">
-        <v>0.99641308487583879</v>
+        <v>0.99653588726932718</v>
       </c>
       <c r="AP21">
-        <v>65.760110609622657</v>
+        <v>63.508733395668145</v>
       </c>
     </row>
     <row r="22" spans="2:56">
@@ -7652,16 +7652,16 @@
         <v>239</v>
       </c>
       <c r="Y22" t="s">
-        <v>198</v>
+        <v>207</v>
       </c>
       <c r="Z22" t="s">
         <v>270</v>
       </c>
       <c r="AA22">
-        <v>0.99658775492800411</v>
+        <v>0.99826037700975512</v>
       </c>
       <c r="AB22">
-        <v>62.557826319923819</v>
+        <v>31.893088154488542</v>
       </c>
       <c r="AD22" t="s">
         <v>214</v>
@@ -7688,16 +7688,16 @@
         <v>301</v>
       </c>
       <c r="AM22" t="s">
+        <v>340</v>
+      </c>
+      <c r="AN22" t="s">
         <v>341</v>
       </c>
-      <c r="AN22" t="s">
-        <v>342</v>
-      </c>
       <c r="AO22">
-        <v>0.99449756685866841</v>
+        <v>0.99802303154782224</v>
       </c>
       <c r="AP22">
-        <v>100.87794092441324</v>
+        <v>36.244421623259619</v>
       </c>
     </row>
     <row r="23" spans="2:56">
@@ -7762,16 +7762,16 @@
         <v>241</v>
       </c>
       <c r="Y23" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="Z23" t="s">
         <v>271</v>
       </c>
       <c r="AA23">
-        <v>0.99510886326373238</v>
+        <v>0.99922515067657613</v>
       </c>
       <c r="AB23">
-        <v>89.670840164906522</v>
+        <v>14.205570929438155</v>
       </c>
       <c r="AD23" t="s">
         <v>214</v>
@@ -7798,16 +7798,16 @@
         <v>303</v>
       </c>
       <c r="AM23" t="s">
+        <v>342</v>
+      </c>
+      <c r="AN23" t="s">
         <v>343</v>
       </c>
-      <c r="AN23" t="s">
-        <v>344</v>
-      </c>
       <c r="AO23">
-        <v>0.99883902037019667</v>
+        <v>0.99714358927215652</v>
       </c>
       <c r="AP23">
-        <v>21.284626546395259</v>
+        <v>52.367530010463909</v>
       </c>
     </row>
     <row r="24" spans="2:56">
@@ -7872,16 +7872,16 @@
         <v>243</v>
       </c>
       <c r="Y24" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="Z24" t="s">
         <v>272</v>
       </c>
       <c r="AA24">
-        <v>0.99707401400885998</v>
+        <v>0.99770934816564383</v>
       </c>
       <c r="AB24">
-        <v>53.643076504234422</v>
+        <v>41.995283629862939</v>
       </c>
       <c r="AD24" t="s">
         <v>214</v>
@@ -7908,16 +7908,16 @@
         <v>305</v>
       </c>
       <c r="AM24" t="s">
+        <v>344</v>
+      </c>
+      <c r="AN24" t="s">
         <v>345</v>
       </c>
-      <c r="AN24" t="s">
-        <v>346</v>
-      </c>
       <c r="AO24">
-        <v>0.99521984547821263</v>
+        <v>0.9963019969989696</v>
       </c>
       <c r="AP24">
-        <v>87.636166232768815</v>
+        <v>67.796721685557472</v>
       </c>
     </row>
     <row r="25" spans="2:56">
@@ -7982,16 +7982,16 @@
         <v>245</v>
       </c>
       <c r="Y25" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="Z25" t="s">
         <v>273</v>
       </c>
       <c r="AA25">
-        <v>0.99826037700975512</v>
+        <v>0.9970292559096442</v>
       </c>
       <c r="AB25">
-        <v>31.893088154488542</v>
+        <v>54.463641656523762</v>
       </c>
       <c r="AD25" t="s">
         <v>214</v>
@@ -8018,16 +8018,16 @@
         <v>307</v>
       </c>
       <c r="AM25" t="s">
+        <v>346</v>
+      </c>
+      <c r="AN25" t="s">
         <v>347</v>
       </c>
-      <c r="AN25" t="s">
-        <v>348</v>
-      </c>
       <c r="AO25">
-        <v>0.99730422320290779</v>
+        <v>0.99845791964146047</v>
       </c>
       <c r="AP25">
-        <v>49.422574613357185</v>
+        <v>28.2714732398913</v>
       </c>
     </row>
     <row r="26" spans="2:56">
@@ -8092,16 +8092,16 @@
         <v>247</v>
       </c>
       <c r="Y26" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="Z26" t="s">
         <v>274</v>
       </c>
       <c r="AA26">
-        <v>0.99922515067657613</v>
+        <v>0.9982126095160021</v>
       </c>
       <c r="AB26">
-        <v>14.205570929438155</v>
+        <v>32.768825539961391</v>
       </c>
       <c r="AD26" t="s">
         <v>214</v>
@@ -8128,16 +8128,16 @@
         <v>309</v>
       </c>
       <c r="AM26" t="s">
+        <v>348</v>
+      </c>
+      <c r="AN26" t="s">
         <v>349</v>
       </c>
-      <c r="AN26" t="s">
-        <v>350</v>
-      </c>
       <c r="AO26">
-        <v>0.99805709209211746</v>
+        <v>0.99641308487583879</v>
       </c>
       <c r="AP26">
-        <v>35.619978311179104</v>
+        <v>65.760110609622657</v>
       </c>
     </row>
     <row r="27" spans="2:56">
@@ -8202,16 +8202,16 @@
         <v>249</v>
       </c>
       <c r="Y27" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Z27" t="s">
         <v>275</v>
       </c>
       <c r="AA27">
-        <v>0.99730738889353909</v>
+        <v>0.99785589517057005</v>
       </c>
       <c r="AB27">
-        <v>49.364536951784054</v>
+        <v>39.308588539549028</v>
       </c>
       <c r="AD27" t="s">
         <v>214</v>
@@ -8238,16 +8238,16 @@
         <v>311</v>
       </c>
       <c r="AM27" t="s">
+        <v>350</v>
+      </c>
+      <c r="AN27" t="s">
         <v>351</v>
       </c>
-      <c r="AN27" t="s">
-        <v>352</v>
-      </c>
       <c r="AO27">
-        <v>0.99827231256984739</v>
+        <v>0.99449756685866841</v>
       </c>
       <c r="AP27">
-        <v>31.674269552798414</v>
+        <v>100.87794092441324</v>
       </c>
     </row>
     <row r="28" spans="2:56">
@@ -8312,16 +8312,16 @@
         <v>251</v>
       </c>
       <c r="Y28" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="Z28" t="s">
         <v>276</v>
       </c>
       <c r="AA28">
-        <v>0.99790408176624201</v>
+        <v>0.99481478101166732</v>
       </c>
       <c r="AB28">
-        <v>38.425167618896296</v>
+        <v>95.062348119433295</v>
       </c>
       <c r="AD28" t="s">
         <v>214</v>
@@ -8348,16 +8348,16 @@
         <v>313</v>
       </c>
       <c r="AM28" t="s">
+        <v>352</v>
+      </c>
+      <c r="AN28" t="s">
         <v>353</v>
       </c>
-      <c r="AN28" t="s">
-        <v>354</v>
-      </c>
       <c r="AO28">
-        <v>0.99635146162488653</v>
+        <v>0.99883902037019667</v>
       </c>
       <c r="AP28">
-        <v>66.889870210414614</v>
+        <v>21.284626546395259</v>
       </c>
     </row>
     <row r="29" spans="2:56">
@@ -8422,16 +8422,16 @@
         <v>253</v>
       </c>
       <c r="Y29" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="Z29" t="s">
         <v>277</v>
       </c>
       <c r="AA29">
-        <v>0.99930490342600053</v>
+        <v>0.99681878296180493</v>
       </c>
       <c r="AB29">
-        <v>12.743437189989784</v>
+        <v>58.322312366909152</v>
       </c>
       <c r="AD29" t="s">
         <v>214</v>
@@ -8458,16 +8458,16 @@
         <v>315</v>
       </c>
       <c r="AM29" t="s">
+        <v>354</v>
+      </c>
+      <c r="AN29" t="s">
         <v>355</v>
       </c>
-      <c r="AN29" t="s">
-        <v>260</v>
-      </c>
       <c r="AO29">
-        <v>0.99586212495478665</v>
+        <v>0.99521984547821263</v>
       </c>
       <c r="AP29">
-        <v>75.861042495577635</v>
+        <v>87.636166232768815</v>
       </c>
     </row>
     <row r="30" spans="2:56">
@@ -8532,16 +8532,16 @@
         <v>255</v>
       </c>
       <c r="Y30" t="s">
-        <v>212</v>
+        <v>200</v>
       </c>
       <c r="Z30" t="s">
         <v>278</v>
       </c>
       <c r="AA30">
-        <v>0.99881801309037566</v>
+        <v>0.99693515631487983</v>
       </c>
       <c r="AB30">
-        <v>21.669760009780138</v>
+        <v>56.188800893869058</v>
       </c>
       <c r="AD30" t="s">
         <v>214</v>
@@ -8586,7 +8586,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59151317-8DD6-4792-A37C-CEF8C67A62EE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19FD8E05-430E-4DA8-9DE8-20D898A6DE14}">
   <dimension ref="B9:Z30"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -8731,7 +8731,7 @@
         <v>435</v>
       </c>
       <c r="X11" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="Y11">
         <v>0.83925000000000005</v>
@@ -8766,7 +8766,7 @@
         <v>397</v>
       </c>
       <c r="K12" t="s">
-        <v>337</v>
+        <v>346</v>
       </c>
       <c r="L12">
         <v>0.42035497786033621</v>
@@ -8799,7 +8799,7 @@
         <v>437</v>
       </c>
       <c r="X12" t="s">
-        <v>382</v>
+        <v>389</v>
       </c>
       <c r="Y12">
         <v>16.887</v>
@@ -8834,7 +8834,7 @@
         <v>399</v>
       </c>
       <c r="K13" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="L13">
         <v>1.6077871713950227</v>
@@ -8867,7 +8867,7 @@
         <v>439</v>
       </c>
       <c r="X13" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="Y13">
         <v>11.2965</v>
@@ -8902,7 +8902,7 @@
         <v>401</v>
       </c>
       <c r="K14" t="s">
-        <v>355</v>
+        <v>329</v>
       </c>
       <c r="L14">
         <v>2.531891424764753</v>
@@ -8935,7 +8935,7 @@
         <v>441</v>
       </c>
       <c r="X14" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="Y14">
         <v>6.6577500000000001</v>
@@ -8970,7 +8970,7 @@
         <v>403</v>
       </c>
       <c r="K15" t="s">
-        <v>325</v>
+        <v>344</v>
       </c>
       <c r="L15">
         <v>7.6497810049421515</v>
@@ -9003,7 +9003,7 @@
         <v>443</v>
       </c>
       <c r="X15" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="Y15">
         <v>17.089500000000001</v>
@@ -9038,7 +9038,7 @@
         <v>405</v>
       </c>
       <c r="K16" t="s">
-        <v>351</v>
+        <v>325</v>
       </c>
       <c r="L16">
         <v>0.60733325583919984</v>
@@ -9071,7 +9071,7 @@
         <v>445</v>
       </c>
       <c r="X16" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="Y16">
         <v>8.8230000000000004</v>
@@ -9106,7 +9106,7 @@
         <v>407</v>
       </c>
       <c r="K17" t="s">
-        <v>323</v>
+        <v>338</v>
       </c>
       <c r="L17">
         <v>0.78389041837100704</v>
@@ -9174,7 +9174,7 @@
         <v>409</v>
       </c>
       <c r="K18" t="s">
-        <v>345</v>
+        <v>354</v>
       </c>
       <c r="L18">
         <v>3.0365724666245324</v>
@@ -9242,7 +9242,7 @@
         <v>411</v>
       </c>
       <c r="K19" t="s">
-        <v>353</v>
+        <v>327</v>
       </c>
       <c r="L19">
         <v>0.22970161230087291</v>
@@ -9275,7 +9275,7 @@
         <v>451</v>
       </c>
       <c r="X19" t="s">
-        <v>389</v>
+        <v>383</v>
       </c>
       <c r="Y19">
         <v>13.37175</v>
@@ -9310,7 +9310,7 @@
         <v>413</v>
       </c>
       <c r="K20" t="s">
-        <v>331</v>
+        <v>342</v>
       </c>
       <c r="L20">
         <v>0.27066515065379043</v>
@@ -9343,7 +9343,7 @@
         <v>453</v>
       </c>
       <c r="X20" t="s">
-        <v>388</v>
+        <v>382</v>
       </c>
       <c r="Y20">
         <v>3.9427500000000002</v>
@@ -9378,7 +9378,7 @@
         <v>415</v>
       </c>
       <c r="K21" t="s">
-        <v>329</v>
+        <v>340</v>
       </c>
       <c r="L21">
         <v>0.32193208719379746</v>
@@ -9413,7 +9413,7 @@
         <v>417</v>
       </c>
       <c r="K22" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="L22">
         <v>0.6573344927201471</v>
@@ -9448,7 +9448,7 @@
         <v>419</v>
       </c>
       <c r="K23" t="s">
-        <v>343</v>
+        <v>352</v>
       </c>
       <c r="L23">
         <v>0.28992997651770519</v>
@@ -9483,7 +9483,7 @@
         <v>421</v>
       </c>
       <c r="K24" t="s">
-        <v>347</v>
+        <v>319</v>
       </c>
       <c r="L24">
         <v>0.74609319967150689</v>
@@ -9518,7 +9518,7 @@
         <v>423</v>
       </c>
       <c r="K25" t="s">
-        <v>339</v>
+        <v>348</v>
       </c>
       <c r="L25">
         <v>0.35328950844501877</v>
@@ -9553,7 +9553,7 @@
         <v>425</v>
       </c>
       <c r="K26" t="s">
-        <v>341</v>
+        <v>350</v>
       </c>
       <c r="L26">
         <v>0.7924639655878376</v>
@@ -9588,7 +9588,7 @@
         <v>427</v>
       </c>
       <c r="K27" t="s">
-        <v>321</v>
+        <v>336</v>
       </c>
       <c r="L27">
         <v>0.55411362221124194</v>
@@ -9623,7 +9623,7 @@
         <v>429</v>
       </c>
       <c r="K28" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="L28">
         <v>1.4327274230737423</v>
@@ -9658,7 +9658,7 @@
         <v>431</v>
       </c>
       <c r="K29" t="s">
-        <v>319</v>
+        <v>334</v>
       </c>
       <c r="L29">
         <v>0.56742801517356967</v>
@@ -9693,7 +9693,7 @@
         <v>433</v>
       </c>
       <c r="K30" t="s">
-        <v>349</v>
+        <v>321</v>
       </c>
       <c r="L30">
         <v>0.35405891742987328</v>
@@ -9708,7 +9708,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{339FE14C-E19A-4BFE-A95A-E195613017B1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4BEB3642-4757-487B-BE5B-3F7C2E0C5BED}">
   <dimension ref="B9:Y136"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -14069,7 +14069,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B9325FF-5D1B-41D3-B3B3-572D34CFCA51}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A2659BC-18B1-4844-A6BC-86A7AC754AB2}">
   <dimension ref="B9:T88"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_POL_grids_kan50/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_POL_grids_kan50/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1593261B-018E-42A2-8374-FD8809C3FAAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED96CF02-0040-41D0-9880-EE0143F7B2E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -723,6 +723,42 @@
     <t>daynite</t>
   </si>
   <si>
+    <t>distr_solelc_spv_POL_003</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_007</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_016</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_014</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_008</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_004</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 4</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_POL_006</t>
   </si>
   <si>
@@ -735,6 +771,18 @@
     <t>connecting solar to buses in cluster 10</t>
   </si>
   <si>
+    <t>distr_solelc_spv_POL_017</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_020</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 20</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_POL_002</t>
   </si>
   <si>
@@ -753,22 +801,34 @@
     <t>connecting solar to buses in cluster 9</t>
   </si>
   <si>
-    <t>distr_solelc_spv_POL_017</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_020</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_014</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 14</t>
+    <t>distr_solelc_spv_POL_001</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_015</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_018</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_012</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_011</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 11</t>
   </si>
   <si>
     <t>distr_solelc_spv_POL_013</t>
@@ -777,66 +837,6 @@
     <t>connecting solar to buses in cluster 13</t>
   </si>
   <si>
-    <t>distr_solelc_spv_POL_001</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_015</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_018</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_003</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_007</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_016</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_004</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_012</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_011</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_008</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 8</t>
-  </si>
-  <si>
     <t>comm-in</t>
   </si>
   <si>
@@ -846,12 +846,36 @@
     <t>e_Lubin_POL,e_Poznan_POL,e_Koszalin_POL,e_Bydgoszcz_POL</t>
   </si>
   <si>
+    <t>e_Lubin_POL,e_Swidnica_POL,e_Wroclaw_POL,e_Poznan_POL,e_Olesnica_POL</t>
+  </si>
+  <si>
+    <t>e_Koszalin_POL,e_Ustka_POL,e_Slupsk_POL</t>
+  </si>
+  <si>
+    <t>e_Olesnica_POL,e_Konin_POL,e_PiotrkowTrybunalsk_POL,e_Plock_POL</t>
+  </si>
+  <si>
+    <t>e_BielskoBiala_POL,e_Katowice_POL,e_Krakow_POL,e_Tarnow_POL</t>
+  </si>
+  <si>
+    <t>e_Bydgoszcz_POL,e_Gdansk_POL,e_Grudziadz_POL,e_Kwidzyn_POL</t>
+  </si>
+  <si>
+    <t>e_GorzowWielkopolski_POL,e_Szczecin_POL,e_Police_POL</t>
+  </si>
+  <si>
     <t>e_Plock_POL,e_Olsztyn_POL,e_Warsaw_POL</t>
   </si>
   <si>
     <t>e_Elk_POL,e_Grajewo_POL</t>
   </si>
   <si>
+    <t>e_Konin_POL,e_Bydgoszcz_POL,e_Wloclawek_POL,e_Kwidzyn_POL,e_Plock_POL</t>
+  </si>
+  <si>
+    <t>e_OstrowiecSwietokrz_POL,e_Pulawy_POL,e_Warsaw_POL</t>
+  </si>
+  <si>
     <t>e_Legnica_POL,e_Swidnica_POL,e_KedzierzynKozle_POL,e_Opole_POL</t>
   </si>
   <si>
@@ -861,46 +885,94 @@
     <t>e_Pulawy_POL,e_Bialystok_POL,e_Chelm_POL</t>
   </si>
   <si>
-    <t>e_Konin_POL,e_Bydgoszcz_POL,e_Wloclawek_POL,e_Kwidzyn_POL,e_Plock_POL</t>
-  </si>
-  <si>
-    <t>e_OstrowiecSwietokrz_POL,e_Pulawy_POL,e_Warsaw_POL</t>
-  </si>
-  <si>
-    <t>e_BielskoBiala_POL,e_Katowice_POL,e_Krakow_POL,e_Tarnow_POL</t>
+    <t>e_Boleslawiec_POL,e_ZielonaGora_POL</t>
+  </si>
+  <si>
+    <t>e_Sosnowiec_POL,e_KedzierzynKozle_POL,e_Olesnica_POL,e_Gliwice_POL,e_Czestochowa_POL,e_Radomsko_POL,e_PiotrkowTrybunalsk_POL,e_Kielce_POL</t>
+  </si>
+  <si>
+    <t>e_Warsaw_POL,e_Lomza_POL</t>
+  </si>
+  <si>
+    <t>e_Krosno_POL,e_Mielec_POL,e_Debica_POL,e_Zamosc_POL</t>
+  </si>
+  <si>
+    <t>e_Lomza_POL,e_Elk_POL,e_Bialystok_POL,e_Grajewo_POL</t>
   </si>
   <si>
     <t>e_Rzeszow_POL,e_Zamosc_POL,e_Pulawy_POL,e_Chelm_POL</t>
   </si>
   <si>
-    <t>e_Boleslawiec_POL,e_ZielonaGora_POL</t>
-  </si>
-  <si>
-    <t>e_Sosnowiec_POL,e_KedzierzynKozle_POL,e_Olesnica_POL,e_Gliwice_POL,e_Czestochowa_POL,e_Radomsko_POL,e_PiotrkowTrybunalsk_POL,e_Kielce_POL</t>
-  </si>
-  <si>
-    <t>e_Warsaw_POL,e_Lomza_POL</t>
-  </si>
-  <si>
-    <t>e_Lubin_POL,e_Swidnica_POL,e_Wroclaw_POL,e_Poznan_POL,e_Olesnica_POL</t>
-  </si>
-  <si>
-    <t>e_Koszalin_POL,e_Ustka_POL,e_Slupsk_POL</t>
-  </si>
-  <si>
-    <t>e_Olesnica_POL,e_Konin_POL,e_PiotrkowTrybunalsk_POL,e_Plock_POL</t>
-  </si>
-  <si>
-    <t>e_GorzowWielkopolski_POL,e_Szczecin_POL,e_Police_POL</t>
-  </si>
-  <si>
-    <t>e_Krosno_POL,e_Mielec_POL,e_Debica_POL,e_Zamosc_POL</t>
-  </si>
-  <si>
-    <t>e_Lomza_POL,e_Elk_POL,e_Bialystok_POL,e_Grajewo_POL</t>
-  </si>
-  <si>
-    <t>e_Bydgoszcz_POL,e_Gdansk_POL,e_Grudziadz_POL,e_Kwidzyn_POL</t>
+    <t>distr_wonelc_won_POL_005</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_018</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_019</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_017</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_007</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_006</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_009</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_004</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_015</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_016</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_001</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_002</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 2</t>
   </si>
   <si>
     <t>distr_wonelc_won_POL_014</t>
@@ -915,28 +987,28 @@
     <t>connecting wind onshore to buses in cluster 20</t>
   </si>
   <si>
-    <t>distr_wonelc_won_POL_018</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_006</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_009</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_004</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 4</t>
+    <t>distr_wonelc_won_POL_013</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_008</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_011</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_010</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 10</t>
   </si>
   <si>
     <t>distr_wonelc_won_POL_012</t>
@@ -951,76 +1023,73 @@
     <t>connecting wind onshore to buses in cluster 3</t>
   </si>
   <si>
-    <t>distr_wonelc_won_POL_019</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_017</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_007</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_011</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_010</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_005</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_002</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_015</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_016</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_013</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_008</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_001</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 1</t>
+    <t>elc_won_POL_005</t>
+  </si>
+  <si>
+    <t>e_Lomza_POL,e_Elk_POL,e_Grajewo_POL,e_Bialystok_POL,e_Chelm_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_018</t>
+  </si>
+  <si>
+    <t>e_Boleslawiec_POL,e_Legnica_POL,e_Swidnica_POL,e_KedzierzynKozle_POL,e_Opole_POL,e_Olesnica_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_019</t>
+  </si>
+  <si>
+    <t>e_Katowice_POL,e_Czestochowa_POL,e_Krakow_POL,e_Kielce_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_017</t>
+  </si>
+  <si>
+    <t>e_Tarnow_POL,e_Krosno_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_007</t>
+  </si>
+  <si>
+    <t>e_Warsaw_POL,e_Plock_POL,e_Olsztyn_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_006</t>
+  </si>
+  <si>
+    <t>e_Olesnica_POL,e_Konin_POL,e_Bydgoszcz_POL,e_Wloclawek_POL,e_Kwidzyn_POL,e_Plock_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_009</t>
+  </si>
+  <si>
+    <t>e_Gdansk_POL,e_Grudziadz_POL,e_Kwidzyn_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_004</t>
+  </si>
+  <si>
+    <t>elc_won_POL_015</t>
+  </si>
+  <si>
+    <t>e_BielskoBiala_POL,e_Krakow_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_016</t>
+  </si>
+  <si>
+    <t>e_Krosno_POL,e_Debica_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_001</t>
+  </si>
+  <si>
+    <t>e_PiotrkowTrybunalsk_POL,e_Kielce_POL,e_Warsaw_POL,e_OstrowiecSwietokrz_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_002</t>
+  </si>
+  <si>
+    <t>e_Tarnow_POL,e_Kielce_POL,e_OstrowiecSwietokrz_POL,e_Mielec_POL,e_Pulawy_POL,e_Rzeszow_POL</t>
   </si>
   <si>
     <t>elc_won_POL_014</t>
@@ -1035,25 +1104,28 @@
     <t>e_Sosnowiec_POL,e_KedzierzynKozle_POL,e_Olesnica_POL,e_Gliwice_POL,e_Czestochowa_POL,e_Radomsko_POL</t>
   </si>
   <si>
-    <t>elc_won_POL_018</t>
-  </si>
-  <si>
-    <t>e_Boleslawiec_POL,e_Legnica_POL,e_Swidnica_POL,e_KedzierzynKozle_POL,e_Opole_POL,e_Olesnica_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_006</t>
-  </si>
-  <si>
-    <t>e_Olesnica_POL,e_Konin_POL,e_Bydgoszcz_POL,e_Wloclawek_POL,e_Kwidzyn_POL,e_Plock_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_009</t>
-  </si>
-  <si>
-    <t>e_Gdansk_POL,e_Grudziadz_POL,e_Kwidzyn_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_004</t>
+    <t>elc_won_POL_013</t>
+  </si>
+  <si>
+    <t>e_Lubin_POL,e_Wroclaw_POL,e_Poznan_POL,e_Olesnica_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_008</t>
+  </si>
+  <si>
+    <t>e_Olsztyn_POL,e_Elk_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_011</t>
+  </si>
+  <si>
+    <t>e_Boleslawiec_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_010</t>
+  </si>
+  <si>
+    <t>e_Police_POL,e_Koszalin_POL,e_Poznan_POL,e_Ustka_POL,e_Bydgoszcz_POL,e_Slupsk_POL,e_Gdansk_POL</t>
   </si>
   <si>
     <t>elc_won_POL_012</t>
@@ -1068,76 +1140,34 @@
     <t>e_Warsaw_POL,e_Lomza_POL,e_Pulawy_POL,e_Bialystok_POL</t>
   </si>
   <si>
-    <t>elc_won_POL_019</t>
-  </si>
-  <si>
-    <t>e_Katowice_POL,e_Czestochowa_POL,e_Krakow_POL,e_Kielce_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_017</t>
-  </si>
-  <si>
-    <t>e_Tarnow_POL,e_Krosno_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_007</t>
-  </si>
-  <si>
-    <t>e_Warsaw_POL,e_Plock_POL,e_Olsztyn_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_011</t>
-  </si>
-  <si>
-    <t>e_Boleslawiec_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_010</t>
-  </si>
-  <si>
-    <t>e_Police_POL,e_Koszalin_POL,e_Poznan_POL,e_Ustka_POL,e_Bydgoszcz_POL,e_Slupsk_POL,e_Gdansk_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_005</t>
-  </si>
-  <si>
-    <t>e_Lomza_POL,e_Elk_POL,e_Grajewo_POL,e_Bialystok_POL,e_Chelm_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_002</t>
-  </si>
-  <si>
-    <t>e_Tarnow_POL,e_Kielce_POL,e_OstrowiecSwietokrz_POL,e_Mielec_POL,e_Pulawy_POL,e_Rzeszow_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_015</t>
-  </si>
-  <si>
-    <t>e_BielskoBiala_POL,e_Krakow_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_016</t>
-  </si>
-  <si>
-    <t>e_Krosno_POL,e_Debica_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_013</t>
-  </si>
-  <si>
-    <t>e_Lubin_POL,e_Wroclaw_POL,e_Poznan_POL,e_Olesnica_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_008</t>
-  </si>
-  <si>
-    <t>e_Olsztyn_POL,e_Elk_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_001</t>
-  </si>
-  <si>
-    <t>e_PiotrkowTrybunalsk_POL,e_Kielce_POL,e_Warsaw_POL,e_OstrowiecSwietokrz_POL</t>
+    <t>distr_wofelc_wof_POL_002</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_POL_004</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_POL_006</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_POL_005</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_POL_001</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 1</t>
   </si>
   <si>
     <t>distr_wofelc_wof_POL_008</t>
@@ -1152,6 +1182,12 @@
     <t>connecting wind offshore to buses in cluster 7</t>
   </si>
   <si>
+    <t>distr_wofelc_wof_POL_003</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 3</t>
+  </si>
+  <si>
     <t>distr_wofelc_wof_POL_010</t>
   </si>
   <si>
@@ -1164,40 +1200,31 @@
     <t>connecting wind offshore to buses in cluster 9</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_POL_004</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_POL_006</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_POL_002</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_POL_005</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_POL_001</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_POL_003</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 3</t>
+    <t>elc_wof_POL_002</t>
+  </si>
+  <si>
+    <t>e_Gdynia_POL,e_Gdansk_POL</t>
+  </si>
+  <si>
+    <t>elc_wof_POL_004</t>
+  </si>
+  <si>
+    <t>e_Ustka_POL,e_Gdynia_POL</t>
+  </si>
+  <si>
+    <t>elc_wof_POL_006</t>
+  </si>
+  <si>
+    <t>e_Gdynia_POL</t>
+  </si>
+  <si>
+    <t>elc_wof_POL_005</t>
+  </si>
+  <si>
+    <t>elc_wof_POL_001</t>
+  </si>
+  <si>
+    <t>e_Gdansk_POL</t>
   </si>
   <si>
     <t>elc_wof_POL_008</t>
@@ -1212,6 +1239,9 @@
     <t>e_Koszalin_POL</t>
   </si>
   <si>
+    <t>elc_wof_POL_003</t>
+  </si>
+  <si>
     <t>elc_wof_POL_010</t>
   </si>
   <si>
@@ -1219,36 +1249,6 @@
   </si>
   <si>
     <t>e_Koszalin_POL,e_Ustka_POL</t>
-  </si>
-  <si>
-    <t>elc_wof_POL_004</t>
-  </si>
-  <si>
-    <t>e_Ustka_POL,e_Gdynia_POL</t>
-  </si>
-  <si>
-    <t>elc_wof_POL_006</t>
-  </si>
-  <si>
-    <t>e_Gdynia_POL</t>
-  </si>
-  <si>
-    <t>elc_wof_POL_002</t>
-  </si>
-  <si>
-    <t>e_Gdynia_POL,e_Gdansk_POL</t>
-  </si>
-  <si>
-    <t>elc_wof_POL_005</t>
-  </si>
-  <si>
-    <t>elc_wof_POL_001</t>
-  </si>
-  <si>
-    <t>e_Gdansk_POL</t>
-  </si>
-  <si>
-    <t>elc_wof_POL_003</t>
   </si>
   <si>
     <t>e_won_POL_001</t>
@@ -5844,7 +5844,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0C0ECA9-2976-4949-BB23-4E467F422200}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{015DDA11-CC52-47AB-805C-AA4E40561873}">
   <dimension ref="B9:BD30"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -6124,10 +6124,10 @@
         <v>320</v>
       </c>
       <c r="AO11">
-        <v>0.99730422320290779</v>
+        <v>0.9963019969989696</v>
       </c>
       <c r="AP11">
-        <v>49.422574613357185</v>
+        <v>67.796721685557472</v>
       </c>
       <c r="AR11" t="s">
         <v>214</v>
@@ -6160,10 +6160,10 @@
         <v>379</v>
       </c>
       <c r="BC11">
-        <v>0.99383352379209899</v>
+        <v>0.99353721168226494</v>
       </c>
       <c r="BD11">
-        <v>758.43022352327353</v>
+        <v>780.55486105754892</v>
       </c>
     </row>
     <row r="12" spans="2:56">
@@ -6228,16 +6228,16 @@
         <v>219</v>
       </c>
       <c r="Y12" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="Z12" t="s">
         <v>260</v>
       </c>
       <c r="AA12">
-        <v>0.99658775492800411</v>
+        <v>0.99770934816564383</v>
       </c>
       <c r="AB12">
-        <v>62.557826319923819</v>
+        <v>41.995283629862939</v>
       </c>
       <c r="AD12" t="s">
         <v>214</v>
@@ -6270,10 +6270,10 @@
         <v>322</v>
       </c>
       <c r="AO12">
-        <v>0.99805709209211746</v>
+        <v>0.99622969699231045</v>
       </c>
       <c r="AP12">
-        <v>35.619978311179104</v>
+        <v>69.122221807641537</v>
       </c>
       <c r="AR12" t="s">
         <v>214</v>
@@ -6306,10 +6306,10 @@
         <v>381</v>
       </c>
       <c r="BC12">
-        <v>0.99603306101923861</v>
+        <v>0.99255663966463281</v>
       </c>
       <c r="BD12">
-        <v>594.19811056351818</v>
+        <v>853.77090504074806</v>
       </c>
     </row>
     <row r="13" spans="2:56">
@@ -6374,16 +6374,16 @@
         <v>221</v>
       </c>
       <c r="Y13" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="Z13" t="s">
         <v>261</v>
       </c>
       <c r="AA13">
-        <v>0.99510886326373238</v>
+        <v>0.9970292559096442</v>
       </c>
       <c r="AB13">
-        <v>89.670840164906522</v>
+        <v>54.463641656523762</v>
       </c>
       <c r="AD13" t="s">
         <v>214</v>
@@ -6416,10 +6416,10 @@
         <v>324</v>
       </c>
       <c r="AO13">
-        <v>0.99622969699231045</v>
+        <v>0.99872641243407079</v>
       </c>
       <c r="AP13">
-        <v>69.122221807641537</v>
+        <v>23.349105375368897</v>
       </c>
       <c r="AR13" t="s">
         <v>214</v>
@@ -6449,13 +6449,13 @@
         <v>382</v>
       </c>
       <c r="BB13" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="BC13">
-        <v>0.99608994650263638</v>
+        <v>0.99615739524125424</v>
       </c>
       <c r="BD13">
-        <v>589.950661136485</v>
+        <v>584.91448865302027</v>
       </c>
     </row>
     <row r="14" spans="2:56">
@@ -6520,16 +6520,16 @@
         <v>223</v>
       </c>
       <c r="Y14" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
       <c r="Z14" t="s">
         <v>262</v>
       </c>
       <c r="AA14">
-        <v>0.99515616506526205</v>
+        <v>0.9982126095160021</v>
       </c>
       <c r="AB14">
-        <v>88.803640470195262</v>
+        <v>32.768825539961391</v>
       </c>
       <c r="AD14" t="s">
         <v>214</v>
@@ -6562,10 +6562,10 @@
         <v>326</v>
       </c>
       <c r="AO14">
-        <v>0.99827231256984739</v>
+        <v>0.99776911581804295</v>
       </c>
       <c r="AP14">
-        <v>31.674269552798414</v>
+        <v>40.899543335879912</v>
       </c>
       <c r="AR14" t="s">
         <v>214</v>
@@ -6592,16 +6592,16 @@
         <v>364</v>
       </c>
       <c r="BA14" t="s">
+        <v>384</v>
+      </c>
+      <c r="BB14" t="s">
         <v>383</v>
       </c>
-      <c r="BB14" t="s">
-        <v>384</v>
-      </c>
       <c r="BC14">
-        <v>0.99399682431672776</v>
+        <v>0.99328660064428831</v>
       </c>
       <c r="BD14">
-        <v>746.2371176843244</v>
+        <v>799.26715189313825</v>
       </c>
     </row>
     <row r="15" spans="2:56">
@@ -6666,16 +6666,16 @@
         <v>225</v>
       </c>
       <c r="Y15" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="Z15" t="s">
         <v>263</v>
       </c>
       <c r="AA15">
-        <v>0.99728872234103139</v>
+        <v>0.99790408176624201</v>
       </c>
       <c r="AB15">
-        <v>49.70675708109188</v>
+        <v>38.425167618896296</v>
       </c>
       <c r="AD15" t="s">
         <v>214</v>
@@ -6708,10 +6708,10 @@
         <v>328</v>
       </c>
       <c r="AO15">
-        <v>0.99635146162488653</v>
+        <v>0.99653588726932718</v>
       </c>
       <c r="AP15">
-        <v>66.889870210414614</v>
+        <v>63.508733395668145</v>
       </c>
       <c r="AR15" t="s">
         <v>214</v>
@@ -6744,10 +6744,10 @@
         <v>386</v>
       </c>
       <c r="BC15">
-        <v>0.99255663966463281</v>
+        <v>0.99644441082752833</v>
       </c>
       <c r="BD15">
-        <v>853.77090504074806</v>
+        <v>563.48399154455342</v>
       </c>
     </row>
     <row r="16" spans="2:56">
@@ -6812,16 +6812,16 @@
         <v>227</v>
       </c>
       <c r="Y16" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="Z16" t="s">
         <v>264</v>
       </c>
       <c r="AA16">
-        <v>0.99583567586599486</v>
+        <v>0.99693515631487983</v>
       </c>
       <c r="AB16">
-        <v>76.34594245676044</v>
+        <v>56.188800893869058</v>
       </c>
       <c r="AD16" t="s">
         <v>214</v>
@@ -6851,13 +6851,13 @@
         <v>329</v>
       </c>
       <c r="AN16" t="s">
-        <v>268</v>
+        <v>330</v>
       </c>
       <c r="AO16">
-        <v>0.99586212495478665</v>
+        <v>0.99827231256984739</v>
       </c>
       <c r="AP16">
-        <v>75.861042495577635</v>
+        <v>31.674269552798414</v>
       </c>
       <c r="AR16" t="s">
         <v>214</v>
@@ -6890,10 +6890,10 @@
         <v>388</v>
       </c>
       <c r="BC16">
-        <v>0.99615739524125424</v>
+        <v>0.99383352379209899</v>
       </c>
       <c r="BD16">
-        <v>584.91448865302027</v>
+        <v>758.43022352327353</v>
       </c>
     </row>
     <row r="17" spans="2:56">
@@ -6958,16 +6958,16 @@
         <v>229</v>
       </c>
       <c r="Y17" t="s">
-        <v>209</v>
+        <v>196</v>
       </c>
       <c r="Z17" t="s">
         <v>265</v>
       </c>
       <c r="AA17">
-        <v>0.99930490342600053</v>
+        <v>0.99785589517057005</v>
       </c>
       <c r="AB17">
-        <v>12.743437189989784</v>
+        <v>39.308588539549028</v>
       </c>
       <c r="AD17" t="s">
         <v>214</v>
@@ -6994,16 +6994,16 @@
         <v>291</v>
       </c>
       <c r="AM17" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AN17" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AO17">
-        <v>0.99749126227646956</v>
+        <v>0.99635146162488653</v>
       </c>
       <c r="AP17">
-        <v>45.993524931390482</v>
+        <v>66.889870210414614</v>
       </c>
       <c r="AR17" t="s">
         <v>214</v>
@@ -7036,10 +7036,10 @@
         <v>390</v>
       </c>
       <c r="BC17">
-        <v>0.99353721168226494</v>
+        <v>0.99603306101923861</v>
       </c>
       <c r="BD17">
-        <v>780.55486105754892</v>
+        <v>594.19811056351818</v>
       </c>
     </row>
     <row r="18" spans="2:56">
@@ -7104,16 +7104,16 @@
         <v>231</v>
       </c>
       <c r="Y18" t="s">
-        <v>212</v>
+        <v>198</v>
       </c>
       <c r="Z18" t="s">
         <v>266</v>
       </c>
       <c r="AA18">
-        <v>0.99881801309037566</v>
+        <v>0.99658775492800411</v>
       </c>
       <c r="AB18">
-        <v>21.669760009780138</v>
+        <v>62.557826319923819</v>
       </c>
       <c r="AD18" t="s">
         <v>214</v>
@@ -7140,16 +7140,16 @@
         <v>293</v>
       </c>
       <c r="AM18" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AN18" t="s">
-        <v>333</v>
+        <v>278</v>
       </c>
       <c r="AO18">
-        <v>0.99807543246352515</v>
+        <v>0.99586212495478665</v>
       </c>
       <c r="AP18">
-        <v>35.283738168705199</v>
+        <v>75.861042495577635</v>
       </c>
       <c r="AR18" t="s">
         <v>214</v>
@@ -7179,13 +7179,13 @@
         <v>391</v>
       </c>
       <c r="BB18" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="BC18">
-        <v>0.99328660064428831</v>
+        <v>0.99564787435456037</v>
       </c>
       <c r="BD18">
-        <v>799.26715189313825</v>
+        <v>622.95871485949408</v>
       </c>
     </row>
     <row r="19" spans="2:56">
@@ -7250,16 +7250,16 @@
         <v>233</v>
       </c>
       <c r="Y19" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="Z19" t="s">
         <v>267</v>
       </c>
       <c r="AA19">
-        <v>0.99790408176624201</v>
+        <v>0.99510886326373238</v>
       </c>
       <c r="AB19">
-        <v>38.425167618896296</v>
+        <v>89.670840164906522</v>
       </c>
       <c r="AD19" t="s">
         <v>214</v>
@@ -7292,10 +7292,10 @@
         <v>335</v>
       </c>
       <c r="AO19">
-        <v>0.99872641243407079</v>
+        <v>0.99641308487583879</v>
       </c>
       <c r="AP19">
-        <v>23.349105375368897</v>
+        <v>65.760110609622657</v>
       </c>
       <c r="AR19" t="s">
         <v>214</v>
@@ -7325,13 +7325,13 @@
         <v>392</v>
       </c>
       <c r="BB19" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="BC19">
-        <v>0.99644441082752833</v>
+        <v>0.99608994650263638</v>
       </c>
       <c r="BD19">
-        <v>563.48399154455342</v>
+        <v>589.950661136485</v>
       </c>
     </row>
     <row r="20" spans="2:56">
@@ -7396,16 +7396,16 @@
         <v>235</v>
       </c>
       <c r="Y20" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="Z20" t="s">
         <v>268</v>
       </c>
       <c r="AA20">
-        <v>0.99606480786442353</v>
+        <v>0.99930490342600053</v>
       </c>
       <c r="AB20">
-        <v>72.145189152235062</v>
+        <v>12.743437189989784</v>
       </c>
       <c r="AD20" t="s">
         <v>214</v>
@@ -7438,10 +7438,10 @@
         <v>337</v>
       </c>
       <c r="AO20">
-        <v>0.99776911581804295</v>
+        <v>0.99449756685866841</v>
       </c>
       <c r="AP20">
-        <v>40.899543335879912</v>
+        <v>100.87794092441324</v>
       </c>
       <c r="AR20" t="s">
         <v>214</v>
@@ -7468,16 +7468,16 @@
         <v>376</v>
       </c>
       <c r="BA20" t="s">
+        <v>393</v>
+      </c>
+      <c r="BB20" t="s">
         <v>394</v>
       </c>
-      <c r="BB20" t="s">
-        <v>393</v>
-      </c>
       <c r="BC20">
-        <v>0.99564787435456037</v>
+        <v>0.99399682431672776</v>
       </c>
       <c r="BD20">
-        <v>622.95871485949408</v>
+        <v>746.2371176843244</v>
       </c>
     </row>
     <row r="21" spans="2:56">
@@ -7542,16 +7542,16 @@
         <v>237</v>
       </c>
       <c r="Y21" t="s">
-        <v>193</v>
+        <v>212</v>
       </c>
       <c r="Z21" t="s">
         <v>269</v>
       </c>
       <c r="AA21">
-        <v>0.99707401400885998</v>
+        <v>0.99881801309037566</v>
       </c>
       <c r="AB21">
-        <v>53.643076504234422</v>
+        <v>21.669760009780138</v>
       </c>
       <c r="AD21" t="s">
         <v>214</v>
@@ -7584,10 +7584,10 @@
         <v>339</v>
       </c>
       <c r="AO21">
-        <v>0.99653588726932718</v>
+        <v>0.99871360797890252</v>
       </c>
       <c r="AP21">
-        <v>63.508733395668145</v>
+        <v>23.583853720120768</v>
       </c>
     </row>
     <row r="22" spans="2:56">
@@ -7652,16 +7652,16 @@
         <v>239</v>
       </c>
       <c r="Y22" t="s">
-        <v>207</v>
+        <v>194</v>
       </c>
       <c r="Z22" t="s">
         <v>270</v>
       </c>
       <c r="AA22">
-        <v>0.99826037700975512</v>
+        <v>0.99515616506526205</v>
       </c>
       <c r="AB22">
-        <v>31.893088154488542</v>
+        <v>88.803640470195262</v>
       </c>
       <c r="AD22" t="s">
         <v>214</v>
@@ -7694,10 +7694,10 @@
         <v>341</v>
       </c>
       <c r="AO22">
-        <v>0.99802303154782224</v>
+        <v>0.99845791964146047</v>
       </c>
       <c r="AP22">
-        <v>36.244421623259619</v>
+        <v>28.2714732398913</v>
       </c>
     </row>
     <row r="23" spans="2:56">
@@ -7762,16 +7762,16 @@
         <v>241</v>
       </c>
       <c r="Y23" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Z23" t="s">
         <v>271</v>
       </c>
       <c r="AA23">
-        <v>0.99922515067657613</v>
+        <v>0.99728872234103139</v>
       </c>
       <c r="AB23">
-        <v>14.205570929438155</v>
+        <v>49.70675708109188</v>
       </c>
       <c r="AD23" t="s">
         <v>214</v>
@@ -7804,10 +7804,10 @@
         <v>343</v>
       </c>
       <c r="AO23">
-        <v>0.99714358927215652</v>
+        <v>0.99730422320290779</v>
       </c>
       <c r="AP23">
-        <v>52.367530010463909</v>
+        <v>49.422574613357185</v>
       </c>
     </row>
     <row r="24" spans="2:56">
@@ -7872,16 +7872,16 @@
         <v>243</v>
       </c>
       <c r="Y24" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="Z24" t="s">
         <v>272</v>
       </c>
       <c r="AA24">
-        <v>0.99770934816564383</v>
+        <v>0.99583567586599486</v>
       </c>
       <c r="AB24">
-        <v>41.995283629862939</v>
+        <v>76.34594245676044</v>
       </c>
       <c r="AD24" t="s">
         <v>214</v>
@@ -7914,10 +7914,10 @@
         <v>345</v>
       </c>
       <c r="AO24">
-        <v>0.9963019969989696</v>
+        <v>0.99805709209211746</v>
       </c>
       <c r="AP24">
-        <v>67.796721685557472</v>
+        <v>35.619978311179104</v>
       </c>
     </row>
     <row r="25" spans="2:56">
@@ -7982,16 +7982,16 @@
         <v>245</v>
       </c>
       <c r="Y25" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="Z25" t="s">
         <v>273</v>
       </c>
       <c r="AA25">
-        <v>0.9970292559096442</v>
+        <v>0.99707401400885998</v>
       </c>
       <c r="AB25">
-        <v>54.463641656523762</v>
+        <v>53.643076504234422</v>
       </c>
       <c r="AD25" t="s">
         <v>214</v>
@@ -8024,10 +8024,10 @@
         <v>347</v>
       </c>
       <c r="AO25">
-        <v>0.99845791964146047</v>
+        <v>0.99883902037019667</v>
       </c>
       <c r="AP25">
-        <v>28.2714732398913</v>
+        <v>21.284626546395259</v>
       </c>
     </row>
     <row r="26" spans="2:56">
@@ -8092,16 +8092,16 @@
         <v>247</v>
       </c>
       <c r="Y26" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="Z26" t="s">
         <v>274</v>
       </c>
       <c r="AA26">
-        <v>0.9982126095160021</v>
+        <v>0.99826037700975512</v>
       </c>
       <c r="AB26">
-        <v>32.768825539961391</v>
+        <v>31.893088154488542</v>
       </c>
       <c r="AD26" t="s">
         <v>214</v>
@@ -8134,10 +8134,10 @@
         <v>349</v>
       </c>
       <c r="AO26">
-        <v>0.99641308487583879</v>
+        <v>0.99521984547821263</v>
       </c>
       <c r="AP26">
-        <v>65.760110609622657</v>
+        <v>87.636166232768815</v>
       </c>
     </row>
     <row r="27" spans="2:56">
@@ -8202,16 +8202,16 @@
         <v>249</v>
       </c>
       <c r="Y27" t="s">
-        <v>196</v>
+        <v>210</v>
       </c>
       <c r="Z27" t="s">
         <v>275</v>
       </c>
       <c r="AA27">
-        <v>0.99785589517057005</v>
+        <v>0.99922515067657613</v>
       </c>
       <c r="AB27">
-        <v>39.308588539549028</v>
+        <v>14.205570929438155</v>
       </c>
       <c r="AD27" t="s">
         <v>214</v>
@@ -8244,10 +8244,10 @@
         <v>351</v>
       </c>
       <c r="AO27">
-        <v>0.99449756685866841</v>
+        <v>0.99802303154782224</v>
       </c>
       <c r="AP27">
-        <v>100.87794092441324</v>
+        <v>36.244421623259619</v>
       </c>
     </row>
     <row r="28" spans="2:56">
@@ -8354,10 +8354,10 @@
         <v>353</v>
       </c>
       <c r="AO28">
-        <v>0.99883902037019667</v>
+        <v>0.99714358927215652</v>
       </c>
       <c r="AP28">
-        <v>21.284626546395259</v>
+        <v>52.367530010463909</v>
       </c>
     </row>
     <row r="29" spans="2:56">
@@ -8464,10 +8464,10 @@
         <v>355</v>
       </c>
       <c r="AO29">
-        <v>0.99521984547821263</v>
+        <v>0.99749126227646956</v>
       </c>
       <c r="AP29">
-        <v>87.636166232768815</v>
+        <v>45.993524931390482</v>
       </c>
     </row>
     <row r="30" spans="2:56">
@@ -8532,16 +8532,16 @@
         <v>255</v>
       </c>
       <c r="Y30" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="Z30" t="s">
         <v>278</v>
       </c>
       <c r="AA30">
-        <v>0.99693515631487983</v>
+        <v>0.99606480786442353</v>
       </c>
       <c r="AB30">
-        <v>56.188800893869058</v>
+        <v>72.145189152235062</v>
       </c>
       <c r="AD30" t="s">
         <v>214</v>
@@ -8574,10 +8574,10 @@
         <v>357</v>
       </c>
       <c r="AO30">
-        <v>0.99871360797890252</v>
+        <v>0.99807543246352515</v>
       </c>
       <c r="AP30">
-        <v>23.583853720120768</v>
+        <v>35.283738168705199</v>
       </c>
     </row>
   </sheetData>
@@ -8586,7 +8586,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19FD8E05-430E-4DA8-9DE8-20D898A6DE14}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4DE3BD5-D628-494D-886B-3AAD1B93E6F3}">
   <dimension ref="B9:Z30"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -8698,7 +8698,7 @@
         <v>395</v>
       </c>
       <c r="K11" t="s">
-        <v>356</v>
+        <v>338</v>
       </c>
       <c r="L11">
         <v>0.30278350605008381</v>
@@ -8731,7 +8731,7 @@
         <v>435</v>
       </c>
       <c r="X11" t="s">
-        <v>392</v>
+        <v>385</v>
       </c>
       <c r="Y11">
         <v>0.83925000000000005</v>
@@ -8766,7 +8766,7 @@
         <v>397</v>
       </c>
       <c r="K12" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="L12">
         <v>0.42035497786033621</v>
@@ -8799,7 +8799,7 @@
         <v>437</v>
       </c>
       <c r="X12" t="s">
-        <v>389</v>
+        <v>378</v>
       </c>
       <c r="Y12">
         <v>16.887</v>
@@ -8834,7 +8834,7 @@
         <v>399</v>
       </c>
       <c r="K13" t="s">
-        <v>332</v>
+        <v>356</v>
       </c>
       <c r="L13">
         <v>1.6077871713950227</v>
@@ -8867,7 +8867,7 @@
         <v>439</v>
       </c>
       <c r="X13" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="Y13">
         <v>11.2965</v>
@@ -8902,7 +8902,7 @@
         <v>401</v>
       </c>
       <c r="K14" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="L14">
         <v>2.531891424764753</v>
@@ -8935,7 +8935,7 @@
         <v>441</v>
       </c>
       <c r="X14" t="s">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="Y14">
         <v>6.6577500000000001</v>
@@ -8970,7 +8970,7 @@
         <v>403</v>
       </c>
       <c r="K15" t="s">
-        <v>344</v>
+        <v>319</v>
       </c>
       <c r="L15">
         <v>7.6497810049421515</v>
@@ -9003,7 +9003,7 @@
         <v>443</v>
       </c>
       <c r="X15" t="s">
-        <v>391</v>
+        <v>384</v>
       </c>
       <c r="Y15">
         <v>17.089500000000001</v>
@@ -9038,7 +9038,7 @@
         <v>405</v>
       </c>
       <c r="K16" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="L16">
         <v>0.60733325583919984</v>
@@ -9071,7 +9071,7 @@
         <v>445</v>
       </c>
       <c r="X16" t="s">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="Y16">
         <v>8.8230000000000004</v>
@@ -9106,7 +9106,7 @@
         <v>407</v>
       </c>
       <c r="K17" t="s">
-        <v>338</v>
+        <v>327</v>
       </c>
       <c r="L17">
         <v>0.78389041837100704</v>
@@ -9139,7 +9139,7 @@
         <v>447</v>
       </c>
       <c r="X17" t="s">
-        <v>380</v>
+        <v>389</v>
       </c>
       <c r="Y17">
         <v>0.22650000000000001</v>
@@ -9174,7 +9174,7 @@
         <v>409</v>
       </c>
       <c r="K18" t="s">
-        <v>354</v>
+        <v>348</v>
       </c>
       <c r="L18">
         <v>3.0365724666245324</v>
@@ -9207,7 +9207,7 @@
         <v>449</v>
       </c>
       <c r="X18" t="s">
-        <v>378</v>
+        <v>387</v>
       </c>
       <c r="Y18">
         <v>9.5062499999999996</v>
@@ -9242,7 +9242,7 @@
         <v>411</v>
       </c>
       <c r="K19" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="L19">
         <v>0.22970161230087291</v>
@@ -9275,7 +9275,7 @@
         <v>451</v>
       </c>
       <c r="X19" t="s">
-        <v>383</v>
+        <v>393</v>
       </c>
       <c r="Y19">
         <v>13.37175</v>
@@ -9310,7 +9310,7 @@
         <v>413</v>
       </c>
       <c r="K20" t="s">
-        <v>342</v>
+        <v>352</v>
       </c>
       <c r="L20">
         <v>0.27066515065379043</v>
@@ -9343,7 +9343,7 @@
         <v>453</v>
       </c>
       <c r="X20" t="s">
-        <v>382</v>
+        <v>392</v>
       </c>
       <c r="Y20">
         <v>3.9427500000000002</v>
@@ -9378,7 +9378,7 @@
         <v>415</v>
       </c>
       <c r="K21" t="s">
-        <v>340</v>
+        <v>350</v>
       </c>
       <c r="L21">
         <v>0.32193208719379746</v>
@@ -9413,7 +9413,7 @@
         <v>417</v>
       </c>
       <c r="K22" t="s">
-        <v>330</v>
+        <v>354</v>
       </c>
       <c r="L22">
         <v>0.6573344927201471</v>
@@ -9448,7 +9448,7 @@
         <v>419</v>
       </c>
       <c r="K23" t="s">
-        <v>352</v>
+        <v>346</v>
       </c>
       <c r="L23">
         <v>0.28992997651770519</v>
@@ -9483,7 +9483,7 @@
         <v>421</v>
       </c>
       <c r="K24" t="s">
-        <v>319</v>
+        <v>342</v>
       </c>
       <c r="L24">
         <v>0.74609319967150689</v>
@@ -9518,7 +9518,7 @@
         <v>423</v>
       </c>
       <c r="K25" t="s">
-        <v>348</v>
+        <v>334</v>
       </c>
       <c r="L25">
         <v>0.35328950844501877</v>
@@ -9553,7 +9553,7 @@
         <v>425</v>
       </c>
       <c r="K26" t="s">
-        <v>350</v>
+        <v>336</v>
       </c>
       <c r="L26">
         <v>0.7924639655878376</v>
@@ -9588,7 +9588,7 @@
         <v>427</v>
       </c>
       <c r="K27" t="s">
-        <v>336</v>
+        <v>325</v>
       </c>
       <c r="L27">
         <v>0.55411362221124194</v>
@@ -9623,7 +9623,7 @@
         <v>429</v>
       </c>
       <c r="K28" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="L28">
         <v>1.4327274230737423</v>
@@ -9658,7 +9658,7 @@
         <v>431</v>
       </c>
       <c r="K29" t="s">
-        <v>334</v>
+        <v>323</v>
       </c>
       <c r="L29">
         <v>0.56742801517356967</v>
@@ -9693,7 +9693,7 @@
         <v>433</v>
       </c>
       <c r="K30" t="s">
-        <v>321</v>
+        <v>344</v>
       </c>
       <c r="L30">
         <v>0.35405891742987328</v>
@@ -9708,7 +9708,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4BEB3642-4757-487B-BE5B-3F7C2E0C5BED}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50359684-D83D-45E3-9B6B-8FF18A0F48EC}">
   <dimension ref="B9:Y136"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -14069,7 +14069,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A2659BC-18B1-4844-A6BC-86A7AC754AB2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D7A9747E-B0EF-458E-A091-675018C9E90C}">
   <dimension ref="B9:T88"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_POL_grids_kan50/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_POL_grids_kan50/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5370310-7BF5-4A77-9504-850E654E3B5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{935E0AED-3C6F-4E4C-82E2-7FFF8449DE6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -711,198 +711,198 @@
     <t>pre</t>
   </si>
   <si>
+    <t>distr_solelc_spv_POL_016</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>NRGI</t>
+  </si>
+  <si>
+    <t>daynite</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_017</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_001</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_014</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_007</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_004</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 4</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_POL_018</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 18</t>
   </si>
   <si>
-    <t>NRGI</t>
-  </si>
-  <si>
-    <t>daynite</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_POL_002</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 2</t>
   </si>
   <si>
+    <t>distr_solelc_spv_POL_003</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_015</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_008</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_013</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_019</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_010</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_005</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_020</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_006</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_011</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 11</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_POL_009</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 9</t>
   </si>
   <si>
-    <t>distr_solelc_spv_POL_003</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_015</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_008</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_013</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_019</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_010</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_014</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_007</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_004</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 4</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_POL_012</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 12</t>
   </si>
   <si>
-    <t>distr_solelc_spv_POL_016</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_017</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_011</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_020</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_006</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_005</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_001</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 1</t>
-  </si>
-  <si>
     <t>comm-in</t>
   </si>
   <si>
     <t>ncap_cost~USD21_alt</t>
   </si>
   <si>
+    <t>e_Legnica_POL,e_Swidnica_POL,e_KedzierzynKozle_POL,e_Opole_POL,e_Olesnica_POL</t>
+  </si>
+  <si>
+    <t>e_Sosnowiec_POL,e_BielskoBiala_POL,e_Gliwice_POL,e_Katowice_POL</t>
+  </si>
+  <si>
+    <t>e_Lomza_POL,e_Pulawy_POL,e_Bialystok_POL</t>
+  </si>
+  <si>
+    <t>e_Boleslawiec_POL</t>
+  </si>
+  <si>
+    <t>e_Szczecin_POL,e_Police_POL,e_GorzowWielkopolski_POL</t>
+  </si>
+  <si>
+    <t>e_Krakow_POL,e_Tarnow_POL</t>
+  </si>
+  <si>
     <t>e_Warsaw_POL,e_Plock_POL,e_OstrowiecSwietokrz_POL,e_Pulawy_POL</t>
   </si>
   <si>
     <t>e_Lomza_POL,e_Elk_POL,e_Grajewo_POL,e_Bialystok_POL</t>
   </si>
   <si>
+    <t>e_Krosno_POL,e_Mielec_POL,e_Debica_POL,e_Zamosc_POL</t>
+  </si>
+  <si>
+    <t>e_ZielonaGora_POL,e_GorzowWielkopolski_POL</t>
+  </si>
+  <si>
+    <t>e_Poznan_POL,e_Koszalin_POL,e_Ustka_POL,e_Bydgoszcz_POL,e_Slupsk_POL</t>
+  </si>
+  <si>
+    <t>e_Lubin_POL,e_Wroclaw_POL,e_Poznan_POL,e_Olesnica_POL</t>
+  </si>
+  <si>
+    <t>e_Kielce_POL,e_Warsaw_POL,e_OstrowiecSwietokrz_POL</t>
+  </si>
+  <si>
+    <t>e_Olsztyn_POL</t>
+  </si>
+  <si>
+    <t>e_Pulawy_POL,e_Chelm_POL</t>
+  </si>
+  <si>
+    <t>e_KedzierzynKozle_POL,e_Olesnica_POL,e_Konin_POL,e_Czestochowa_POL,e_Radomsko_POL,e_PiotrkowTrybunalsk_POL,e_Plock_POL</t>
+  </si>
+  <si>
+    <t>e_OstrowiecSwietokrz_POL,e_Rzeszow_POL,e_Zamosc_POL,e_Chelm_POL</t>
+  </si>
+  <si>
+    <t>e_Bydgoszcz_POL,e_Gdansk_POL,e_Grudziadz_POL,e_Kwidzyn_POL</t>
+  </si>
+  <si>
     <t>e_Konin_POL,e_Bydgoszcz_POL,e_Wloclawek_POL,e_Kwidzyn_POL,e_Plock_POL</t>
   </si>
   <si>
-    <t>e_Krosno_POL,e_Mielec_POL,e_Debica_POL,e_Zamosc_POL</t>
-  </si>
-  <si>
-    <t>e_ZielonaGora_POL,e_GorzowWielkopolski_POL</t>
-  </si>
-  <si>
-    <t>e_Poznan_POL,e_Koszalin_POL,e_Ustka_POL,e_Bydgoszcz_POL,e_Slupsk_POL</t>
-  </si>
-  <si>
-    <t>e_Lubin_POL,e_Wroclaw_POL,e_Poznan_POL,e_Olesnica_POL</t>
-  </si>
-  <si>
-    <t>e_Kielce_POL,e_Warsaw_POL,e_OstrowiecSwietokrz_POL</t>
-  </si>
-  <si>
-    <t>e_Olsztyn_POL</t>
-  </si>
-  <si>
-    <t>e_Boleslawiec_POL</t>
-  </si>
-  <si>
-    <t>e_Szczecin_POL,e_Police_POL,e_GorzowWielkopolski_POL</t>
-  </si>
-  <si>
-    <t>e_Krakow_POL,e_Tarnow_POL</t>
-  </si>
-  <si>
     <t>e_Lubin_POL,e_Poznan_POL</t>
   </si>
   <si>
-    <t>e_Legnica_POL,e_Swidnica_POL,e_KedzierzynKozle_POL,e_Opole_POL,e_Olesnica_POL</t>
-  </si>
-  <si>
-    <t>e_Sosnowiec_POL,e_BielskoBiala_POL,e_Gliwice_POL,e_Katowice_POL</t>
-  </si>
-  <si>
-    <t>e_Bydgoszcz_POL,e_Gdansk_POL,e_Grudziadz_POL,e_Kwidzyn_POL</t>
-  </si>
-  <si>
-    <t>e_KedzierzynKozle_POL,e_Olesnica_POL,e_Konin_POL,e_Czestochowa_POL,e_Radomsko_POL,e_PiotrkowTrybunalsk_POL,e_Plock_POL</t>
-  </si>
-  <si>
-    <t>e_OstrowiecSwietokrz_POL,e_Rzeszow_POL,e_Zamosc_POL,e_Chelm_POL</t>
-  </si>
-  <si>
-    <t>e_Pulawy_POL,e_Chelm_POL</t>
-  </si>
-  <si>
-    <t>e_Lomza_POL,e_Pulawy_POL,e_Bialystok_POL</t>
-  </si>
-  <si>
     <t>distr_wonelc_won_POL_006</t>
   </si>
   <si>
@@ -921,6 +921,84 @@
     <t>connecting wind onshore to buses in cluster 20</t>
   </si>
   <si>
+    <t>distr_wonelc_won_POL_013</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_010</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_016</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_012</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_009</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_017</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_001</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_008</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_007</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_002</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_005</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_003</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_019</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 19</t>
+  </si>
+  <si>
     <t>distr_wonelc_won_POL_004</t>
   </si>
   <si>
@@ -933,18 +1011,6 @@
     <t>connecting wind onshore to buses in cluster 14</t>
   </si>
   <si>
-    <t>distr_wonelc_won_POL_016</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_013</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 13</t>
-  </si>
-  <si>
     <t>distr_wonelc_won_POL_015</t>
   </si>
   <si>
@@ -957,72 +1023,6 @@
     <t>connecting wind onshore to buses in cluster 11</t>
   </si>
   <si>
-    <t>distr_wonelc_won_POL_008</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_012</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_007</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_002</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_005</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_003</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_019</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_010</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_001</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_009</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_017</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 17</t>
-  </si>
-  <si>
     <t>elc_won_POL_006</t>
   </si>
   <si>
@@ -1038,6 +1038,81 @@
     <t>e_Elk_POL,e_Grajewo_POL,e_Bialystok_POL</t>
   </si>
   <si>
+    <t>elc_won_POL_013</t>
+  </si>
+  <si>
+    <t>e_BielskoBiala_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_010</t>
+  </si>
+  <si>
+    <t>e_Boleslawiec_POL,e_Legnica_POL,e_Swidnica_POL,e_Opole_POL,e_Olesnica_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_016</t>
+  </si>
+  <si>
+    <t>e_Rzeszow_POL,e_Zamosc_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_012</t>
+  </si>
+  <si>
+    <t>e_Tarnow_POL,e_Krosno_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_009</t>
+  </si>
+  <si>
+    <t>e_Swidnica_POL,e_KedzierzynKozle_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_017</t>
+  </si>
+  <si>
+    <t>e_Pulawy_POL,e_Zamosc_POL,e_Chelm_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_001</t>
+  </si>
+  <si>
+    <t>e_Gdansk_POL,e_Grudziadz_POL,e_Kwidzyn_POL,e_Olsztyn_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_008</t>
+  </si>
+  <si>
+    <t>e_Sosnowiec_POL,e_KedzierzynKozle_POL,e_Gliwice_POL,e_Czestochowa_POL,e_Katowice_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_007</t>
+  </si>
+  <si>
+    <t>e_ZielonaGora_POL,e_GorzowWielkopolski_POL,e_Szczecin_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_002</t>
+  </si>
+  <si>
+    <t>e_Police_POL,e_Poznan_POL,e_Koszalin_POL,e_Ustka_POL,e_Bydgoszcz_POL,e_Slupsk_POL,e_Gdansk_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_005</t>
+  </si>
+  <si>
+    <t>e_Lubin_POL,e_Poznan_POL,e_Wroclaw_POL,e_Olesnica_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_003</t>
+  </si>
+  <si>
+    <t>elc_won_POL_019</t>
+  </si>
+  <si>
+    <t>e_Pulawy_POL,e_Lomza_POL,e_Bialystok_POL,e_Chelm_POL</t>
+  </si>
+  <si>
     <t>elc_won_POL_004</t>
   </si>
   <si>
@@ -1050,18 +1125,6 @@
     <t>e_Katowice_POL,e_Krakow_POL</t>
   </si>
   <si>
-    <t>elc_won_POL_016</t>
-  </si>
-  <si>
-    <t>e_Rzeszow_POL,e_Zamosc_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_013</t>
-  </si>
-  <si>
-    <t>e_BielskoBiala_POL</t>
-  </si>
-  <si>
     <t>elc_won_POL_015</t>
   </si>
   <si>
@@ -1074,67 +1137,34 @@
     <t>e_Krosno_POL,e_Debica_POL</t>
   </si>
   <si>
-    <t>elc_won_POL_008</t>
-  </si>
-  <si>
-    <t>e_Sosnowiec_POL,e_KedzierzynKozle_POL,e_Gliwice_POL,e_Czestochowa_POL,e_Katowice_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_012</t>
-  </si>
-  <si>
-    <t>e_Tarnow_POL,e_Krosno_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_007</t>
-  </si>
-  <si>
-    <t>e_ZielonaGora_POL,e_GorzowWielkopolski_POL,e_Szczecin_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_002</t>
-  </si>
-  <si>
-    <t>e_Police_POL,e_Poznan_POL,e_Koszalin_POL,e_Ustka_POL,e_Bydgoszcz_POL,e_Slupsk_POL,e_Gdansk_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_005</t>
-  </si>
-  <si>
-    <t>e_Lubin_POL,e_Poznan_POL,e_Wroclaw_POL,e_Olesnica_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_003</t>
-  </si>
-  <si>
-    <t>elc_won_POL_019</t>
-  </si>
-  <si>
-    <t>e_Pulawy_POL,e_Lomza_POL,e_Bialystok_POL,e_Chelm_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_010</t>
-  </si>
-  <si>
-    <t>e_Boleslawiec_POL,e_Legnica_POL,e_Swidnica_POL,e_Opole_POL,e_Olesnica_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_001</t>
-  </si>
-  <si>
-    <t>e_Gdansk_POL,e_Grudziadz_POL,e_Kwidzyn_POL,e_Olsztyn_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_009</t>
-  </si>
-  <si>
-    <t>e_Swidnica_POL,e_KedzierzynKozle_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_017</t>
-  </si>
-  <si>
-    <t>e_Pulawy_POL,e_Zamosc_POL,e_Chelm_POL</t>
+    <t>distr_wofelc_wof_POL_005</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_POL_001</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_POL_008</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_POL_007</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_POL_004</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 4</t>
   </si>
   <si>
     <t>distr_wofelc_wof_POL_002</t>
@@ -1143,58 +1173,58 @@
     <t>connecting wind offshore to buses in cluster 2</t>
   </si>
   <si>
+    <t>distr_wofelc_wof_POL_010</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_POL_009</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 9</t>
+  </si>
+  <si>
     <t>distr_wofelc_wof_POL_003</t>
   </si>
   <si>
     <t>connecting wind offshore to buses in cluster 3</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_POL_005</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_POL_001</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_POL_010</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_POL_009</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_POL_008</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_POL_007</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 7</t>
-  </si>
-  <si>
     <t>distr_wofelc_wof_POL_006</t>
   </si>
   <si>
     <t>connecting wind offshore to buses in cluster 6</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_POL_004</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 4</t>
+    <t>elc_wof_POL_005</t>
+  </si>
+  <si>
+    <t>e_Gdynia_POL</t>
+  </si>
+  <si>
+    <t>elc_wof_POL_001</t>
+  </si>
+  <si>
+    <t>e_Gdansk_POL</t>
+  </si>
+  <si>
+    <t>elc_wof_POL_008</t>
+  </si>
+  <si>
+    <t>e_Police_POL,e_Koszalin_POL</t>
+  </si>
+  <si>
+    <t>elc_wof_POL_007</t>
+  </si>
+  <si>
+    <t>e_Koszalin_POL</t>
+  </si>
+  <si>
+    <t>elc_wof_POL_004</t>
+  </si>
+  <si>
+    <t>e_Ustka_POL,e_Gdynia_POL</t>
   </si>
   <si>
     <t>elc_wof_POL_002</t>
@@ -1203,49 +1233,19 @@
     <t>e_Gdynia_POL,e_Gdansk_POL</t>
   </si>
   <si>
+    <t>elc_wof_POL_010</t>
+  </si>
+  <si>
+    <t>elc_wof_POL_009</t>
+  </si>
+  <si>
+    <t>e_Koszalin_POL,e_Ustka_POL</t>
+  </si>
+  <si>
     <t>elc_wof_POL_003</t>
   </si>
   <si>
-    <t>e_Gdansk_POL</t>
-  </si>
-  <si>
-    <t>elc_wof_POL_005</t>
-  </si>
-  <si>
-    <t>e_Gdynia_POL</t>
-  </si>
-  <si>
-    <t>elc_wof_POL_001</t>
-  </si>
-  <si>
-    <t>elc_wof_POL_010</t>
-  </si>
-  <si>
-    <t>e_Koszalin_POL</t>
-  </si>
-  <si>
-    <t>elc_wof_POL_009</t>
-  </si>
-  <si>
-    <t>e_Koszalin_POL,e_Ustka_POL</t>
-  </si>
-  <si>
-    <t>elc_wof_POL_008</t>
-  </si>
-  <si>
-    <t>e_Police_POL,e_Koszalin_POL</t>
-  </si>
-  <si>
-    <t>elc_wof_POL_007</t>
-  </si>
-  <si>
     <t>elc_wof_POL_006</t>
-  </si>
-  <si>
-    <t>elc_wof_POL_004</t>
-  </si>
-  <si>
-    <t>e_Ustka_POL,e_Gdynia_POL</t>
   </si>
   <si>
     <t>e_won_POL_001</t>
@@ -5841,7 +5841,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{44B02BF0-56B7-4D04-91D9-398C7EE2ED50}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AEDADE3B-75CF-43C7-82E9-F6867E763EDC}">
   <dimension ref="B9:BD30"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -6079,16 +6079,16 @@
         <v>215</v>
       </c>
       <c r="Y11" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="Z11" t="s">
         <v>259</v>
       </c>
       <c r="AA11">
-        <v>0.99879459732803533</v>
+        <v>0.99527941978256373</v>
       </c>
       <c r="AB11">
-        <v>22.099048986019618</v>
+        <v>86.543970652997501</v>
       </c>
       <c r="AD11" t="s">
         <v>214</v>
@@ -6118,7 +6118,7 @@
         <v>319</v>
       </c>
       <c r="AN11" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="AO11">
         <v>0.99802303154782224</v>
@@ -6157,10 +6157,10 @@
         <v>378</v>
       </c>
       <c r="BC11">
-        <v>0.99353721168226494</v>
+        <v>0.99328660064428831</v>
       </c>
       <c r="BD11">
-        <v>780.55486105754892</v>
+        <v>799.26715189313825</v>
       </c>
     </row>
     <row r="12" spans="2:56">
@@ -6225,16 +6225,16 @@
         <v>219</v>
       </c>
       <c r="Y12" t="s">
-        <v>194</v>
+        <v>209</v>
       </c>
       <c r="Z12" t="s">
         <v>260</v>
       </c>
       <c r="AA12">
-        <v>0.99528472132468926</v>
+        <v>0.99816212475700461</v>
       </c>
       <c r="AB12">
-        <v>86.446775714029911</v>
+        <v>33.694379454915534</v>
       </c>
       <c r="AD12" t="s">
         <v>214</v>
@@ -6303,10 +6303,10 @@
         <v>380</v>
       </c>
       <c r="BC12">
-        <v>0.99564787435456037</v>
+        <v>0.99644441082752833</v>
       </c>
       <c r="BD12">
-        <v>622.95871485949408</v>
+        <v>563.48399154455342</v>
       </c>
     </row>
     <row r="13" spans="2:56">
@@ -6371,16 +6371,16 @@
         <v>221</v>
       </c>
       <c r="Y13" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="Z13" t="s">
         <v>261</v>
       </c>
       <c r="AA13">
-        <v>0.99930490342600053</v>
+        <v>0.9982777178598693</v>
       </c>
       <c r="AB13">
-        <v>12.743437189989784</v>
+        <v>31.57517256906204</v>
       </c>
       <c r="AD13" t="s">
         <v>214</v>
@@ -6449,10 +6449,10 @@
         <v>382</v>
       </c>
       <c r="BC13">
-        <v>0.99328660064428831</v>
+        <v>0.99383352379209899</v>
       </c>
       <c r="BD13">
-        <v>799.26715189313825</v>
+        <v>758.43022352327353</v>
       </c>
     </row>
     <row r="14" spans="2:56">
@@ -6517,16 +6517,16 @@
         <v>223</v>
       </c>
       <c r="Y14" t="s">
-        <v>195</v>
+        <v>206</v>
       </c>
       <c r="Z14" t="s">
         <v>262</v>
       </c>
       <c r="AA14">
-        <v>0.99481478101166732</v>
+        <v>0.99790924430977568</v>
       </c>
       <c r="AB14">
-        <v>95.062348119433295</v>
+        <v>38.330520987445141</v>
       </c>
       <c r="AD14" t="s">
         <v>214</v>
@@ -6559,10 +6559,10 @@
         <v>325</v>
       </c>
       <c r="AO14">
-        <v>0.99820603964897492</v>
+        <v>0.9970175669053517</v>
       </c>
       <c r="AP14">
-        <v>32.889273102125877</v>
+        <v>54.677940068551905</v>
       </c>
       <c r="AR14" t="s">
         <v>214</v>
@@ -6592,13 +6592,13 @@
         <v>383</v>
       </c>
       <c r="BB14" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="BC14">
-        <v>0.99644441082752833</v>
+        <v>0.99603306101923861</v>
       </c>
       <c r="BD14">
-        <v>563.48399154455342</v>
+        <v>594.19811056351818</v>
       </c>
     </row>
     <row r="15" spans="2:56">
@@ -6663,16 +6663,16 @@
         <v>225</v>
       </c>
       <c r="Y15" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="Z15" t="s">
         <v>263</v>
       </c>
       <c r="AA15">
-        <v>0.99722308378470115</v>
+        <v>0.99800043478959211</v>
       </c>
       <c r="AB15">
-        <v>50.910130613812505</v>
+        <v>36.658695524144065</v>
       </c>
       <c r="AD15" t="s">
         <v>214</v>
@@ -6705,10 +6705,10 @@
         <v>327</v>
       </c>
       <c r="AO15">
-        <v>0.9974949209720726</v>
+        <v>0.99807680391993525</v>
       </c>
       <c r="AP15">
-        <v>45.926448845335997</v>
+        <v>35.258594801187613</v>
       </c>
       <c r="AR15" t="s">
         <v>214</v>
@@ -6735,16 +6735,16 @@
         <v>365</v>
       </c>
       <c r="BA15" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="BB15" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="BC15">
-        <v>0.99608994650263638</v>
+        <v>0.99255663966463281</v>
       </c>
       <c r="BD15">
-        <v>589.950661136485</v>
+        <v>853.77090504074806</v>
       </c>
     </row>
     <row r="16" spans="2:56">
@@ -6809,16 +6809,16 @@
         <v>227</v>
       </c>
       <c r="Y16" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="Z16" t="s">
         <v>264</v>
       </c>
       <c r="AA16">
-        <v>0.99722902196587604</v>
+        <v>0.99736542216816171</v>
       </c>
       <c r="AB16">
-        <v>50.801263958939998</v>
+        <v>48.30059358370243</v>
       </c>
       <c r="AD16" t="s">
         <v>214</v>
@@ -6881,16 +6881,16 @@
         <v>367</v>
       </c>
       <c r="BA16" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="BB16" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="BC16">
-        <v>0.99399682431672776</v>
+        <v>0.99353721168226494</v>
       </c>
       <c r="BD16">
-        <v>746.2371176843244</v>
+        <v>780.55486105754892</v>
       </c>
     </row>
     <row r="17" spans="2:56">
@@ -6955,16 +6955,16 @@
         <v>229</v>
       </c>
       <c r="Y17" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="Z17" t="s">
         <v>265</v>
       </c>
       <c r="AA17">
-        <v>0.99798192111760586</v>
+        <v>0.99879459732803533</v>
       </c>
       <c r="AB17">
-        <v>36.998112843893345</v>
+        <v>22.099048986019618</v>
       </c>
       <c r="AD17" t="s">
         <v>214</v>
@@ -6997,10 +6997,10 @@
         <v>331</v>
       </c>
       <c r="AO17">
-        <v>0.9970175669053517</v>
+        <v>0.99776911581804295</v>
       </c>
       <c r="AP17">
-        <v>54.677940068551905</v>
+        <v>40.899543335879912</v>
       </c>
       <c r="AR17" t="s">
         <v>214</v>
@@ -7027,16 +7027,16 @@
         <v>369</v>
       </c>
       <c r="BA17" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="BB17" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="BC17">
-        <v>0.99383352379209899</v>
+        <v>0.99608994650263638</v>
       </c>
       <c r="BD17">
-        <v>758.43022352327353</v>
+        <v>589.950661136485</v>
       </c>
     </row>
     <row r="18" spans="2:56">
@@ -7101,16 +7101,16 @@
         <v>231</v>
       </c>
       <c r="Y18" t="s">
-        <v>211</v>
+        <v>194</v>
       </c>
       <c r="Z18" t="s">
         <v>266</v>
       </c>
       <c r="AA18">
-        <v>0.9976725421604733</v>
+        <v>0.99528472132468926</v>
       </c>
       <c r="AB18">
-        <v>42.670060391322053</v>
+        <v>86.446775714029911</v>
       </c>
       <c r="AD18" t="s">
         <v>214</v>
@@ -7143,10 +7143,10 @@
         <v>333</v>
       </c>
       <c r="AO18">
-        <v>0.99823649129166203</v>
+        <v>0.99417507204056121</v>
       </c>
       <c r="AP18">
-        <v>32.33099298619527</v>
+        <v>106.79034592304365</v>
       </c>
       <c r="AR18" t="s">
         <v>214</v>
@@ -7176,13 +7176,13 @@
         <v>390</v>
       </c>
       <c r="BB18" t="s">
-        <v>385</v>
+        <v>391</v>
       </c>
       <c r="BC18">
-        <v>0.99603306101923861</v>
+        <v>0.99399682431672776</v>
       </c>
       <c r="BD18">
-        <v>594.19811056351818</v>
+        <v>746.2371176843244</v>
       </c>
     </row>
     <row r="19" spans="2:56">
@@ -7247,16 +7247,16 @@
         <v>233</v>
       </c>
       <c r="Y19" t="s">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="Z19" t="s">
         <v>267</v>
       </c>
       <c r="AA19">
-        <v>0.99658775492800411</v>
+        <v>0.99481478101166732</v>
       </c>
       <c r="AB19">
-        <v>62.557826319923819</v>
+        <v>95.062348119433295</v>
       </c>
       <c r="AD19" t="s">
         <v>214</v>
@@ -7289,10 +7289,10 @@
         <v>335</v>
       </c>
       <c r="AO19">
-        <v>0.99449756685866841</v>
+        <v>0.99792720516317523</v>
       </c>
       <c r="AP19">
-        <v>100.87794092441324</v>
+        <v>38.001238675119851</v>
       </c>
       <c r="AR19" t="s">
         <v>214</v>
@@ -7319,16 +7319,16 @@
         <v>373</v>
       </c>
       <c r="BA19" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="BB19" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="BC19">
-        <v>0.99615739524125424</v>
+        <v>0.99564787435456037</v>
       </c>
       <c r="BD19">
-        <v>584.91448865302027</v>
+        <v>622.95871485949408</v>
       </c>
     </row>
     <row r="20" spans="2:56">
@@ -7393,16 +7393,16 @@
         <v>235</v>
       </c>
       <c r="Y20" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Z20" t="s">
         <v>268</v>
       </c>
       <c r="AA20">
-        <v>0.99790924430977568</v>
+        <v>0.99722308378470115</v>
       </c>
       <c r="AB20">
-        <v>38.330520987445141</v>
+        <v>50.910130613812505</v>
       </c>
       <c r="AD20" t="s">
         <v>214</v>
@@ -7435,10 +7435,10 @@
         <v>337</v>
       </c>
       <c r="AO20">
-        <v>0.9984386919037852</v>
+        <v>0.99645544727444857</v>
       </c>
       <c r="AP20">
-        <v>28.623981763938804</v>
+        <v>64.983466635109991</v>
       </c>
       <c r="AR20" t="s">
         <v>214</v>
@@ -7465,16 +7465,16 @@
         <v>375</v>
       </c>
       <c r="BA20" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="BB20" t="s">
-        <v>393</v>
+        <v>378</v>
       </c>
       <c r="BC20">
-        <v>0.99255663966463281</v>
+        <v>0.99615739524125424</v>
       </c>
       <c r="BD20">
-        <v>853.77090504074806</v>
+        <v>584.91448865302027</v>
       </c>
     </row>
     <row r="21" spans="2:56">
@@ -7539,16 +7539,16 @@
         <v>237</v>
       </c>
       <c r="Y21" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Z21" t="s">
         <v>269</v>
       </c>
       <c r="AA21">
-        <v>0.99800043478959211</v>
+        <v>0.99722902196587604</v>
       </c>
       <c r="AB21">
-        <v>36.658695524144065</v>
+        <v>50.801263958939998</v>
       </c>
       <c r="AD21" t="s">
         <v>214</v>
@@ -7581,10 +7581,10 @@
         <v>339</v>
       </c>
       <c r="AO21">
-        <v>0.99776911581804295</v>
+        <v>0.9984386919037852</v>
       </c>
       <c r="AP21">
-        <v>40.899543335879912</v>
+        <v>28.623981763938804</v>
       </c>
     </row>
     <row r="22" spans="2:56">
@@ -7649,16 +7649,16 @@
         <v>239</v>
       </c>
       <c r="Y22" t="s">
-        <v>196</v>
+        <v>205</v>
       </c>
       <c r="Z22" t="s">
         <v>270</v>
       </c>
       <c r="AA22">
-        <v>0.99736542216816171</v>
+        <v>0.99798192111760586</v>
       </c>
       <c r="AB22">
-        <v>48.30059358370243</v>
+        <v>36.998112843893345</v>
       </c>
       <c r="AD22" t="s">
         <v>214</v>
@@ -7759,16 +7759,16 @@
         <v>241</v>
       </c>
       <c r="Y23" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="Z23" t="s">
         <v>271</v>
       </c>
       <c r="AA23">
-        <v>0.9973355530571224</v>
+        <v>0.9976725421604733</v>
       </c>
       <c r="AB23">
-        <v>48.848193952756368</v>
+        <v>42.670060391322053</v>
       </c>
       <c r="AD23" t="s">
         <v>214</v>
@@ -7869,16 +7869,16 @@
         <v>243</v>
       </c>
       <c r="Y24" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="Z24" t="s">
         <v>272</v>
       </c>
       <c r="AA24">
-        <v>0.99527941978256373</v>
+        <v>0.99658775492800411</v>
       </c>
       <c r="AB24">
-        <v>86.543970652997501</v>
+        <v>62.557826319923819</v>
       </c>
       <c r="AD24" t="s">
         <v>214</v>
@@ -7979,16 +7979,16 @@
         <v>245</v>
       </c>
       <c r="Y25" t="s">
-        <v>209</v>
+        <v>197</v>
       </c>
       <c r="Z25" t="s">
         <v>273</v>
       </c>
       <c r="AA25">
-        <v>0.99816212475700461</v>
+        <v>0.9960245226928881</v>
       </c>
       <c r="AB25">
-        <v>33.694379454915534</v>
+        <v>72.883750630384142</v>
       </c>
       <c r="AD25" t="s">
         <v>214</v>
@@ -8018,7 +8018,7 @@
         <v>346</v>
       </c>
       <c r="AN25" t="s">
-        <v>261</v>
+        <v>277</v>
       </c>
       <c r="AO25">
         <v>0.99848572822013582</v>
@@ -8089,16 +8089,16 @@
         <v>247</v>
       </c>
       <c r="Y26" t="s">
-        <v>203</v>
+        <v>212</v>
       </c>
       <c r="Z26" t="s">
         <v>274</v>
       </c>
       <c r="AA26">
-        <v>0.99693515631487983</v>
+        <v>0.99860864755073686</v>
       </c>
       <c r="AB26">
-        <v>56.188800893869058</v>
+        <v>25.508128236491515</v>
       </c>
       <c r="AD26" t="s">
         <v>214</v>
@@ -8199,16 +8199,16 @@
         <v>249</v>
       </c>
       <c r="Y27" t="s">
-        <v>212</v>
+        <v>198</v>
       </c>
       <c r="Z27" t="s">
         <v>275</v>
       </c>
       <c r="AA27">
-        <v>0.99860864755073686</v>
+        <v>0.99596909671058553</v>
       </c>
       <c r="AB27">
-        <v>25.508128236491515</v>
+        <v>73.89989363926469</v>
       </c>
       <c r="AD27" t="s">
         <v>214</v>
@@ -8241,10 +8241,10 @@
         <v>350</v>
       </c>
       <c r="AO27">
-        <v>0.99807680391993525</v>
+        <v>0.99820603964897492</v>
       </c>
       <c r="AP27">
-        <v>35.258594801187613</v>
+        <v>32.889273102125877</v>
       </c>
     </row>
     <row r="28" spans="2:56">
@@ -8309,16 +8309,16 @@
         <v>251</v>
       </c>
       <c r="Y28" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="Z28" t="s">
         <v>276</v>
       </c>
       <c r="AA28">
-        <v>0.99596909671058553</v>
+        <v>0.99693515631487983</v>
       </c>
       <c r="AB28">
-        <v>73.89989363926469</v>
+        <v>56.188800893869058</v>
       </c>
       <c r="AD28" t="s">
         <v>214</v>
@@ -8351,10 +8351,10 @@
         <v>352</v>
       </c>
       <c r="AO28">
-        <v>0.99645544727444857</v>
+        <v>0.9974949209720726</v>
       </c>
       <c r="AP28">
-        <v>64.983466635109991</v>
+        <v>45.926448845335997</v>
       </c>
     </row>
     <row r="29" spans="2:56">
@@ -8419,16 +8419,16 @@
         <v>253</v>
       </c>
       <c r="Y29" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="Z29" t="s">
         <v>277</v>
       </c>
       <c r="AA29">
-        <v>0.9960245226928881</v>
+        <v>0.99930490342600053</v>
       </c>
       <c r="AB29">
-        <v>72.883750630384142</v>
+        <v>12.743437189989784</v>
       </c>
       <c r="AD29" t="s">
         <v>214</v>
@@ -8461,10 +8461,10 @@
         <v>354</v>
       </c>
       <c r="AO29">
-        <v>0.99417507204056121</v>
+        <v>0.99823649129166203</v>
       </c>
       <c r="AP29">
-        <v>106.79034592304365</v>
+        <v>32.33099298619527</v>
       </c>
     </row>
     <row r="30" spans="2:56">
@@ -8529,16 +8529,16 @@
         <v>255</v>
       </c>
       <c r="Y30" t="s">
-        <v>193</v>
+        <v>204</v>
       </c>
       <c r="Z30" t="s">
         <v>278</v>
       </c>
       <c r="AA30">
-        <v>0.9982777178598693</v>
+        <v>0.9973355530571224</v>
       </c>
       <c r="AB30">
-        <v>31.57517256906204</v>
+        <v>48.848193952756368</v>
       </c>
       <c r="AD30" t="s">
         <v>214</v>
@@ -8571,10 +8571,10 @@
         <v>356</v>
       </c>
       <c r="AO30">
-        <v>0.99792720516317523</v>
+        <v>0.99449756685866841</v>
       </c>
       <c r="AP30">
-        <v>38.001238675119851</v>
+        <v>100.87794092441324</v>
       </c>
     </row>
   </sheetData>
@@ -8583,7 +8583,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{131EE3F6-7CDB-4279-85A3-B89717113460}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E4A7F53-CDFC-4899-856D-6EF496356697}">
   <dimension ref="B9:Z30"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -8695,7 +8695,7 @@
         <v>394</v>
       </c>
       <c r="K11" t="s">
-        <v>351</v>
+        <v>336</v>
       </c>
       <c r="L11">
         <v>1.9280734277521856</v>
@@ -8728,7 +8728,7 @@
         <v>434</v>
       </c>
       <c r="X11" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="Y11">
         <v>0.83925000000000005</v>
@@ -8796,7 +8796,7 @@
         <v>436</v>
       </c>
       <c r="X12" t="s">
-        <v>377</v>
+        <v>387</v>
       </c>
       <c r="Y12">
         <v>16.887</v>
@@ -8864,7 +8864,7 @@
         <v>438</v>
       </c>
       <c r="X13" t="s">
-        <v>379</v>
+        <v>392</v>
       </c>
       <c r="Y13">
         <v>11.2965</v>
@@ -8899,7 +8899,7 @@
         <v>400</v>
       </c>
       <c r="K14" t="s">
-        <v>324</v>
+        <v>349</v>
       </c>
       <c r="L14">
         <v>0.38418098169506976</v>
@@ -8932,7 +8932,7 @@
         <v>440</v>
       </c>
       <c r="X14" t="s">
-        <v>392</v>
+        <v>385</v>
       </c>
       <c r="Y14">
         <v>6.6577500000000001</v>
@@ -9000,7 +9000,7 @@
         <v>442</v>
       </c>
       <c r="X15" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="Y15">
         <v>17.089500000000001</v>
@@ -9068,7 +9068,7 @@
         <v>444</v>
       </c>
       <c r="X16" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="Y16">
         <v>8.8230000000000004</v>
@@ -9136,7 +9136,7 @@
         <v>446</v>
       </c>
       <c r="X17" t="s">
-        <v>390</v>
+        <v>383</v>
       </c>
       <c r="Y17">
         <v>0.22650000000000001</v>
@@ -9171,7 +9171,7 @@
         <v>408</v>
       </c>
       <c r="K18" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="L18">
         <v>0.5763849443065614</v>
@@ -9204,7 +9204,7 @@
         <v>448</v>
       </c>
       <c r="X18" t="s">
-        <v>388</v>
+        <v>381</v>
       </c>
       <c r="Y18">
         <v>9.5062499999999996</v>
@@ -9239,7 +9239,7 @@
         <v>410</v>
       </c>
       <c r="K19" t="s">
-        <v>353</v>
+        <v>332</v>
       </c>
       <c r="L19">
         <v>0.67826309709986921</v>
@@ -9272,7 +9272,7 @@
         <v>450</v>
       </c>
       <c r="X19" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="Y19">
         <v>13.37175</v>
@@ -9307,7 +9307,7 @@
         <v>412</v>
       </c>
       <c r="K20" t="s">
-        <v>349</v>
+        <v>326</v>
       </c>
       <c r="L20">
         <v>0.75446432597387325</v>
@@ -9340,7 +9340,7 @@
         <v>452</v>
       </c>
       <c r="X20" t="s">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="Y20">
         <v>3.9427500000000002</v>
@@ -9375,7 +9375,7 @@
         <v>414</v>
       </c>
       <c r="K21" t="s">
-        <v>334</v>
+        <v>355</v>
       </c>
       <c r="L21">
         <v>0.7924639655878376</v>
@@ -9410,7 +9410,7 @@
         <v>416</v>
       </c>
       <c r="K22" t="s">
-        <v>338</v>
+        <v>330</v>
       </c>
       <c r="L22">
         <v>0.55411362221124194</v>
@@ -9445,7 +9445,7 @@
         <v>418</v>
       </c>
       <c r="K23" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="L23">
         <v>0.17045566395647468</v>
@@ -9480,7 +9480,7 @@
         <v>420</v>
       </c>
       <c r="K24" t="s">
-        <v>326</v>
+        <v>351</v>
       </c>
       <c r="L24">
         <v>0.45447951042003487</v>
@@ -9515,7 +9515,7 @@
         <v>422</v>
       </c>
       <c r="K25" t="s">
-        <v>332</v>
+        <v>353</v>
       </c>
       <c r="L25">
         <v>0.58930389251851034</v>
@@ -9585,7 +9585,7 @@
         <v>426</v>
       </c>
       <c r="K27" t="s">
-        <v>355</v>
+        <v>334</v>
       </c>
       <c r="L27">
         <v>1.1409691335703016</v>
@@ -9705,7 +9705,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE9C9918-3B4D-4D0F-8975-A0649DD51843}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF12E265-993A-47E8-88B7-CA25CF571838}">
   <dimension ref="B9:Y136"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -14066,7 +14066,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3586B4C-4DD3-42D4-9EC1-6A658B435F0A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC3C7FFC-EB62-49C0-AD24-BB54203FD50D}">
   <dimension ref="B9:T88"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_POL_grids_kan50/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_POL_grids_kan50/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF8DF6A8-6E4C-4E87-AFCF-30971B0BFAA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95126D06-2786-4050-A8E7-2416DE14A4D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="368" yWindow="368" windowWidth="21599" windowHeight="12772" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1005,6 +1005,138 @@
     <t>connecting solar to buses in cluster 40</t>
   </si>
   <si>
+    <t>distr_solelc_spv_POL_031</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 31</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_033</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 33</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_019</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_020</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_046</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 46</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_047</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 47</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_002</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_034</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 34</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_045</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 45</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_011</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_041</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 41</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_026</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_005</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_009</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_021</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_003</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_017</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_030</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 30</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_042</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 42</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_007</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_032</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 32</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_039</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 39</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_POL_006</t>
   </si>
   <si>
@@ -1035,6 +1167,54 @@
     <t>connecting solar to buses in cluster 43</t>
   </si>
   <si>
+    <t>distr_solelc_spv_POL_008</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_012</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_044</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 44</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_018</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_029</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 29</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_048</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 48</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_004</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_015</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 15</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_POL_016</t>
   </si>
   <si>
@@ -1053,168 +1233,6 @@
     <t>connecting solar to buses in cluster 37</t>
   </si>
   <si>
-    <t>distr_solelc_spv_POL_026</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_019</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_020</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_046</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 46</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_047</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 47</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_003</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_017</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_030</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 30</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_042</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 42</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_007</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_032</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 32</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_039</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 39</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_004</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_015</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_002</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_034</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 34</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_045</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 45</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_012</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_044</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 44</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_011</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_041</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 41</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_008</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_031</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 31</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_033</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 33</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_005</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_009</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_021</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 21</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_POL_014</t>
   </si>
   <si>
@@ -1239,24 +1257,6 @@
     <t>connecting solar to buses in cluster 38</t>
   </si>
   <si>
-    <t>distr_solelc_spv_POL_018</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_029</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 29</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_048</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 48</t>
-  </si>
-  <si>
     <t>comm-in</t>
   </si>
   <si>
@@ -1281,6 +1281,72 @@
     <t>e_Szczecin_POL</t>
   </si>
   <si>
+    <t>e_OstrowiecSwietokrz_POL</t>
+  </si>
+  <si>
+    <t>e_Konin_POL</t>
+  </si>
+  <si>
+    <t>e_Zamosc_POL</t>
+  </si>
+  <si>
+    <t>e_Koszalin_POL</t>
+  </si>
+  <si>
+    <t>e_Gdynia_POL</t>
+  </si>
+  <si>
+    <t>e_Krakow_POL</t>
+  </si>
+  <si>
+    <t>e_Bialystok_POL</t>
+  </si>
+  <si>
+    <t>e_Ustka_POL</t>
+  </si>
+  <si>
+    <t>e_Wroclaw_POL</t>
+  </si>
+  <si>
+    <t>e_Gdansk_POL</t>
+  </si>
+  <si>
+    <t>e_Katowice_POL</t>
+  </si>
+  <si>
+    <t>e_Kielce_POL</t>
+  </si>
+  <si>
+    <t>e_Olesnica_POL</t>
+  </si>
+  <si>
+    <t>e_Olsztyn_POL</t>
+  </si>
+  <si>
+    <t>e_Lubin_POL</t>
+  </si>
+  <si>
+    <t>e_GorzowWielkopolski_POL</t>
+  </si>
+  <si>
+    <t>e_PiotrkowTrybunalsk_POL</t>
+  </si>
+  <si>
+    <t>e_Wloclawek_POL</t>
+  </si>
+  <si>
+    <t>e_BielskoBiala_POL</t>
+  </si>
+  <si>
+    <t>e_Kwidzyn_POL</t>
+  </si>
+  <si>
+    <t>e_Opole_POL</t>
+  </si>
+  <si>
+    <t>e_KedzierzynKozle_POL</t>
+  </si>
+  <si>
     <t>e_Swidnica_POL</t>
   </si>
   <si>
@@ -1296,6 +1362,30 @@
     <t>e_Grudziadz_POL</t>
   </si>
   <si>
+    <t>e_Slupsk_POL</t>
+  </si>
+  <si>
+    <t>e_Lomza_POL</t>
+  </si>
+  <si>
+    <t>e_Plock_POL</t>
+  </si>
+  <si>
+    <t>e_Radomsko_POL</t>
+  </si>
+  <si>
+    <t>e_Czestochowa_POL</t>
+  </si>
+  <si>
+    <t>e_Pulawy_POL</t>
+  </si>
+  <si>
+    <t>e_Legnica_POL</t>
+  </si>
+  <si>
+    <t>e_Krosno_POL</t>
+  </si>
+  <si>
     <t>e_Grajewo_POL</t>
   </si>
   <si>
@@ -1305,87 +1395,6 @@
     <t>e_Elk_POL</t>
   </si>
   <si>
-    <t>e_Kielce_POL</t>
-  </si>
-  <si>
-    <t>e_Zamosc_POL</t>
-  </si>
-  <si>
-    <t>e_Koszalin_POL</t>
-  </si>
-  <si>
-    <t>e_Gdynia_POL</t>
-  </si>
-  <si>
-    <t>e_Krakow_POL</t>
-  </si>
-  <si>
-    <t>e_GorzowWielkopolski_POL</t>
-  </si>
-  <si>
-    <t>e_PiotrkowTrybunalsk_POL</t>
-  </si>
-  <si>
-    <t>e_Wloclawek_POL</t>
-  </si>
-  <si>
-    <t>e_BielskoBiala_POL</t>
-  </si>
-  <si>
-    <t>e_Kwidzyn_POL</t>
-  </si>
-  <si>
-    <t>e_Opole_POL</t>
-  </si>
-  <si>
-    <t>e_KedzierzynKozle_POL</t>
-  </si>
-  <si>
-    <t>e_Legnica_POL</t>
-  </si>
-  <si>
-    <t>e_Krosno_POL</t>
-  </si>
-  <si>
-    <t>e_Bialystok_POL</t>
-  </si>
-  <si>
-    <t>e_Ustka_POL</t>
-  </si>
-  <si>
-    <t>e_Wroclaw_POL</t>
-  </si>
-  <si>
-    <t>e_Lomza_POL</t>
-  </si>
-  <si>
-    <t>e_Plock_POL</t>
-  </si>
-  <si>
-    <t>e_Gdansk_POL</t>
-  </si>
-  <si>
-    <t>e_Katowice_POL</t>
-  </si>
-  <si>
-    <t>e_Slupsk_POL</t>
-  </si>
-  <si>
-    <t>e_OstrowiecSwietokrz_POL</t>
-  </si>
-  <si>
-    <t>e_Konin_POL</t>
-  </si>
-  <si>
-    <t>e_Olesnica_POL</t>
-  </si>
-  <si>
-    <t>e_Olsztyn_POL</t>
-  </si>
-  <si>
-    <t>e_Lubin_POL</t>
-  </si>
-  <si>
     <t>e_Police_POL</t>
   </si>
   <si>
@@ -1398,13 +1407,112 @@
     <t>e_Poznan_POL</t>
   </si>
   <si>
-    <t>e_Radomsko_POL</t>
-  </si>
-  <si>
-    <t>e_Czestochowa_POL</t>
-  </si>
-  <si>
-    <t>e_Pulawy_POL</t>
+    <t>distr_wonelc_won_POL_005</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_013</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_028</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_038</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 38</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_003</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_022</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_026</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_036</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 36</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_015</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_030</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 30</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_045</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 45</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_021</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_016</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_039</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 39</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_017</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_011</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_012</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_035</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 35</t>
   </si>
   <si>
     <t>distr_wonelc_won_POL_004</t>
@@ -1455,6 +1563,90 @@
     <t>connecting wind onshore to buses in cluster 44</t>
   </si>
   <si>
+    <t>distr_wonelc_won_POL_009</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_018</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_025</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_033</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 33</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_043</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 43</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_002</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_014</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_031</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 31</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_034</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 34</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_019</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_024</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_027</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_029</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 29</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_040</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 40</t>
+  </si>
+  <si>
     <t>distr_wonelc_won_POL_007</t>
   </si>
   <si>
@@ -1467,108 +1659,6 @@
     <t>connecting wind onshore to buses in cluster 8</t>
   </si>
   <si>
-    <t>distr_wonelc_won_POL_005</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_013</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_028</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_038</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 38</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_011</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_012</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_035</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 35</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_015</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_030</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 30</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_045</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 45</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_017</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_003</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_022</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_026</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_036</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 36</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_016</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_039</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 39</t>
-  </si>
-  <si>
     <t>distr_wonelc_won_POL_001</t>
   </si>
   <si>
@@ -1587,94 +1677,58 @@
     <t>connecting wind onshore to buses in cluster 41</t>
   </si>
   <si>
-    <t>distr_wonelc_won_POL_009</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_018</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_025</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_033</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 33</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_043</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 43</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_034</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 34</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_019</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_024</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_027</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_029</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 29</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_040</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 40</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_002</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_014</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_031</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 31</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_021</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 21</t>
+    <t>elc_won_POL_005</t>
+  </si>
+  <si>
+    <t>elc_won_POL_013</t>
+  </si>
+  <si>
+    <t>elc_won_POL_028</t>
+  </si>
+  <si>
+    <t>elc_won_POL_038</t>
+  </si>
+  <si>
+    <t>elc_won_POL_003</t>
+  </si>
+  <si>
+    <t>elc_won_POL_022</t>
+  </si>
+  <si>
+    <t>elc_won_POL_026</t>
+  </si>
+  <si>
+    <t>elc_won_POL_036</t>
+  </si>
+  <si>
+    <t>elc_won_POL_015</t>
+  </si>
+  <si>
+    <t>elc_won_POL_030</t>
+  </si>
+  <si>
+    <t>elc_won_POL_045</t>
+  </si>
+  <si>
+    <t>elc_won_POL_021</t>
+  </si>
+  <si>
+    <t>elc_won_POL_016</t>
+  </si>
+  <si>
+    <t>elc_won_POL_039</t>
+  </si>
+  <si>
+    <t>elc_won_POL_017</t>
+  </si>
+  <si>
+    <t>elc_won_POL_011</t>
+  </si>
+  <si>
+    <t>elc_won_POL_012</t>
+  </si>
+  <si>
+    <t>elc_won_POL_035</t>
   </si>
   <si>
     <t>elc_won_POL_004</t>
@@ -1701,63 +1755,54 @@
     <t>elc_won_POL_044</t>
   </si>
   <si>
+    <t>elc_won_POL_009</t>
+  </si>
+  <si>
+    <t>elc_won_POL_018</t>
+  </si>
+  <si>
+    <t>elc_won_POL_025</t>
+  </si>
+  <si>
+    <t>elc_won_POL_033</t>
+  </si>
+  <si>
+    <t>elc_won_POL_043</t>
+  </si>
+  <si>
+    <t>elc_won_POL_002</t>
+  </si>
+  <si>
+    <t>elc_won_POL_014</t>
+  </si>
+  <si>
+    <t>elc_won_POL_031</t>
+  </si>
+  <si>
+    <t>elc_won_POL_034</t>
+  </si>
+  <si>
+    <t>elc_won_POL_019</t>
+  </si>
+  <si>
+    <t>elc_won_POL_024</t>
+  </si>
+  <si>
+    <t>elc_won_POL_027</t>
+  </si>
+  <si>
+    <t>elc_won_POL_029</t>
+  </si>
+  <si>
+    <t>elc_won_POL_040</t>
+  </si>
+  <si>
     <t>elc_won_POL_007</t>
   </si>
   <si>
     <t>elc_won_POL_008</t>
   </si>
   <si>
-    <t>elc_won_POL_005</t>
-  </si>
-  <si>
-    <t>elc_won_POL_013</t>
-  </si>
-  <si>
-    <t>elc_won_POL_028</t>
-  </si>
-  <si>
-    <t>elc_won_POL_038</t>
-  </si>
-  <si>
-    <t>elc_won_POL_011</t>
-  </si>
-  <si>
-    <t>elc_won_POL_012</t>
-  </si>
-  <si>
-    <t>elc_won_POL_035</t>
-  </si>
-  <si>
-    <t>elc_won_POL_015</t>
-  </si>
-  <si>
-    <t>elc_won_POL_030</t>
-  </si>
-  <si>
-    <t>elc_won_POL_045</t>
-  </si>
-  <si>
-    <t>elc_won_POL_017</t>
-  </si>
-  <si>
-    <t>elc_won_POL_003</t>
-  </si>
-  <si>
-    <t>elc_won_POL_022</t>
-  </si>
-  <si>
-    <t>elc_won_POL_026</t>
-  </si>
-  <si>
-    <t>elc_won_POL_036</t>
-  </si>
-  <si>
-    <t>elc_won_POL_016</t>
-  </si>
-  <si>
-    <t>elc_won_POL_039</t>
-  </si>
-  <si>
     <t>elc_won_POL_001</t>
   </si>
   <si>
@@ -1767,49 +1812,16 @@
     <t>elc_won_POL_041</t>
   </si>
   <si>
-    <t>elc_won_POL_009</t>
-  </si>
-  <si>
-    <t>elc_won_POL_018</t>
-  </si>
-  <si>
-    <t>elc_won_POL_025</t>
-  </si>
-  <si>
-    <t>elc_won_POL_033</t>
-  </si>
-  <si>
-    <t>elc_won_POL_043</t>
-  </si>
-  <si>
-    <t>elc_won_POL_034</t>
-  </si>
-  <si>
-    <t>elc_won_POL_019</t>
-  </si>
-  <si>
-    <t>elc_won_POL_024</t>
-  </si>
-  <si>
-    <t>elc_won_POL_027</t>
-  </si>
-  <si>
-    <t>elc_won_POL_029</t>
-  </si>
-  <si>
-    <t>elc_won_POL_040</t>
-  </si>
-  <si>
-    <t>elc_won_POL_002</t>
-  </si>
-  <si>
-    <t>elc_won_POL_014</t>
-  </si>
-  <si>
-    <t>elc_won_POL_031</t>
-  </si>
-  <si>
-    <t>elc_won_POL_021</t>
+    <t>distr_wofelc_wof_POL_006</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_POL_010</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 10</t>
   </si>
   <si>
     <t>distr_wofelc_wof_POL_007</t>
@@ -1824,6 +1836,18 @@
     <t>connecting wind offshore to buses in cluster 2</t>
   </si>
   <si>
+    <t>distr_wofelc_wof_POL_003</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_POL_009</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 9</t>
+  </si>
+  <si>
     <t>distr_wofelc_wof_POL_001</t>
   </si>
   <si>
@@ -1848,28 +1872,10 @@
     <t>connecting wind offshore to buses in cluster 8</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_POL_006</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_POL_010</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_POL_003</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_POL_009</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 9</t>
+    <t>elc_wof_POL_006</t>
+  </si>
+  <si>
+    <t>elc_wof_POL_010</t>
   </si>
   <si>
     <t>elc_wof_POL_007</t>
@@ -1878,6 +1884,12 @@
     <t>elc_wof_POL_002</t>
   </si>
   <si>
+    <t>elc_wof_POL_003</t>
+  </si>
+  <si>
+    <t>elc_wof_POL_009</t>
+  </si>
+  <si>
     <t>elc_wof_POL_001</t>
   </si>
   <si>
@@ -1888,18 +1900,6 @@
   </si>
   <si>
     <t>elc_wof_POL_008</t>
-  </si>
-  <si>
-    <t>elc_wof_POL_006</t>
-  </si>
-  <si>
-    <t>elc_wof_POL_010</t>
-  </si>
-  <si>
-    <t>elc_wof_POL_003</t>
-  </si>
-  <si>
-    <t>elc_wof_POL_009</t>
   </si>
   <si>
     <t>e_won_POL_001</t>
@@ -6642,7 +6642,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB487618-E8E0-4BE6-BC5E-BCB19B5A11F7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8FFA92B7-891A-4186-BE26-DC297ADF135B}">
   <dimension ref="B9:BD58"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -6919,13 +6919,13 @@
         <v>537</v>
       </c>
       <c r="AN11" t="s">
-        <v>425</v>
+        <v>417</v>
       </c>
       <c r="AO11">
-        <v>0.99637106510563223</v>
+        <v>0.99710630405324308</v>
       </c>
       <c r="AP11">
-        <v>66.530473063409573</v>
+        <v>53.05109235721072</v>
       </c>
       <c r="AR11" t="s">
         <v>298</v>
@@ -6955,13 +6955,13 @@
         <v>602</v>
       </c>
       <c r="BB11" t="s">
-        <v>428</v>
+        <v>412</v>
       </c>
       <c r="BC11">
-        <v>0.99420331794923078</v>
+        <v>0.99353496437690181</v>
       </c>
       <c r="BD11">
-        <v>730.81892645743346</v>
+        <v>780.72265985800163</v>
       </c>
     </row>
     <row r="12" spans="2:56">
@@ -7065,13 +7065,13 @@
         <v>538</v>
       </c>
       <c r="AN12" t="s">
-        <v>405</v>
+        <v>429</v>
       </c>
       <c r="AO12">
-        <v>0.99858273852997215</v>
+        <v>0.99790619485356269</v>
       </c>
       <c r="AP12">
-        <v>25.983126950510407</v>
+        <v>38.386427684684513</v>
       </c>
       <c r="AR12" t="s">
         <v>298</v>
@@ -7101,13 +7101,13 @@
         <v>603</v>
       </c>
       <c r="BB12" t="s">
-        <v>432</v>
+        <v>409</v>
       </c>
       <c r="BC12">
-        <v>0.99430080016911837</v>
+        <v>0.99554220720080044</v>
       </c>
       <c r="BD12">
-        <v>723.54025403916376</v>
+        <v>630.84852900690294</v>
       </c>
     </row>
     <row r="13" spans="2:56">
@@ -7211,13 +7211,13 @@
         <v>539</v>
       </c>
       <c r="AN13" t="s">
-        <v>406</v>
+        <v>436</v>
       </c>
       <c r="AO13">
-        <v>0.99746457853070669</v>
+        <v>0.99769655918709399</v>
       </c>
       <c r="AP13">
-        <v>46.482726937045001</v>
+        <v>42.229748236609375</v>
       </c>
       <c r="AR13" t="s">
         <v>298</v>
@@ -7247,13 +7247,13 @@
         <v>604</v>
       </c>
       <c r="BB13" t="s">
-        <v>432</v>
+        <v>412</v>
       </c>
       <c r="BC13">
-        <v>0.99644441082752833</v>
+        <v>0.99420331794923078</v>
       </c>
       <c r="BD13">
-        <v>563.48399154455342</v>
+        <v>730.81892645743346</v>
       </c>
     </row>
     <row r="14" spans="2:56">
@@ -7357,13 +7357,13 @@
         <v>540</v>
       </c>
       <c r="AN14" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="AO14">
-        <v>0.99607102778768364</v>
+        <v>0.99831856205423208</v>
       </c>
       <c r="AP14">
-        <v>72.031157225799802</v>
+        <v>30.826362339077892</v>
       </c>
       <c r="AR14" t="s">
         <v>298</v>
@@ -7393,13 +7393,13 @@
         <v>605</v>
       </c>
       <c r="BB14" t="s">
-        <v>440</v>
+        <v>414</v>
       </c>
       <c r="BC14">
-        <v>0.99271345576813386</v>
+        <v>0.99430080016911837</v>
       </c>
       <c r="BD14">
-        <v>842.06196931267482</v>
+        <v>723.54025403916376</v>
       </c>
     </row>
     <row r="15" spans="2:56">
@@ -7503,13 +7503,13 @@
         <v>541</v>
       </c>
       <c r="AN15" t="s">
-        <v>428</v>
+        <v>420</v>
       </c>
       <c r="AO15">
-        <v>0.99872163833602245</v>
+        <v>0.99618708835855785</v>
       </c>
       <c r="AP15">
-        <v>23.43663050625544</v>
+        <v>69.903380093106392</v>
       </c>
       <c r="AR15" t="s">
         <v>298</v>
@@ -7539,13 +7539,13 @@
         <v>606</v>
       </c>
       <c r="BB15" t="s">
-        <v>415</v>
+        <v>443</v>
       </c>
       <c r="BC15">
-        <v>0.99530309222972468</v>
+        <v>0.99085736230959864</v>
       </c>
       <c r="BD15">
-        <v>648.70244684722252</v>
+        <v>980.65028088329757</v>
       </c>
     </row>
     <row r="16" spans="2:56">
@@ -7649,13 +7649,13 @@
         <v>542</v>
       </c>
       <c r="AN16" t="s">
-        <v>424</v>
+        <v>445</v>
       </c>
       <c r="AO16">
-        <v>0.99395242381797833</v>
+        <v>0.99833671361519116</v>
       </c>
       <c r="AP16">
-        <v>110.87223000373062</v>
+        <v>30.493583721495042</v>
       </c>
       <c r="AR16" t="s">
         <v>298</v>
@@ -7685,13 +7685,13 @@
         <v>607</v>
       </c>
       <c r="BB16" t="s">
-        <v>416</v>
+        <v>409</v>
       </c>
       <c r="BC16">
-        <v>0.99367569996430205</v>
+        <v>0.99327606149844871</v>
       </c>
       <c r="BD16">
-        <v>770.21440266544937</v>
+        <v>800.05407478249322</v>
       </c>
     </row>
     <row r="17" spans="2:56">
@@ -7756,16 +7756,16 @@
         <v>313</v>
       </c>
       <c r="Y17" t="s">
-        <v>254</v>
+        <v>279</v>
       </c>
       <c r="Z17" t="s">
         <v>405</v>
       </c>
       <c r="AA17">
-        <v>0.99843597467175715</v>
+        <v>0.99837269295343656</v>
       </c>
       <c r="AB17">
-        <v>28.673797684451465</v>
+        <v>29.833962520329422</v>
       </c>
       <c r="AD17" t="s">
         <v>298</v>
@@ -7795,13 +7795,13 @@
         <v>543</v>
       </c>
       <c r="AN17" t="s">
-        <v>429</v>
+        <v>402</v>
       </c>
       <c r="AO17">
-        <v>0.99667991040280568</v>
+        <v>0.99848139574142536</v>
       </c>
       <c r="AP17">
-        <v>60.868309281895392</v>
+        <v>27.841078073867958</v>
       </c>
       <c r="AR17" t="s">
         <v>298</v>
@@ -7831,13 +7831,13 @@
         <v>608</v>
       </c>
       <c r="BB17" t="s">
-        <v>428</v>
+        <v>414</v>
       </c>
       <c r="BC17">
-        <v>0.99353496437690181</v>
+        <v>0.99644441082752833</v>
       </c>
       <c r="BD17">
-        <v>780.72265985800163</v>
+        <v>563.48399154455342</v>
       </c>
     </row>
     <row r="18" spans="2:56">
@@ -7902,16 +7902,16 @@
         <v>315</v>
       </c>
       <c r="Y18" t="s">
-        <v>258</v>
+        <v>281</v>
       </c>
       <c r="Z18" t="s">
         <v>406</v>
       </c>
       <c r="AA18">
-        <v>0.9978441728294174</v>
+        <v>0.99721661922905269</v>
       </c>
       <c r="AB18">
-        <v>39.52349812734775</v>
+        <v>51.028647467367875</v>
       </c>
       <c r="AD18" t="s">
         <v>298</v>
@@ -7941,13 +7941,13 @@
         <v>544</v>
       </c>
       <c r="AN18" t="s">
-        <v>417</v>
+        <v>446</v>
       </c>
       <c r="AO18">
-        <v>0.99828011941724693</v>
+        <v>0.99647205231329106</v>
       </c>
       <c r="AP18">
-        <v>31.53114401714058</v>
+        <v>64.67904092299645</v>
       </c>
       <c r="AR18" t="s">
         <v>298</v>
@@ -7977,13 +7977,13 @@
         <v>609</v>
       </c>
       <c r="BB18" t="s">
-        <v>416</v>
+        <v>443</v>
       </c>
       <c r="BC18">
-        <v>0.99554220720080044</v>
+        <v>0.99271345576813386</v>
       </c>
       <c r="BD18">
-        <v>630.84852900690294</v>
+        <v>842.06196931267482</v>
       </c>
     </row>
     <row r="19" spans="2:56">
@@ -8048,16 +8048,16 @@
         <v>317</v>
       </c>
       <c r="Y19" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="Z19" t="s">
         <v>407</v>
       </c>
       <c r="AA19">
-        <v>0.99742460390003085</v>
+        <v>0.99599533664322148</v>
       </c>
       <c r="AB19">
-        <v>47.215595166102005</v>
+        <v>73.418828207606111</v>
       </c>
       <c r="AD19" t="s">
         <v>298</v>
@@ -8087,13 +8087,13 @@
         <v>545</v>
       </c>
       <c r="AN19" t="s">
-        <v>422</v>
+        <v>439</v>
       </c>
       <c r="AO19">
-        <v>0.99549746393702321</v>
+        <v>0.99732374082025621</v>
       </c>
       <c r="AP19">
-        <v>82.546494487907452</v>
+        <v>49.064751628636806</v>
       </c>
       <c r="AR19" t="s">
         <v>298</v>
@@ -8123,13 +8123,13 @@
         <v>610</v>
       </c>
       <c r="BB19" t="s">
-        <v>440</v>
+        <v>408</v>
       </c>
       <c r="BC19">
-        <v>0.99085736230959864</v>
+        <v>0.99530309222972468</v>
       </c>
       <c r="BD19">
-        <v>980.65028088329757</v>
+        <v>648.70244684722252</v>
       </c>
     </row>
     <row r="20" spans="2:56">
@@ -8194,16 +8194,16 @@
         <v>319</v>
       </c>
       <c r="Y20" t="s">
-        <v>283</v>
+        <v>268</v>
       </c>
       <c r="Z20" t="s">
         <v>408</v>
       </c>
       <c r="AA20">
-        <v>0.99726229290154123</v>
+        <v>0.99597518091211446</v>
       </c>
       <c r="AB20">
-        <v>50.191296805077087</v>
+        <v>73.788349944568822</v>
       </c>
       <c r="AD20" t="s">
         <v>298</v>
@@ -8233,13 +8233,13 @@
         <v>546</v>
       </c>
       <c r="AN20" t="s">
-        <v>434</v>
+        <v>405</v>
       </c>
       <c r="AO20">
-        <v>0.9963955080465341</v>
+        <v>0.99822748431408481</v>
       </c>
       <c r="AP20">
-        <v>66.082352480207561</v>
+        <v>32.496120908444247</v>
       </c>
       <c r="AR20" t="s">
         <v>298</v>
@@ -8269,13 +8269,13 @@
         <v>611</v>
       </c>
       <c r="BB20" t="s">
-        <v>416</v>
+        <v>409</v>
       </c>
       <c r="BC20">
-        <v>0.99327606149844871</v>
+        <v>0.99367569996430205</v>
       </c>
       <c r="BD20">
-        <v>800.05407478249322</v>
+        <v>770.21440266544937</v>
       </c>
     </row>
     <row r="21" spans="2:56">
@@ -8340,16 +8340,16 @@
         <v>321</v>
       </c>
       <c r="Y21" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="Z21" t="s">
         <v>409</v>
       </c>
       <c r="AA21">
-        <v>0.99690217083770882</v>
+        <v>0.99781775104585479</v>
       </c>
       <c r="AB21">
-        <v>56.793534642004325</v>
+        <v>40.00789749266211</v>
       </c>
       <c r="AD21" t="s">
         <v>298</v>
@@ -8382,10 +8382,10 @@
         <v>437</v>
       </c>
       <c r="AO21">
-        <v>0.99710630405324308</v>
+        <v>0.99664897656614915</v>
       </c>
       <c r="AP21">
-        <v>53.05109235721072</v>
+        <v>61.435429620598065</v>
       </c>
     </row>
     <row r="22" spans="2:56">
@@ -8450,16 +8450,16 @@
         <v>323</v>
       </c>
       <c r="Y22" t="s">
-        <v>264</v>
+        <v>295</v>
       </c>
       <c r="Z22" t="s">
         <v>410</v>
       </c>
       <c r="AA22">
-        <v>0.9966781224752207</v>
+        <v>0.99812825439018349</v>
       </c>
       <c r="AB22">
-        <v>60.901087954288208</v>
+        <v>34.315336179968583</v>
       </c>
       <c r="AD22" t="s">
         <v>298</v>
@@ -8489,13 +8489,13 @@
         <v>548</v>
       </c>
       <c r="AN22" t="s">
-        <v>407</v>
+        <v>419</v>
       </c>
       <c r="AO22">
-        <v>0.99790619485356269</v>
+        <v>0.99805304129458994</v>
       </c>
       <c r="AP22">
-        <v>38.386427684684513</v>
+        <v>35.694242932517511</v>
       </c>
     </row>
     <row r="23" spans="2:56">
@@ -8560,16 +8560,16 @@
         <v>325</v>
       </c>
       <c r="Y23" t="s">
-        <v>284</v>
+        <v>250</v>
       </c>
       <c r="Z23" t="s">
         <v>411</v>
       </c>
       <c r="AA23">
-        <v>0.99981234635886196</v>
+        <v>0.99629199875237673</v>
       </c>
       <c r="AB23">
-        <v>3.4403167541969326</v>
+        <v>67.980022873093773</v>
       </c>
       <c r="AD23" t="s">
         <v>298</v>
@@ -8599,13 +8599,13 @@
         <v>549</v>
       </c>
       <c r="AN23" t="s">
-        <v>445</v>
+        <v>440</v>
       </c>
       <c r="AO23">
-        <v>0.99769655918709399</v>
+        <v>0.99680838391616855</v>
       </c>
       <c r="AP23">
-        <v>42.229748236609375</v>
+        <v>58.512961536909224</v>
       </c>
     </row>
     <row r="24" spans="2:56">
@@ -8670,16 +8670,16 @@
         <v>327</v>
       </c>
       <c r="Y24" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="Z24" t="s">
         <v>412</v>
       </c>
       <c r="AA24">
-        <v>0.99601304617251241</v>
+        <v>0.99872163833602245</v>
       </c>
       <c r="AB24">
-        <v>73.094153503939168</v>
+        <v>23.43663050625544</v>
       </c>
       <c r="AD24" t="s">
         <v>298</v>
@@ -8709,13 +8709,13 @@
         <v>550</v>
       </c>
       <c r="AN24" t="s">
-        <v>404</v>
+        <v>415</v>
       </c>
       <c r="AO24">
-        <v>0.99831856205423208</v>
+        <v>0.99860547433316238</v>
       </c>
       <c r="AP24">
-        <v>30.826362339077892</v>
+        <v>25.566303892023345</v>
       </c>
     </row>
     <row r="25" spans="2:56">
@@ -8780,16 +8780,16 @@
         <v>329</v>
       </c>
       <c r="Y25" t="s">
-        <v>274</v>
+        <v>293</v>
       </c>
       <c r="Z25" t="s">
         <v>413</v>
       </c>
       <c r="AA25">
-        <v>0.99724663742006237</v>
+        <v>0.99742650690351664</v>
       </c>
       <c r="AB25">
-        <v>50.478313965522325</v>
+        <v>47.180706768861114</v>
       </c>
       <c r="AD25" t="s">
         <v>298</v>
@@ -8819,13 +8819,13 @@
         <v>551</v>
       </c>
       <c r="AN25" t="s">
-        <v>432</v>
+        <v>421</v>
       </c>
       <c r="AO25">
-        <v>0.99685495193349705</v>
+        <v>0.99734647676885635</v>
       </c>
       <c r="AP25">
-        <v>57.659214552554296</v>
+        <v>48.647925904299434</v>
       </c>
     </row>
     <row r="26" spans="2:56">
@@ -8890,16 +8890,16 @@
         <v>331</v>
       </c>
       <c r="Y26" t="s">
-        <v>267</v>
+        <v>259</v>
       </c>
       <c r="Z26" t="s">
         <v>414</v>
       </c>
       <c r="AA26">
-        <v>0.99599533664322148</v>
+        <v>0.99726620602429616</v>
       </c>
       <c r="AB26">
-        <v>73.418828207606111</v>
+        <v>50.11955622123601</v>
       </c>
       <c r="AD26" t="s">
         <v>298</v>
@@ -8929,13 +8929,13 @@
         <v>552</v>
       </c>
       <c r="AN26" t="s">
-        <v>430</v>
+        <v>414</v>
       </c>
       <c r="AO26">
-        <v>0.99598227212496737</v>
+        <v>0.99685495193349705</v>
       </c>
       <c r="AP26">
-        <v>73.658344375598276</v>
+        <v>57.659214552554296</v>
       </c>
     </row>
     <row r="27" spans="2:56">
@@ -9000,16 +9000,16 @@
         <v>333</v>
       </c>
       <c r="Y27" t="s">
-        <v>268</v>
+        <v>289</v>
       </c>
       <c r="Z27" t="s">
         <v>415</v>
       </c>
       <c r="AA27">
-        <v>0.99597518091211446</v>
+        <v>0.99860547433316238</v>
       </c>
       <c r="AB27">
-        <v>73.788349944568822</v>
+        <v>25.566303892023345</v>
       </c>
       <c r="AD27" t="s">
         <v>298</v>
@@ -9039,13 +9039,13 @@
         <v>553</v>
       </c>
       <c r="AN27" t="s">
-        <v>412</v>
+        <v>433</v>
       </c>
       <c r="AO27">
-        <v>0.99590634111935905</v>
+        <v>0.99598227212496737</v>
       </c>
       <c r="AP27">
-        <v>75.050412811751528</v>
+        <v>73.658344375598276</v>
       </c>
     </row>
     <row r="28" spans="2:56">
@@ -9110,16 +9110,16 @@
         <v>335</v>
       </c>
       <c r="Y28" t="s">
-        <v>294</v>
+        <v>274</v>
       </c>
       <c r="Z28" t="s">
         <v>416</v>
       </c>
       <c r="AA28">
-        <v>0.99781775104585479</v>
+        <v>0.99724663742006237</v>
       </c>
       <c r="AB28">
-        <v>40.00789749266211</v>
+        <v>50.478313965522325</v>
       </c>
       <c r="AD28" t="s">
         <v>298</v>
@@ -9149,13 +9149,13 @@
         <v>554</v>
       </c>
       <c r="AN28" t="s">
-        <v>426</v>
+        <v>442</v>
       </c>
       <c r="AO28">
-        <v>0.99732374082025621</v>
+        <v>0.99590634111935905</v>
       </c>
       <c r="AP28">
-        <v>49.064751628636806</v>
+        <v>75.050412811751528</v>
       </c>
     </row>
     <row r="29" spans="2:56">
@@ -9220,16 +9220,16 @@
         <v>337</v>
       </c>
       <c r="Y29" t="s">
-        <v>295</v>
+        <v>253</v>
       </c>
       <c r="Z29" t="s">
         <v>417</v>
       </c>
       <c r="AA29">
-        <v>0.99812825439018349</v>
+        <v>0.99718236526914339</v>
       </c>
       <c r="AB29">
-        <v>34.315336179968583</v>
+        <v>51.656636732372107</v>
       </c>
       <c r="AD29" t="s">
         <v>298</v>
@@ -9259,13 +9259,13 @@
         <v>555</v>
       </c>
       <c r="AN29" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="AO29">
-        <v>0.99822748431408481</v>
+        <v>0.99637106510563223</v>
       </c>
       <c r="AP29">
-        <v>32.496120908444247</v>
+        <v>66.530473063409573</v>
       </c>
     </row>
     <row r="30" spans="2:56">
@@ -9330,16 +9330,16 @@
         <v>339</v>
       </c>
       <c r="Y30" t="s">
-        <v>251</v>
+        <v>257</v>
       </c>
       <c r="Z30" t="s">
         <v>418</v>
       </c>
       <c r="AA30">
-        <v>0.99686199227105832</v>
+        <v>0.9969349663191277</v>
       </c>
       <c r="AB30">
-        <v>57.530141697264057</v>
+        <v>56.19228414932568</v>
       </c>
       <c r="AD30" t="s">
         <v>298</v>
@@ -9369,13 +9369,13 @@
         <v>556</v>
       </c>
       <c r="AN30" t="s">
-        <v>446</v>
+        <v>427</v>
       </c>
       <c r="AO30">
-        <v>0.99664897656614915</v>
+        <v>0.99858273852997215</v>
       </c>
       <c r="AP30">
-        <v>61.435429620598065</v>
+        <v>25.983126950510407</v>
       </c>
     </row>
     <row r="31" spans="2:56">
@@ -9440,16 +9440,16 @@
         <v>341</v>
       </c>
       <c r="Y31" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="Z31" t="s">
         <v>419</v>
       </c>
       <c r="AA31">
-        <v>0.99738123071621287</v>
+        <v>0.9986488565028202</v>
       </c>
       <c r="AB31">
-        <v>48.010770202763901</v>
+        <v>24.77096411496214</v>
       </c>
       <c r="AD31" t="s">
         <v>298</v>
@@ -9479,13 +9479,13 @@
         <v>557</v>
       </c>
       <c r="AN31" t="s">
-        <v>419</v>
+        <v>428</v>
       </c>
       <c r="AO31">
-        <v>0.99734647676885635</v>
+        <v>0.99746457853070669</v>
       </c>
       <c r="AP31">
-        <v>48.647925904299434</v>
+        <v>46.482726937045001</v>
       </c>
     </row>
     <row r="32" spans="2:56">
@@ -9550,16 +9550,16 @@
         <v>343</v>
       </c>
       <c r="Y32" t="s">
-        <v>278</v>
+        <v>251</v>
       </c>
       <c r="Z32" t="s">
         <v>420</v>
       </c>
       <c r="AA32">
-        <v>0.99802582646217142</v>
+        <v>0.99686199227105832</v>
       </c>
       <c r="AB32">
-        <v>36.193181526857884</v>
+        <v>57.530141697264057</v>
       </c>
       <c r="AD32" t="s">
         <v>298</v>
@@ -9589,13 +9589,13 @@
         <v>558</v>
       </c>
       <c r="AN32" t="s">
-        <v>418</v>
+        <v>400</v>
       </c>
       <c r="AO32">
-        <v>0.99618708835855785</v>
+        <v>0.99607102778768364</v>
       </c>
       <c r="AP32">
-        <v>69.903380093106392</v>
+        <v>72.031157225799802</v>
       </c>
     </row>
     <row r="33" spans="2:42">
@@ -9660,16 +9660,16 @@
         <v>345</v>
       </c>
       <c r="Y33" t="s">
-        <v>290</v>
+        <v>265</v>
       </c>
       <c r="Z33" t="s">
         <v>421</v>
       </c>
       <c r="AA33">
-        <v>0.99799386853297711</v>
+        <v>0.99738123071621287</v>
       </c>
       <c r="AB33">
-        <v>36.779076895420076</v>
+        <v>48.010770202763901</v>
       </c>
       <c r="AD33" t="s">
         <v>298</v>
@@ -9699,13 +9699,13 @@
         <v>559</v>
       </c>
       <c r="AN33" t="s">
-        <v>442</v>
+        <v>412</v>
       </c>
       <c r="AO33">
-        <v>0.99833671361519116</v>
+        <v>0.99872163833602245</v>
       </c>
       <c r="AP33">
-        <v>30.493583721495042</v>
+        <v>23.43663050625544</v>
       </c>
     </row>
     <row r="34" spans="2:42">
@@ -9770,16 +9770,16 @@
         <v>347</v>
       </c>
       <c r="Y34" t="s">
-        <v>255</v>
+        <v>278</v>
       </c>
       <c r="Z34" t="s">
         <v>422</v>
       </c>
       <c r="AA34">
-        <v>0.99549746393702321</v>
+        <v>0.99802582646217142</v>
       </c>
       <c r="AB34">
-        <v>82.546494487907452</v>
+        <v>36.193181526857884</v>
       </c>
       <c r="AD34" t="s">
         <v>298</v>
@@ -9809,13 +9809,13 @@
         <v>560</v>
       </c>
       <c r="AN34" t="s">
-        <v>402</v>
+        <v>426</v>
       </c>
       <c r="AO34">
-        <v>0.99848139574142536</v>
+        <v>0.99395242381797833</v>
       </c>
       <c r="AP34">
-        <v>27.841078073867958</v>
+        <v>110.87223000373062</v>
       </c>
     </row>
     <row r="35" spans="2:42">
@@ -9880,16 +9880,16 @@
         <v>349</v>
       </c>
       <c r="Y35" t="s">
-        <v>280</v>
+        <v>290</v>
       </c>
       <c r="Z35" t="s">
         <v>423</v>
       </c>
       <c r="AA35">
-        <v>0.99595758935481538</v>
+        <v>0.99799386853297711</v>
       </c>
       <c r="AB35">
-        <v>74.11086182838541</v>
+        <v>36.779076895420076</v>
       </c>
       <c r="AD35" t="s">
         <v>298</v>
@@ -9919,13 +9919,13 @@
         <v>561</v>
       </c>
       <c r="AN35" t="s">
-        <v>443</v>
+        <v>413</v>
       </c>
       <c r="AO35">
-        <v>0.99647205231329106</v>
+        <v>0.99667991040280568</v>
       </c>
       <c r="AP35">
-        <v>64.67904092299645</v>
+        <v>60.868309281895392</v>
       </c>
     </row>
     <row r="36" spans="2:42">
@@ -9990,16 +9990,16 @@
         <v>351</v>
       </c>
       <c r="Y36" t="s">
-        <v>287</v>
+        <v>255</v>
       </c>
       <c r="Z36" t="s">
         <v>424</v>
       </c>
       <c r="AA36">
-        <v>0.99738380907420521</v>
+        <v>0.99549746393702321</v>
       </c>
       <c r="AB36">
-        <v>47.963500306237819</v>
+        <v>82.546494487907452</v>
       </c>
       <c r="AD36" t="s">
         <v>298</v>
@@ -10032,10 +10032,10 @@
         <v>410</v>
       </c>
       <c r="AO36">
-        <v>0.99680838391616855</v>
+        <v>0.99828011941724693</v>
       </c>
       <c r="AP36">
-        <v>58.512961536909224</v>
+        <v>31.53114401714058</v>
       </c>
     </row>
     <row r="37" spans="2:42">
@@ -10100,16 +10100,16 @@
         <v>353</v>
       </c>
       <c r="Y37" t="s">
-        <v>252</v>
+        <v>280</v>
       </c>
       <c r="Z37" t="s">
         <v>425</v>
       </c>
       <c r="AA37">
-        <v>0.99728892162739502</v>
+        <v>0.99595758935481538</v>
       </c>
       <c r="AB37">
-        <v>49.703103497758356</v>
+        <v>74.11086182838541</v>
       </c>
       <c r="AD37" t="s">
         <v>298</v>
@@ -10139,13 +10139,13 @@
         <v>563</v>
       </c>
       <c r="AN37" t="s">
-        <v>433</v>
+        <v>418</v>
       </c>
       <c r="AO37">
-        <v>0.99860547433316238</v>
+        <v>0.99687826280430603</v>
       </c>
       <c r="AP37">
-        <v>25.566303892023345</v>
+        <v>57.231848587722098</v>
       </c>
     </row>
     <row r="38" spans="2:42">
@@ -10210,16 +10210,16 @@
         <v>355</v>
       </c>
       <c r="Y38" t="s">
-        <v>263</v>
+        <v>287</v>
       </c>
       <c r="Z38" t="s">
         <v>426</v>
       </c>
       <c r="AA38">
-        <v>0.99712760177041293</v>
+        <v>0.99738380907420521</v>
       </c>
       <c r="AB38">
-        <v>52.660634209097303</v>
+        <v>47.963500306237819</v>
       </c>
       <c r="AD38" t="s">
         <v>298</v>
@@ -10249,13 +10249,13 @@
         <v>564</v>
       </c>
       <c r="AN38" t="s">
-        <v>399</v>
+        <v>435</v>
       </c>
       <c r="AO38">
-        <v>0.99613577684801091</v>
+        <v>0.99699364492988352</v>
       </c>
       <c r="AP38">
-        <v>70.84409111980095</v>
+        <v>55.11650961880288</v>
       </c>
     </row>
     <row r="39" spans="2:42">
@@ -10320,16 +10320,16 @@
         <v>357</v>
       </c>
       <c r="Y39" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="Z39" t="s">
         <v>427</v>
       </c>
       <c r="AA39">
-        <v>0.99629199875237673</v>
+        <v>0.99843597467175715</v>
       </c>
       <c r="AB39">
-        <v>67.980022873093773</v>
+        <v>28.673797684451465</v>
       </c>
       <c r="AD39" t="s">
         <v>298</v>
@@ -10359,13 +10359,13 @@
         <v>565</v>
       </c>
       <c r="AN39" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AO39">
-        <v>0.99565692288848451</v>
+        <v>0.99671282097572789</v>
       </c>
       <c r="AP39">
-        <v>79.623080377784689</v>
+        <v>60.264948778321823</v>
       </c>
     </row>
     <row r="40" spans="2:42">
@@ -10430,16 +10430,16 @@
         <v>359</v>
       </c>
       <c r="Y40" t="s">
-        <v>282</v>
+        <v>258</v>
       </c>
       <c r="Z40" t="s">
         <v>428</v>
       </c>
       <c r="AA40">
-        <v>0.99872163833602245</v>
+        <v>0.9978441728294174</v>
       </c>
       <c r="AB40">
-        <v>23.43663050625544</v>
+        <v>39.52349812734775</v>
       </c>
       <c r="AD40" t="s">
         <v>298</v>
@@ -10469,13 +10469,13 @@
         <v>566</v>
       </c>
       <c r="AN40" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="AO40">
-        <v>0.99659482771051944</v>
+        <v>0.99716516865497618</v>
       </c>
       <c r="AP40">
-        <v>62.428158640477555</v>
+        <v>51.971907992102771</v>
       </c>
     </row>
     <row r="41" spans="2:42">
@@ -10540,16 +10540,16 @@
         <v>361</v>
       </c>
       <c r="Y41" t="s">
-        <v>293</v>
+        <v>261</v>
       </c>
       <c r="Z41" t="s">
         <v>429</v>
       </c>
       <c r="AA41">
-        <v>0.99742650690351664</v>
+        <v>0.99742460390003085</v>
       </c>
       <c r="AB41">
-        <v>47.180706768861114</v>
+        <v>47.215595166102005</v>
       </c>
       <c r="AD41" t="s">
         <v>298</v>
@@ -10579,13 +10579,13 @@
         <v>567</v>
       </c>
       <c r="AN41" t="s">
-        <v>438</v>
+        <v>409</v>
       </c>
       <c r="AO41">
-        <v>0.99687826280430603</v>
+        <v>0.99781775104585479</v>
       </c>
       <c r="AP41">
-        <v>57.231848587722098</v>
+        <v>40.00789749266211</v>
       </c>
     </row>
     <row r="42" spans="2:42">
@@ -10650,16 +10650,16 @@
         <v>363</v>
       </c>
       <c r="Y42" t="s">
-        <v>260</v>
+        <v>283</v>
       </c>
       <c r="Z42" t="s">
         <v>430</v>
       </c>
       <c r="AA42">
-        <v>0.99614768552045674</v>
+        <v>0.99726229290154123</v>
       </c>
       <c r="AB42">
-        <v>70.625765458293685</v>
+        <v>50.191296805077087</v>
       </c>
       <c r="AD42" t="s">
         <v>298</v>
@@ -10689,13 +10689,13 @@
         <v>568</v>
       </c>
       <c r="AN42" t="s">
-        <v>444</v>
+        <v>411</v>
       </c>
       <c r="AO42">
-        <v>0.99699364492988352</v>
+        <v>0.99645529726643833</v>
       </c>
       <c r="AP42">
-        <v>55.11650961880288</v>
+        <v>64.986216781964885</v>
       </c>
     </row>
     <row r="43" spans="2:42">
@@ -10760,16 +10760,16 @@
         <v>365</v>
       </c>
       <c r="Y43" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="Z43" t="s">
         <v>431</v>
       </c>
       <c r="AA43">
-        <v>0.99662210970297749</v>
+        <v>0.99690217083770882</v>
       </c>
       <c r="AB43">
-        <v>61.927988778745295</v>
+        <v>56.793534642004325</v>
       </c>
       <c r="AD43" t="s">
         <v>298</v>
@@ -10799,13 +10799,13 @@
         <v>569</v>
       </c>
       <c r="AN43" t="s">
-        <v>413</v>
+        <v>443</v>
       </c>
       <c r="AO43">
-        <v>0.99671282097572789</v>
+        <v>0.99384744606594821</v>
       </c>
       <c r="AP43">
-        <v>60.264948778321823</v>
+        <v>112.79682212428183</v>
       </c>
     </row>
     <row r="44" spans="2:42">
@@ -10870,16 +10870,16 @@
         <v>367</v>
       </c>
       <c r="Y44" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="Z44" t="s">
         <v>432</v>
       </c>
       <c r="AA44">
-        <v>0.99726620602429616</v>
+        <v>0.9963955080465341</v>
       </c>
       <c r="AB44">
-        <v>50.11955622123601</v>
+        <v>66.082352480207561</v>
       </c>
       <c r="AD44" t="s">
         <v>298</v>
@@ -10909,13 +10909,13 @@
         <v>570</v>
       </c>
       <c r="AN44" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="AO44">
-        <v>0.99716516865497618</v>
+        <v>0.99698481435147746</v>
       </c>
       <c r="AP44">
-        <v>51.971907992102771</v>
+        <v>55.278403556247454</v>
       </c>
     </row>
     <row r="45" spans="2:42">
@@ -10980,16 +10980,16 @@
         <v>369</v>
       </c>
       <c r="Y45" t="s">
-        <v>289</v>
+        <v>260</v>
       </c>
       <c r="Z45" t="s">
         <v>433</v>
       </c>
       <c r="AA45">
-        <v>0.99860547433316238</v>
+        <v>0.99614768552045674</v>
       </c>
       <c r="AB45">
-        <v>25.566303892023345</v>
+        <v>70.625765458293685</v>
       </c>
       <c r="AD45" t="s">
         <v>298</v>
@@ -11019,13 +11019,13 @@
         <v>571</v>
       </c>
       <c r="AN45" t="s">
-        <v>416</v>
+        <v>441</v>
       </c>
       <c r="AO45">
-        <v>0.99781775104585479</v>
+        <v>0.99981234635886196</v>
       </c>
       <c r="AP45">
-        <v>40.00789749266211</v>
+        <v>3.4403167541969326</v>
       </c>
     </row>
     <row r="46" spans="2:42">
@@ -11090,16 +11090,16 @@
         <v>371</v>
       </c>
       <c r="Y46" t="s">
-        <v>256</v>
+        <v>292</v>
       </c>
       <c r="Z46" t="s">
         <v>434</v>
       </c>
       <c r="AA46">
-        <v>0.9963955080465341</v>
+        <v>0.99662210970297749</v>
       </c>
       <c r="AB46">
-        <v>66.082352480207561</v>
+        <v>61.927988778745295</v>
       </c>
       <c r="AD46" t="s">
         <v>298</v>
@@ -11129,13 +11129,13 @@
         <v>572</v>
       </c>
       <c r="AN46" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="AO46">
-        <v>0.99981234635886196</v>
+        <v>0.99719738668750013</v>
       </c>
       <c r="AP46">
-        <v>3.4403167541969326</v>
+        <v>51.381244062497984</v>
       </c>
     </row>
     <row r="47" spans="2:42">
@@ -11200,16 +11200,16 @@
         <v>373</v>
       </c>
       <c r="Y47" t="s">
-        <v>279</v>
+        <v>266</v>
       </c>
       <c r="Z47" t="s">
         <v>435</v>
       </c>
       <c r="AA47">
-        <v>0.99837269295343656</v>
+        <v>0.99780371642234478</v>
       </c>
       <c r="AB47">
-        <v>29.833962520329422</v>
+        <v>40.265198923679918</v>
       </c>
       <c r="AD47" t="s">
         <v>298</v>
@@ -11239,13 +11239,13 @@
         <v>573</v>
       </c>
       <c r="AN47" t="s">
-        <v>414</v>
+        <v>401</v>
       </c>
       <c r="AO47">
-        <v>0.99719738668750013</v>
+        <v>0.99796516192404061</v>
       </c>
       <c r="AP47">
-        <v>51.381244062497984</v>
+        <v>37.305364725922644</v>
       </c>
     </row>
     <row r="48" spans="2:42">
@@ -11310,16 +11310,16 @@
         <v>375</v>
       </c>
       <c r="Y48" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="Z48" t="s">
         <v>436</v>
       </c>
       <c r="AA48">
-        <v>0.99721661922905269</v>
+        <v>0.99769575851681602</v>
       </c>
       <c r="AB48">
-        <v>51.028647467367875</v>
+        <v>42.244427191705796</v>
       </c>
       <c r="AD48" t="s">
         <v>298</v>
@@ -11349,13 +11349,13 @@
         <v>574</v>
       </c>
       <c r="AN48" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="AO48">
-        <v>0.99796516192404061</v>
+        <v>0.9959465500877519</v>
       </c>
       <c r="AP48">
-        <v>37.305364725922644</v>
+        <v>74.313248391216121</v>
       </c>
     </row>
     <row r="49" spans="2:42">
@@ -11420,16 +11420,16 @@
         <v>377</v>
       </c>
       <c r="Y49" t="s">
-        <v>253</v>
+        <v>296</v>
       </c>
       <c r="Z49" t="s">
         <v>437</v>
       </c>
       <c r="AA49">
-        <v>0.99718236526914339</v>
+        <v>0.99679813939088713</v>
       </c>
       <c r="AB49">
-        <v>51.656636732372107</v>
+        <v>58.700777833736801</v>
       </c>
       <c r="AD49" t="s">
         <v>298</v>
@@ -11459,13 +11459,13 @@
         <v>575</v>
       </c>
       <c r="AN49" t="s">
-        <v>403</v>
+        <v>422</v>
       </c>
       <c r="AO49">
-        <v>0.9959465500877519</v>
+        <v>0.99801149212126983</v>
       </c>
       <c r="AP49">
-        <v>74.313248391216121</v>
+        <v>36.455977776719045</v>
       </c>
     </row>
     <row r="50" spans="2:42">
@@ -11530,16 +11530,16 @@
         <v>379</v>
       </c>
       <c r="Y50" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="Z50" t="s">
         <v>438</v>
       </c>
       <c r="AA50">
-        <v>0.9969349663191277</v>
+        <v>0.99728892162739502</v>
       </c>
       <c r="AB50">
-        <v>56.19228414932568</v>
+        <v>49.703103497758356</v>
       </c>
       <c r="AD50" t="s">
         <v>298</v>
@@ -11569,13 +11569,13 @@
         <v>576</v>
       </c>
       <c r="AN50" t="s">
-        <v>420</v>
+        <v>431</v>
       </c>
       <c r="AO50">
-        <v>0.99801149212126983</v>
+        <v>0.99612567652967976</v>
       </c>
       <c r="AP50">
-        <v>36.455977776719045</v>
+        <v>71.029263622537798</v>
       </c>
     </row>
     <row r="51" spans="2:42">
@@ -11640,16 +11640,16 @@
         <v>381</v>
       </c>
       <c r="Y51" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="Z51" t="s">
         <v>439</v>
       </c>
       <c r="AA51">
-        <v>0.9986488565028202</v>
+        <v>0.99712760177041293</v>
       </c>
       <c r="AB51">
-        <v>24.77096411496214</v>
+        <v>52.660634209097303</v>
       </c>
       <c r="AD51" t="s">
         <v>298</v>
@@ -11679,13 +11679,13 @@
         <v>577</v>
       </c>
       <c r="AN51" t="s">
-        <v>409</v>
+        <v>424</v>
       </c>
       <c r="AO51">
-        <v>0.99612567652967976</v>
+        <v>0.99549746393702321</v>
       </c>
       <c r="AP51">
-        <v>71.029263622537798</v>
+        <v>82.546494487907452</v>
       </c>
     </row>
     <row r="52" spans="2:42">
@@ -11750,16 +11750,16 @@
         <v>383</v>
       </c>
       <c r="Y52" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Z52" t="s">
         <v>440</v>
       </c>
       <c r="AA52">
-        <v>0.99426155007999251</v>
+        <v>0.9966781224752207</v>
       </c>
       <c r="AB52">
-        <v>105.20491520013644</v>
+        <v>60.901087954288208</v>
       </c>
       <c r="AD52" t="s">
         <v>298</v>
@@ -11789,13 +11789,13 @@
         <v>578</v>
       </c>
       <c r="AN52" t="s">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c r="AO52">
-        <v>0.99645529726643833</v>
+        <v>0.9963955080465341</v>
       </c>
       <c r="AP52">
-        <v>64.986216781964885</v>
+        <v>66.082352480207561</v>
       </c>
     </row>
     <row r="53" spans="2:42">
@@ -11860,16 +11860,16 @@
         <v>385</v>
       </c>
       <c r="Y53" t="s">
-        <v>270</v>
+        <v>284</v>
       </c>
       <c r="Z53" t="s">
         <v>441</v>
       </c>
       <c r="AA53">
-        <v>0.99838277460902491</v>
+        <v>0.99981234635886196</v>
       </c>
       <c r="AB53">
-        <v>29.649132167876981</v>
+        <v>3.4403167541969326</v>
       </c>
       <c r="AD53" t="s">
         <v>298</v>
@@ -11899,13 +11899,13 @@
         <v>579</v>
       </c>
       <c r="AN53" t="s">
-        <v>440</v>
+        <v>399</v>
       </c>
       <c r="AO53">
-        <v>0.99384744606594821</v>
+        <v>0.99613577684801091</v>
       </c>
       <c r="AP53">
-        <v>112.79682212428183</v>
+        <v>70.84409111980095</v>
       </c>
     </row>
     <row r="54" spans="2:42">
@@ -11970,16 +11970,16 @@
         <v>387</v>
       </c>
       <c r="Y54" t="s">
-        <v>271</v>
+        <v>285</v>
       </c>
       <c r="Z54" t="s">
         <v>442</v>
       </c>
       <c r="AA54">
-        <v>0.99809131232622839</v>
+        <v>0.99601304617251241</v>
       </c>
       <c r="AB54">
-        <v>34.992607352478593</v>
+        <v>73.094153503939168</v>
       </c>
       <c r="AD54" t="s">
         <v>298</v>
@@ -12009,13 +12009,13 @@
         <v>580</v>
       </c>
       <c r="AN54" t="s">
-        <v>436</v>
+        <v>408</v>
       </c>
       <c r="AO54">
-        <v>0.99698481435147746</v>
+        <v>0.99565692288848451</v>
       </c>
       <c r="AP54">
-        <v>55.278403556247454</v>
+        <v>79.623080377784689</v>
       </c>
     </row>
     <row r="55" spans="2:42">
@@ -12080,16 +12080,16 @@
         <v>389</v>
       </c>
       <c r="Y55" t="s">
-        <v>286</v>
+        <v>262</v>
       </c>
       <c r="Z55" t="s">
         <v>443</v>
       </c>
       <c r="AA55">
-        <v>0.99579033105838544</v>
+        <v>0.99426155007999251</v>
       </c>
       <c r="AB55">
-        <v>77.177263929600329</v>
+        <v>105.20491520013644</v>
       </c>
       <c r="AD55" t="s">
         <v>298</v>
@@ -12119,13 +12119,13 @@
         <v>581</v>
       </c>
       <c r="AN55" t="s">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="AO55">
-        <v>0.99805304129458994</v>
+        <v>0.99659482771051944</v>
       </c>
       <c r="AP55">
-        <v>35.694242932517511</v>
+        <v>62.428158640477555</v>
       </c>
     </row>
     <row r="56" spans="2:42">
@@ -12190,16 +12190,16 @@
         <v>391</v>
       </c>
       <c r="Y56" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="Z56" t="s">
         <v>444</v>
       </c>
       <c r="AA56">
-        <v>0.99780371642234478</v>
+        <v>0.99838277460902491</v>
       </c>
       <c r="AB56">
-        <v>40.265198923679918</v>
+        <v>29.649132167876981</v>
       </c>
     </row>
     <row r="57" spans="2:42">
@@ -12264,16 +12264,16 @@
         <v>393</v>
       </c>
       <c r="Y57" t="s">
-        <v>277</v>
+        <v>271</v>
       </c>
       <c r="Z57" t="s">
         <v>445</v>
       </c>
       <c r="AA57">
-        <v>0.99769575851681602</v>
+        <v>0.99809131232622839</v>
       </c>
       <c r="AB57">
-        <v>42.244427191705796</v>
+        <v>34.992607352478593</v>
       </c>
     </row>
     <row r="58" spans="2:42">
@@ -12338,16 +12338,16 @@
         <v>395</v>
       </c>
       <c r="Y58" t="s">
-        <v>296</v>
+        <v>286</v>
       </c>
       <c r="Z58" t="s">
         <v>446</v>
       </c>
       <c r="AA58">
-        <v>0.99679813939088713</v>
+        <v>0.99579033105838544</v>
       </c>
       <c r="AB58">
-        <v>58.700777833736801</v>
+        <v>77.177263929600329</v>
       </c>
     </row>
   </sheetData>
@@ -12356,7 +12356,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6141B49-C1C7-4983-8180-028CD5A8E757}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{169823F0-5D7F-4E1C-8003-A13C95E1571F}">
   <dimension ref="B9:Z55"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -12468,7 +12468,7 @@
         <v>612</v>
       </c>
       <c r="K11" t="s">
-        <v>564</v>
+        <v>579</v>
       </c>
       <c r="L11">
         <v>2.0644299871134622</v>
@@ -12501,7 +12501,7 @@
         <v>702</v>
       </c>
       <c r="X11" t="s">
-        <v>604</v>
+        <v>608</v>
       </c>
       <c r="Y11">
         <v>0.83925000000000005</v>
@@ -12536,7 +12536,7 @@
         <v>614</v>
       </c>
       <c r="K12" t="s">
-        <v>578</v>
+        <v>568</v>
       </c>
       <c r="L12">
         <v>5.6562172505218191</v>
@@ -12569,7 +12569,7 @@
         <v>704</v>
       </c>
       <c r="X12" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="Y12">
         <v>19.703250000000001</v>
@@ -12604,7 +12604,7 @@
         <v>616</v>
       </c>
       <c r="K13" t="s">
-        <v>558</v>
+        <v>541</v>
       </c>
       <c r="L13">
         <v>1.8909299975727167</v>
@@ -12637,7 +12637,7 @@
         <v>706</v>
       </c>
       <c r="X13" t="s">
-        <v>610</v>
+        <v>606</v>
       </c>
       <c r="Y13">
         <v>9.5062499999999996</v>
@@ -12672,7 +12672,7 @@
         <v>618</v>
       </c>
       <c r="K14" t="s">
-        <v>537</v>
+        <v>555</v>
       </c>
       <c r="L14">
         <v>0.61763438605424437</v>
@@ -12705,7 +12705,7 @@
         <v>708</v>
       </c>
       <c r="X14" t="s">
-        <v>605</v>
+        <v>609</v>
       </c>
       <c r="Y14">
         <v>0.16950000000000001</v>
@@ -12740,7 +12740,7 @@
         <v>620</v>
       </c>
       <c r="K15" t="s">
-        <v>547</v>
+        <v>537</v>
       </c>
       <c r="L15">
         <v>0.12973508759817037</v>
@@ -12773,7 +12773,7 @@
         <v>710</v>
       </c>
       <c r="X15" t="s">
-        <v>606</v>
+        <v>610</v>
       </c>
       <c r="Y15">
         <v>5.7000000000000002E-2</v>
@@ -12808,7 +12808,7 @@
         <v>622</v>
       </c>
       <c r="K16" t="s">
-        <v>538</v>
+        <v>556</v>
       </c>
       <c r="L16">
         <v>0.26374115795515951</v>
@@ -12841,7 +12841,7 @@
         <v>712</v>
       </c>
       <c r="X16" t="s">
-        <v>608</v>
+        <v>602</v>
       </c>
       <c r="Y16">
         <v>17.603249999999999</v>
@@ -12876,7 +12876,7 @@
         <v>624</v>
       </c>
       <c r="K17" t="s">
-        <v>545</v>
+        <v>577</v>
       </c>
       <c r="L17">
         <v>0.64796828373237858</v>
@@ -12909,7 +12909,7 @@
         <v>714</v>
       </c>
       <c r="X17" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="Y17">
         <v>3.9427500000000002</v>
@@ -12944,7 +12944,7 @@
         <v>626</v>
       </c>
       <c r="K18" t="s">
-        <v>546</v>
+        <v>578</v>
       </c>
       <c r="L18">
         <v>0.63517423417111829</v>
@@ -12977,7 +12977,7 @@
         <v>716</v>
       </c>
       <c r="X18" t="s">
-        <v>607</v>
+        <v>611</v>
       </c>
       <c r="Y18">
         <v>5.8237500000000004</v>
@@ -13012,7 +13012,7 @@
         <v>628</v>
       </c>
       <c r="K19" t="s">
-        <v>567</v>
+        <v>563</v>
       </c>
       <c r="L19">
         <v>4.1793335626386838</v>
@@ -13045,7 +13045,7 @@
         <v>718</v>
       </c>
       <c r="X19" t="s">
-        <v>611</v>
+        <v>607</v>
       </c>
       <c r="Y19">
         <v>17.089500000000001</v>
@@ -13080,7 +13080,7 @@
         <v>630</v>
       </c>
       <c r="K20" t="s">
-        <v>539</v>
+        <v>557</v>
       </c>
       <c r="L20">
         <v>0.10220883742433164</v>
@@ -13113,7 +13113,7 @@
         <v>720</v>
       </c>
       <c r="X20" t="s">
-        <v>609</v>
+        <v>603</v>
       </c>
       <c r="Y20">
         <v>13.905749999999999</v>
@@ -13148,7 +13148,7 @@
         <v>632</v>
       </c>
       <c r="K21" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="L21">
         <v>1.8851727881959806</v>
@@ -13183,7 +13183,7 @@
         <v>634</v>
       </c>
       <c r="K22" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="L22">
         <v>5.7123185944284298</v>
@@ -13218,7 +13218,7 @@
         <v>636</v>
       </c>
       <c r="K23" t="s">
-        <v>548</v>
+        <v>538</v>
       </c>
       <c r="L23">
         <v>0.18120178223038519</v>
@@ -13253,7 +13253,7 @@
         <v>638</v>
       </c>
       <c r="K24" t="s">
-        <v>579</v>
+        <v>569</v>
       </c>
       <c r="L24">
         <v>0.48612534522992462</v>
@@ -13288,7 +13288,7 @@
         <v>640</v>
       </c>
       <c r="K25" t="s">
-        <v>554</v>
+        <v>545</v>
       </c>
       <c r="L25">
         <v>0.53652528976360103</v>
@@ -13323,7 +13323,7 @@
         <v>642</v>
       </c>
       <c r="K26" t="s">
-        <v>562</v>
+        <v>549</v>
       </c>
       <c r="L26">
         <v>2.2806390094229081</v>
@@ -13358,7 +13358,7 @@
         <v>644</v>
       </c>
       <c r="K27" t="s">
-        <v>557</v>
+        <v>551</v>
       </c>
       <c r="L27">
         <v>1.3748361910948423</v>
@@ -13393,7 +13393,7 @@
         <v>646</v>
       </c>
       <c r="K28" t="s">
-        <v>568</v>
+        <v>564</v>
       </c>
       <c r="L28">
         <v>0.70923183131021872</v>
@@ -13428,7 +13428,7 @@
         <v>648</v>
       </c>
       <c r="K29" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="L29">
         <v>2.6443685969158697</v>
@@ -13463,7 +13463,7 @@
         <v>650</v>
       </c>
       <c r="K30" t="s">
-        <v>565</v>
+        <v>580</v>
       </c>
       <c r="L30">
         <v>1.8465848586004447</v>
@@ -13498,7 +13498,7 @@
         <v>652</v>
       </c>
       <c r="K31" t="s">
-        <v>581</v>
+        <v>548</v>
       </c>
       <c r="L31">
         <v>0.37765422623164041</v>
@@ -13533,7 +13533,7 @@
         <v>654</v>
       </c>
       <c r="K32" t="s">
-        <v>559</v>
+        <v>542</v>
       </c>
       <c r="L32">
         <v>3.5561524889077649E-2</v>
@@ -13568,7 +13568,7 @@
         <v>656</v>
       </c>
       <c r="K33" t="s">
-        <v>540</v>
+        <v>558</v>
       </c>
       <c r="L33">
         <v>2.1908201095270803</v>
@@ -13603,7 +13603,7 @@
         <v>658</v>
       </c>
       <c r="K34" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="L34">
         <v>0.36415471855093817</v>
@@ -13638,7 +13638,7 @@
         <v>660</v>
       </c>
       <c r="K35" t="s">
-        <v>569</v>
+        <v>565</v>
       </c>
       <c r="L35">
         <v>0.61002023046213527</v>
@@ -13673,7 +13673,7 @@
         <v>662</v>
       </c>
       <c r="K36" t="s">
-        <v>560</v>
+        <v>543</v>
       </c>
       <c r="L36">
         <v>4.4698593612657496E-2</v>
@@ -13708,7 +13708,7 @@
         <v>664</v>
       </c>
       <c r="K37" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="L37">
         <v>0.68027360026848571</v>
@@ -13743,7 +13743,7 @@
         <v>666</v>
       </c>
       <c r="K38" t="s">
-        <v>549</v>
+        <v>539</v>
       </c>
       <c r="L38">
         <v>0.37453679972687481</v>
@@ -13778,7 +13778,7 @@
         <v>668</v>
       </c>
       <c r="K39" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="L39">
         <v>2.0981614345618582</v>
@@ -13813,7 +13813,7 @@
         <v>670</v>
       </c>
       <c r="K40" t="s">
-        <v>555</v>
+        <v>546</v>
       </c>
       <c r="L40">
         <v>0.46102512715199689</v>
@@ -13848,7 +13848,7 @@
         <v>672</v>
       </c>
       <c r="K41" t="s">
-        <v>580</v>
+        <v>570</v>
       </c>
       <c r="L41">
         <v>2.3941340716848205</v>
@@ -13883,7 +13883,7 @@
         <v>674</v>
       </c>
       <c r="K42" t="s">
-        <v>541</v>
+        <v>559</v>
       </c>
       <c r="L42">
         <v>8.0093311734422176E-2</v>
@@ -13918,7 +13918,7 @@
         <v>676</v>
       </c>
       <c r="K43" t="s">
-        <v>570</v>
+        <v>566</v>
       </c>
       <c r="L43">
         <v>2.484585483662062</v>
@@ -13953,7 +13953,7 @@
         <v>678</v>
       </c>
       <c r="K44" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="L44">
         <v>0</v>
@@ -13988,7 +13988,7 @@
         <v>680</v>
       </c>
       <c r="K45" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="L45">
         <v>2.8202141054326137</v>
@@ -14023,7 +14023,7 @@
         <v>682</v>
       </c>
       <c r="K46" t="s">
-        <v>561</v>
+        <v>544</v>
       </c>
       <c r="L46">
         <v>2.0496044753053133</v>
@@ -14058,7 +14058,7 @@
         <v>684</v>
       </c>
       <c r="K47" t="s">
-        <v>542</v>
+        <v>560</v>
       </c>
       <c r="L47">
         <v>4.3172734082397007E-3</v>
@@ -14093,7 +14093,7 @@
         <v>686</v>
       </c>
       <c r="K48" t="s">
-        <v>550</v>
+        <v>540</v>
       </c>
       <c r="L48">
         <v>0.64220735366408732</v>
@@ -14128,7 +14128,7 @@
         <v>688</v>
       </c>
       <c r="K49" t="s">
-        <v>563</v>
+        <v>550</v>
       </c>
       <c r="L49">
         <v>0.20805219904440039</v>
@@ -14163,7 +14163,7 @@
         <v>690</v>
       </c>
       <c r="K50" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="L50">
         <v>2.0142732687279992</v>
@@ -14198,7 +14198,7 @@
         <v>692</v>
       </c>
       <c r="K51" t="s">
-        <v>566</v>
+        <v>581</v>
       </c>
       <c r="L51">
         <v>5.8843723867425011</v>
@@ -14233,7 +14233,7 @@
         <v>694</v>
       </c>
       <c r="K52" t="s">
-        <v>543</v>
+        <v>561</v>
       </c>
       <c r="L52">
         <v>0.35433566672314526</v>
@@ -14268,7 +14268,7 @@
         <v>696</v>
       </c>
       <c r="K53" t="s">
-        <v>571</v>
+        <v>567</v>
       </c>
       <c r="L53">
         <v>0.28717016660662842</v>
@@ -14303,7 +14303,7 @@
         <v>698</v>
       </c>
       <c r="K54" t="s">
-        <v>544</v>
+        <v>562</v>
       </c>
       <c r="L54">
         <v>0.14326997649193718</v>
@@ -14338,7 +14338,7 @@
         <v>700</v>
       </c>
       <c r="K55" t="s">
-        <v>556</v>
+        <v>547</v>
       </c>
       <c r="L55">
         <v>3.1006662748324816</v>
@@ -14353,7 +14353,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C68D3699-5810-40A0-AB37-0A7C968D79A5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A863215-354A-484B-AC67-E1F9B02DF816}">
   <dimension ref="B9:Y136"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -18714,7 +18714,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A7F888B-A904-4169-93D8-B76B04A17680}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFE9A0C8-0985-4B9F-9C2D-617CD9501C92}">
   <dimension ref="B9:T88"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
